--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:37:21</t>
+          <t>Last Updated: 13-09-2026 22:05:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 12-09-2026)</t>
+          <t>MTD (01-09-2026 → 13-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>89252.92999999999</v>
+        <v>94277.05</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>7808.19</v>
+        <v>8759.290000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>76933.98</v>
+        <v>84400.31</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7808.19</v>
+        <v>8759.290000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>166186.91</v>
+        <v>178677.36</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 11-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 12-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>81827.55</v>
+        <v>89253.42</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>6805.83</v>
+        <v>7813.81</v>
       </c>
       <c r="D11" t="n">
-        <v>69818.7</v>
+        <v>76944.53999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>6805.83</v>
+        <v>7813.81</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>151646.25</v>
+        <v>166197.96</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7425.38</v>
+        <v>5023.63</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.36</v>
+        <v>945.48</v>
       </c>
       <c r="D17" t="n">
-        <v>7115.28</v>
+        <v>7455.77</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1002.36</v>
+        <v>945.48</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14540.66</v>
+        <v>12479.4</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:37:52</t>
+          <t>Last Updated: 13-09-2026 22:06:28</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-12 | MTD-1: 2026-09-01 → 2026-09-11</t>
+          <t>MTD: 2026-09-01 → 2026-09-13 | MTD-1: 2026-09-01 → 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-12)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -1545,19 +1545,19 @@
         <v>1458</v>
       </c>
       <c r="C8" t="n">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="D8" t="n">
         <v>4.84</v>
       </c>
       <c r="E8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-12)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32718</v>
+        <v>33511</v>
       </c>
       <c r="C14" t="n">
-        <v>243779</v>
+        <v>264747</v>
       </c>
       <c r="D14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>7.45</v>
+        <v>7.9</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7756.61</v>
+        <v>8707.700000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-11)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
         <v>1458</v>
       </c>
       <c r="C20" t="n">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D20" t="n">
         <v>4.84</v>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-11)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32074</v>
+        <v>32718</v>
       </c>
       <c r="C26" t="n">
-        <v>223162</v>
+        <v>243919</v>
       </c>
       <c r="D26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="E26" t="n">
-        <v>6.96</v>
+        <v>7.46</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>6754.25</v>
+        <v>7762.23</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2135,19 +2135,19 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>644</v>
+        <v>793</v>
       </c>
       <c r="C38" t="n">
-        <v>20617</v>
+        <v>20828</v>
       </c>
       <c r="D38" t="n">
         <v>-0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1002.36</v>
+        <v>945.47</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:38:29</t>
+          <t>Last Updated: 13-09-2026 22:07:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-12)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>71680</v>
+        <v>73951</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1245272</v>
+        <v>1355464</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>66179.78</v>
+        <v>72504.22</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>89215</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1570561</v>
+        <v>1661921</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>89252.94</v>
+        <v>94277.06</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160895</v>
+        <v>163166</v>
       </c>
       <c r="C7" t="n">
-        <v>2815833</v>
+        <v>3017385</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>155432.72</v>
+        <v>166781.28</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-12)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1245272</v>
+        <v>1355464</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>66179.78</v>
+        <v>72504.22</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-12)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1281595</v>
+        <v>1370652</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>82006.36</v>
+        <v>86962.03</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>288966</v>
+        <v>291269</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7246.58</v>
+        <v>7315.03</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-11)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>71680</v>
+        <v>73951</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>71680</v>
+        <v>73951</v>
       </c>
       <c r="C39" t="n">
-        <v>1141616</v>
+        <v>1246046</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>60463.4</v>
+        <v>66189.03</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>89215</v>
       </c>
       <c r="C44" t="n">
-        <v>1132443</v>
+        <v>1281597</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>74707.75999999999</v>
+        <v>82006.97</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>13.2</v>
+        <v>6.9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:39:05</t>
+          <t>Last Updated: 13-09-2026 22:07:43</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-12</t>
+          <t>MTD: 2026-09-01 → 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:39:39</t>
+          <t>Last Updated: 13-09-2026 22:08:17</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:39:39</t>
+          <t>Last Updated: 13-09-2026 22:08:17</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:40:13</t>
+          <t>Last Updated: 13-09-2026 22:08:51</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 05:40:47</t>
+          <t>Last Updated: 13-09-2026 22:09:27</t>
         </is>
       </c>
     </row>
@@ -4799,13 +4799,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1570561</v>
+        <v>1661921</v>
       </c>
       <c r="E4" t="n">
         <v>89215</v>
       </c>
       <c r="F4" t="n">
-        <v>11849</v>
+        <v>12520</v>
       </c>
       <c r="G4" t="n">
         <v>0.75</v>
@@ -4843,16 +4843,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>631590</v>
+        <v>698386</v>
       </c>
       <c r="E5" t="n">
-        <v>41315</v>
+        <v>42799</v>
       </c>
       <c r="F5" t="n">
-        <v>10323</v>
+        <v>11297</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4887,13 +4887,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>361674</v>
+        <v>382867</v>
       </c>
       <c r="E6" t="n">
-        <v>18690</v>
+        <v>19201</v>
       </c>
       <c r="F6" t="n">
-        <v>5276</v>
+        <v>5584</v>
       </c>
       <c r="G6" t="n">
         <v>1.46</v>
@@ -4931,16 +4931,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>252008</v>
+        <v>274211</v>
       </c>
       <c r="E7" t="n">
-        <v>11675</v>
+        <v>11951</v>
       </c>
       <c r="F7" t="n">
-        <v>5461</v>
+        <v>5898</v>
       </c>
       <c r="G7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4975,13 +4975,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>243713</v>
+        <v>264615</v>
       </c>
       <c r="E8" t="n">
-        <v>32718</v>
+        <v>33511</v>
       </c>
       <c r="F8" t="n">
-        <v>2509</v>
+        <v>2714</v>
       </c>
       <c r="G8" t="n">
         <v>1.03</v>
@@ -5019,16 +5019,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>162497</v>
+        <v>179190</v>
       </c>
       <c r="E9" t="n">
-        <v>14720</v>
+        <v>15117</v>
       </c>
       <c r="F9" t="n">
-        <v>10816</v>
+        <v>11797</v>
       </c>
       <c r="G9" t="n">
-        <v>6.66</v>
+        <v>6.58</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="E10" t="n">
         <v>1458</v>
@@ -5072,7 +5072,7 @@
         <v>97</v>
       </c>
       <c r="G10" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:05:57</t>
+          <t>Last Updated: 14-09-2026 05:50:26</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>94277.05</v>
+        <v>96568.53</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8759.290000000001</v>
+        <v>8849.139999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>84400.31</v>
+        <v>84850.21000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8759.290000000001</v>
+        <v>8849.139999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>178677.36</v>
+        <v>181418.74</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5023.63</v>
+        <v>7315.11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>945.48</v>
+        <v>1035.33</v>
       </c>
       <c r="D17" t="n">
-        <v>7455.77</v>
+        <v>7905.67</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>945.48</v>
+        <v>1035.33</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12479.4</v>
+        <v>15220.78</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:06:28</t>
+          <t>Last Updated: 14-09-2026 05:50:57</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33511</v>
+        <v>33517</v>
       </c>
       <c r="C14" t="n">
-        <v>264747</v>
+        <v>266333</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8707.700000000001</v>
+        <v>8797.549999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>32718</v>
       </c>
       <c r="C26" t="n">
-        <v>243919</v>
+        <v>243926</v>
       </c>
       <c r="D26" t="n">
         <v>1.21</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="C38" t="n">
-        <v>20828</v>
+        <v>22407</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>945.47</v>
+        <v>1035.32</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:07:07</t>
+          <t>Last Updated: 14-09-2026 05:51:35</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>73951</v>
+        <v>74114</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1355464</v>
+        <v>1360382</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>72504.22</v>
+        <v>72780.62</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>89215</v>
+        <v>91599</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1661921</v>
+        <v>1702320</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>94277.06</v>
+        <v>96568.53</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>163166</v>
+        <v>165713</v>
       </c>
       <c r="C7" t="n">
-        <v>3017385</v>
+        <v>3062702</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>166781.28</v>
+        <v>169349.15</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1355464</v>
+        <v>1360382</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>72504.22</v>
+        <v>72780.62</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1370652</v>
+        <v>1410052</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>86962.03</v>
+        <v>89221.89999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>291269</v>
+        <v>292268</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7315.03</v>
+        <v>7346.63</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>73951</v>
+        <v>74114</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>73951</v>
+        <v>74114</v>
       </c>
       <c r="C39" t="n">
         <v>1246046</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>89215</v>
+        <v>91599</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>89215</v>
+        <v>91599</v>
       </c>
       <c r="C44" t="n">
         <v>1281597</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:07:43</t>
+          <t>Last Updated: 14-09-2026 05:52:12</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,17 +3276,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Product 2</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3344,12 +3344,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3372,40 +3372,6 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Retention Price Increase Agro Tools</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>08-07-2026</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3437,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:08:17</t>
+          <t>Last Updated: 14-09-2026 05:52:46</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:08:17</t>
+          <t>Last Updated: 14-09-2026 05:52:46</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:08:51</t>
+          <t>Last Updated: 14-09-2026 05:53:20</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-09-2026 22:09:27</t>
+          <t>Last Updated: 14-09-2026 05:53:55</t>
         </is>
       </c>
     </row>
@@ -4799,16 +4765,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1661921</v>
+        <v>1702320</v>
       </c>
       <c r="E4" t="n">
-        <v>89215</v>
+        <v>91599</v>
       </c>
       <c r="F4" t="n">
-        <v>12520</v>
+        <v>12892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4843,13 +4809,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>698386</v>
+        <v>700928</v>
       </c>
       <c r="E5" t="n">
-        <v>42799</v>
+        <v>42875</v>
       </c>
       <c r="F5" t="n">
-        <v>11297</v>
+        <v>11341</v>
       </c>
       <c r="G5" t="n">
         <v>1.62</v>
@@ -4887,13 +4853,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>382867</v>
+        <v>384871</v>
       </c>
       <c r="E6" t="n">
-        <v>19201</v>
+        <v>19282</v>
       </c>
       <c r="F6" t="n">
-        <v>5584</v>
+        <v>5624</v>
       </c>
       <c r="G6" t="n">
         <v>1.46</v>
@@ -4931,13 +4897,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>274211</v>
+        <v>274583</v>
       </c>
       <c r="E7" t="n">
-        <v>11951</v>
+        <v>11957</v>
       </c>
       <c r="F7" t="n">
-        <v>5898</v>
+        <v>5910</v>
       </c>
       <c r="G7" t="n">
         <v>2.15</v>
@@ -4975,13 +4941,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>264615</v>
+        <v>266249</v>
       </c>
       <c r="E8" t="n">
-        <v>33511</v>
+        <v>33517</v>
       </c>
       <c r="F8" t="n">
-        <v>2714</v>
+        <v>2739</v>
       </c>
       <c r="G8" t="n">
         <v>1.03</v>
@@ -5019,16 +4985,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>179190</v>
+        <v>181331</v>
       </c>
       <c r="E9" t="n">
-        <v>15117</v>
+        <v>15145</v>
       </c>
       <c r="F9" t="n">
-        <v>11797</v>
+        <v>11918</v>
       </c>
       <c r="G9" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:50:26</t>
+          <t>Last Updated: 14-09-2026 23:40:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 13-09-2026)</t>
+          <t>MTD (01-09-2026 → 14-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>96568.53</v>
+        <v>101236.35</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8849.139999999999</v>
+        <v>10061.29</v>
       </c>
       <c r="D5" t="n">
-        <v>84850.21000000001</v>
+        <v>91573.91</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8849.139999999999</v>
+        <v>10061.29</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>181418.74</v>
+        <v>192810.26</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 12-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 13-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>89253.42</v>
+        <v>96575.42999999999</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>7813.81</v>
+        <v>8857.76</v>
       </c>
       <c r="D11" t="n">
-        <v>76944.53999999999</v>
+        <v>84932.49000000001</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>7813.81</v>
+        <v>8857.76</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>166197.96</v>
+        <v>181507.92</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7315.11</v>
+        <v>4660.92</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1035.33</v>
+        <v>1203.53</v>
       </c>
       <c r="D17" t="n">
-        <v>7905.67</v>
+        <v>6641.42</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1035.33</v>
+        <v>1203.53</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15220.78</v>
+        <v>11302.34</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:50:57</t>
+          <t>Last Updated: 14-09-2026 23:41:14</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-13 | MTD-1: 2026-09-01 → 2026-09-12</t>
+          <t>MTD: 2026-09-01 → 2026-09-14 | MTD-1: 2026-09-01 → 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-13)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C8" t="n">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D8" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="E8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-13)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33517</v>
+        <v>34313</v>
       </c>
       <c r="C14" t="n">
-        <v>266333</v>
+        <v>290357</v>
       </c>
       <c r="D14" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>7.95</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8797.549999999999</v>
+        <v>10009.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-12)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -1843,19 +1843,19 @@
         <v>1458</v>
       </c>
       <c r="C20" t="n">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="D20" t="n">
         <v>4.84</v>
       </c>
       <c r="E20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-12)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32718</v>
+        <v>33517</v>
       </c>
       <c r="C26" t="n">
-        <v>243926</v>
+        <v>266559</v>
       </c>
       <c r="D26" t="n">
         <v>1.21</v>
       </c>
       <c r="E26" t="n">
-        <v>7.46</v>
+        <v>7.95</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>7762.23</v>
+        <v>8806.17</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C38" t="n">
-        <v>22407</v>
+        <v>23798</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E38" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1035.32</v>
+        <v>1203.53</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:51:35</t>
+          <t>Last Updated: 14-09-2026 23:41:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-13)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>74114</v>
+        <v>75670</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1360382</v>
+        <v>1460228</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>72780.62</v>
+        <v>78412.13</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>91599</v>
+        <v>93778</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1702320</v>
+        <v>1829718</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>96568.53</v>
+        <v>101236.34</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165713</v>
+        <v>169448</v>
       </c>
       <c r="C7" t="n">
-        <v>3062702</v>
+        <v>3289946</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>169349.15</v>
+        <v>179648.47</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-13)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1360382</v>
+        <v>1460228</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>72780.62</v>
+        <v>78412.13</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-13)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410052</v>
+        <v>1533404</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>89221.89999999999</v>
+        <v>93813.60000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>292268</v>
+        <v>296314</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7346.63</v>
+        <v>7422.74</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-12)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-13)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>74114</v>
+        <v>75670</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>74114</v>
+        <v>75670</v>
       </c>
       <c r="C39" t="n">
-        <v>1246046</v>
+        <v>1361389</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>66189.03</v>
+        <v>72837.78999999999</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>91599</v>
+        <v>93778</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>91599</v>
+        <v>93778</v>
       </c>
       <c r="C44" t="n">
-        <v>1281597</v>
+        <v>1410041</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>82006.97</v>
+        <v>89228.8</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:52:12</t>
+          <t>Last Updated: 14-09-2026 23:42:30</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-13</t>
+          <t>MTD: 2026-09-01 → 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:52:46</t>
+          <t>Last Updated: 14-09-2026 23:43:08</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:52:46</t>
+          <t>Last Updated: 14-09-2026 23:43:08</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:53:20</t>
+          <t>Last Updated: 14-09-2026 23:43:44</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 05:53:55</t>
+          <t>Last Updated: 14-09-2026 23:44:19</t>
         </is>
       </c>
     </row>
@@ -4765,16 +4765,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1702320</v>
+        <v>1829718</v>
       </c>
       <c r="E4" t="n">
-        <v>91599</v>
+        <v>93778</v>
       </c>
       <c r="F4" t="n">
-        <v>12892</v>
+        <v>13579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4809,16 +4809,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>700928</v>
+        <v>758120</v>
       </c>
       <c r="E5" t="n">
-        <v>42875</v>
+        <v>43577</v>
       </c>
       <c r="F5" t="n">
-        <v>11341</v>
+        <v>12156</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4853,13 +4853,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>384871</v>
+        <v>406777</v>
       </c>
       <c r="E6" t="n">
-        <v>19282</v>
+        <v>19796</v>
       </c>
       <c r="F6" t="n">
-        <v>5624</v>
+        <v>5935</v>
       </c>
       <c r="G6" t="n">
         <v>1.46</v>
@@ -4897,16 +4897,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>274583</v>
+        <v>295331</v>
       </c>
       <c r="E7" t="n">
-        <v>11957</v>
+        <v>12297</v>
       </c>
       <c r="F7" t="n">
-        <v>5910</v>
+        <v>6284</v>
       </c>
       <c r="G7" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4941,16 +4941,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>266249</v>
+        <v>290245</v>
       </c>
       <c r="E8" t="n">
-        <v>33517</v>
+        <v>34313</v>
       </c>
       <c r="F8" t="n">
-        <v>2739</v>
+        <v>2958</v>
       </c>
       <c r="G8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>181331</v>
+        <v>198182</v>
       </c>
       <c r="E9" t="n">
-        <v>15145</v>
+        <v>15528</v>
       </c>
       <c r="F9" t="n">
-        <v>11918</v>
+        <v>12908</v>
       </c>
       <c r="G9" t="n">
-        <v>6.57</v>
+        <v>6.51</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="E10" t="n">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="F10" t="n">
         <v>97</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:40:43</t>
+          <t>Last Updated: 15-09-2026 06:16:58</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>101236.35</v>
+        <v>103542.99</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>10061.29</v>
+        <v>10075.77</v>
       </c>
       <c r="D5" t="n">
-        <v>91573.91</v>
+        <v>91644.52</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>10061.29</v>
+        <v>10075.77</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>192810.26</v>
+        <v>195187.51</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4660.92</v>
+        <v>6967.56</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1203.53</v>
+        <v>1218.01</v>
       </c>
       <c r="D17" t="n">
-        <v>6641.42</v>
+        <v>6712.03</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1203.53</v>
+        <v>1218.01</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11302.34</v>
+        <v>13679.59</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:41:14</t>
+          <t>Last Updated: 15-09-2026 06:17:29</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C8" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="D8" t="n">
         <v>4.83</v>
@@ -1694,19 +1694,19 @@
         <v>34313</v>
       </c>
       <c r="C14" t="n">
-        <v>290357</v>
+        <v>290597</v>
       </c>
       <c r="D14" t="n">
         <v>1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>10009.7</v>
+        <v>10024.18</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>33517</v>
       </c>
       <c r="C26" t="n">
-        <v>266559</v>
+        <v>266562</v>
       </c>
       <c r="D26" t="n">
         <v>1.21</v>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>-0.01</v>
@@ -2268,19 +2268,19 @@
         <v>796</v>
       </c>
       <c r="C38" t="n">
-        <v>23798</v>
+        <v>24035</v>
       </c>
       <c r="D38" t="n">
         <v>-0.02</v>
       </c>
       <c r="E38" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1203.53</v>
+        <v>1218.01</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:41:53</t>
+          <t>Last Updated: 15-09-2026 06:18:08</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>75670</v>
+        <v>75680</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1460228</v>
+        <v>1461277</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>78412.13</v>
+        <v>78467.97</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>93778</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1829718</v>
+        <v>1875951</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>101236.34</v>
+        <v>103542.99</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>169448</v>
+        <v>169458</v>
       </c>
       <c r="C7" t="n">
-        <v>3289946</v>
+        <v>3337228</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>179648.47</v>
+        <v>182010.96</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1460228</v>
+        <v>1461277</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>78412.13</v>
+        <v>78467.97</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1533404</v>
+        <v>1578508</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>93813.60000000001</v>
+        <v>96086.7</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>296314</v>
+        <v>297443</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7422.74</v>
+        <v>7456.29</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>75670</v>
+        <v>75680</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>75670</v>
+        <v>75680</v>
       </c>
       <c r="C39" t="n">
         <v>1361389</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>8.699999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:42:30</t>
+          <t>Last Updated: 15-09-2026 06:18:44</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3310,12 +3310,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:43:08</t>
+          <t>Last Updated: 15-09-2026 06:19:19</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:43:08</t>
+          <t>Last Updated: 15-09-2026 06:19:19</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:43:44</t>
+          <t>Last Updated: 15-09-2026 06:19:54</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-09-2026 23:44:19</t>
+          <t>Last Updated: 15-09-2026 06:20:31</t>
         </is>
       </c>
     </row>
@@ -4765,13 +4765,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1829718</v>
+        <v>1875951</v>
       </c>
       <c r="E4" t="n">
         <v>93778</v>
       </c>
       <c r="F4" t="n">
-        <v>13579</v>
+        <v>13927</v>
       </c>
       <c r="G4" t="n">
         <v>0.74</v>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>758120</v>
+        <v>758859</v>
       </c>
       <c r="E5" t="n">
         <v>43577</v>
       </c>
       <c r="F5" t="n">
-        <v>12156</v>
+        <v>12169</v>
       </c>
       <c r="G5" t="n">
         <v>1.6</v>
@@ -4853,13 +4853,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>406777</v>
+        <v>406882</v>
       </c>
       <c r="E6" t="n">
         <v>19796</v>
       </c>
       <c r="F6" t="n">
-        <v>5935</v>
+        <v>5936</v>
       </c>
       <c r="G6" t="n">
         <v>1.46</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>295331</v>
+        <v>295536</v>
       </c>
       <c r="E7" t="n">
-        <v>12297</v>
+        <v>12307</v>
       </c>
       <c r="F7" t="n">
         <v>6284</v>
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>290245</v>
+        <v>290504</v>
       </c>
       <c r="E8" t="n">
         <v>34313</v>
       </c>
       <c r="F8" t="n">
-        <v>2958</v>
+        <v>2960</v>
       </c>
       <c r="G8" t="n">
         <v>1.02</v>
@@ -4985,13 +4985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>198182</v>
+        <v>198343</v>
       </c>
       <c r="E9" t="n">
         <v>15528</v>
       </c>
       <c r="F9" t="n">
-        <v>12908</v>
+        <v>12911</v>
       </c>
       <c r="G9" t="n">
         <v>6.51</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="E10" t="n">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="F10" t="n">
         <v>97</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:16:58</t>
+          <t>Last Updated: 15-09-2026 22:44:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 14-09-2026)</t>
+          <t>MTD (01-09-2026 → 15-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>103542.99</v>
+        <v>108968.22</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>10075.77</v>
+        <v>11013.33</v>
       </c>
       <c r="D5" t="n">
-        <v>91644.52</v>
+        <v>97580.71000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>10075.77</v>
+        <v>11013.33</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>195187.51</v>
+        <v>206548.93</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 13-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 14-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>96575.42999999999</v>
+        <v>103552.95</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8857.76</v>
+        <v>10086.35</v>
       </c>
       <c r="D11" t="n">
-        <v>84932.49000000001</v>
+        <v>91699.48</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8857.76</v>
+        <v>10086.35</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>181507.92</v>
+        <v>195252.43</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6967.56</v>
+        <v>5415.27</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1218.01</v>
+        <v>926.98</v>
       </c>
       <c r="D17" t="n">
-        <v>6712.03</v>
+        <v>5881.23</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1218.01</v>
+        <v>926.98</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13679.59</v>
+        <v>11296.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:17:29</t>
+          <t>Last Updated: 15-09-2026 22:45:30</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-14 | MTD-1: 2026-09-01 → 2026-09-13</t>
+          <t>MTD: 2026-09-01 → 2026-09-15 | MTD-1: 2026-09-01 → 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-14)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C8" t="n">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D8" t="n">
         <v>4.83</v>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-14)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34313</v>
+        <v>34832</v>
       </c>
       <c r="C14" t="n">
-        <v>290597</v>
+        <v>311910</v>
       </c>
       <c r="D14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>8.470000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>10024.18</v>
+        <v>10961.74</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-13)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="C20" t="n">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="D20" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="E20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-13)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>33517</v>
+        <v>34313</v>
       </c>
       <c r="C26" t="n">
-        <v>266562</v>
+        <v>290825</v>
       </c>
       <c r="D26" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="E26" t="n">
-        <v>7.95</v>
+        <v>8.48</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>8806.17</v>
+        <v>10034.76</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>796</v>
+        <v>519</v>
       </c>
       <c r="C38" t="n">
-        <v>24035</v>
+        <v>21085</v>
       </c>
       <c r="D38" t="n">
         <v>-0.02</v>
       </c>
       <c r="E38" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1218.01</v>
+        <v>926.98</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:18:08</t>
+          <t>Last Updated: 15-09-2026 22:46:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-14)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>75680</v>
+        <v>77977</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1461277</v>
+        <v>1553940</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>78467.97</v>
+        <v>83417.92999999999</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>93778</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1875951</v>
+        <v>2016430</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>103542.99</v>
+        <v>108968.22</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>169458</v>
+        <v>171755</v>
       </c>
       <c r="C7" t="n">
-        <v>3337228</v>
+        <v>3570370</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>182010.96</v>
+        <v>192386.15</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-14)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1461277</v>
+        <v>1553940</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>78467.97</v>
+        <v>83417.92999999999</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-14)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1578508</v>
+        <v>1715764</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>96086.7</v>
+        <v>101438.13</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>297443</v>
+        <v>300666</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7456.29</v>
+        <v>7530.09</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-13)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>75680</v>
+        <v>77977</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>75680</v>
+        <v>77977</v>
       </c>
       <c r="C39" t="n">
-        <v>1361389</v>
+        <v>1462181</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>72837.78999999999</v>
+        <v>78514.23</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>93778</v>
       </c>
       <c r="C44" t="n">
-        <v>1410041</v>
+        <v>1578598</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>89228.8</v>
+        <v>96096.48</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>11.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:18:44</t>
+          <t>Last Updated: 15-09-2026 22:46:46</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-14</t>
+          <t>MTD: 2026-09-01 → 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:19:19</t>
+          <t>Last Updated: 15-09-2026 22:47:21</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:19:19</t>
+          <t>Last Updated: 15-09-2026 22:47:21</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:19:54</t>
+          <t>Last Updated: 15-09-2026 22:47:55</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 06:20:31</t>
+          <t>Last Updated: 15-09-2026 22:48:31</t>
         </is>
       </c>
     </row>
@@ -4765,16 +4765,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1875951</v>
+        <v>2016430</v>
       </c>
       <c r="E4" t="n">
         <v>93778</v>
       </c>
       <c r="F4" t="n">
-        <v>13927</v>
+        <v>14593</v>
       </c>
       <c r="G4" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4809,16 +4809,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>758859</v>
+        <v>816886</v>
       </c>
       <c r="E5" t="n">
-        <v>43577</v>
+        <v>44597</v>
       </c>
       <c r="F5" t="n">
-        <v>12169</v>
+        <v>12983</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4853,13 +4853,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>406882</v>
+        <v>422143</v>
       </c>
       <c r="E6" t="n">
-        <v>19796</v>
+        <v>20639</v>
       </c>
       <c r="F6" t="n">
-        <v>5936</v>
+        <v>6172</v>
       </c>
       <c r="G6" t="n">
         <v>1.46</v>
@@ -4897,16 +4897,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>295536</v>
+        <v>314911</v>
       </c>
       <c r="E7" t="n">
-        <v>12307</v>
+        <v>12741</v>
       </c>
       <c r="F7" t="n">
-        <v>6284</v>
+        <v>6689</v>
       </c>
       <c r="G7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4941,16 +4941,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>290504</v>
+        <v>311744</v>
       </c>
       <c r="E8" t="n">
-        <v>34313</v>
+        <v>34832</v>
       </c>
       <c r="F8" t="n">
-        <v>2960</v>
+        <v>3127</v>
       </c>
       <c r="G8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>198343</v>
+        <v>213872</v>
       </c>
       <c r="E9" t="n">
-        <v>15528</v>
+        <v>15921</v>
       </c>
       <c r="F9" t="n">
-        <v>12911</v>
+        <v>13842</v>
       </c>
       <c r="G9" t="n">
-        <v>6.51</v>
+        <v>6.47</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5029,16 +5029,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="E10" t="n">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="F10" t="n">
         <v>97</v>
       </c>
       <c r="G10" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:44:59</t>
+          <t>Last Updated: 16-09-2026 06:08:35</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>108968.22</v>
+        <v>111278.2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>11013.33</v>
+        <v>11056.59</v>
       </c>
       <c r="D5" t="n">
-        <v>97580.71000000001</v>
+        <v>97879.62</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11013.33</v>
+        <v>11056.59</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>206548.93</v>
+        <v>209157.82</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5415.27</v>
+        <v>7725.25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>926.98</v>
+        <v>970.24</v>
       </c>
       <c r="D17" t="n">
-        <v>5881.23</v>
+        <v>6180.14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>926.98</v>
+        <v>970.24</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11296.5</v>
+        <v>13905.39</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:45:30</t>
+          <t>Last Updated: 16-09-2026 06:09:06</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34832</v>
+        <v>34901</v>
       </c>
       <c r="C14" t="n">
-        <v>311910</v>
+        <v>312843</v>
       </c>
       <c r="D14" t="n">
         <v>1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>10961.74</v>
+        <v>11005</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>34313</v>
       </c>
       <c r="C26" t="n">
-        <v>290825</v>
+        <v>290828</v>
       </c>
       <c r="D26" t="n">
         <v>1.19</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>519</v>
+        <v>588</v>
       </c>
       <c r="C38" t="n">
-        <v>21085</v>
+        <v>22015</v>
       </c>
       <c r="D38" t="n">
         <v>-0.02</v>
       </c>
       <c r="E38" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>926.98</v>
+        <v>970.24</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:46:09</t>
+          <t>Last Updated: 16-09-2026 06:09:46</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>77977</v>
+        <v>78096</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1553940</v>
+        <v>1558439</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>83417.92999999999</v>
+        <v>83669.60000000001</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>93778</v>
+        <v>96070</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2016430</v>
+        <v>2055949</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>108968.22</v>
+        <v>111278.2</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171755</v>
+        <v>174166</v>
       </c>
       <c r="C7" t="n">
-        <v>3570370</v>
+        <v>3614388</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>192386.15</v>
+        <v>194947.8</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1553940</v>
+        <v>1558439</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>83417.92999999999</v>
+        <v>83669.60000000001</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1715764</v>
+        <v>1754238</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>101438.13</v>
+        <v>103717.81</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>300666</v>
+        <v>301711</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7530.09</v>
+        <v>7560.39</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>77977</v>
+        <v>78096</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>77977</v>
+        <v>78096</v>
       </c>
       <c r="C39" t="n">
         <v>1462181</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>93778</v>
+        <v>96070</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>93778</v>
+        <v>96070</v>
       </c>
       <c r="C44" t="n">
         <v>1578598</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>8.699999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:46:46</t>
+          <t>Last Updated: 16-09-2026 06:10:22</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:47:21</t>
+          <t>Last Updated: 16-09-2026 06:10:56</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:47:21</t>
+          <t>Last Updated: 16-09-2026 06:10:56</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:47:55</t>
+          <t>Last Updated: 16-09-2026 06:11:33</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-09-2026 22:48:31</t>
+          <t>Last Updated: 16-09-2026 06:12:09</t>
         </is>
       </c>
     </row>
@@ -4765,16 +4765,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2016430</v>
+        <v>2055949</v>
       </c>
       <c r="E4" t="n">
-        <v>93778</v>
+        <v>96070</v>
       </c>
       <c r="F4" t="n">
-        <v>14593</v>
+        <v>14975</v>
       </c>
       <c r="G4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>816886</v>
+        <v>820088</v>
       </c>
       <c r="E5" t="n">
-        <v>44597</v>
+        <v>44713</v>
       </c>
       <c r="F5" t="n">
-        <v>12983</v>
+        <v>13029</v>
       </c>
       <c r="G5" t="n">
         <v>1.59</v>
@@ -4853,13 +4853,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>422143</v>
+        <v>422468</v>
       </c>
       <c r="E6" t="n">
         <v>20639</v>
       </c>
       <c r="F6" t="n">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="G6" t="n">
         <v>1.46</v>
@@ -4897,16 +4897,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>314911</v>
+        <v>315883</v>
       </c>
       <c r="E7" t="n">
-        <v>12741</v>
+        <v>12744</v>
       </c>
       <c r="F7" t="n">
-        <v>6689</v>
+        <v>6720</v>
       </c>
       <c r="G7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>311744</v>
+        <v>312741</v>
       </c>
       <c r="E8" t="n">
-        <v>34832</v>
+        <v>34901</v>
       </c>
       <c r="F8" t="n">
-        <v>3127</v>
+        <v>3137</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -4985,13 +4985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>213872</v>
+        <v>214614</v>
       </c>
       <c r="E9" t="n">
-        <v>15921</v>
+        <v>15929</v>
       </c>
       <c r="F9" t="n">
-        <v>13842</v>
+        <v>13877</v>
       </c>
       <c r="G9" t="n">
         <v>6.47</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:08:35</t>
+          <t>Last Updated: 16-09-2026 22:45:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 15-09-2026)</t>
+          <t>MTD (01-09-2026 → 16-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>111278.2</v>
+        <v>116695.47</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>11056.59</v>
+        <v>11946.54</v>
       </c>
       <c r="D5" t="n">
-        <v>97879.62</v>
+        <v>104078.43</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11056.59</v>
+        <v>11946.54</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>209157.82</v>
+        <v>220773.9</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 14-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 15-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>103552.95</v>
+        <v>111279.64</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>10086.35</v>
+        <v>11067.26</v>
       </c>
       <c r="D11" t="n">
-        <v>91699.48</v>
+        <v>97955.82000000001</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>10086.35</v>
+        <v>11067.26</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>195252.43</v>
+        <v>209235.46</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7725.25</v>
+        <v>5415.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>970.24</v>
+        <v>879.28</v>
       </c>
       <c r="D17" t="n">
-        <v>6180.14</v>
+        <v>6122.61</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>970.24</v>
+        <v>879.28</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13905.39</v>
+        <v>11538.44</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:09:06</t>
+          <t>Last Updated: 16-09-2026 22:45:59</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-15 | MTD-1: 2026-09-01 → 2026-09-14</t>
+          <t>MTD: 2026-09-01 → 2026-09-16 | MTD-1: 2026-09-01 → 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-15)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C8" t="n">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="D8" t="n">
-        <v>4.83</v>
+        <v>4.82</v>
       </c>
       <c r="E8" t="n">
         <v>1.64</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>51.59</v>
+        <v>51.63</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-15)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34901</v>
+        <v>36002</v>
       </c>
       <c r="C14" t="n">
-        <v>312843</v>
+        <v>334363</v>
       </c>
       <c r="D14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="E14" t="n">
-        <v>8.960000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>11005</v>
+        <v>11894.91</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-14)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C20" t="n">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D20" t="n">
         <v>4.83</v>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-14)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>34313</v>
+        <v>34901</v>
       </c>
       <c r="C26" t="n">
-        <v>290828</v>
+        <v>313094</v>
       </c>
       <c r="D26" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="E26" t="n">
-        <v>8.48</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>10034.76</v>
+        <v>11015.67</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>588</v>
+        <v>1101</v>
       </c>
       <c r="C38" t="n">
-        <v>22015</v>
+        <v>21269</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>970.24</v>
+        <v>879.24</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:09:46</t>
+          <t>Last Updated: 16-09-2026 22:46:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-15)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>78096</v>
+        <v>79645</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1558439</v>
+        <v>1644196</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>83669.60000000001</v>
+        <v>88676.61</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>96070</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2055949</v>
+        <v>2181483</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>111278.2</v>
+        <v>116695.47</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>174166</v>
+        <v>175715</v>
       </c>
       <c r="C7" t="n">
-        <v>3614388</v>
+        <v>3825679</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>194947.8</v>
+        <v>205372.08</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-15)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1558439</v>
+        <v>1644196</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>83669.60000000001</v>
+        <v>88676.61</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-15)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1754238</v>
+        <v>1876117</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>103717.81</v>
+        <v>109047.23</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>301711</v>
+        <v>305366</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7560.39</v>
+        <v>7648.24</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-14)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>78096</v>
+        <v>79645</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>78096</v>
+        <v>79645</v>
       </c>
       <c r="C39" t="n">
-        <v>1462181</v>
+        <v>1559518</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>78514.23</v>
+        <v>83732.28999999999</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>96070</v>
       </c>
       <c r="C44" t="n">
-        <v>1578598</v>
+        <v>1754197</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>96096.48</v>
+        <v>103719.26</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>11.1</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:10:22</t>
+          <t>Last Updated: 16-09-2026 22:47:27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-15</t>
+          <t>MTD: 2026-09-01 → 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:10:56</t>
+          <t>Last Updated: 16-09-2026 22:48:02</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:10:56</t>
+          <t>Last Updated: 16-09-2026 22:48:02</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:11:33</t>
+          <t>Last Updated: 16-09-2026 22:48:38</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 06:12:09</t>
+          <t>Last Updated: 16-09-2026 22:49:15</t>
         </is>
       </c>
     </row>
@@ -4765,16 +4765,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2055949</v>
+        <v>2181483</v>
       </c>
       <c r="E4" t="n">
         <v>96070</v>
       </c>
       <c r="F4" t="n">
-        <v>14975</v>
+        <v>15632</v>
       </c>
       <c r="G4" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4809,16 +4809,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>820088</v>
+        <v>879980</v>
       </c>
       <c r="E5" t="n">
-        <v>44713</v>
+        <v>45804</v>
       </c>
       <c r="F5" t="n">
-        <v>13029</v>
+        <v>13913</v>
       </c>
       <c r="G5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4853,16 +4853,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>422468</v>
+        <v>430075</v>
       </c>
       <c r="E6" t="n">
-        <v>20639</v>
+        <v>20807</v>
       </c>
       <c r="F6" t="n">
-        <v>6176</v>
+        <v>6303</v>
       </c>
       <c r="G6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4888,25 +4888,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>AR_Onboarding_KYC_But_Not_Transacted_1P_6June26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>315883</v>
+        <v>334195</v>
       </c>
       <c r="E7" t="n">
-        <v>12744</v>
+        <v>36002</v>
       </c>
       <c r="F7" t="n">
-        <v>6720</v>
+        <v>3323</v>
       </c>
       <c r="G7" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4932,25 +4932,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AR_Onboarding_KYC_But_Not_Transacted_1P_6June26</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>312741</v>
+        <v>334141</v>
       </c>
       <c r="E8" t="n">
-        <v>34901</v>
+        <v>13034</v>
       </c>
       <c r="F8" t="n">
-        <v>3137</v>
+        <v>7123</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2.13</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>214614</v>
+        <v>230387</v>
       </c>
       <c r="E9" t="n">
-        <v>15929</v>
+        <v>16301</v>
       </c>
       <c r="F9" t="n">
-        <v>13877</v>
+        <v>14888</v>
       </c>
       <c r="G9" t="n">
-        <v>6.47</v>
+        <v>6.46</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="E10" t="n">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="F10" t="n">
         <v>97</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:45:28</t>
+          <t>Last Updated: 17-09-2026 06:16:15</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>116695.47</v>
+        <v>118549.3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>11946.54</v>
+        <v>11991</v>
       </c>
       <c r="D5" t="n">
-        <v>104078.43</v>
+        <v>104363.86</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11946.54</v>
+        <v>11991</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>220773.9</v>
+        <v>222913.16</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5415.83</v>
+        <v>7269.66</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>879.28</v>
+        <v>923.74</v>
       </c>
       <c r="D17" t="n">
-        <v>6122.61</v>
+        <v>6408.04</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>879.28</v>
+        <v>923.74</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11538.44</v>
+        <v>13677.7</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:45:59</t>
+          <t>Last Updated: 17-09-2026 06:16:46</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36002</v>
+        <v>36026</v>
       </c>
       <c r="C14" t="n">
-        <v>334363</v>
+        <v>335221</v>
       </c>
       <c r="D14" t="n">
         <v>1.16</v>
       </c>
       <c r="E14" t="n">
-        <v>9.289999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>11894.91</v>
+        <v>11939.37</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>34901</v>
       </c>
       <c r="C26" t="n">
-        <v>313094</v>
+        <v>313098</v>
       </c>
       <c r="D26" t="n">
         <v>1.17</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1101</v>
+        <v>1125</v>
       </c>
       <c r="C38" t="n">
-        <v>21269</v>
+        <v>22123</v>
       </c>
       <c r="D38" t="n">
         <v>-0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>879.24</v>
+        <v>923.7</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:46:49</t>
+          <t>Last Updated: 17-09-2026 06:17:27</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>79645</v>
+        <v>79710</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1644196</v>
+        <v>1647976</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>88676.61</v>
+        <v>88911.94</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>96070</v>
+        <v>97934</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2181483</v>
+        <v>2218769</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>116695.47</v>
+        <v>118549.3</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>175715</v>
+        <v>177644</v>
       </c>
       <c r="C7" t="n">
-        <v>3825679</v>
+        <v>3866745</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>205372.08</v>
+        <v>207461.24</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1644196</v>
+        <v>1647976</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>88676.61</v>
+        <v>88911.94</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1876117</v>
+        <v>1912651</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>109047.23</v>
+        <v>110878.87</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>305366</v>
+        <v>306118</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7648.24</v>
+        <v>7670.43</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>79645</v>
+        <v>79710</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79645</v>
+        <v>79710</v>
       </c>
       <c r="C39" t="n">
         <v>1559518</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>96070</v>
+        <v>97934</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>96070</v>
+        <v>97934</v>
       </c>
       <c r="C44" t="n">
         <v>1754197</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:47:27</t>
+          <t>Last Updated: 17-09-2026 06:18:05</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3310,12 +3310,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:48:02</t>
+          <t>Last Updated: 17-09-2026 06:18:42</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:48:02</t>
+          <t>Last Updated: 17-09-2026 06:18:42</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:48:38</t>
+          <t>Last Updated: 17-09-2026 06:19:18</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-09-2026 22:49:15</t>
+          <t>Last Updated: 17-09-2026 06:19:54</t>
         </is>
       </c>
     </row>
@@ -4765,13 +4765,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2181483</v>
+        <v>2218769</v>
       </c>
       <c r="E4" t="n">
-        <v>96070</v>
+        <v>97934</v>
       </c>
       <c r="F4" t="n">
-        <v>15632</v>
+        <v>15909</v>
       </c>
       <c r="G4" t="n">
         <v>0.72</v>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>879980</v>
+        <v>882601</v>
       </c>
       <c r="E5" t="n">
-        <v>45804</v>
+        <v>45848</v>
       </c>
       <c r="F5" t="n">
-        <v>13913</v>
+        <v>13960</v>
       </c>
       <c r="G5" t="n">
         <v>1.58</v>
@@ -4853,13 +4853,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>430075</v>
+        <v>430399</v>
       </c>
       <c r="E6" t="n">
-        <v>20807</v>
+        <v>20824</v>
       </c>
       <c r="F6" t="n">
-        <v>6303</v>
+        <v>6311</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4897,16 +4897,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>334195</v>
+        <v>335098</v>
       </c>
       <c r="E7" t="n">
-        <v>36002</v>
+        <v>36026</v>
       </c>
       <c r="F7" t="n">
-        <v>3323</v>
+        <v>3336</v>
       </c>
       <c r="G7" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>334141</v>
+        <v>334976</v>
       </c>
       <c r="E8" t="n">
-        <v>13034</v>
+        <v>13038</v>
       </c>
       <c r="F8" t="n">
-        <v>7123</v>
+        <v>7146</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4985,13 +4985,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>230387</v>
+        <v>231022</v>
       </c>
       <c r="E9" t="n">
         <v>16301</v>
       </c>
       <c r="F9" t="n">
-        <v>14888</v>
+        <v>14924</v>
       </c>
       <c r="G9" t="n">
         <v>6.46</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:16:15</t>
+          <t>Last Updated: 17-09-2026 22:44:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 16-09-2026)</t>
+          <t>MTD (01-09-2026 → 17-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>118549.3</v>
+        <v>123490.68</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>11991</v>
+        <v>13096.38</v>
       </c>
       <c r="D5" t="n">
-        <v>104363.86</v>
+        <v>111062.05</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11991</v>
+        <v>13096.38</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>222913.16</v>
+        <v>234552.73</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 15-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 16-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>111279.64</v>
+        <v>118549.95</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>11067.26</v>
+        <v>11999.94</v>
       </c>
       <c r="D11" t="n">
-        <v>97955.82000000001</v>
+        <v>104436.61</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11067.26</v>
+        <v>11999.94</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>209235.46</v>
+        <v>222986.56</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7269.66</v>
+        <v>4940.73</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>923.74</v>
+        <v>1096.44</v>
       </c>
       <c r="D17" t="n">
-        <v>6408.04</v>
+        <v>6625.44</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>923.74</v>
+        <v>1096.44</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13677.7</v>
+        <v>11566.17</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:16:46</t>
+          <t>Last Updated: 17-09-2026 22:45:04</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-16 | MTD-1: 2026-09-01 → 2026-09-15</t>
+          <t>MTD: 2026-09-01 → 2026-09-17 | MTD-1: 2026-09-01 → 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-16)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>1466</v>
       </c>
       <c r="C8" t="n">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D8" t="n">
         <v>4.82</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>51.63</v>
+        <v>51.73</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-16)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36026</v>
+        <v>37087</v>
       </c>
       <c r="C14" t="n">
-        <v>335221</v>
+        <v>358906</v>
       </c>
       <c r="D14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>11939.37</v>
+        <v>13044.65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-15)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C20" t="n">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="D20" t="n">
-        <v>4.83</v>
+        <v>4.82</v>
       </c>
       <c r="E20" t="n">
         <v>1.64</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>51.59</v>
+        <v>51.63</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-15)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>34901</v>
+        <v>36026</v>
       </c>
       <c r="C26" t="n">
-        <v>313098</v>
+        <v>335489</v>
       </c>
       <c r="D26" t="n">
         <v>1.17</v>
       </c>
       <c r="E26" t="n">
-        <v>8.970000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>11015.67</v>
+        <v>11948.31</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1125</v>
+        <v>1061</v>
       </c>
       <c r="C38" t="n">
-        <v>22123</v>
+        <v>23417</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>923.7</v>
+        <v>1096.34</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:17:27</t>
+          <t>Last Updated: 17-09-2026 22:45:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-16)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>79710</v>
+        <v>80978</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1647976</v>
+        <v>1742861</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>88911.94</v>
+        <v>94371.33</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>97934</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2218769</v>
+        <v>2328710</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>118549.3</v>
+        <v>123490.69</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>177644</v>
+        <v>178912</v>
       </c>
       <c r="C7" t="n">
-        <v>3866745</v>
+        <v>4071571</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>207461.24</v>
+        <v>217862.02</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-16)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1647976</v>
+        <v>1742861</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>88911.94</v>
+        <v>94371.33</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-16)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1912651</v>
+        <v>2019376</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>110878.87</v>
+        <v>115739.33</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>306118</v>
+        <v>309334</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7670.43</v>
+        <v>7751.36</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-15)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>79710</v>
+        <v>80978</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79710</v>
+        <v>80978</v>
       </c>
       <c r="C39" t="n">
-        <v>1559518</v>
+        <v>1648952</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>83732.28999999999</v>
+        <v>88973.71000000001</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>97934</v>
       </c>
       <c r="C44" t="n">
-        <v>1754197</v>
+        <v>1912642</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>103719.26</v>
+        <v>110879.52</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:18:05</t>
+          <t>Last Updated: 17-09-2026 22:46:21</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-16</t>
+          <t>MTD: 2026-09-01 → 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:18:42</t>
+          <t>Last Updated: 17-09-2026 22:46:57</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:18:42</t>
+          <t>Last Updated: 17-09-2026 22:46:57</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:19:18</t>
+          <t>Last Updated: 17-09-2026 22:47:33</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 06:19:54</t>
+          <t>Last Updated: 17-09-2026 22:48:09</t>
         </is>
       </c>
     </row>
@@ -4765,16 +4765,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2218769</v>
+        <v>2328710</v>
       </c>
       <c r="E4" t="n">
         <v>97934</v>
       </c>
       <c r="F4" t="n">
-        <v>15909</v>
+        <v>16510</v>
       </c>
       <c r="G4" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>882601</v>
+        <v>942553</v>
       </c>
       <c r="E5" t="n">
-        <v>45848</v>
+        <v>46351</v>
       </c>
       <c r="F5" t="n">
-        <v>13960</v>
+        <v>14846</v>
       </c>
       <c r="G5" t="n">
         <v>1.58</v>
@@ -4853,13 +4853,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>430399</v>
+        <v>445708</v>
       </c>
       <c r="E6" t="n">
-        <v>20824</v>
+        <v>21292</v>
       </c>
       <c r="F6" t="n">
-        <v>6311</v>
+        <v>6533</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>335098</v>
+        <v>358694</v>
       </c>
       <c r="E7" t="n">
-        <v>36026</v>
+        <v>37087</v>
       </c>
       <c r="F7" t="n">
-        <v>3336</v>
+        <v>3575</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>334976</v>
+        <v>354600</v>
       </c>
       <c r="E8" t="n">
-        <v>13038</v>
+        <v>13335</v>
       </c>
       <c r="F8" t="n">
-        <v>7146</v>
+        <v>7547</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4985,16 +4985,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>231022</v>
+        <v>247459</v>
       </c>
       <c r="E9" t="n">
-        <v>16301</v>
+        <v>16629</v>
       </c>
       <c r="F9" t="n">
-        <v>14924</v>
+        <v>15873</v>
       </c>
       <c r="G9" t="n">
-        <v>6.46</v>
+        <v>6.41</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="E10" t="n">
         <v>1466</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:44:33</t>
+          <t>Last Updated: 18-09-2026 06:05:07</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>123490.68</v>
+        <v>125803.66</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>13096.38</v>
+        <v>13194.62</v>
       </c>
       <c r="D5" t="n">
-        <v>111062.05</v>
+        <v>111283.83</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>13096.38</v>
+        <v>13194.62</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>234552.73</v>
+        <v>237087.49</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4940.73</v>
+        <v>7253.71</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1096.44</v>
+        <v>1194.68</v>
       </c>
       <c r="D17" t="n">
-        <v>6625.44</v>
+        <v>6847.22</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1096.44</v>
+        <v>1194.68</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11566.17</v>
+        <v>14100.93</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:45:04</t>
+          <t>Last Updated: 18-09-2026 06:05:38</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37087</v>
+        <v>37204</v>
       </c>
       <c r="C14" t="n">
-        <v>358906</v>
+        <v>360718</v>
       </c>
       <c r="D14" t="n">
         <v>1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>9.68</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>13044.65</v>
+        <v>13142.89</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>36026</v>
       </c>
       <c r="C26" t="n">
-        <v>335489</v>
+        <v>335492</v>
       </c>
       <c r="D26" t="n">
         <v>1.17</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1061</v>
+        <v>1178</v>
       </c>
       <c r="C38" t="n">
-        <v>23417</v>
+        <v>25226</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1096.34</v>
+        <v>1194.58</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:45:44</t>
+          <t>Last Updated: 18-09-2026 06:06:17</t>
         </is>
       </c>
     </row>
@@ -2398,13 +2398,13 @@
         <v>80978</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1742861</v>
+        <v>1745764</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>94371.33</v>
+        <v>94537.85000000001</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>97934</v>
+        <v>99685</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2328710</v>
+        <v>2365816</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>123490.69</v>
+        <v>125803.66</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>178912</v>
+        <v>180663</v>
       </c>
       <c r="C7" t="n">
-        <v>4071571</v>
+        <v>4111580</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>217862.02</v>
+        <v>220341.51</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1742861</v>
+        <v>1745764</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>94371.33</v>
+        <v>94537.85000000001</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2019376</v>
+        <v>2055655</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>115739.33</v>
+        <v>118016.33</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>309334</v>
+        <v>310161</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7751.36</v>
+        <v>7787.33</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>97934</v>
+        <v>99685</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>97934</v>
+        <v>99685</v>
       </c>
       <c r="C44" t="n">
         <v>1912642</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:46:21</t>
+          <t>Last Updated: 18-09-2026 06:06:55</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3208,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SasteKaSahiAddress Category</t>
+          <t>Retention SasteKaSahiAddress Product 1 6June</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3242,17 +3242,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Product 1 6June</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>20-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3276,12 +3276,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>21-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3310,12 +3310,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3338,40 +3338,6 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Retention Price Increase Agro Tools</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>08-07-2026</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3403,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:46:57</t>
+          <t>Last Updated: 18-09-2026 06:07:30</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:46:57</t>
+          <t>Last Updated: 18-09-2026 06:07:30</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:47:33</t>
+          <t>Last Updated: 18-09-2026 06:08:05</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-09-2026 22:48:09</t>
+          <t>Last Updated: 18-09-2026 06:08:42</t>
         </is>
       </c>
     </row>
@@ -4765,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2328710</v>
+        <v>2365816</v>
       </c>
       <c r="E4" t="n">
-        <v>97934</v>
+        <v>99685</v>
       </c>
       <c r="F4" t="n">
-        <v>16510</v>
+        <v>16829</v>
       </c>
       <c r="G4" t="n">
         <v>0.71</v>
@@ -4809,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>942553</v>
+        <v>944777</v>
       </c>
       <c r="E5" t="n">
         <v>46351</v>
       </c>
       <c r="F5" t="n">
-        <v>14846</v>
+        <v>14891</v>
       </c>
       <c r="G5" t="n">
         <v>1.58</v>
@@ -4853,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>445708</v>
+        <v>446143</v>
       </c>
       <c r="E6" t="n">
         <v>21292</v>
       </c>
       <c r="F6" t="n">
-        <v>6533</v>
+        <v>6542</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4897,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>358694</v>
+        <v>360582</v>
       </c>
       <c r="E7" t="n">
-        <v>37087</v>
+        <v>37204</v>
       </c>
       <c r="F7" t="n">
-        <v>3575</v>
+        <v>3596</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -4941,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>354600</v>
+        <v>354844</v>
       </c>
       <c r="E8" t="n">
         <v>13335</v>
       </c>
       <c r="F8" t="n">
-        <v>7547</v>
+        <v>7555</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4985,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>247459</v>
+        <v>248129</v>
       </c>
       <c r="E9" t="n">
         <v>16629</v>
       </c>
       <c r="F9" t="n">
-        <v>15873</v>
+        <v>15910</v>
       </c>
       <c r="G9" t="n">
         <v>6.41</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:05:07</t>
+          <t>Last Updated: 18-09-2026 22:10:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 17-09-2026)</t>
+          <t>MTD (01-09-2026 → 18-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>125803.66</v>
+        <v>130531.62</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>13194.62</v>
+        <v>15024.7</v>
       </c>
       <c r="D5" t="n">
-        <v>111283.83</v>
+        <v>117350.52</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>13194.62</v>
+        <v>15024.7</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>237087.49</v>
+        <v>247882.14</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 16-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 17-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>118549.95</v>
+        <v>125809.7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>11999.94</v>
+        <v>13210.09</v>
       </c>
       <c r="D11" t="n">
-        <v>104436.61</v>
+        <v>111352.46</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11999.94</v>
+        <v>13210.09</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>222986.56</v>
+        <v>237162.16</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7253.71</v>
+        <v>4721.92</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1194.68</v>
+        <v>1814.61</v>
       </c>
       <c r="D17" t="n">
-        <v>6847.22</v>
+        <v>5998.06</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1194.68</v>
+        <v>1814.61</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14100.93</v>
+        <v>10719.98</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:05:38</t>
+          <t>Last Updated: 18-09-2026 22:10:54</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-17 | MTD-1: 2026-09-01 → 2026-09-16</t>
+          <t>MTD: 2026-09-01 → 2026-09-18 | MTD-1: 2026-09-01 → 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-17)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1466</v>
+        <v>2756</v>
       </c>
       <c r="C8" t="n">
-        <v>2406</v>
+        <v>4160</v>
       </c>
       <c r="D8" t="n">
-        <v>4.82</v>
+        <v>4.88</v>
       </c>
       <c r="E8" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>51.73</v>
+        <v>215.39</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-17)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37204</v>
+        <v>39370</v>
       </c>
       <c r="C14" t="n">
-        <v>360718</v>
+        <v>394875</v>
       </c>
       <c r="D14" t="n">
         <v>1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>9.699999999999999</v>
+        <v>10.03</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>13142.89</v>
+        <v>14809.32</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-16)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
         <v>1466</v>
       </c>
       <c r="C20" t="n">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D20" t="n">
         <v>4.82</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>51.63</v>
+        <v>51.73</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-16)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>36026</v>
+        <v>37254</v>
       </c>
       <c r="C26" t="n">
-        <v>335492</v>
+        <v>361011</v>
       </c>
       <c r="D26" t="n">
         <v>1.17</v>
       </c>
       <c r="E26" t="n">
-        <v>9.31</v>
+        <v>9.69</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>11948.31</v>
+        <v>13158.36</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>1754</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1</v>
+        <v>163.66</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1178</v>
+        <v>2116</v>
       </c>
       <c r="C38" t="n">
-        <v>25226</v>
+        <v>33864</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1194.58</v>
+        <v>1650.96</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:06:17</t>
+          <t>Last Updated: 18-09-2026 22:11:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-17)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>80978</v>
+        <v>83080</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1745764</v>
+        <v>1835592</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>94537.85000000001</v>
+        <v>99587.61</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>99685</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2365816</v>
+        <v>2482314</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>125803.66</v>
+        <v>130531.63</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>180663</v>
+        <v>182765</v>
       </c>
       <c r="C7" t="n">
-        <v>4111580</v>
+        <v>4317906</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>220341.51</v>
+        <v>230119.24</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-17)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1745764</v>
+        <v>1835592</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>94537.85000000001</v>
+        <v>99587.61</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-17)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2055655</v>
+        <v>2169769</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>118016.33</v>
+        <v>122681.88</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>310161</v>
+        <v>312545</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7787.33</v>
+        <v>7849.75</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-16)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-17)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>80978</v>
+        <v>83080</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>80978</v>
+        <v>83080</v>
       </c>
       <c r="C39" t="n">
-        <v>1648952</v>
+        <v>1746667</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>88973.71000000001</v>
+        <v>94593.47</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>99685</v>
       </c>
       <c r="C44" t="n">
-        <v>1912642</v>
+        <v>2055652</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>110879.52</v>
+        <v>118022.37</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:06:55</t>
+          <t>Last Updated: 18-09-2026 22:12:10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-17</t>
+          <t>MTD: 2026-09-01 → 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:07:30</t>
+          <t>Last Updated: 18-09-2026 22:12:45</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:07:30</t>
+          <t>Last Updated: 18-09-2026 22:12:45</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:08:05</t>
+          <t>Last Updated: 18-09-2026 22:13:20</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 06:08:42</t>
+          <t>Last Updated: 18-09-2026 22:13:57</t>
         </is>
       </c>
     </row>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2365816</v>
+        <v>2482314</v>
       </c>
       <c r="E4" t="n">
         <v>99685</v>
       </c>
       <c r="F4" t="n">
-        <v>16829</v>
+        <v>17348</v>
       </c>
       <c r="G4" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4775,16 +4775,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>944777</v>
+        <v>997104</v>
       </c>
       <c r="E5" t="n">
-        <v>46351</v>
+        <v>46719</v>
       </c>
       <c r="F5" t="n">
-        <v>14891</v>
+        <v>15602</v>
       </c>
       <c r="G5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>446143</v>
+        <v>466238</v>
       </c>
       <c r="E6" t="n">
-        <v>21292</v>
+        <v>22839</v>
       </c>
       <c r="F6" t="n">
-        <v>6542</v>
+        <v>6842</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>360582</v>
+        <v>394653</v>
       </c>
       <c r="E7" t="n">
-        <v>37204</v>
+        <v>39370</v>
       </c>
       <c r="F7" t="n">
-        <v>3596</v>
+        <v>3913</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>354844</v>
+        <v>372250</v>
       </c>
       <c r="E8" t="n">
-        <v>13335</v>
+        <v>13522</v>
       </c>
       <c r="F8" t="n">
-        <v>7555</v>
+        <v>7911</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,16 +4951,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>248129</v>
+        <v>261825</v>
       </c>
       <c r="E9" t="n">
-        <v>16629</v>
+        <v>16724</v>
       </c>
       <c r="F9" t="n">
-        <v>15910</v>
+        <v>16680</v>
       </c>
       <c r="G9" t="n">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="E10" t="n">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="F10" t="n">
         <v>97</v>
@@ -5019,6 +5019,50 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1735</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1349</v>
+      </c>
+      <c r="F11" t="n">
+        <v>56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:10:23</t>
+          <t>Last Updated: 19-09-2026 05:59:36</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>130531.62</v>
+        <v>132644.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>15024.7</v>
+        <v>15135.22</v>
       </c>
       <c r="D5" t="n">
-        <v>117350.52</v>
+        <v>117799.37</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>15024.7</v>
+        <v>15135.22</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>247882.14</v>
+        <v>250444.12</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4721.92</v>
+        <v>6835.05</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1814.61</v>
+        <v>1925.13</v>
       </c>
       <c r="D17" t="n">
-        <v>5998.06</v>
+        <v>6446.91</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1814.61</v>
+        <v>1925.13</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>10719.98</v>
+        <v>13281.96</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:10:54</t>
+          <t>Last Updated: 19-09-2026 06:00:07</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2756</v>
+        <v>3172</v>
       </c>
       <c r="C8" t="n">
-        <v>4160</v>
+        <v>4746</v>
       </c>
       <c r="D8" t="n">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
       <c r="E8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>215.39</v>
+        <v>258.86</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39370</v>
+        <v>39620</v>
       </c>
       <c r="C14" t="n">
-        <v>394875</v>
+        <v>396187</v>
       </c>
       <c r="D14" t="n">
         <v>1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>14809.32</v>
+        <v>14876.37</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>37254</v>
       </c>
       <c r="C26" t="n">
-        <v>361011</v>
+        <v>361014</v>
       </c>
       <c r="D26" t="n">
         <v>1.17</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1290</v>
+        <v>1706</v>
       </c>
       <c r="C32" t="n">
-        <v>1754</v>
+        <v>2340</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>163.66</v>
+        <v>207.13</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2116</v>
+        <v>2366</v>
       </c>
       <c r="C38" t="n">
-        <v>33864</v>
+        <v>35173</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1650.96</v>
+        <v>1718.01</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:11:33</t>
+          <t>Last Updated: 19-09-2026 06:00:46</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>83080</v>
+        <v>83129</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1835592</v>
+        <v>1842329</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>99587.61</v>
+        <v>99965.67999999999</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>99685</v>
+        <v>101135</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2482314</v>
+        <v>2522105</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>130531.63</v>
+        <v>132644.75</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>182765</v>
+        <v>184264</v>
       </c>
       <c r="C7" t="n">
-        <v>4317906</v>
+        <v>4364434</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>230119.24</v>
+        <v>232610.43</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1835592</v>
+        <v>1842329</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>99587.61</v>
+        <v>99965.67999999999</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2169769</v>
+        <v>2208511</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>122681.88</v>
+        <v>124760.92</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>312545</v>
+        <v>313594</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7849.75</v>
+        <v>7883.83</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>83080</v>
+        <v>83129</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>83080</v>
+        <v>83129</v>
       </c>
       <c r="C39" t="n">
         <v>1746667</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>99685</v>
+        <v>101135</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>99685</v>
+        <v>101135</v>
       </c>
       <c r="C44" t="n">
         <v>2055652</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:12:10</t>
+          <t>Last Updated: 19-09-2026 06:01:23</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>21-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20-06-2026</t>
+          <t>21-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,7 +3276,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:12:45</t>
+          <t>Last Updated: 19-09-2026 06:01:58</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:12:45</t>
+          <t>Last Updated: 19-09-2026 06:01:58</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:13:20</t>
+          <t>Last Updated: 19-09-2026 06:02:33</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
     <col width="63" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-09-2026 22:13:57</t>
+          <t>Last Updated: 19-09-2026 06:03:09</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2482314</v>
+        <v>2522105</v>
       </c>
       <c r="E4" t="n">
-        <v>99685</v>
+        <v>101135</v>
       </c>
       <c r="F4" t="n">
-        <v>17348</v>
+        <v>17632</v>
       </c>
       <c r="G4" t="n">
         <v>0.7</v>
@@ -4775,16 +4775,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>997104</v>
+        <v>1001243</v>
       </c>
       <c r="E5" t="n">
         <v>46719</v>
       </c>
       <c r="F5" t="n">
-        <v>15602</v>
+        <v>15670</v>
       </c>
       <c r="G5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>466238</v>
+        <v>467492</v>
       </c>
       <c r="E6" t="n">
-        <v>22839</v>
+        <v>22856</v>
       </c>
       <c r="F6" t="n">
-        <v>6842</v>
+        <v>6864</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>394653</v>
+        <v>396036</v>
       </c>
       <c r="E7" t="n">
-        <v>39370</v>
+        <v>39620</v>
       </c>
       <c r="F7" t="n">
-        <v>3913</v>
+        <v>3929</v>
       </c>
       <c r="G7" t="n">
         <v>0.99</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>372250</v>
+        <v>373594</v>
       </c>
       <c r="E8" t="n">
-        <v>13522</v>
+        <v>13554</v>
       </c>
       <c r="F8" t="n">
-        <v>7911</v>
+        <v>7944</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>261825</v>
+        <v>262690</v>
       </c>
       <c r="E9" t="n">
-        <v>16724</v>
+        <v>16731</v>
       </c>
       <c r="F9" t="n">
-        <v>16680</v>
+        <v>16726</v>
       </c>
       <c r="G9" t="n">
         <v>6.37</v>
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1735</v>
+        <v>2337</v>
       </c>
       <c r="E11" t="n">
-        <v>1349</v>
+        <v>1704</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G11" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 05:59:36</t>
+          <t>Last Updated: 19-09-2026 21:32:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 18-09-2026)</t>
+          <t>MTD (01-09-2026 → 19-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>132644.75</v>
+        <v>137853.13</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>15135.22</v>
+        <v>16706.87</v>
       </c>
       <c r="D5" t="n">
-        <v>117799.37</v>
+        <v>123759.58</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>15135.22</v>
+        <v>16706.87</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>250444.12</v>
+        <v>261612.71</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 17-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 18-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>125809.7</v>
+        <v>132647.42</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>13210.09</v>
+        <v>15154.61</v>
       </c>
       <c r="D11" t="n">
-        <v>111352.46</v>
+        <v>117881.02</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>13210.09</v>
+        <v>15154.61</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>237162.16</v>
+        <v>250528.44</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6835.05</v>
+        <v>5205.71</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1925.13</v>
+        <v>1552.26</v>
       </c>
       <c r="D17" t="n">
-        <v>6446.91</v>
+        <v>5878.56</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1925.13</v>
+        <v>1552.26</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13281.96</v>
+        <v>11084.27</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 06:00:07</t>
+          <t>Last Updated: 19-09-2026 21:32:46</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-18 | MTD-1: 2026-09-01 → 2026-09-17</t>
+          <t>MTD: 2026-09-01 → 2026-09-19 | MTD-1: 2026-09-01 → 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-18)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3172</v>
+        <v>6372</v>
       </c>
       <c r="C8" t="n">
-        <v>4746</v>
+        <v>11698</v>
       </c>
       <c r="D8" t="n">
-        <v>4.87</v>
+        <v>3.91</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>258.86</v>
+        <v>767.51</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-18)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39620</v>
+        <v>40417</v>
       </c>
       <c r="C14" t="n">
-        <v>396187</v>
+        <v>418969</v>
       </c>
       <c r="D14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>10.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>14876.37</v>
+        <v>15939.36</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-17)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1466</v>
+        <v>3221</v>
       </c>
       <c r="C20" t="n">
-        <v>2406</v>
+        <v>4821</v>
       </c>
       <c r="D20" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="E20" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>51.73</v>
+        <v>265.79</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-17)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>37254</v>
+        <v>39636</v>
       </c>
       <c r="C26" t="n">
-        <v>361014</v>
+        <v>396488</v>
       </c>
       <c r="D26" t="n">
         <v>1.17</v>
       </c>
       <c r="E26" t="n">
-        <v>9.69</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>13158.36</v>
+        <v>14888.82</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1706</v>
+        <v>3151</v>
       </c>
       <c r="C32" t="n">
-        <v>2340</v>
+        <v>6877</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.14</v>
+        <v>0.34</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>207.13</v>
+        <v>501.72</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2366</v>
+        <v>781</v>
       </c>
       <c r="C38" t="n">
-        <v>35173</v>
+        <v>22481</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1718.01</v>
+        <v>1050.54</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 06:00:46</t>
+          <t>Last Updated: 19-09-2026 21:33:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-18)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>83129</v>
+        <v>85219</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1842329</v>
+        <v>1924163</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>99965.67999999999</v>
+        <v>104908.28</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>101135</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2522105</v>
+        <v>2650775</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>132644.75</v>
+        <v>137853.13</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>184264</v>
+        <v>186354</v>
       </c>
       <c r="C7" t="n">
-        <v>4364434</v>
+        <v>4574938</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>232610.43</v>
+        <v>242761.41</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-18)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1842329</v>
+        <v>1924163</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>99965.67999999999</v>
+        <v>104908.28</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-18)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2208511</v>
+        <v>2334080</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>124760.92</v>
+        <v>129893.13</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>313594</v>
+        <v>316695</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7883.83</v>
+        <v>7960</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-17)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>83129</v>
+        <v>85219</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>83129</v>
+        <v>85219</v>
       </c>
       <c r="C39" t="n">
-        <v>1746667</v>
+        <v>1843434</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>94593.47</v>
+        <v>100032.03</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>101135</v>
       </c>
       <c r="C44" t="n">
-        <v>2055652</v>
+        <v>2208506</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>118022.37</v>
+        <v>124763.59</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 06:01:23</t>
+          <t>Last Updated: 19-09-2026 21:33:59</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-18</t>
+          <t>MTD: 2026-09-01 → 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 06:01:58</t>
+          <t>Last Updated: 19-09-2026 21:34:33</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 06:01:58</t>
+          <t>Last Updated: 19-09-2026 21:34:33</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 06:02:33</t>
+          <t>Last Updated: 19-09-2026 21:35:07</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 06:03:09</t>
+          <t>Last Updated: 19-09-2026 21:35:43</t>
         </is>
       </c>
     </row>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2522105</v>
+        <v>2650775</v>
       </c>
       <c r="E4" t="n">
         <v>101135</v>
       </c>
       <c r="F4" t="n">
-        <v>17632</v>
+        <v>18165</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1001243</v>
+        <v>1045472</v>
       </c>
       <c r="E5" t="n">
-        <v>46719</v>
+        <v>47082</v>
       </c>
       <c r="F5" t="n">
-        <v>15670</v>
+        <v>16375</v>
       </c>
       <c r="G5" t="n">
         <v>1.57</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>467492</v>
+        <v>490134</v>
       </c>
       <c r="E6" t="n">
-        <v>22856</v>
+        <v>24409</v>
       </c>
       <c r="F6" t="n">
-        <v>6864</v>
+        <v>7226</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>396036</v>
+        <v>418756</v>
       </c>
       <c r="E7" t="n">
-        <v>39620</v>
+        <v>40417</v>
       </c>
       <c r="F7" t="n">
-        <v>3929</v>
+        <v>4158</v>
       </c>
       <c r="G7" t="n">
         <v>0.99</v>
@@ -4907,16 +4907,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>373594</v>
+        <v>388557</v>
       </c>
       <c r="E8" t="n">
-        <v>13554</v>
+        <v>13786</v>
       </c>
       <c r="F8" t="n">
-        <v>7944</v>
+        <v>8298</v>
       </c>
       <c r="G8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4951,16 +4951,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>262690</v>
+        <v>275398</v>
       </c>
       <c r="E9" t="n">
-        <v>16731</v>
+        <v>16844</v>
       </c>
       <c r="F9" t="n">
-        <v>16726</v>
+        <v>17524</v>
       </c>
       <c r="G9" t="n">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2408</v>
+        <v>9260</v>
       </c>
       <c r="E10" t="n">
-        <v>1468</v>
+        <v>4883</v>
       </c>
       <c r="F10" t="n">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="G10" t="n">
-        <v>4.03</v>
+        <v>2.93</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2337</v>
+        <v>2432</v>
       </c>
       <c r="E11" t="n">
-        <v>1704</v>
+        <v>1489</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>3.99</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:32:15</t>
+          <t>Last Updated: 20-09-2026 05:44:38</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>137853.13</v>
+        <v>140104.3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>16706.87</v>
+        <v>16779.65</v>
       </c>
       <c r="D5" t="n">
-        <v>123759.58</v>
+        <v>124270.16</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16706.87</v>
+        <v>16779.65</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>261612.71</v>
+        <v>264374.46</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5205.71</v>
+        <v>7456.88</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1552.26</v>
+        <v>1625.04</v>
       </c>
       <c r="D17" t="n">
-        <v>5878.56</v>
+        <v>6389.14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1552.26</v>
+        <v>1625.04</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11084.27</v>
+        <v>13846.02</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:32:46</t>
+          <t>Last Updated: 20-09-2026 05:45:08</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6372</v>
+        <v>6409</v>
       </c>
       <c r="C8" t="n">
-        <v>11698</v>
+        <v>11829</v>
       </c>
       <c r="D8" t="n">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="E8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>767.51</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40417</v>
+        <v>40434</v>
       </c>
       <c r="C14" t="n">
-        <v>418969</v>
+        <v>420657</v>
       </c>
       <c r="D14" t="n">
         <v>1.18</v>
       </c>
       <c r="E14" t="n">
-        <v>10.37</v>
+        <v>10.4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>15939.36</v>
+        <v>16008.82</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>3221</v>
       </c>
       <c r="C20" t="n">
-        <v>4821</v>
+        <v>4822</v>
       </c>
       <c r="D20" t="n">
         <v>4.81</v>
@@ -1992,7 +1992,7 @@
         <v>39636</v>
       </c>
       <c r="C26" t="n">
-        <v>396488</v>
+        <v>396502</v>
       </c>
       <c r="D26" t="n">
         <v>1.17</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3151</v>
+        <v>3188</v>
       </c>
       <c r="C32" t="n">
-        <v>6877</v>
+        <v>7007</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9</v>
+        <v>-0.83</v>
       </c>
       <c r="E32" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>501.72</v>
+        <v>505.03</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="C38" t="n">
-        <v>22481</v>
+        <v>24155</v>
       </c>
       <c r="D38" t="n">
         <v>0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1050.54</v>
+        <v>1120</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:33:24</t>
+          <t>Last Updated: 20-09-2026 05:45:47</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>85219</v>
+        <v>85407</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1924163</v>
+        <v>1932077</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>104908.28</v>
+        <v>105301.25</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>101135</v>
+        <v>102842</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2650775</v>
+        <v>2694043</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137853.13</v>
+        <v>140104.3</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>186354</v>
+        <v>188249</v>
       </c>
       <c r="C7" t="n">
-        <v>4574938</v>
+        <v>4626120</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>242761.41</v>
+        <v>245405.55</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1924163</v>
+        <v>1932077</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>104908.28</v>
+        <v>105301.25</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2334080</v>
+        <v>2376456</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>129893.13</v>
+        <v>132113.95</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>316695</v>
+        <v>317587</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7960</v>
+        <v>7990.35</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>85219</v>
+        <v>85407</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>85219</v>
+        <v>85407</v>
       </c>
       <c r="C39" t="n">
         <v>1843434</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>101135</v>
+        <v>102842</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>101135</v>
+        <v>102842</v>
       </c>
       <c r="C44" t="n">
         <v>2208506</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:33:59</t>
+          <t>Last Updated: 20-09-2026 05:46:24</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:34:33</t>
+          <t>Last Updated: 20-09-2026 05:47:00</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:34:33</t>
+          <t>Last Updated: 20-09-2026 05:47:00</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:35:07</t>
+          <t>Last Updated: 20-09-2026 05:47:35</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-09-2026 21:35:43</t>
+          <t>Last Updated: 20-09-2026 05:48:11</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2650775</v>
+        <v>2694043</v>
       </c>
       <c r="E4" t="n">
-        <v>101135</v>
+        <v>102842</v>
       </c>
       <c r="F4" t="n">
-        <v>18165</v>
+        <v>18486</v>
       </c>
       <c r="G4" t="n">
         <v>0.6899999999999999</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1045472</v>
+        <v>1050140</v>
       </c>
       <c r="E5" t="n">
         <v>47082</v>
       </c>
       <c r="F5" t="n">
-        <v>16375</v>
+        <v>16473</v>
       </c>
       <c r="G5" t="n">
         <v>1.57</v>
@@ -4819,16 +4819,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>490134</v>
+        <v>492146</v>
       </c>
       <c r="E6" t="n">
-        <v>24409</v>
+        <v>24504</v>
       </c>
       <c r="F6" t="n">
-        <v>7226</v>
+        <v>7264</v>
       </c>
       <c r="G6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>418756</v>
+        <v>420480</v>
       </c>
       <c r="E7" t="n">
-        <v>40417</v>
+        <v>40434</v>
       </c>
       <c r="F7" t="n">
-        <v>4158</v>
+        <v>4177</v>
       </c>
       <c r="G7" t="n">
         <v>0.99</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>388557</v>
+        <v>389791</v>
       </c>
       <c r="E8" t="n">
-        <v>13786</v>
+        <v>13821</v>
       </c>
       <c r="F8" t="n">
-        <v>8298</v>
+        <v>8342</v>
       </c>
       <c r="G8" t="n">
         <v>2.14</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>275398</v>
+        <v>276954</v>
       </c>
       <c r="E9" t="n">
         <v>16844</v>
       </c>
       <c r="F9" t="n">
-        <v>17524</v>
+        <v>17605</v>
       </c>
       <c r="G9" t="n">
         <v>6.36</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9260</v>
+        <v>9390</v>
       </c>
       <c r="E10" t="n">
-        <v>4883</v>
+        <v>4920</v>
       </c>
       <c r="F10" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G10" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2432</v>
+        <v>2437</v>
       </c>
       <c r="E11" t="n">
         <v>1489</v>
@@ -5048,7 +5048,7 @@
         <v>97</v>
       </c>
       <c r="G11" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:44:38</t>
+          <t>Last Updated: 20-09-2026 21:55:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 19-09-2026)</t>
+          <t>MTD (01-09-2026 → 20-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>140104.3</v>
+        <v>144724.86</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>16779.65</v>
+        <v>18532.63</v>
       </c>
       <c r="D5" t="n">
-        <v>124270.16</v>
+        <v>130891.81</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16779.65</v>
+        <v>18532.63</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>264374.46</v>
+        <v>275616.67</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 18-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 19-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>132647.42</v>
+        <v>140111.38</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15154.61</v>
+        <v>16782.38</v>
       </c>
       <c r="D11" t="n">
-        <v>117881.02</v>
+        <v>124291.01</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>15154.61</v>
+        <v>16782.38</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>250528.44</v>
+        <v>264402.39</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7456.88</v>
+        <v>4613.48</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1625.04</v>
+        <v>1750.25</v>
       </c>
       <c r="D17" t="n">
-        <v>6389.14</v>
+        <v>6600.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1625.04</v>
+        <v>1750.25</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13846.02</v>
+        <v>11214.28</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:45:08</t>
+          <t>Last Updated: 20-09-2026 21:55:41</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-19 | MTD-1: 2026-09-01 → 2026-09-18</t>
+          <t>MTD: 2026-09-01 → 2026-09-20 | MTD-1: 2026-09-01 → 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-19)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6409</v>
+        <v>8887</v>
       </c>
       <c r="C8" t="n">
-        <v>11829</v>
+        <v>23392</v>
       </c>
       <c r="D8" t="n">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="E8" t="n">
-        <v>1.85</v>
+        <v>2.63</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>770.8200000000001</v>
+        <v>1298.47</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-19)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40434</v>
+        <v>41884</v>
       </c>
       <c r="C14" t="n">
-        <v>420657</v>
+        <v>448869</v>
       </c>
       <c r="D14" t="n">
         <v>1.18</v>
       </c>
       <c r="E14" t="n">
-        <v>10.4</v>
+        <v>10.72</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>16008.82</v>
+        <v>17234.15</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-18)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3221</v>
+        <v>6414</v>
       </c>
       <c r="C20" t="n">
-        <v>4822</v>
+        <v>11846</v>
       </c>
       <c r="D20" t="n">
-        <v>4.81</v>
+        <v>3.98</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>265.79</v>
+        <v>770.8200000000001</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-18)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39636</v>
+        <v>40434</v>
       </c>
       <c r="C26" t="n">
-        <v>396502</v>
+        <v>420846</v>
       </c>
       <c r="D26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>10.41</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>14888.82</v>
+        <v>16011.55</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3188</v>
+        <v>2473</v>
       </c>
       <c r="C32" t="n">
-        <v>7007</v>
+        <v>11546</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.83</v>
+        <v>-0.37</v>
       </c>
       <c r="E32" t="n">
-        <v>0.35</v>
+        <v>0.78</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>505.03</v>
+        <v>527.65</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>798</v>
+        <v>1450</v>
       </c>
       <c r="C38" t="n">
-        <v>24155</v>
+        <v>28023</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1120</v>
+        <v>1222.6</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:45:47</t>
+          <t>Last Updated: 20-09-2026 21:56:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-19)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>85407</v>
+        <v>87136</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1932077</v>
+        <v>2028109</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>105301.25</v>
+        <v>111104.61</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>102842</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2694043</v>
+        <v>2792311</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>140104.3</v>
+        <v>144724.86</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>188249</v>
+        <v>189978</v>
       </c>
       <c r="C7" t="n">
-        <v>4626120</v>
+        <v>4820420</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>245405.55</v>
+        <v>255829.47</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-19)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1932077</v>
+        <v>2028109</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>105301.25</v>
+        <v>111104.61</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-19)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2376456</v>
+        <v>2471972</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>132113.95</v>
+        <v>136671.79</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>317587</v>
+        <v>320339</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7990.35</v>
+        <v>8053.07</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-18)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-19)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>85407</v>
+        <v>87136</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>85407</v>
+        <v>87136</v>
       </c>
       <c r="C39" t="n">
-        <v>1843434</v>
+        <v>1932856</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>100032.03</v>
+        <v>105314.34</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>102842</v>
       </c>
       <c r="C44" t="n">
-        <v>2208506</v>
+        <v>2376456</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>124763.59</v>
+        <v>132121.03</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:46:24</t>
+          <t>Last Updated: 20-09-2026 21:56:54</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-19</t>
+          <t>MTD: 2026-09-01 → 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:47:00</t>
+          <t>Last Updated: 20-09-2026 21:57:29</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:47:00</t>
+          <t>Last Updated: 20-09-2026 21:57:29</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:47:35</t>
+          <t>Last Updated: 20-09-2026 21:58:04</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 05:48:11</t>
+          <t>Last Updated: 20-09-2026 21:58:39</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2694043</v>
+        <v>2792311</v>
       </c>
       <c r="E4" t="n">
         <v>102842</v>
       </c>
       <c r="F4" t="n">
-        <v>18486</v>
+        <v>19133</v>
       </c>
       <c r="G4" t="n">
         <v>0.6899999999999999</v>
@@ -4775,16 +4775,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1050140</v>
+        <v>1110925</v>
       </c>
       <c r="E5" t="n">
-        <v>47082</v>
+        <v>47667</v>
       </c>
       <c r="F5" t="n">
-        <v>16473</v>
+        <v>17309</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4819,16 +4819,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>492146</v>
+        <v>507459</v>
       </c>
       <c r="E6" t="n">
-        <v>24504</v>
+        <v>25280</v>
       </c>
       <c r="F6" t="n">
-        <v>7264</v>
+        <v>7466</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>420480</v>
+        <v>448616</v>
       </c>
       <c r="E7" t="n">
-        <v>40434</v>
+        <v>41884</v>
       </c>
       <c r="F7" t="n">
-        <v>4177</v>
+        <v>4484</v>
       </c>
       <c r="G7" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4907,16 +4907,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>389791</v>
+        <v>409725</v>
       </c>
       <c r="E8" t="n">
-        <v>13821</v>
+        <v>14189</v>
       </c>
       <c r="F8" t="n">
-        <v>8342</v>
+        <v>8734</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>276954</v>
+        <v>287645</v>
       </c>
       <c r="E9" t="n">
-        <v>16844</v>
+        <v>16995</v>
       </c>
       <c r="F9" t="n">
-        <v>17605</v>
+        <v>18291</v>
       </c>
       <c r="G9" t="n">
         <v>6.36</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9390</v>
+        <v>20910</v>
       </c>
       <c r="E10" t="n">
-        <v>4920</v>
+        <v>7420</v>
       </c>
       <c r="F10" t="n">
-        <v>281</v>
+        <v>545</v>
       </c>
       <c r="G10" t="n">
-        <v>2.99</v>
+        <v>2.61</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2437</v>
+        <v>2444</v>
       </c>
       <c r="E11" t="n">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="F11" t="n">
         <v>97</v>
       </c>
       <c r="G11" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:55:10</t>
+          <t>Last Updated: 21-09-2026 05:53:04</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>144724.86</v>
+        <v>146913.36</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>18532.63</v>
+        <v>18723.43</v>
       </c>
       <c r="D5" t="n">
-        <v>130891.81</v>
+        <v>131474.94</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18532.63</v>
+        <v>18723.43</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>275616.67</v>
+        <v>278388.3</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4613.48</v>
+        <v>6801.98</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1750.25</v>
+        <v>1941.05</v>
       </c>
       <c r="D17" t="n">
-        <v>6600.8</v>
+        <v>7183.93</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1750.25</v>
+        <v>1941.05</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11214.28</v>
+        <v>13985.91</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:55:41</t>
+          <t>Last Updated: 21-09-2026 05:53:34</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8887</v>
+        <v>9134</v>
       </c>
       <c r="C8" t="n">
-        <v>23392</v>
+        <v>24449</v>
       </c>
       <c r="D8" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="E8" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1298.47</v>
+        <v>1359.94</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41884</v>
+        <v>41954</v>
       </c>
       <c r="C14" t="n">
-        <v>448869</v>
+        <v>451410</v>
       </c>
       <c r="D14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>10.72</v>
+        <v>10.76</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>17234.15</v>
+        <v>17363.49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>40434</v>
       </c>
       <c r="C26" t="n">
-        <v>420846</v>
+        <v>420850</v>
       </c>
       <c r="D26" t="n">
         <v>1.18</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2473</v>
+        <v>2720</v>
       </c>
       <c r="C32" t="n">
-        <v>11546</v>
+        <v>12603</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="E32" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>527.65</v>
+        <v>589.12</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1450</v>
+        <v>1520</v>
       </c>
       <c r="C38" t="n">
-        <v>28023</v>
+        <v>30560</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1222.6</v>
+        <v>1351.94</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:56:19</t>
+          <t>Last Updated: 21-09-2026 05:54:12</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>87136</v>
+        <v>87208</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2028109</v>
+        <v>2035969</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>111104.61</v>
+        <v>111559.22</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>102842</v>
+        <v>104397</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2792311</v>
+        <v>2832605</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>144724.86</v>
+        <v>146913.36</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>189978</v>
+        <v>191605</v>
       </c>
       <c r="C7" t="n">
-        <v>4820420</v>
+        <v>4868574</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>255829.47</v>
+        <v>258472.58</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2028109</v>
+        <v>2035969</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>111104.61</v>
+        <v>111559.22</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2471972</v>
+        <v>2511368</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>136671.79</v>
+        <v>138834.88</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>320339</v>
+        <v>321237</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8053.07</v>
+        <v>8078.48</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>87136</v>
+        <v>87208</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>87136</v>
+        <v>87208</v>
       </c>
       <c r="C39" t="n">
         <v>1932856</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>102842</v>
+        <v>104397</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>102842</v>
+        <v>104397</v>
       </c>
       <c r="C44" t="n">
         <v>2376456</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:56:54</t>
+          <t>Last Updated: 21-09-2026 05:54:47</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:57:29</t>
+          <t>Last Updated: 21-09-2026 05:55:21</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:57:29</t>
+          <t>Last Updated: 21-09-2026 05:55:21</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:58:04</t>
+          <t>Last Updated: 21-09-2026 05:55:55</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-09-2026 21:58:39</t>
+          <t>Last Updated: 21-09-2026 05:56:29</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2792311</v>
+        <v>2832605</v>
       </c>
       <c r="E4" t="n">
-        <v>102842</v>
+        <v>104397</v>
       </c>
       <c r="F4" t="n">
-        <v>19133</v>
+        <v>19458</v>
       </c>
       <c r="G4" t="n">
         <v>0.6899999999999999</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1110925</v>
+        <v>1116432</v>
       </c>
       <c r="E5" t="n">
         <v>47667</v>
       </c>
       <c r="F5" t="n">
-        <v>17309</v>
+        <v>17403</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>507459</v>
+        <v>508508</v>
       </c>
       <c r="E6" t="n">
-        <v>25280</v>
+        <v>25329</v>
       </c>
       <c r="F6" t="n">
-        <v>7466</v>
+        <v>7491</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>448616</v>
+        <v>451215</v>
       </c>
       <c r="E7" t="n">
-        <v>41884</v>
+        <v>41954</v>
       </c>
       <c r="F7" t="n">
-        <v>4484</v>
+        <v>4518</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>409725</v>
+        <v>411029</v>
       </c>
       <c r="E8" t="n">
-        <v>14189</v>
+        <v>14212</v>
       </c>
       <c r="F8" t="n">
-        <v>8734</v>
+        <v>8772</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>287645</v>
+        <v>289093</v>
       </c>
       <c r="E9" t="n">
-        <v>16995</v>
+        <v>17073</v>
       </c>
       <c r="F9" t="n">
-        <v>18291</v>
+        <v>18400</v>
       </c>
       <c r="G9" t="n">
         <v>6.36</v>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20910</v>
+        <v>22003</v>
       </c>
       <c r="E10" t="n">
-        <v>7420</v>
+        <v>7639</v>
       </c>
       <c r="F10" t="n">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="G10" t="n">
         <v>2.61</v>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="E11" t="n">
         <v>1495</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:53:04</t>
+          <t>Last Updated: 21-09-2026 23:49:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 20-09-2026)</t>
+          <t>MTD (01-09-2026 → 21-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>146913.36</v>
+        <v>151619.02</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>18723.43</v>
+        <v>20621.83</v>
       </c>
       <c r="D5" t="n">
-        <v>131474.94</v>
+        <v>138075.94</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18723.43</v>
+        <v>20621.83</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>278388.3</v>
+        <v>289694.96</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 19-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 20-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>140111.38</v>
+        <v>146919.18</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16782.38</v>
+        <v>18747.27</v>
       </c>
       <c r="D11" t="n">
-        <v>124291.01</v>
+        <v>131552.26</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>16782.38</v>
+        <v>18747.27</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>264402.39</v>
+        <v>278471.44</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6801.98</v>
+        <v>4699.84</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1941.05</v>
+        <v>1874.56</v>
       </c>
       <c r="D17" t="n">
-        <v>7183.93</v>
+        <v>6523.68</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1941.05</v>
+        <v>1874.56</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13985.91</v>
+        <v>11223.52</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:53:34</t>
+          <t>Last Updated: 21-09-2026 23:50:17</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-20 | MTD-1: 2026-09-01 → 2026-09-19</t>
+          <t>MTD: 2026-09-01 → 2026-09-21 | MTD-1: 2026-09-01 → 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-20)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9134</v>
+        <v>11644</v>
       </c>
       <c r="C8" t="n">
-        <v>24449</v>
+        <v>39623</v>
       </c>
       <c r="D8" t="n">
-        <v>3.63</v>
+        <v>3.13</v>
       </c>
       <c r="E8" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1359.94</v>
+        <v>1998.75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-20)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41954</v>
+        <v>43183</v>
       </c>
       <c r="C14" t="n">
-        <v>451410</v>
+        <v>480054</v>
       </c>
       <c r="D14" t="n">
         <v>1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>10.76</v>
+        <v>11.12</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>17363.49</v>
+        <v>18623.08</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-19)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6414</v>
+        <v>9155</v>
       </c>
       <c r="C20" t="n">
-        <v>11846</v>
+        <v>24596</v>
       </c>
       <c r="D20" t="n">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="E20" t="n">
-        <v>1.85</v>
+        <v>2.69</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>770.8200000000001</v>
+        <v>1367.16</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-19)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40434</v>
+        <v>41954</v>
       </c>
       <c r="C26" t="n">
-        <v>420850</v>
+        <v>451798</v>
       </c>
       <c r="D26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="E26" t="n">
-        <v>10.41</v>
+        <v>10.77</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>16011.55</v>
+        <v>17380.11</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2720</v>
+        <v>2489</v>
       </c>
       <c r="C32" t="n">
-        <v>12603</v>
+        <v>15027</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.35</v>
+        <v>-0.49</v>
       </c>
       <c r="E32" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>589.12</v>
+        <v>631.59</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1520</v>
+        <v>1229</v>
       </c>
       <c r="C38" t="n">
-        <v>30560</v>
+        <v>28256</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0.35</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1351.94</v>
+        <v>1242.97</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:54:12</t>
+          <t>Last Updated: 21-09-2026 23:50:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-20)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>87208</v>
+        <v>88921</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2035969</v>
+        <v>2124448</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>111559.22</v>
+        <v>116972.61</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>104397</v>
+        <v>105834</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2832605</v>
+        <v>2957143</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>146913.36</v>
+        <v>151619.02</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>191605</v>
+        <v>194755</v>
       </c>
       <c r="C7" t="n">
-        <v>4868574</v>
+        <v>5081591</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>258472.58</v>
+        <v>268591.63</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-20)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2035969</v>
+        <v>2124448</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>111559.22</v>
+        <v>116972.61</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-20)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2511368</v>
+        <v>2632397</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>138834.88</v>
+        <v>143460.64</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>321237</v>
+        <v>324746</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8078.48</v>
+        <v>8158.38</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-19)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-20)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>87208</v>
+        <v>88921</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>87208</v>
+        <v>88921</v>
       </c>
       <c r="C39" t="n">
-        <v>1932856</v>
+        <v>2036909</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>105314.34</v>
+        <v>111623.54</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>104397</v>
+        <v>105834</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>104397</v>
+        <v>105834</v>
       </c>
       <c r="C44" t="n">
-        <v>2376456</v>
+        <v>2511366</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>132121.03</v>
+        <v>138840.63</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:54:47</t>
+          <t>Last Updated: 21-09-2026 23:51:33</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-20</t>
+          <t>MTD: 2026-09-01 → 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:55:21</t>
+          <t>Last Updated: 21-09-2026 23:52:08</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:55:21</t>
+          <t>Last Updated: 21-09-2026 23:52:08</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:55:55</t>
+          <t>Last Updated: 21-09-2026 23:52:43</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 05:56:29</t>
+          <t>Last Updated: 21-09-2026 23:53:20</t>
         </is>
       </c>
     </row>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2832605</v>
+        <v>2957143</v>
       </c>
       <c r="E4" t="n">
-        <v>104397</v>
+        <v>105834</v>
       </c>
       <c r="F4" t="n">
-        <v>19458</v>
+        <v>19967</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1116432</v>
+        <v>1175311</v>
       </c>
       <c r="E5" t="n">
-        <v>47667</v>
+        <v>48756</v>
       </c>
       <c r="F5" t="n">
-        <v>17403</v>
+        <v>18281</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>508508</v>
+        <v>519596</v>
       </c>
       <c r="E6" t="n">
-        <v>25329</v>
+        <v>25708</v>
       </c>
       <c r="F6" t="n">
-        <v>7491</v>
+        <v>7647</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>451215</v>
+        <v>479827</v>
       </c>
       <c r="E7" t="n">
-        <v>41954</v>
+        <v>43183</v>
       </c>
       <c r="F7" t="n">
-        <v>4518</v>
+        <v>4794</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>411029</v>
+        <v>429541</v>
       </c>
       <c r="E8" t="n">
-        <v>14212</v>
+        <v>14457</v>
       </c>
       <c r="F8" t="n">
-        <v>8772</v>
+        <v>9136</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,16 +4951,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>289093</v>
+        <v>304025</v>
       </c>
       <c r="E9" t="n">
-        <v>17073</v>
+        <v>17239</v>
       </c>
       <c r="F9" t="n">
-        <v>18400</v>
+        <v>19313</v>
       </c>
       <c r="G9" t="n">
-        <v>6.36</v>
+        <v>6.35</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22003</v>
+        <v>37133</v>
       </c>
       <c r="E10" t="n">
-        <v>7639</v>
+        <v>10128</v>
       </c>
       <c r="F10" t="n">
-        <v>575</v>
+        <v>840</v>
       </c>
       <c r="G10" t="n">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,13 +5039,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2445</v>
+        <v>2470</v>
       </c>
       <c r="E11" t="n">
-        <v>1495</v>
+        <v>1516</v>
       </c>
       <c r="F11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G11" t="n">
         <v>3.97</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:49:46</t>
+          <t>Last Updated: 22-09-2026 06:30:40</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>151619.02</v>
+        <v>154059.04</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>20621.83</v>
+        <v>20643.94</v>
       </c>
       <c r="D5" t="n">
-        <v>138075.94</v>
+        <v>138132.07</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>20621.83</v>
+        <v>20643.94</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>289694.96</v>
+        <v>292191.11</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4699.84</v>
+        <v>7139.86</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1874.56</v>
+        <v>1896.67</v>
       </c>
       <c r="D17" t="n">
-        <v>6523.68</v>
+        <v>6579.81</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1874.56</v>
+        <v>1896.67</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11223.52</v>
+        <v>13719.67</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:50:17</t>
+          <t>Last Updated: 22-09-2026 06:31:11</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11644</v>
+        <v>11664</v>
       </c>
       <c r="C8" t="n">
-        <v>39623</v>
+        <v>39750</v>
       </c>
       <c r="D8" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1998.75</v>
+        <v>2006.35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43183</v>
+        <v>43230</v>
       </c>
       <c r="C14" t="n">
-        <v>480054</v>
+        <v>480326</v>
       </c>
       <c r="D14" t="n">
         <v>1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>18623.08</v>
+        <v>18637.59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>41954</v>
       </c>
       <c r="C26" t="n">
-        <v>451798</v>
+        <v>451802</v>
       </c>
       <c r="D26" t="n">
         <v>1.19</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2489</v>
+        <v>2509</v>
       </c>
       <c r="C32" t="n">
-        <v>15027</v>
+        <v>15154</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>631.59</v>
+        <v>639.1900000000001</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1229</v>
+        <v>1276</v>
       </c>
       <c r="C38" t="n">
-        <v>28256</v>
+        <v>28524</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1242.97</v>
+        <v>1257.48</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:50:56</t>
+          <t>Last Updated: 22-09-2026 06:31:51</t>
         </is>
       </c>
     </row>
@@ -2398,13 +2398,13 @@
         <v>88921</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2124448</v>
+        <v>2125136</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>116972.61</v>
+        <v>117020.45</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>105834</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2957143</v>
+        <v>2999680</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>151619.02</v>
+        <v>154059.04</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2448,13 +2448,13 @@
         <v>194755</v>
       </c>
       <c r="C7" t="n">
-        <v>5081591</v>
+        <v>5124816</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>268591.63</v>
+        <v>271079.49</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2124448</v>
+        <v>2125136</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>116972.61</v>
+        <v>117020.45</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2632397</v>
+        <v>2673980</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>143460.64</v>
+        <v>145868.64</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>324746</v>
+        <v>325700</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8158.38</v>
+        <v>8190.4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:51:33</t>
+          <t>Last Updated: 22-09-2026 06:32:28</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:52:08</t>
+          <t>Last Updated: 22-09-2026 06:33:04</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:52:08</t>
+          <t>Last Updated: 22-09-2026 06:33:04</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:52:43</t>
+          <t>Last Updated: 22-09-2026 06:33:40</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-09-2026 23:53:20</t>
+          <t>Last Updated: 22-09-2026 06:34:18</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2957143</v>
+        <v>2999680</v>
       </c>
       <c r="E4" t="n">
         <v>105834</v>
       </c>
       <c r="F4" t="n">
-        <v>19967</v>
+        <v>20343</v>
       </c>
       <c r="G4" t="n">
         <v>0.68</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1175311</v>
+        <v>1175765</v>
       </c>
       <c r="E5" t="n">
         <v>48756</v>
       </c>
       <c r="F5" t="n">
-        <v>18281</v>
+        <v>18288</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>519596</v>
+        <v>519674</v>
       </c>
       <c r="E6" t="n">
         <v>25708</v>
       </c>
       <c r="F6" t="n">
-        <v>7647</v>
+        <v>7650</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>479827</v>
+        <v>480121</v>
       </c>
       <c r="E7" t="n">
-        <v>43183</v>
+        <v>43230</v>
       </c>
       <c r="F7" t="n">
-        <v>4794</v>
+        <v>4798</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>429541</v>
+        <v>429697</v>
       </c>
       <c r="E8" t="n">
         <v>14457</v>
       </c>
       <c r="F8" t="n">
-        <v>9136</v>
+        <v>9145</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>304025</v>
+        <v>304119</v>
       </c>
       <c r="E9" t="n">
         <v>17239</v>
       </c>
       <c r="F9" t="n">
-        <v>19313</v>
+        <v>19316</v>
       </c>
       <c r="G9" t="n">
         <v>6.35</v>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37133</v>
+        <v>37279</v>
       </c>
       <c r="E10" t="n">
-        <v>10128</v>
+        <v>10148</v>
       </c>
       <c r="F10" t="n">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G10" t="n">
         <v>2.26</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:30:40</t>
+          <t>Last Updated: 22-09-2026 22:42:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 21-09-2026)</t>
+          <t>MTD (01-09-2026 → 22-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>154059.04</v>
+        <v>159267.97</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>20643.94</v>
+        <v>22459.62</v>
       </c>
       <c r="D5" t="n">
-        <v>138132.07</v>
+        <v>144589.77</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>20643.94</v>
+        <v>22459.62</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>292191.11</v>
+        <v>303857.74</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 20-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 21-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>146919.18</v>
+        <v>154063.66</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>18747.27</v>
+        <v>20658.29</v>
       </c>
       <c r="D11" t="n">
-        <v>131552.26</v>
+        <v>138186.58</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>18747.27</v>
+        <v>20658.29</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>278471.44</v>
+        <v>292250.24</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7139.86</v>
+        <v>5204.31</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1896.67</v>
+        <v>1801.33</v>
       </c>
       <c r="D17" t="n">
-        <v>6579.81</v>
+        <v>6403.19</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1896.67</v>
+        <v>1801.33</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13719.67</v>
+        <v>11607.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:31:11</t>
+          <t>Last Updated: 22-09-2026 22:43:14</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-21 | MTD-1: 2026-09-01 → 2026-09-20</t>
+          <t>MTD: 2026-09-01 → 2026-09-22 | MTD-1: 2026-09-01 → 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-21)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11664</v>
+        <v>13088</v>
       </c>
       <c r="C8" t="n">
-        <v>39750</v>
+        <v>52620</v>
       </c>
       <c r="D8" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="E8" t="n">
-        <v>3.41</v>
+        <v>4.02</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2006.35</v>
+        <v>2480.58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-21)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43230</v>
+        <v>45738</v>
       </c>
       <c r="C14" t="n">
-        <v>480326</v>
+        <v>509613</v>
       </c>
       <c r="D14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>11.11</v>
+        <v>11.14</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>18637.59</v>
+        <v>19979.04</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-20)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9155</v>
+        <v>11702</v>
       </c>
       <c r="C20" t="n">
-        <v>24596</v>
+        <v>39896</v>
       </c>
       <c r="D20" t="n">
-        <v>3.62</v>
+        <v>3.12</v>
       </c>
       <c r="E20" t="n">
-        <v>2.69</v>
+        <v>3.41</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1367.16</v>
+        <v>2011.82</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-20)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>41954</v>
+        <v>43230</v>
       </c>
       <c r="C26" t="n">
-        <v>451802</v>
+        <v>480575</v>
       </c>
       <c r="D26" t="n">
         <v>1.19</v>
       </c>
       <c r="E26" t="n">
-        <v>10.77</v>
+        <v>11.12</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>17380.11</v>
+        <v>18646.48</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2509</v>
+        <v>1386</v>
       </c>
       <c r="C32" t="n">
-        <v>15154</v>
+        <v>12724</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5</v>
+        <v>-0.26</v>
       </c>
       <c r="E32" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>639.1900000000001</v>
+        <v>468.76</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1276</v>
+        <v>2508</v>
       </c>
       <c r="C38" t="n">
-        <v>28524</v>
+        <v>29038</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.34</v>
+        <v>0.02</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1257.48</v>
+        <v>1332.56</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:31:51</t>
+          <t>Last Updated: 22-09-2026 22:43:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-21)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>88921</v>
+        <v>90555</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2125136</v>
+        <v>2212506</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>117020.45</v>
+        <v>122352.5</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>105834</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2999680</v>
+        <v>3108912</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>154059.04</v>
+        <v>159267.97</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194755</v>
+        <v>196389</v>
       </c>
       <c r="C7" t="n">
-        <v>5124816</v>
+        <v>5321418</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>271079.49</v>
+        <v>281620.47</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-21)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2125136</v>
+        <v>2212506</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>117020.45</v>
+        <v>122352.5</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-21)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2673980</v>
+        <v>2776418</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>145868.64</v>
+        <v>150853.76</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>325700</v>
+        <v>332494</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8190.4</v>
+        <v>8414.209999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-20)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-21)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>88921</v>
+        <v>90555</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>88921</v>
+        <v>90555</v>
       </c>
       <c r="C39" t="n">
-        <v>2036909</v>
+        <v>2125799</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>111623.54</v>
+        <v>117067.74</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>105834</v>
       </c>
       <c r="C44" t="n">
-        <v>2511366</v>
+        <v>2673931</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>138840.63</v>
+        <v>145873.36</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:32:28</t>
+          <t>Last Updated: 22-09-2026 22:44:29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-21</t>
+          <t>MTD: 2026-09-01 → 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:33:04</t>
+          <t>Last Updated: 22-09-2026 22:45:04</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:33:04</t>
+          <t>Last Updated: 22-09-2026 22:45:04</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:33:40</t>
+          <t>Last Updated: 22-09-2026 22:45:38</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 06:34:18</t>
+          <t>Last Updated: 22-09-2026 22:46:14</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2999680</v>
+        <v>3108912</v>
       </c>
       <c r="E4" t="n">
         <v>105834</v>
       </c>
       <c r="F4" t="n">
-        <v>20343</v>
+        <v>20987</v>
       </c>
       <c r="G4" t="n">
         <v>0.68</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1175765</v>
+        <v>1232207</v>
       </c>
       <c r="E5" t="n">
-        <v>48756</v>
+        <v>49675</v>
       </c>
       <c r="F5" t="n">
-        <v>18288</v>
+        <v>19187</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>519674</v>
+        <v>532093</v>
       </c>
       <c r="E6" t="n">
-        <v>25708</v>
+        <v>26124</v>
       </c>
       <c r="F6" t="n">
-        <v>7650</v>
+        <v>7844</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>480121</v>
+        <v>509327</v>
       </c>
       <c r="E7" t="n">
-        <v>43230</v>
+        <v>45738</v>
       </c>
       <c r="F7" t="n">
-        <v>4798</v>
+        <v>5151</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>429697</v>
+        <v>448206</v>
       </c>
       <c r="E8" t="n">
-        <v>14457</v>
+        <v>14756</v>
       </c>
       <c r="F8" t="n">
-        <v>9145</v>
+        <v>9536</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,16 +4951,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>304119</v>
+        <v>318020</v>
       </c>
       <c r="E9" t="n">
-        <v>17239</v>
+        <v>17453</v>
       </c>
       <c r="F9" t="n">
-        <v>19316</v>
+        <v>20175</v>
       </c>
       <c r="G9" t="n">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37279</v>
+        <v>50119</v>
       </c>
       <c r="E10" t="n">
-        <v>10148</v>
+        <v>11568</v>
       </c>
       <c r="F10" t="n">
-        <v>841</v>
+        <v>1047</v>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2470</v>
+        <v>2485</v>
       </c>
       <c r="E11" t="n">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="F11" t="n">
         <v>98</v>
       </c>
       <c r="G11" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:42:43</t>
+          <t>Last Updated: 23-09-2026 06:20:04</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>159267.97</v>
+        <v>159646.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>22459.62</v>
+        <v>22530.83</v>
       </c>
       <c r="D5" t="n">
-        <v>144589.77</v>
+        <v>144861.34</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>22459.62</v>
+        <v>22530.83</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>303857.74</v>
+        <v>304507.94</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5204.31</v>
+        <v>5582.94</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1801.33</v>
+        <v>1872.54</v>
       </c>
       <c r="D17" t="n">
-        <v>6403.19</v>
+        <v>6674.76</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1801.33</v>
+        <v>1872.54</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11607.5</v>
+        <v>12257.7</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:43:14</t>
+          <t>Last Updated: 23-09-2026 06:20:35</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13088</v>
+        <v>13139</v>
       </c>
       <c r="C8" t="n">
-        <v>52620</v>
+        <v>53016</v>
       </c>
       <c r="D8" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="E8" t="n">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2480.58</v>
+        <v>2496.18</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45738</v>
+        <v>45782</v>
       </c>
       <c r="C14" t="n">
-        <v>509613</v>
+        <v>510757</v>
       </c>
       <c r="D14" t="n">
         <v>1.2</v>
       </c>
       <c r="E14" t="n">
-        <v>11.14</v>
+        <v>11.16</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>19979.04</v>
+        <v>20034.65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>43230</v>
       </c>
       <c r="C26" t="n">
-        <v>480575</v>
+        <v>480581</v>
       </c>
       <c r="D26" t="n">
         <v>1.19</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1386</v>
+        <v>1437</v>
       </c>
       <c r="C32" t="n">
-        <v>12724</v>
+        <v>13120</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="E32" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>468.76</v>
+        <v>484.36</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2508</v>
+        <v>2552</v>
       </c>
       <c r="C38" t="n">
-        <v>29038</v>
+        <v>30176</v>
       </c>
       <c r="D38" t="n">
         <v>0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1332.56</v>
+        <v>1388.17</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:43:53</t>
+          <t>Last Updated: 23-09-2026 06:21:15</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>90555</v>
+        <v>90574</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2212506</v>
+        <v>2215995</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>122352.5</v>
+        <v>122580.78</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>105834</v>
+        <v>107027</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3108912</v>
+        <v>3116457</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>159267.97</v>
+        <v>159646.6</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>196389</v>
+        <v>197601</v>
       </c>
       <c r="C7" t="n">
-        <v>5321418</v>
+        <v>5332452</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>281620.47</v>
+        <v>282227.38</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2212506</v>
+        <v>2215995</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>122352.5</v>
+        <v>122580.78</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2776418</v>
+        <v>2776395</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>150853.76</v>
+        <v>150854.78</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>332494</v>
+        <v>340062</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8414.209999999999</v>
+        <v>8791.82</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>90555</v>
+        <v>90574</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>90555</v>
+        <v>90574</v>
       </c>
       <c r="C39" t="n">
         <v>2125799</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>105834</v>
+        <v>107027</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>105834</v>
+        <v>107027</v>
       </c>
       <c r="C44" t="n">
         <v>2673931</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:44:29</t>
+          <t>Last Updated: 23-09-2026 06:21:52</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3310,12 +3310,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:45:04</t>
+          <t>Last Updated: 23-09-2026 06:22:27</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:45:04</t>
+          <t>Last Updated: 23-09-2026 06:22:27</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:45:38</t>
+          <t>Last Updated: 23-09-2026 06:23:03</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-09-2026 22:46:14</t>
+          <t>Last Updated: 23-09-2026 06:23:39</t>
         </is>
       </c>
     </row>
@@ -4731,16 +4731,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3108912</v>
+        <v>3116457</v>
       </c>
       <c r="E4" t="n">
-        <v>105834</v>
+        <v>107027</v>
       </c>
       <c r="F4" t="n">
-        <v>20987</v>
+        <v>21020</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1232207</v>
+        <v>1234569</v>
       </c>
       <c r="E5" t="n">
         <v>49675</v>
       </c>
       <c r="F5" t="n">
-        <v>19187</v>
+        <v>19229</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,16 +4819,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>532093</v>
+        <v>532531</v>
       </c>
       <c r="E6" t="n">
         <v>26124</v>
       </c>
       <c r="F6" t="n">
-        <v>7844</v>
+        <v>7857</v>
       </c>
       <c r="G6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>509327</v>
+        <v>510536</v>
       </c>
       <c r="E7" t="n">
-        <v>45738</v>
+        <v>45782</v>
       </c>
       <c r="F7" t="n">
-        <v>5151</v>
+        <v>5168</v>
       </c>
       <c r="G7" t="n">
         <v>1.01</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>448206</v>
+        <v>448895</v>
       </c>
       <c r="E8" t="n">
-        <v>14756</v>
+        <v>14775</v>
       </c>
       <c r="F8" t="n">
-        <v>9536</v>
+        <v>9560</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>318020</v>
+        <v>318521</v>
       </c>
       <c r="E9" t="n">
-        <v>17453</v>
+        <v>17456</v>
       </c>
       <c r="F9" t="n">
-        <v>20175</v>
+        <v>20192</v>
       </c>
       <c r="G9" t="n">
         <v>6.34</v>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50119</v>
+        <v>50528</v>
       </c>
       <c r="E10" t="n">
-        <v>11568</v>
+        <v>11619</v>
       </c>
       <c r="F10" t="n">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="G10" t="n">
         <v>2.09</v>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="E11" t="n">
         <v>1520</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:20:04</t>
+          <t>Last Updated: 23-09-2026 22:54:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 22-09-2026)</t>
+          <t>MTD (01-09-2026 → 23-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>159646.6</v>
+        <v>160509.3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>22530.83</v>
+        <v>23515.4</v>
       </c>
       <c r="D5" t="n">
-        <v>144861.34</v>
+        <v>151735.22</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>22530.83</v>
+        <v>23515.4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>304507.94</v>
+        <v>312244.52</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 21-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 22-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>154063.66</v>
+        <v>159647.39</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>20658.29</v>
+        <v>22547.21</v>
       </c>
       <c r="D11" t="n">
-        <v>138186.58</v>
+        <v>144927.08</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>20658.29</v>
+        <v>22547.21</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>292250.24</v>
+        <v>304574.47</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5582.94</v>
+        <v>861.91</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1872.54</v>
+        <v>968.1900000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>6674.76</v>
+        <v>6808.14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1872.54</v>
+        <v>968.1900000000001</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12257.7</v>
+        <v>7670.05</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:20:35</t>
+          <t>Last Updated: 23-09-2026 22:55:03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-22 | MTD-1: 2026-09-01 → 2026-09-21</t>
+          <t>MTD: 2026-09-01 → 2026-09-23 | MTD-1: 2026-09-01 → 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-22)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13139</v>
+        <v>14327</v>
       </c>
       <c r="C8" t="n">
-        <v>53016</v>
+        <v>65858</v>
       </c>
       <c r="D8" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="E8" t="n">
-        <v>4.04</v>
+        <v>4.6</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2496.18</v>
+        <v>2970.34</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-22)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45782</v>
+        <v>46200</v>
       </c>
       <c r="C14" t="n">
-        <v>510757</v>
+        <v>521987</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="E14" t="n">
-        <v>11.16</v>
+        <v>11.3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>20034.65</v>
+        <v>20545.05</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-21)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11702</v>
+        <v>13147</v>
       </c>
       <c r="C20" t="n">
-        <v>39896</v>
+        <v>53128</v>
       </c>
       <c r="D20" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="E20" t="n">
-        <v>3.41</v>
+        <v>4.04</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2011.82</v>
+        <v>2500.71</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-21)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43230</v>
+        <v>45803</v>
       </c>
       <c r="C26" t="n">
-        <v>480581</v>
+        <v>511098</v>
       </c>
       <c r="D26" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
-        <v>11.12</v>
+        <v>11.16</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>18646.48</v>
+        <v>20046.5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1437</v>
+        <v>1180</v>
       </c>
       <c r="C32" t="n">
-        <v>13120</v>
+        <v>12730</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.27</v>
+        <v>-0.13</v>
       </c>
       <c r="E32" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>484.36</v>
+        <v>469.63</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2552</v>
+        <v>397</v>
       </c>
       <c r="C38" t="n">
-        <v>30176</v>
+        <v>10889</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1388.17</v>
+        <v>498.55</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:21:15</t>
+          <t>Last Updated: 23-09-2026 22:55:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-22)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>90574</v>
+        <v>92179</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2215995</v>
+        <v>2307173</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>122580.78</v>
+        <v>128254.29</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>107027</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3116457</v>
+        <v>3138108</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>159646.6</v>
+        <v>160509.31</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>197601</v>
+        <v>199206</v>
       </c>
       <c r="C7" t="n">
-        <v>5332452</v>
+        <v>5445281</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>282227.38</v>
+        <v>288763.6</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-22)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2215995</v>
+        <v>2307173</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>122580.78</v>
+        <v>128254.29</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-22)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2776395</v>
+        <v>2776365</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>150854.78</v>
+        <v>150854.89</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>340062</v>
+        <v>361743</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>8791.82</v>
+        <v>9654.42</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-21)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>90574</v>
+        <v>92179</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>90574</v>
+        <v>92179</v>
       </c>
       <c r="C39" t="n">
-        <v>2125799</v>
+        <v>2216835</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>117067.74</v>
+        <v>122635.77</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2857,13 +2857,13 @@
         <v>107027</v>
       </c>
       <c r="C44" t="n">
-        <v>2673931</v>
+        <v>2776365</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>145873.36</v>
+        <v>150854.89</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:21:52</t>
+          <t>Last Updated: 23-09-2026 22:56:20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-22</t>
+          <t>MTD: 2026-09-01 → 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:22:27</t>
+          <t>Last Updated: 23-09-2026 22:56:55</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:22:27</t>
+          <t>Last Updated: 23-09-2026 22:56:55</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:23:03</t>
+          <t>Last Updated: 23-09-2026 22:57:30</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 06:23:39</t>
+          <t>Last Updated: 23-09-2026 22:58:06</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3116457</v>
+        <v>3138108</v>
       </c>
       <c r="E4" t="n">
         <v>107027</v>
       </c>
       <c r="F4" t="n">
-        <v>21020</v>
+        <v>21103</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1234569</v>
+        <v>1290050</v>
       </c>
       <c r="E5" t="n">
-        <v>49675</v>
+        <v>50381</v>
       </c>
       <c r="F5" t="n">
-        <v>19229</v>
+        <v>20132</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>532531</v>
+        <v>550068</v>
       </c>
       <c r="E6" t="n">
-        <v>26124</v>
+        <v>26859</v>
       </c>
       <c r="F6" t="n">
-        <v>7857</v>
+        <v>8144</v>
       </c>
       <c r="G6" t="n">
         <v>1.48</v>
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>510536</v>
+        <v>521708</v>
       </c>
       <c r="E7" t="n">
-        <v>45782</v>
+        <v>46200</v>
       </c>
       <c r="F7" t="n">
-        <v>5168</v>
+        <v>5330</v>
       </c>
       <c r="G7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>448895</v>
+        <v>467055</v>
       </c>
       <c r="E8" t="n">
-        <v>14775</v>
+        <v>14944</v>
       </c>
       <c r="F8" t="n">
-        <v>9560</v>
+        <v>9950</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,16 +4951,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>318521</v>
+        <v>333633</v>
       </c>
       <c r="E9" t="n">
-        <v>17456</v>
+        <v>17681</v>
       </c>
       <c r="F9" t="n">
-        <v>20192</v>
+        <v>21135</v>
       </c>
       <c r="G9" t="n">
-        <v>6.34</v>
+        <v>6.33</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50528</v>
+        <v>63329</v>
       </c>
       <c r="E10" t="n">
-        <v>11619</v>
+        <v>12803</v>
       </c>
       <c r="F10" t="n">
-        <v>1054</v>
+        <v>1278</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="E11" t="n">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="F11" t="n">
         <v>98</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:54:32</t>
+          <t>Last Updated: 24-09-2026 06:11:33</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>160509.3</v>
+        <v>161006.32</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>23515.4</v>
+        <v>23614.74</v>
       </c>
       <c r="D5" t="n">
-        <v>151735.22</v>
+        <v>151953.06</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>23515.4</v>
+        <v>23614.74</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>312244.52</v>
+        <v>312959.38</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>861.91</v>
+        <v>1358.93</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>968.1900000000001</v>
+        <v>1067.53</v>
       </c>
       <c r="D17" t="n">
-        <v>6808.14</v>
+        <v>7025.98</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>968.1900000000001</v>
+        <v>1067.53</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>7670.05</v>
+        <v>8384.91</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:55:03</t>
+          <t>Last Updated: 24-09-2026 06:12:04</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14327</v>
+        <v>14372</v>
       </c>
       <c r="C8" t="n">
-        <v>65858</v>
+        <v>66555</v>
       </c>
       <c r="D8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2970.34</v>
+        <v>3002.83</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46200</v>
+        <v>46309</v>
       </c>
       <c r="C14" t="n">
-        <v>521987</v>
+        <v>523198</v>
       </c>
       <c r="D14" t="n">
         <v>1.22</v>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>20545.05</v>
+        <v>20611.92</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>45803</v>
       </c>
       <c r="C26" t="n">
-        <v>511098</v>
+        <v>511100</v>
       </c>
       <c r="D26" t="n">
         <v>1.2</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1180</v>
+        <v>1225</v>
       </c>
       <c r="C32" t="n">
-        <v>12730</v>
+        <v>13427</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>469.63</v>
+        <v>502.12</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>397</v>
+        <v>506</v>
       </c>
       <c r="C38" t="n">
-        <v>10889</v>
+        <v>12098</v>
       </c>
       <c r="D38" t="n">
         <v>0.02</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>498.55</v>
+        <v>565.42</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:55:43</t>
+          <t>Last Updated: 24-09-2026 06:12:43</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>92179</v>
+        <v>92234</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2307173</v>
+        <v>2309987</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>128254.29</v>
+        <v>128437.47</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>107027</v>
+        <v>107402</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3138108</v>
+        <v>3148221</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>160509.31</v>
+        <v>161006.33</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>199206</v>
+        <v>199636</v>
       </c>
       <c r="C7" t="n">
-        <v>5445281</v>
+        <v>5458208</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>288763.6</v>
+        <v>289443.8</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2307173</v>
+        <v>2309987</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>128254.29</v>
+        <v>128437.47</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>361743</v>
+        <v>371856</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>9654.42</v>
+        <v>10151.44</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>92179</v>
+        <v>92234</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>92179</v>
+        <v>92234</v>
       </c>
       <c r="C39" t="n">
         <v>2216835</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>107027</v>
+        <v>107402</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>107027</v>
+        <v>107402</v>
       </c>
       <c r="C44" t="n">
         <v>2776365</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:56:20</t>
+          <t>Last Updated: 24-09-2026 06:13:20</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:56:55</t>
+          <t>Last Updated: 24-09-2026 06:13:55</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:56:55</t>
+          <t>Last Updated: 24-09-2026 06:13:55</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:57:30</t>
+          <t>Last Updated: 24-09-2026 06:14:31</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-09-2026 22:58:06</t>
+          <t>Last Updated: 24-09-2026 06:15:06</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3138108</v>
+        <v>3148221</v>
       </c>
       <c r="E4" t="n">
-        <v>107027</v>
+        <v>107402</v>
       </c>
       <c r="F4" t="n">
-        <v>21103</v>
+        <v>21163</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1290050</v>
+        <v>1291708</v>
       </c>
       <c r="E5" t="n">
-        <v>50381</v>
+        <v>50401</v>
       </c>
       <c r="F5" t="n">
-        <v>20132</v>
+        <v>20158</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>550068</v>
+        <v>550650</v>
       </c>
       <c r="E6" t="n">
-        <v>26859</v>
+        <v>26889</v>
       </c>
       <c r="F6" t="n">
-        <v>8144</v>
+        <v>8152</v>
       </c>
       <c r="G6" t="n">
         <v>1.48</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>521708</v>
+        <v>522960</v>
       </c>
       <c r="E7" t="n">
-        <v>46200</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="n">
-        <v>5330</v>
+        <v>5346</v>
       </c>
       <c r="G7" t="n">
         <v>1.02</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>467055</v>
+        <v>467629</v>
       </c>
       <c r="E8" t="n">
         <v>14944</v>
       </c>
       <c r="F8" t="n">
-        <v>9950</v>
+        <v>9961</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>333633</v>
+        <v>334096</v>
       </c>
       <c r="E9" t="n">
-        <v>17681</v>
+        <v>17688</v>
       </c>
       <c r="F9" t="n">
-        <v>21135</v>
+        <v>21157</v>
       </c>
       <c r="G9" t="n">
         <v>6.33</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63329</v>
+        <v>64060</v>
       </c>
       <c r="E10" t="n">
-        <v>12803</v>
+        <v>12848</v>
       </c>
       <c r="F10" t="n">
-        <v>1278</v>
+        <v>1288</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="E11" t="n">
         <v>1524</v>
@@ -5048,7 +5048,7 @@
         <v>98</v>
       </c>
       <c r="G11" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:11:33</t>
+          <t>Last Updated: 24-09-2026 22:59:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 23-09-2026)</t>
+          <t>MTD (01-09-2026 → 24-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>161006.32</v>
+        <v>162185.89</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>23614.74</v>
+        <v>25113.03</v>
       </c>
       <c r="D5" t="n">
-        <v>151953.06</v>
+        <v>159208.81</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>23614.74</v>
+        <v>25113.03</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>312959.38</v>
+        <v>321394.7</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 22-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 23-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>159647.39</v>
+        <v>161006.37</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22547.21</v>
+        <v>23629.44</v>
       </c>
       <c r="D11" t="n">
-        <v>144927.08</v>
+        <v>152028.11</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>22547.21</v>
+        <v>23629.44</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>304574.47</v>
+        <v>313034.48</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1358.93</v>
+        <v>1179.52</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1067.53</v>
+        <v>1483.59</v>
       </c>
       <c r="D17" t="n">
-        <v>7025.98</v>
+        <v>7180.7</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1067.53</v>
+        <v>1483.59</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>8384.91</v>
+        <v>8360.219999999999</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:12:04</t>
+          <t>Last Updated: 24-09-2026 23:00:23</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-23 | MTD-1: 2026-09-01 → 2026-09-22</t>
+          <t>MTD: 2026-09-01 → 2026-09-24 | MTD-1: 2026-09-01 → 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-23)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14372</v>
+        <v>15352</v>
       </c>
       <c r="C8" t="n">
-        <v>66555</v>
+        <v>80322</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="E8" t="n">
-        <v>4.63</v>
+        <v>5.23</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3002.83</v>
+        <v>3536.68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-23)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46309</v>
+        <v>47310</v>
       </c>
       <c r="C14" t="n">
-        <v>523198</v>
+        <v>543552</v>
       </c>
       <c r="D14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3</v>
+        <v>11.49</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>20611.92</v>
+        <v>21576.35</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-22)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13147</v>
+        <v>14403</v>
       </c>
       <c r="C20" t="n">
-        <v>53128</v>
+        <v>66765</v>
       </c>
       <c r="D20" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="E20" t="n">
-        <v>4.04</v>
+        <v>4.64</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2500.71</v>
+        <v>3010.99</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-22)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>45803</v>
+        <v>46309</v>
       </c>
       <c r="C26" t="n">
-        <v>511100</v>
+        <v>523345</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="E26" t="n">
-        <v>11.16</v>
+        <v>11.3</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>20046.5</v>
+        <v>20618.45</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1225</v>
+        <v>949</v>
       </c>
       <c r="C32" t="n">
-        <v>13427</v>
+        <v>13557</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="E32" t="n">
         <v>0.59</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>502.12</v>
+        <v>525.6900000000001</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>506</v>
+        <v>1001</v>
       </c>
       <c r="C38" t="n">
-        <v>12098</v>
+        <v>20207</v>
       </c>
       <c r="D38" t="n">
         <v>0.02</v>
       </c>
       <c r="E38" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>565.42</v>
+        <v>957.9</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:12:43</t>
+          <t>Last Updated: 24-09-2026 23:01:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-23)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>92234</v>
+        <v>93538</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2309987</v>
+        <v>2405757</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>128437.47</v>
+        <v>134521.85</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>107402</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3148221</v>
+        <v>3176779</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>161006.33</v>
+        <v>162185.89</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>199636</v>
+        <v>200940</v>
       </c>
       <c r="C7" t="n">
-        <v>5458208</v>
+        <v>5582536</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>289443.8</v>
+        <v>296707.74</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-23)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2309987</v>
+        <v>2405757</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>128437.47</v>
+        <v>134521.85</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-23)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>371856</v>
+        <v>400414</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>10151.44</v>
+        <v>11331</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-22)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>92234</v>
+        <v>93538</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>92234</v>
+        <v>93538</v>
       </c>
       <c r="C39" t="n">
-        <v>2216835</v>
+        <v>2310918</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>122635.77</v>
+        <v>128497.92</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:13:20</t>
+          <t>Last Updated: 24-09-2026 23:01:41</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-23</t>
+          <t>MTD: 2026-09-01 → 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:13:55</t>
+          <t>Last Updated: 24-09-2026 23:02:16</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:13:55</t>
+          <t>Last Updated: 24-09-2026 23:02:16</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:14:31</t>
+          <t>Last Updated: 24-09-2026 23:02:56</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 06:15:06</t>
+          <t>Last Updated: 24-09-2026 23:03:33</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3148221</v>
+        <v>3176779</v>
       </c>
       <c r="E4" t="n">
-        <v>107402</v>
+        <v>107781</v>
       </c>
       <c r="F4" t="n">
-        <v>21163</v>
+        <v>21291</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
@@ -4775,16 +4775,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1291708</v>
+        <v>1345545</v>
       </c>
       <c r="E5" t="n">
-        <v>50401</v>
+        <v>50830</v>
       </c>
       <c r="F5" t="n">
-        <v>20158</v>
+        <v>21103</v>
       </c>
       <c r="G5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4819,16 +4819,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>550650</v>
+        <v>574189</v>
       </c>
       <c r="E6" t="n">
-        <v>26889</v>
+        <v>27507</v>
       </c>
       <c r="F6" t="n">
-        <v>8152</v>
+        <v>8573</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>522960</v>
+        <v>543274</v>
       </c>
       <c r="E7" t="n">
-        <v>46309</v>
+        <v>47310</v>
       </c>
       <c r="F7" t="n">
-        <v>5346</v>
+        <v>5638</v>
       </c>
       <c r="G7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4907,16 +4907,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>467629</v>
+        <v>486023</v>
       </c>
       <c r="E8" t="n">
-        <v>14944</v>
+        <v>15201</v>
       </c>
       <c r="F8" t="n">
-        <v>9961</v>
+        <v>10451</v>
       </c>
       <c r="G8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4951,16 +4951,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>334096</v>
+        <v>348866</v>
       </c>
       <c r="E9" t="n">
-        <v>17688</v>
+        <v>17872</v>
       </c>
       <c r="F9" t="n">
-        <v>21157</v>
+        <v>22059</v>
       </c>
       <c r="G9" t="n">
-        <v>6.33</v>
+        <v>6.32</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>64060</v>
+        <v>77795</v>
       </c>
       <c r="E10" t="n">
-        <v>12848</v>
+        <v>13821</v>
       </c>
       <c r="F10" t="n">
-        <v>1288</v>
+        <v>1465</v>
       </c>
       <c r="G10" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2491</v>
+        <v>2497</v>
       </c>
       <c r="E11" t="n">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="F11" t="n">
         <v>98</v>
       </c>
       <c r="G11" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 22:59:52</t>
+          <t>Last Updated: 25-09-2026 06:11:03</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>162185.89</v>
+        <v>162298.63</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>25113.03</v>
+        <v>25179.25</v>
       </c>
       <c r="D5" t="n">
-        <v>159208.81</v>
+        <v>159343.92</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>25113.03</v>
+        <v>25179.25</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>321394.7</v>
+        <v>321642.55</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1179.52</v>
+        <v>1292.26</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1483.59</v>
+        <v>1549.81</v>
       </c>
       <c r="D17" t="n">
-        <v>7180.7</v>
+        <v>7315.81</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1483.59</v>
+        <v>1549.81</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>8360.219999999999</v>
+        <v>8608.07</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 23:00:23</t>
+          <t>Last Updated: 25-09-2026 06:11:34</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15352</v>
+        <v>15435</v>
       </c>
       <c r="C8" t="n">
-        <v>80322</v>
+        <v>80819</v>
       </c>
       <c r="D8" t="n">
         <v>2.51</v>
       </c>
       <c r="E8" t="n">
-        <v>5.23</v>
+        <v>5.24</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3536.68</v>
+        <v>3567.42</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47310</v>
+        <v>47361</v>
       </c>
       <c r="C14" t="n">
-        <v>543552</v>
+        <v>544053</v>
       </c>
       <c r="D14" t="n">
         <v>1.24</v>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>21576.35</v>
+        <v>21611.83</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46309</v>
       </c>
       <c r="C26" t="n">
-        <v>523345</v>
+        <v>523346</v>
       </c>
       <c r="D26" t="n">
         <v>1.22</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>949</v>
+        <v>1032</v>
       </c>
       <c r="C32" t="n">
-        <v>13557</v>
+        <v>14054</v>
       </c>
       <c r="D32" t="n">
         <v>-0.19</v>
       </c>
       <c r="E32" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>525.6900000000001</v>
+        <v>556.4299999999999</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1001</v>
+        <v>1052</v>
       </c>
       <c r="C38" t="n">
-        <v>20207</v>
+        <v>20707</v>
       </c>
       <c r="D38" t="n">
         <v>0.02</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>957.9</v>
+        <v>993.38</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 23:01:03</t>
+          <t>Last Updated: 25-09-2026 06:12:13</t>
         </is>
       </c>
     </row>
@@ -2398,13 +2398,13 @@
         <v>93538</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2405757</v>
+        <v>2407062</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>134521.85</v>
+        <v>134613.73</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>107402</v>
+        <v>107781</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3176779</v>
+        <v>3178959</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>162185.89</v>
+        <v>162298.63</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200940</v>
+        <v>201319</v>
       </c>
       <c r="C7" t="n">
-        <v>5582536</v>
+        <v>5586021</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>296707.74</v>
+        <v>296912.36</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2405757</v>
+        <v>2407062</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>134521.85</v>
+        <v>134613.73</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>400414</v>
+        <v>402594</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>11331</v>
+        <v>11443.74</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>107402</v>
+        <v>107781</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>107402</v>
+        <v>107781</v>
       </c>
       <c r="C44" t="n">
         <v>2776365</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 23:01:41</t>
+          <t>Last Updated: 25-09-2026 06:12:49</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3208,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Product 1 6June</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3242,12 +3242,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3310,17 +3310,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Product 1 6June</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 23:02:16</t>
+          <t>Last Updated: 25-09-2026 06:13:23</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 23:02:16</t>
+          <t>Last Updated: 25-09-2026 06:13:23</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 23:02:56</t>
+          <t>Last Updated: 25-09-2026 06:13:59</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-09-2026 23:03:33</t>
+          <t>Last Updated: 25-09-2026 06:14:36</t>
         </is>
       </c>
     </row>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3176779</v>
+        <v>3178959</v>
       </c>
       <c r="E4" t="n">
         <v>107781</v>
       </c>
       <c r="F4" t="n">
-        <v>21291</v>
+        <v>21301</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1345545</v>
+        <v>1346337</v>
       </c>
       <c r="E5" t="n">
         <v>50830</v>
       </c>
       <c r="F5" t="n">
-        <v>21103</v>
+        <v>21113</v>
       </c>
       <c r="G5" t="n">
         <v>1.57</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>574189</v>
+        <v>574581</v>
       </c>
       <c r="E6" t="n">
         <v>27507</v>
       </c>
       <c r="F6" t="n">
-        <v>8573</v>
+        <v>8578</v>
       </c>
       <c r="G6" t="n">
         <v>1.49</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>543274</v>
+        <v>543810</v>
       </c>
       <c r="E7" t="n">
-        <v>47310</v>
+        <v>47361</v>
       </c>
       <c r="F7" t="n">
-        <v>5638</v>
+        <v>5642</v>
       </c>
       <c r="G7" t="n">
         <v>1.04</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>486023</v>
+        <v>486144</v>
       </c>
       <c r="E8" t="n">
         <v>15201</v>
       </c>
       <c r="F8" t="n">
-        <v>10451</v>
+        <v>10458</v>
       </c>
       <c r="G8" t="n">
         <v>2.15</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>348866</v>
+        <v>349384</v>
       </c>
       <c r="E9" t="n">
         <v>17872</v>
       </c>
       <c r="F9" t="n">
-        <v>22059</v>
+        <v>22093</v>
       </c>
       <c r="G9" t="n">
         <v>6.32</v>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77795</v>
+        <v>78313</v>
       </c>
       <c r="E10" t="n">
-        <v>13821</v>
+        <v>13904</v>
       </c>
       <c r="F10" t="n">
-        <v>1465</v>
+        <v>1476</v>
       </c>
       <c r="G10" t="n">
         <v>1.88</v>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="E11" t="n">
         <v>1531</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:11:03</t>
+          <t>Last Updated: 25-09-2026 22:58:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 24-09-2026)</t>
+          <t>MTD (01-09-2026 → 25-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>162298.63</v>
+        <v>162298.54</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>25179.25</v>
+        <v>27245.92</v>
       </c>
       <c r="D5" t="n">
-        <v>159343.92</v>
+        <v>165765.71</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>25179.25</v>
+        <v>27245.92</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>321642.55</v>
+        <v>328064.25</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 23-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 24-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>161006.37</v>
+        <v>162298.54</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23629.44</v>
+        <v>25194.95</v>
       </c>
       <c r="D11" t="n">
-        <v>152028.11</v>
+        <v>159420.77</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>23629.44</v>
+        <v>25194.95</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>313034.48</v>
+        <v>321719.31</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1292.26</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1549.81</v>
+        <v>2050.97</v>
       </c>
       <c r="D17" t="n">
-        <v>7315.81</v>
+        <v>6344.94</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1549.81</v>
+        <v>2050.97</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>8608.07</v>
+        <v>6344.94</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:11:34</t>
+          <t>Last Updated: 25-09-2026 22:59:18</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-24 | MTD-1: 2026-09-01 → 2026-09-23</t>
+          <t>MTD: 2026-09-01 → 2026-09-25 | MTD-1: 2026-09-01 → 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-24)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15435</v>
+        <v>17910</v>
       </c>
       <c r="C8" t="n">
-        <v>80819</v>
+        <v>97908</v>
       </c>
       <c r="D8" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="E8" t="n">
-        <v>5.24</v>
+        <v>5.47</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3567.42</v>
+        <v>4240.46</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-24)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47361</v>
+        <v>48174</v>
       </c>
       <c r="C14" t="n">
-        <v>544053</v>
+        <v>573438</v>
       </c>
       <c r="D14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="E14" t="n">
-        <v>11.49</v>
+        <v>11.9</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>21611.83</v>
+        <v>23005.46</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-23)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14403</v>
+        <v>15457</v>
       </c>
       <c r="C20" t="n">
-        <v>66765</v>
+        <v>80987</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="E20" t="n">
-        <v>4.64</v>
+        <v>5.24</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3010.99</v>
+        <v>3576.12</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-23)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>46309</v>
+        <v>47361</v>
       </c>
       <c r="C26" t="n">
-        <v>523346</v>
+        <v>544231</v>
       </c>
       <c r="D26" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="E26" t="n">
-        <v>11.3</v>
+        <v>11.49</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>20618.45</v>
+        <v>21618.83</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1032</v>
+        <v>2453</v>
       </c>
       <c r="C32" t="n">
-        <v>14054</v>
+        <v>16921</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6</v>
+        <v>0.23</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>556.4299999999999</v>
+        <v>664.34</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1052</v>
+        <v>813</v>
       </c>
       <c r="C38" t="n">
-        <v>20707</v>
+        <v>29207</v>
       </c>
       <c r="D38" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>993.38</v>
+        <v>1386.63</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:12:13</t>
+          <t>Last Updated: 25-09-2026 22:59:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-24)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>93538</v>
+        <v>96363</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2407062</v>
+        <v>2494968</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>134613.73</v>
+        <v>139876.27</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>162298.63</v>
+        <v>162298.55</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>201319</v>
+        <v>204144</v>
       </c>
       <c r="C7" t="n">
-        <v>5586021</v>
+        <v>5673927</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>296912.36</v>
+        <v>302174.82</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-24)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2407062</v>
+        <v>2494968</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>134613.73</v>
+        <v>139876.27</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2537,7 +2537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-24)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>11443.74</v>
+        <v>11443.66</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-23)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>93538</v>
+        <v>96363</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>93538</v>
+        <v>96363</v>
       </c>
       <c r="C39" t="n">
-        <v>2310918</v>
+        <v>2408082</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>128497.92</v>
+        <v>134676.96</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3137,14 +3137,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:12:49</t>
+          <t>Last Updated: 25-09-2026 23:00:35</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-24</t>
+          <t>MTD: 2026-09-01 → 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:13:23</t>
+          <t>Last Updated: 25-09-2026 23:01:10</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:13:23</t>
+          <t>Last Updated: 25-09-2026 23:01:10</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:13:59</t>
+          <t>Last Updated: 25-09-2026 23:01:46</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 06:14:36</t>
+          <t>Last Updated: 25-09-2026 23:02:22</t>
         </is>
       </c>
     </row>
@@ -4775,16 +4775,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1346337</v>
+        <v>1391253</v>
       </c>
       <c r="E5" t="n">
-        <v>50830</v>
+        <v>52331</v>
       </c>
       <c r="F5" t="n">
-        <v>21113</v>
+        <v>21760</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>574581</v>
+        <v>601268</v>
       </c>
       <c r="E6" t="n">
-        <v>27507</v>
+        <v>28430</v>
       </c>
       <c r="F6" t="n">
-        <v>8578</v>
+        <v>8978</v>
       </c>
       <c r="G6" t="n">
         <v>1.49</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>543810</v>
+        <v>573165</v>
       </c>
       <c r="E7" t="n">
-        <v>47361</v>
+        <v>48174</v>
       </c>
       <c r="F7" t="n">
-        <v>5642</v>
+        <v>5988</v>
       </c>
       <c r="G7" t="n">
         <v>1.04</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>486144</v>
+        <v>502447</v>
       </c>
       <c r="E8" t="n">
-        <v>15201</v>
+        <v>15602</v>
       </c>
       <c r="F8" t="n">
-        <v>10458</v>
+        <v>10804</v>
       </c>
       <c r="G8" t="n">
         <v>2.15</v>
@@ -4951,16 +4951,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>349384</v>
+        <v>365500</v>
       </c>
       <c r="E9" t="n">
-        <v>17872</v>
+        <v>18172</v>
       </c>
       <c r="F9" t="n">
-        <v>22093</v>
+        <v>23073</v>
       </c>
       <c r="G9" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4995,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78313</v>
+        <v>93274</v>
       </c>
       <c r="E10" t="n">
-        <v>13904</v>
+        <v>14940</v>
       </c>
       <c r="F10" t="n">
-        <v>1476</v>
+        <v>1684</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2499</v>
+        <v>4592</v>
       </c>
       <c r="E11" t="n">
-        <v>1531</v>
+        <v>2988</v>
       </c>
       <c r="F11" t="n">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="G11" t="n">
-        <v>3.92</v>
+        <v>3.09</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 22:58:48</t>
+          <t>Last Updated: 26-09-2026 06:16:31</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>27245.92</v>
+        <v>27293.59</v>
       </c>
       <c r="D5" t="n">
-        <v>165765.71</v>
+        <v>165896.89</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>27245.92</v>
+        <v>27293.59</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>328064.25</v>
+        <v>328195.43</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2050.97</v>
+        <v>2098.64</v>
       </c>
       <c r="D17" t="n">
-        <v>6344.94</v>
+        <v>6476.12</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2050.97</v>
+        <v>2098.64</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6344.94</v>
+        <v>6476.12</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 22:59:18</t>
+          <t>Last Updated: 26-09-2026 06:17:02</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17910</v>
+        <v>18038</v>
       </c>
       <c r="C8" t="n">
-        <v>97908</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="n">
         <v>2.4</v>
       </c>
       <c r="E8" t="n">
-        <v>5.47</v>
+        <v>5.45</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4240.46</v>
+        <v>4259.51</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48174</v>
+        <v>48246</v>
       </c>
       <c r="C14" t="n">
-        <v>573438</v>
+        <v>573936</v>
       </c>
       <c r="D14" t="n">
         <v>1.25</v>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>23005.46</v>
+        <v>23034.08</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>47361</v>
       </c>
       <c r="C26" t="n">
-        <v>544231</v>
+        <v>544232</v>
       </c>
       <c r="D26" t="n">
         <v>1.24</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2453</v>
+        <v>2581</v>
       </c>
       <c r="C32" t="n">
-        <v>16921</v>
+        <v>17373</v>
       </c>
       <c r="D32" t="n">
         <v>-0.11</v>
       </c>
       <c r="E32" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>664.34</v>
+        <v>683.39</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>813</v>
+        <v>885</v>
       </c>
       <c r="C38" t="n">
-        <v>29207</v>
+        <v>29704</v>
       </c>
       <c r="D38" t="n">
         <v>0.01</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1386.63</v>
+        <v>1415.25</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 22:59:57</t>
+          <t>Last Updated: 26-09-2026 06:17:42</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>96363</v>
+        <v>96401</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2494968</v>
+        <v>2496825</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>139876.27</v>
+        <v>139982.7</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>107781</v>
+        <v>107778</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>3178959</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>204144</v>
+        <v>204179</v>
       </c>
       <c r="C7" t="n">
-        <v>5673927</v>
+        <v>5675784</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>302174.82</v>
+        <v>302281.25</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2494968</v>
+        <v>2496825</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>139876.27</v>
+        <v>139982.7</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>96363</v>
+        <v>96401</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>96363</v>
+        <v>96401</v>
       </c>
       <c r="C39" t="n">
         <v>2408082</v>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>107781</v>
+        <v>107778</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>107781</v>
+        <v>107778</v>
       </c>
       <c r="C44" t="n">
         <v>2776365</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 23:00:35</t>
+          <t>Last Updated: 26-09-2026 06:18:18</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>28-06-2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3242,7 +3242,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3369,7 +3369,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 23:01:10</t>
+          <t>Last Updated: 26-09-2026 06:18:54</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 23:01:10</t>
+          <t>Last Updated: 26-09-2026 06:18:54</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 23:01:46</t>
+          <t>Last Updated: 26-09-2026 06:19:28</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-09-2026 23:02:22</t>
+          <t>Last Updated: 26-09-2026 06:20:04</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
         <v>3178959</v>
       </c>
       <c r="E4" t="n">
-        <v>107781</v>
+        <v>107778</v>
       </c>
       <c r="F4" t="n">
         <v>21301</v>
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1391253</v>
+        <v>1392454</v>
       </c>
       <c r="E5" t="n">
-        <v>52331</v>
+        <v>52360</v>
       </c>
       <c r="F5" t="n">
-        <v>21760</v>
+        <v>21783</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>601268</v>
+        <v>601545</v>
       </c>
       <c r="E6" t="n">
-        <v>28430</v>
+        <v>28439</v>
       </c>
       <c r="F6" t="n">
-        <v>8978</v>
+        <v>8987</v>
       </c>
       <c r="G6" t="n">
         <v>1.49</v>
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>573165</v>
+        <v>573690</v>
       </c>
       <c r="E7" t="n">
-        <v>48174</v>
+        <v>48246</v>
       </c>
       <c r="F7" t="n">
-        <v>5988</v>
+        <v>5989</v>
       </c>
       <c r="G7" t="n">
         <v>1.04</v>
@@ -4907,13 +4907,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>502447</v>
+        <v>502826</v>
       </c>
       <c r="E8" t="n">
         <v>15602</v>
       </c>
       <c r="F8" t="n">
-        <v>10804</v>
+        <v>10813</v>
       </c>
       <c r="G8" t="n">
         <v>2.15</v>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>365500</v>
+        <v>365806</v>
       </c>
       <c r="E9" t="n">
         <v>18172</v>
       </c>
       <c r="F9" t="n">
-        <v>23073</v>
+        <v>23098</v>
       </c>
       <c r="G9" t="n">
         <v>6.31</v>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93274</v>
+        <v>93547</v>
       </c>
       <c r="E10" t="n">
         <v>14940</v>
       </c>
       <c r="F10" t="n">
-        <v>1684</v>
+        <v>1690</v>
       </c>
       <c r="G10" t="n">
         <v>1.81</v>
@@ -5039,16 +5039,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4592</v>
+        <v>4808</v>
       </c>
       <c r="E11" t="n">
-        <v>2988</v>
+        <v>3098</v>
       </c>
       <c r="F11" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:16:31</t>
+          <t>Last Updated: 26-09-2026 22:08:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 25-09-2026)</t>
+          <t>MTD (01-09-2026 → 26-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>27293.59</v>
+        <v>29382.92</v>
       </c>
       <c r="D5" t="n">
-        <v>165896.89</v>
+        <v>172475.94</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>27293.59</v>
+        <v>29382.92</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>328195.43</v>
+        <v>334774.48</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 24-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 25-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25194.95</v>
+        <v>27316.83</v>
       </c>
       <c r="D11" t="n">
-        <v>159420.77</v>
+        <v>165964.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>25194.95</v>
+        <v>27316.83</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>321719.31</v>
+        <v>328263.34</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2098.64</v>
+        <v>2066.09</v>
       </c>
       <c r="D17" t="n">
-        <v>6476.12</v>
+        <v>6511.14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2098.64</v>
+        <v>2066.09</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6476.12</v>
+        <v>6511.14</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:17:02</t>
+          <t>Last Updated: 26-09-2026 22:08:40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-25 | MTD-1: 2026-09-01 → 2026-09-24</t>
+          <t>MTD: 2026-09-01 → 2026-09-26 | MTD-1: 2026-09-01 → 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-25)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18038</v>
+        <v>24628</v>
       </c>
       <c r="C8" t="n">
-        <v>98360</v>
+        <v>129451</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="E8" t="n">
-        <v>5.45</v>
+        <v>5.26</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4259.51</v>
+        <v>5455.73</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-25)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48246</v>
+        <v>48577</v>
       </c>
       <c r="C14" t="n">
-        <v>573936</v>
+        <v>594520</v>
       </c>
       <c r="D14" t="n">
         <v>1.25</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9</v>
+        <v>12.24</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>23034.08</v>
+        <v>23927.19</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-24)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15457</v>
+        <v>18069</v>
       </c>
       <c r="C20" t="n">
-        <v>80987</v>
+        <v>98577</v>
       </c>
       <c r="D20" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="E20" t="n">
-        <v>5.24</v>
+        <v>5.46</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3576.12</v>
+        <v>4266.58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-24)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>47361</v>
+        <v>48246</v>
       </c>
       <c r="C26" t="n">
-        <v>544232</v>
+        <v>574290</v>
       </c>
       <c r="D26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
-        <v>11.49</v>
+        <v>11.9</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>21618.83</v>
+        <v>23050.24</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2581</v>
+        <v>6559</v>
       </c>
       <c r="C32" t="n">
-        <v>17373</v>
+        <v>30874</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="E32" t="n">
-        <v>0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>683.39</v>
+        <v>1189.15</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>885</v>
+        <v>331</v>
       </c>
       <c r="C38" t="n">
-        <v>29704</v>
+        <v>20230</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1415.25</v>
+        <v>876.95</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:17:42</t>
+          <t>Last Updated: 26-09-2026 22:09:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-25)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>96401</v>
+        <v>102945</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2496825</v>
+        <v>2576088</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>139982.7</v>
+        <v>144957.45</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>204179</v>
+        <v>210723</v>
       </c>
       <c r="C7" t="n">
-        <v>5675784</v>
+        <v>5755047</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>302281.25</v>
+        <v>307256</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-25)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2496825</v>
+        <v>2568437</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>139982.7</v>
+        <v>144149.59</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2534,10 +2534,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Catalog_TopSellers</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7651</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>807.86</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-25)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2691,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-24)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2752,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>96401</v>
+        <v>102945</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2752,16 +2779,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>96401</v>
+        <v>102945</v>
       </c>
       <c r="C39" t="n">
-        <v>2408082</v>
+        <v>2497745</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>134676.96</v>
+        <v>140042.85</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2974,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2982,7 +3009,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3118,16 +3145,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3137,14 +3164,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:18:18</t>
+          <t>Last Updated: 26-09-2026 22:09:55</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-25</t>
+          <t>MTD: 2026-09-01 → 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3208,32 +3235,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Catalog TopSellers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>08-07-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5297</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>7651</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>807.86</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3242,7 +3262,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3276,7 +3296,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3310,34 +3330,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Retention SasteKaSahiAddress Video</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>28-06-2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>08-07-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Retention SasteKaSahiAddress Product 1 6June</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>29-06-2026</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>04-07-2026</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3369,7 +3423,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:18:54</t>
+          <t>Last Updated: 26-09-2026 22:10:30</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3766,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:18:54</t>
+          <t>Last Updated: 26-09-2026 22:10:30</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3854,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:19:28</t>
+          <t>Last Updated: 26-09-2026 22:11:05</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4647,7 +4701,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 06:20:04</t>
+          <t>Last Updated: 26-09-2026 22:11:41</t>
         </is>
       </c>
     </row>
@@ -4775,13 +4829,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1392454</v>
+        <v>1442855</v>
       </c>
       <c r="E5" t="n">
-        <v>52360</v>
+        <v>53296</v>
       </c>
       <c r="F5" t="n">
-        <v>21783</v>
+        <v>22507</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4819,16 +4873,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>601545</v>
+        <v>607892</v>
       </c>
       <c r="E6" t="n">
-        <v>28439</v>
+        <v>28722</v>
       </c>
       <c r="F6" t="n">
-        <v>8987</v>
+        <v>9105</v>
       </c>
       <c r="G6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4863,13 +4917,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>573690</v>
+        <v>594209</v>
       </c>
       <c r="E7" t="n">
-        <v>48246</v>
+        <v>48577</v>
       </c>
       <c r="F7" t="n">
-        <v>5989</v>
+        <v>6206</v>
       </c>
       <c r="G7" t="n">
         <v>1.04</v>
@@ -4907,13 +4961,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>502826</v>
+        <v>517690</v>
       </c>
       <c r="E8" t="n">
-        <v>15602</v>
+        <v>15865</v>
       </c>
       <c r="F8" t="n">
-        <v>10813</v>
+        <v>11131</v>
       </c>
       <c r="G8" t="n">
         <v>2.15</v>
@@ -4951,16 +5005,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>365806</v>
+        <v>382775</v>
       </c>
       <c r="E9" t="n">
-        <v>18172</v>
+        <v>18374</v>
       </c>
       <c r="F9" t="n">
-        <v>23098</v>
+        <v>24220</v>
       </c>
       <c r="G9" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4995,16 +5049,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93547</v>
+        <v>109588</v>
       </c>
       <c r="E10" t="n">
-        <v>14940</v>
+        <v>15948</v>
       </c>
       <c r="F10" t="n">
-        <v>1690</v>
+        <v>1895</v>
       </c>
       <c r="G10" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5039,16 +5093,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4808</v>
+        <v>19738</v>
       </c>
       <c r="E11" t="n">
-        <v>3098</v>
+        <v>8750</v>
       </c>
       <c r="F11" t="n">
-        <v>149</v>
+        <v>362</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5063,6 +5117,138 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Retention_PurchasersReturning_26Sep</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4867</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2993</v>
+      </c>
+      <c r="F12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Retention_PurchasersNotReturning_26Sep</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2784</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2069</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Activation_SearchIntentNotPurchased_26Sep</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E14" t="n">
+        <v>744</v>
+      </c>
+      <c r="F14" t="n">
+        <v>49</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:08:09</t>
+          <t>Last Updated: 27-09-2026 06:16:59</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>29382.92</v>
+        <v>29543.06</v>
       </c>
       <c r="D5" t="n">
-        <v>172475.94</v>
+        <v>172874.82</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>29382.92</v>
+        <v>29543.06</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>334774.48</v>
+        <v>335173.36</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2066.09</v>
+        <v>2226.23</v>
       </c>
       <c r="D17" t="n">
-        <v>6511.14</v>
+        <v>6910.02</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2066.09</v>
+        <v>2226.23</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6511.14</v>
+        <v>6910.02</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:08:40</t>
+          <t>Last Updated: 27-09-2026 06:17:30</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24628</v>
+        <v>25753</v>
       </c>
       <c r="C8" t="n">
-        <v>129451</v>
+        <v>132146</v>
       </c>
       <c r="D8" t="n">
         <v>2.24</v>
       </c>
       <c r="E8" t="n">
-        <v>5.26</v>
+        <v>5.13</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5455.73</v>
+        <v>5572.38</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48577</v>
+        <v>48601</v>
       </c>
       <c r="C14" t="n">
-        <v>594520</v>
+        <v>595649</v>
       </c>
       <c r="D14" t="n">
         <v>1.25</v>
       </c>
       <c r="E14" t="n">
-        <v>12.24</v>
+        <v>12.26</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>23927.19</v>
+        <v>23970.67</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>18069</v>
       </c>
       <c r="C20" t="n">
-        <v>98577</v>
+        <v>98579</v>
       </c>
       <c r="D20" t="n">
         <v>2.41</v>
@@ -1992,7 +1992,7 @@
         <v>48246</v>
       </c>
       <c r="C26" t="n">
-        <v>574290</v>
+        <v>574291</v>
       </c>
       <c r="D26" t="n">
         <v>1.25</v>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6559</v>
+        <v>7684</v>
       </c>
       <c r="C32" t="n">
-        <v>30874</v>
+        <v>33567</v>
       </c>
       <c r="D32" t="n">
         <v>-0.17</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1189.15</v>
+        <v>1305.8</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="C38" t="n">
-        <v>20230</v>
+        <v>21358</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>876.95</v>
+        <v>920.4299999999999</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:09:19</t>
+          <t>Last Updated: 27-09-2026 06:18:08</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>102945</v>
+        <v>103786</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2576088</v>
+        <v>2581133</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>144957.45</v>
+        <v>145227.8</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>107778</v>
+        <v>107781</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>3178959</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>210723</v>
+        <v>211567</v>
       </c>
       <c r="C7" t="n">
-        <v>5755047</v>
+        <v>5760092</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>307256</v>
+        <v>307526.35</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2568437</v>
+        <v>2571970</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>144149.59</v>
+        <v>144362.18</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7651</v>
+        <v>9163</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>807.86</v>
+        <v>865.62</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>102945</v>
+        <v>103786</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>102945</v>
+        <v>103786</v>
       </c>
       <c r="C39" t="n">
         <v>2497745</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>107778</v>
+        <v>107781</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>107778</v>
+        <v>107781</v>
       </c>
       <c r="C44" t="n">
         <v>2776365</v>
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:09:55</t>
+          <t>Last Updated: 27-09-2026 06:18:44</t>
         </is>
       </c>
     </row>
@@ -3244,16 +3244,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5297</v>
+        <v>6127</v>
       </c>
       <c r="E5" t="n">
-        <v>7651</v>
+        <v>9163</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>807.86</v>
+        <v>865.62</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3262,12 +3262,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3296,17 +3296,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Product 1 6June</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3364,17 +3364,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Product 1 6June</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3423,7 +3423,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:10:30</t>
+          <t>Last Updated: 27-09-2026 06:19:18</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:10:30</t>
+          <t>Last Updated: 27-09-2026 06:19:18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:11:05</t>
+          <t>Last Updated: 27-09-2026 06:19:53</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-09-2026 22:11:41</t>
+          <t>Last Updated: 27-09-2026 06:20:29</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
         <v>3178959</v>
       </c>
       <c r="E4" t="n">
-        <v>107778</v>
+        <v>107781</v>
       </c>
       <c r="F4" t="n">
         <v>21301</v>
@@ -4829,13 +4829,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1442855</v>
+        <v>1445162</v>
       </c>
       <c r="E5" t="n">
-        <v>53296</v>
+        <v>53340</v>
       </c>
       <c r="F5" t="n">
-        <v>22507</v>
+        <v>22548</v>
       </c>
       <c r="G5" t="n">
         <v>1.56</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>607892</v>
+        <v>607963</v>
       </c>
       <c r="E6" t="n">
         <v>28722</v>
@@ -4917,16 +4917,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>594209</v>
+        <v>595398</v>
       </c>
       <c r="E7" t="n">
-        <v>48577</v>
+        <v>48601</v>
       </c>
       <c r="F7" t="n">
-        <v>6206</v>
+        <v>6222</v>
       </c>
       <c r="G7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>517690</v>
+        <v>518845</v>
       </c>
       <c r="E8" t="n">
-        <v>15865</v>
+        <v>15921</v>
       </c>
       <c r="F8" t="n">
-        <v>11131</v>
+        <v>11160</v>
       </c>
       <c r="G8" t="n">
         <v>2.15</v>
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>382775</v>
+        <v>384682</v>
       </c>
       <c r="E9" t="n">
-        <v>18374</v>
+        <v>18437</v>
       </c>
       <c r="F9" t="n">
-        <v>24220</v>
+        <v>24349</v>
       </c>
       <c r="G9" t="n">
         <v>6.33</v>
@@ -5049,13 +5049,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>109588</v>
+        <v>111036</v>
       </c>
       <c r="E10" t="n">
-        <v>15948</v>
+        <v>16211</v>
       </c>
       <c r="F10" t="n">
-        <v>1895</v>
+        <v>1917</v>
       </c>
       <c r="G10" t="n">
         <v>1.73</v>
@@ -5093,16 +5093,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19738</v>
+        <v>21102</v>
       </c>
       <c r="E11" t="n">
-        <v>8750</v>
+        <v>9542</v>
       </c>
       <c r="F11" t="n">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="G11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5137,16 +5137,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4867</v>
+        <v>5951</v>
       </c>
       <c r="E12" t="n">
-        <v>2993</v>
+        <v>3485</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5181,16 +5181,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2784</v>
+        <v>3212</v>
       </c>
       <c r="E13" t="n">
-        <v>2069</v>
+        <v>2318</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5225,16 +5225,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1506</v>
+        <v>1522</v>
       </c>
       <c r="E14" t="n">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:16:59</t>
+          <t>Last Updated: 27-09-2026 22:42:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 26-09-2026)</t>
+          <t>MTD (01-09-2026 → 27-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>29543.06</v>
+        <v>31142.49</v>
       </c>
       <c r="D5" t="n">
-        <v>172874.82</v>
+        <v>183155.57</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>29543.06</v>
+        <v>31142.49</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>335173.36</v>
+        <v>345454.11</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 25-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 26-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27316.83</v>
+        <v>29559.64</v>
       </c>
       <c r="D11" t="n">
-        <v>165964.8</v>
+        <v>172901.27</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>27316.83</v>
+        <v>29559.64</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>328263.34</v>
+        <v>335199.81</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2226.23</v>
+        <v>1582.85</v>
       </c>
       <c r="D17" t="n">
-        <v>6910.02</v>
+        <v>10254.3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2226.23</v>
+        <v>1582.85</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6910.02</v>
+        <v>10254.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:17:30</t>
+          <t>Last Updated: 27-09-2026 22:43:03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-26 | MTD-1: 2026-09-01 → 2026-09-25</t>
+          <t>MTD: 2026-09-01 → 2026-09-27 | MTD-1: 2026-09-01 → 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-26)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25753</v>
+        <v>28173</v>
       </c>
       <c r="C8" t="n">
-        <v>132146</v>
+        <v>150095</v>
       </c>
       <c r="D8" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="E8" t="n">
-        <v>5.13</v>
+        <v>5.33</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5572.38</v>
+        <v>6283.03</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-26)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48601</v>
+        <v>49225</v>
       </c>
       <c r="C14" t="n">
-        <v>595649</v>
+        <v>617522</v>
       </c>
       <c r="D14" t="n">
         <v>1.25</v>
       </c>
       <c r="E14" t="n">
-        <v>12.26</v>
+        <v>12.54</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>23970.67</v>
+        <v>24859.46</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-25)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18069</v>
+        <v>25777</v>
       </c>
       <c r="C20" t="n">
-        <v>98579</v>
+        <v>132474</v>
       </c>
       <c r="D20" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="E20" t="n">
-        <v>5.46</v>
+        <v>5.14</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4266.58</v>
+        <v>5584.36</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-25)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48246</v>
+        <v>48601</v>
       </c>
       <c r="C26" t="n">
-        <v>574291</v>
+        <v>595795</v>
       </c>
       <c r="D26" t="n">
         <v>1.25</v>
       </c>
       <c r="E26" t="n">
-        <v>11.9</v>
+        <v>12.26</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>23050.24</v>
+        <v>23975.28</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7684</v>
+        <v>2396</v>
       </c>
       <c r="C32" t="n">
-        <v>33567</v>
+        <v>17621</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.17</v>
+        <v>-0.03</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.33</v>
+        <v>0.19</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1305.8</v>
+        <v>698.67</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>355</v>
+        <v>624</v>
       </c>
       <c r="C38" t="n">
-        <v>21358</v>
+        <v>21727</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>920.4299999999999</v>
+        <v>884.1799999999999</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:18:08</t>
+          <t>Last Updated: 27-09-2026 22:43:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-26)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>103786</v>
+        <v>112280</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2581133</v>
+        <v>2700174</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>145227.8</v>
+        <v>152625.44</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>211567</v>
+        <v>220061</v>
       </c>
       <c r="C7" t="n">
-        <v>5760092</v>
+        <v>5879133</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>307526.35</v>
+        <v>314923.99</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-26)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2571970</v>
+        <v>2657938</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>144362.18</v>
+        <v>149894.88</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9163</v>
+        <v>42236</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>865.62</v>
+        <v>2730.56</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-26)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-25)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-26)</t>
         </is>
       </c>
     </row>
@@ -2752,18 +2752,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>103786</v>
+        <v>112280</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>9303</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>869.28</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2779,16 +2777,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>103786</v>
+        <v>112280</v>
       </c>
       <c r="C39" t="n">
-        <v>2497745</v>
+        <v>2572556</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>140042.85</v>
+        <v>144373.37</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2965,20 +2963,16 @@
       <c r="B49" t="n">
         <v>0</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C49" t="n">
+        <v>354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E49" t="n">
+        <v>214.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3001,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3009,7 +3003,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3151,10 +3145,10 @@
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3164,14 +3158,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:18:44</t>
+          <t>Last Updated: 27-09-2026 22:44:17</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-26</t>
+          <t>MTD: 2026-09-01 → 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -3244,16 +3238,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6127</v>
+        <v>15715</v>
       </c>
       <c r="E5" t="n">
-        <v>9163</v>
+        <v>42236</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>865.62</v>
+        <v>2730.56</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3423,7 +3417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:19:18</t>
+          <t>Last Updated: 27-09-2026 22:44:52</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3760,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:19:18</t>
+          <t>Last Updated: 27-09-2026 22:44:52</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:19:53</t>
+          <t>Last Updated: 27-09-2026 22:45:27</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 06:20:29</t>
+          <t>Last Updated: 27-09-2026 22:46:03</t>
         </is>
       </c>
     </row>
@@ -4829,16 +4823,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1445162</v>
+        <v>1511612</v>
       </c>
       <c r="E5" t="n">
-        <v>53340</v>
+        <v>54290</v>
       </c>
       <c r="F5" t="n">
-        <v>22548</v>
+        <v>23398</v>
       </c>
       <c r="G5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4864,25 +4858,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_PPV_L7D_17July26</t>
+          <t>AR_Onboarding_KYC_But_Not_Transacted_1P_6June26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>607963</v>
+        <v>617232</v>
       </c>
       <c r="E6" t="n">
-        <v>28722</v>
+        <v>49225</v>
       </c>
       <c r="F6" t="n">
-        <v>9105</v>
+        <v>6437</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4908,25 +4902,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AR_Onboarding_KYC_But_Not_Transacted_1P_6June26</t>
+          <t>AR_Retention_Catalogue_PPV_L7D_17July26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>595398</v>
+        <v>607997</v>
       </c>
       <c r="E7" t="n">
-        <v>48601</v>
+        <v>28722</v>
       </c>
       <c r="F7" t="n">
-        <v>6222</v>
+        <v>9105</v>
       </c>
       <c r="G7" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4961,16 +4955,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>518845</v>
+        <v>538329</v>
       </c>
       <c r="E8" t="n">
-        <v>15921</v>
+        <v>16316</v>
       </c>
       <c r="F8" t="n">
-        <v>11160</v>
+        <v>11529</v>
       </c>
       <c r="G8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -5005,16 +4999,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>384682</v>
+        <v>402957</v>
       </c>
       <c r="E9" t="n">
-        <v>18437</v>
+        <v>18760</v>
       </c>
       <c r="F9" t="n">
-        <v>24349</v>
+        <v>25426</v>
       </c>
       <c r="G9" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5049,16 +5043,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>111036</v>
+        <v>123351</v>
       </c>
       <c r="E10" t="n">
-        <v>16211</v>
+        <v>17091</v>
       </c>
       <c r="F10" t="n">
-        <v>1917</v>
+        <v>2114</v>
       </c>
       <c r="G10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5093,16 +5087,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21102</v>
+        <v>26697</v>
       </c>
       <c r="E11" t="n">
-        <v>9542</v>
+        <v>11082</v>
       </c>
       <c r="F11" t="n">
-        <v>391</v>
+        <v>485</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5128,7 +5122,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Retention_PurchasersReturning_26Sep</t>
+          <t>Retention_PurchasersNotReturning_26Sep</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5137,16 +5131,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5951</v>
+        <v>23680</v>
       </c>
       <c r="E12" t="n">
-        <v>3485</v>
+        <v>6587</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="G12" t="n">
-        <v>1.45</v>
+        <v>0.9</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5172,7 +5166,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Retention_PurchasersNotReturning_26Sep</t>
+          <t>Retention_PurchasersReturning_26Sep</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5181,16 +5175,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3212</v>
+        <v>18556</v>
       </c>
       <c r="E13" t="n">
-        <v>2318</v>
+        <v>6368</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5225,16 +5219,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1522</v>
+        <v>16988</v>
       </c>
       <c r="E14" t="n">
-        <v>747</v>
+        <v>7683</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>274</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>1.61</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:42:32</t>
+          <t>Last Updated: 28-09-2026 06:31:03</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>31142.49</v>
+        <v>31214.84</v>
       </c>
       <c r="D5" t="n">
-        <v>183155.57</v>
+        <v>185009.56</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>31142.49</v>
+        <v>31214.84</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>345454.11</v>
+        <v>347308.1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1582.85</v>
+        <v>1655.2</v>
       </c>
       <c r="D17" t="n">
-        <v>10254.3</v>
+        <v>12108.29</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1582.85</v>
+        <v>1655.2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>10254.3</v>
+        <v>12108.29</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:43:03</t>
+          <t>Last Updated: 28-09-2026 06:31:34</t>
         </is>
       </c>
     </row>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28173</v>
+        <v>28287</v>
       </c>
       <c r="C8" t="n">
-        <v>150095</v>
+        <v>150755</v>
       </c>
       <c r="D8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
         <v>5.33</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6283.03</v>
+        <v>6312.91</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49225</v>
+        <v>49281</v>
       </c>
       <c r="C14" t="n">
-        <v>617522</v>
+        <v>618340</v>
       </c>
       <c r="D14" t="n">
         <v>1.25</v>
       </c>
       <c r="E14" t="n">
-        <v>12.54</v>
+        <v>12.55</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>24859.46</v>
+        <v>24901.93</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2396</v>
+        <v>2510</v>
       </c>
       <c r="C32" t="n">
-        <v>17621</v>
+        <v>18281</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E32" t="n">
         <v>0.19</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>698.67</v>
+        <v>728.55</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>624</v>
+        <v>680</v>
       </c>
       <c r="C38" t="n">
-        <v>21727</v>
+        <v>22545</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>884.1799999999999</v>
+        <v>926.65</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:43:42</t>
+          <t>Last Updated: 28-09-2026 06:32:13</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>112280</v>
+        <v>112424</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2700174</v>
+        <v>2701913</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>152625.44</v>
+        <v>152735.9</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>107781</v>
+        <v>107780</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>3178959</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220061</v>
+        <v>220204</v>
       </c>
       <c r="C7" t="n">
-        <v>5879133</v>
+        <v>5880872</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>314923.99</v>
+        <v>315034.45</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2657938</v>
+        <v>2658577</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>149894.88</v>
+        <v>149937.2</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>42236</v>
+        <v>43336</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2730.56</v>
+        <v>2798.7</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>112280</v>
+        <v>112424</v>
       </c>
       <c r="C38" t="n">
         <v>9303</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112280</v>
+        <v>112424</v>
       </c>
       <c r="C39" t="n">
         <v>2572556</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>107781</v>
+        <v>107780</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>107781</v>
+        <v>107780</v>
       </c>
       <c r="C44" t="n">
         <v>2776365</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>354</v>
+        <v>365.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214.1</v>
+        <v>222</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3158,7 +3158,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:44:17</t>
+          <t>Last Updated: 28-09-2026 06:32:49</t>
         </is>
       </c>
     </row>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15715</v>
+        <v>15868</v>
       </c>
       <c r="E5" t="n">
-        <v>42236</v>
+        <v>43336</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2730.56</v>
+        <v>2798.7</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3256,12 +3256,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3290,17 +3290,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Product 1 6June</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3324,17 +3324,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Product 1 6June</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3417,7 +3417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:44:52</t>
+          <t>Last Updated: 28-09-2026 06:33:24</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:44:52</t>
+          <t>Last Updated: 28-09-2026 06:33:24</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:45:27</t>
+          <t>Last Updated: 28-09-2026 06:33:58</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4695,7 +4695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-09-2026 22:46:03</t>
+          <t>Last Updated: 28-09-2026 06:34:33</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
         <v>3178959</v>
       </c>
       <c r="E4" t="n">
-        <v>107781</v>
+        <v>107780</v>
       </c>
       <c r="F4" t="n">
         <v>21301</v>
@@ -4823,13 +4823,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1511612</v>
+        <v>1512140</v>
       </c>
       <c r="E5" t="n">
         <v>54290</v>
       </c>
       <c r="F5" t="n">
-        <v>23398</v>
+        <v>23404</v>
       </c>
       <c r="G5" t="n">
         <v>1.55</v>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>617232</v>
+        <v>618081</v>
       </c>
       <c r="E6" t="n">
-        <v>49225</v>
+        <v>49281</v>
       </c>
       <c r="F6" t="n">
-        <v>6437</v>
+        <v>6443</v>
       </c>
       <c r="G6" t="n">
         <v>1.04</v>
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>538329</v>
+        <v>538440</v>
       </c>
       <c r="E8" t="n">
-        <v>16316</v>
+        <v>16338</v>
       </c>
       <c r="F8" t="n">
-        <v>11529</v>
+        <v>11530</v>
       </c>
       <c r="G8" t="n">
         <v>2.14</v>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>402957</v>
+        <v>404144</v>
       </c>
       <c r="E9" t="n">
-        <v>18760</v>
+        <v>18822</v>
       </c>
       <c r="F9" t="n">
-        <v>25426</v>
+        <v>25498</v>
       </c>
       <c r="G9" t="n">
         <v>6.31</v>
@@ -5043,13 +5043,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>123351</v>
+        <v>123837</v>
       </c>
       <c r="E10" t="n">
-        <v>17091</v>
+        <v>17111</v>
       </c>
       <c r="F10" t="n">
-        <v>2114</v>
+        <v>2118</v>
       </c>
       <c r="G10" t="n">
         <v>1.71</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>26697</v>
+        <v>26910</v>
       </c>
       <c r="E11" t="n">
-        <v>11082</v>
+        <v>11178</v>
       </c>
       <c r="F11" t="n">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G11" t="n">
         <v>1.82</v>
@@ -5131,16 +5131,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23680</v>
+        <v>24365</v>
       </c>
       <c r="E12" t="n">
-        <v>6587</v>
+        <v>6662</v>
       </c>
       <c r="F12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18556</v>
+        <v>18971</v>
       </c>
       <c r="E13" t="n">
-        <v>6368</v>
+        <v>6412</v>
       </c>
       <c r="F13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
         <v>16988</v>
       </c>
       <c r="E14" t="n">
-        <v>7683</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>274</v>
@@ -5243,6 +5243,50 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Activation_IntentButNotPurchased_26Sep</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15454</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7706</v>
+      </c>
+      <c r="F15" t="n">
+        <v>222</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:31:03</t>
+          <t>Last Updated: 29-09-2026 01:19:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 27-09-2026)</t>
+          <t>MTD (01-09-2026 → 28-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>31214.84</v>
+        <v>33057.09</v>
       </c>
       <c r="D5" t="n">
-        <v>185009.56</v>
+        <v>195974.49</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>31214.84</v>
+        <v>33057.09</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>347308.1</v>
+        <v>358273.03</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 26-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 27-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29559.64</v>
+        <v>31214.84</v>
       </c>
       <c r="D11" t="n">
-        <v>172901.27</v>
+        <v>185009.56</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>29559.64</v>
+        <v>31214.84</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>335199.81</v>
+        <v>347308.1</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1655.2</v>
+        <v>1842.25</v>
       </c>
       <c r="D17" t="n">
-        <v>12108.29</v>
+        <v>10964.93</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1655.2</v>
+        <v>1842.25</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12108.29</v>
+        <v>10964.93</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:31:34</t>
+          <t>Last Updated: 29-09-2026 01:20:29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-27 | MTD-1: 2026-09-01 → 2026-09-26</t>
+          <t>MTD: 2026-09-01 → 2026-09-28 | MTD-1: 2026-09-01 → 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-27)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28287</v>
+        <v>32400</v>
       </c>
       <c r="C8" t="n">
-        <v>150755</v>
+        <v>172910</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="E8" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6312.91</v>
+        <v>7170.97</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-27)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49281</v>
+        <v>50118</v>
       </c>
       <c r="C14" t="n">
-        <v>618340</v>
+        <v>643253</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="E14" t="n">
-        <v>12.55</v>
+        <v>12.83</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>24901.93</v>
+        <v>25886.13</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-26)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25777</v>
+        <v>28345</v>
       </c>
       <c r="C20" t="n">
-        <v>132474</v>
+        <v>150993</v>
       </c>
       <c r="D20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
-        <v>5.14</v>
+        <v>5.33</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5584.36</v>
+        <v>6312.91</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-26)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48601</v>
+        <v>49331</v>
       </c>
       <c r="C26" t="n">
-        <v>595795</v>
+        <v>618604</v>
       </c>
       <c r="D26" t="n">
         <v>1.25</v>
       </c>
       <c r="E26" t="n">
-        <v>12.26</v>
+        <v>12.54</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>23975.28</v>
+        <v>24901.93</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2510</v>
+        <v>4055</v>
       </c>
       <c r="C32" t="n">
-        <v>18281</v>
+        <v>21917</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E32" t="n">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>728.55</v>
+        <v>858.0599999999999</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>680</v>
+        <v>787</v>
       </c>
       <c r="C38" t="n">
-        <v>22545</v>
+        <v>24649</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E38" t="n">
         <v>0.29</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>926.65</v>
+        <v>984.2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:32:13</t>
+          <t>Last Updated: 29-09-2026 01:21:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-27)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>112424</v>
+        <v>130643</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2701913</v>
+        <v>2815905</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>152735.9</v>
+        <v>160767.43</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>107780</v>
+        <v>107779</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>3178959</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220204</v>
+        <v>238422</v>
       </c>
       <c r="C7" t="n">
-        <v>5880872</v>
+        <v>5994864</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>315034.45</v>
+        <v>323065.98</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-27)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2658577</v>
+        <v>2732322</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>149937.2</v>
+        <v>155035.7</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43336</v>
+        <v>83583</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2798.7</v>
+        <v>5731.73</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-27)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-26)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-27)</t>
         </is>
       </c>
     </row>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>112424</v>
+        <v>130643</v>
       </c>
       <c r="C38" t="n">
-        <v>9303</v>
+        <v>43336</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>869.28</v>
+        <v>2798.7</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2777,16 +2777,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112424</v>
+        <v>130643</v>
       </c>
       <c r="C39" t="n">
-        <v>2572556</v>
+        <v>2658577</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>144373.37</v>
+        <v>149937.2</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>107780</v>
+        <v>107779</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>107780</v>
+        <v>107779</v>
       </c>
       <c r="C44" t="n">
         <v>2776365</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>365.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222</v>
+        <v>104.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3158,14 +3158,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:32:49</t>
+          <t>Last Updated: 29-09-2026 01:21:45</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-27</t>
+          <t>MTD: 2026-09-01 → 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15868</v>
+        <v>38257</v>
       </c>
       <c r="E5" t="n">
-        <v>43336</v>
+        <v>83583</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2798.7</v>
+        <v>5731.73</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3256,17 +3256,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention SasteKaSahiAddress Product 1 6June</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3290,12 +3290,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3324,7 +3324,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Product 1 6June</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3358,7 +3358,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:33:24</t>
+          <t>Last Updated: 29-09-2026 01:22:20</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:33:24</t>
+          <t>Last Updated: 29-09-2026 01:22:20</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:33:58</t>
+          <t>Last Updated: 29-09-2026 01:22:55</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4695,7 +4695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-09-2026 06:34:33</t>
+          <t>Last Updated: 29-09-2026 01:23:30</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
         <v>3178959</v>
       </c>
       <c r="E4" t="n">
-        <v>107780</v>
+        <v>107779</v>
       </c>
       <c r="F4" t="n">
         <v>21301</v>
@@ -4823,16 +4823,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1512140</v>
+        <v>1568073</v>
       </c>
       <c r="E5" t="n">
-        <v>54290</v>
+        <v>55164</v>
       </c>
       <c r="F5" t="n">
-        <v>23404</v>
+        <v>24144</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>618081</v>
+        <v>642730</v>
       </c>
       <c r="E6" t="n">
-        <v>49281</v>
+        <v>50118</v>
       </c>
       <c r="F6" t="n">
-        <v>6443</v>
+        <v>6671</v>
       </c>
       <c r="G6" t="n">
         <v>1.04</v>
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>538440</v>
+        <v>556252</v>
       </c>
       <c r="E8" t="n">
-        <v>16338</v>
+        <v>16782</v>
       </c>
       <c r="F8" t="n">
-        <v>11530</v>
+        <v>11913</v>
       </c>
       <c r="G8" t="n">
         <v>2.14</v>
@@ -4999,16 +4999,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>404144</v>
+        <v>418786</v>
       </c>
       <c r="E9" t="n">
-        <v>18822</v>
+        <v>19113</v>
       </c>
       <c r="F9" t="n">
-        <v>25498</v>
+        <v>26514</v>
       </c>
       <c r="G9" t="n">
-        <v>6.31</v>
+        <v>6.33</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>123837</v>
+        <v>134495</v>
       </c>
       <c r="E10" t="n">
-        <v>17111</v>
+        <v>17762</v>
       </c>
       <c r="F10" t="n">
-        <v>2118</v>
+        <v>2268</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>26910</v>
+        <v>38169</v>
       </c>
       <c r="E11" t="n">
-        <v>11178</v>
+        <v>14638</v>
       </c>
       <c r="F11" t="n">
-        <v>489</v>
+        <v>670</v>
       </c>
       <c r="G11" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Retention_PurchasersNotReturning_26Sep</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5131,16 +5131,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24365</v>
+        <v>27269</v>
       </c>
       <c r="E12" t="n">
-        <v>6662</v>
+        <v>19472</v>
       </c>
       <c r="F12" t="n">
-        <v>221</v>
+        <v>627</v>
       </c>
       <c r="G12" t="n">
-        <v>0.91</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Retention_PurchasersReturning_26Sep</t>
+          <t>Retention_PurchasersNotReturning_26Sep</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18971</v>
+        <v>25097</v>
       </c>
       <c r="E13" t="n">
-        <v>6412</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G13" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Activation_SearchIntentNotPurchased_26Sep</t>
+          <t>Activation_IntentButNotPurchased_26Sep</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16988</v>
+        <v>22181</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>274</v>
+        <v>341</v>
       </c>
       <c r="G14" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Activation_IntentButNotPurchased_26Sep</t>
+          <t>Activation_FirstPurchase_26Sep</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5263,16 +5263,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15454</v>
+        <v>22075</v>
       </c>
       <c r="E15" t="n">
-        <v>7706</v>
+        <v>18032</v>
       </c>
       <c r="F15" t="n">
-        <v>222</v>
+        <v>462</v>
       </c>
       <c r="G15" t="n">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5287,6 +5287,138 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Retention_PurchasersReturning_26Sep</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>19278</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>221</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Activation_SearchIntentNotPurchased_26Sep</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>16988</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>274</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Retention_ActivePurchasers_26Sep</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11939</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10503</v>
+      </c>
+      <c r="F18" t="n">
+        <v>338</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:19:59</t>
+          <t>Last Updated: 29-09-2026 07:40:13</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>33057.09</v>
+        <v>33074.62</v>
       </c>
       <c r="D5" t="n">
-        <v>195974.49</v>
+        <v>196029.88</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>33057.09</v>
+        <v>33074.62</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>358273.03</v>
+        <v>358328.42</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1842.25</v>
+        <v>1859.78</v>
       </c>
       <c r="D17" t="n">
-        <v>10964.93</v>
+        <v>11020.32</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1842.25</v>
+        <v>1859.78</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>10964.93</v>
+        <v>11020.32</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:20:29</t>
+          <t>Last Updated: 29-09-2026 07:40:45</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32400</v>
+        <v>32490</v>
       </c>
       <c r="C8" t="n">
-        <v>172910</v>
+        <v>173142</v>
       </c>
       <c r="D8" t="n">
         <v>2.14</v>
       </c>
       <c r="E8" t="n">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7170.97</v>
+        <v>7180.19</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1694,19 +1694,19 @@
         <v>50118</v>
       </c>
       <c r="C14" t="n">
-        <v>643253</v>
+        <v>643436</v>
       </c>
       <c r="D14" t="n">
         <v>1.24</v>
       </c>
       <c r="E14" t="n">
-        <v>12.83</v>
+        <v>12.84</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>25886.13</v>
+        <v>25894.43</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4055</v>
+        <v>4145</v>
       </c>
       <c r="C32" t="n">
-        <v>21917</v>
+        <v>22149</v>
       </c>
       <c r="D32" t="n">
         <v>-0.06</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>858.0599999999999</v>
+        <v>867.28</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
         <v>787</v>
       </c>
       <c r="C38" t="n">
-        <v>24649</v>
+        <v>24832</v>
       </c>
       <c r="D38" t="n">
         <v>-0.01</v>
       </c>
       <c r="E38" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>984.2</v>
+        <v>992.5</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:21:09</t>
+          <t>Last Updated: 29-09-2026 07:41:26</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>130643</v>
+        <v>130705</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2815905</v>
+        <v>2816455</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>160767.43</v>
+        <v>160811.33</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>238422</v>
+        <v>238484</v>
       </c>
       <c r="C7" t="n">
-        <v>5994864</v>
+        <v>5995414</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>323065.98</v>
+        <v>323109.88</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2732322</v>
+        <v>2732752</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>155035.7</v>
+        <v>155074.02</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83583</v>
+        <v>83703</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5731.73</v>
+        <v>5737.31</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>130643</v>
+        <v>130705</v>
       </c>
       <c r="C38" t="n">
         <v>43336</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>130643</v>
+        <v>130705</v>
       </c>
       <c r="C39" t="n">
         <v>2658577</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>104.8</v>
+        <v>105</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:21:45</t>
+          <t>Last Updated: 29-09-2026 07:42:04</t>
         </is>
       </c>
     </row>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>38257</v>
+        <v>38307</v>
       </c>
       <c r="E5" t="n">
-        <v>83583</v>
+        <v>83703</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5731.73</v>
+        <v>5737.31</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3417,7 +3417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:22:20</t>
+          <t>Last Updated: 29-09-2026 07:42:40</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:22:20</t>
+          <t>Last Updated: 29-09-2026 07:42:40</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:22:55</t>
+          <t>Last Updated: 29-09-2026 07:43:15</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 01:23:30</t>
+          <t>Last Updated: 29-09-2026 07:44:33</t>
         </is>
       </c>
     </row>
@@ -4823,13 +4823,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1568073</v>
+        <v>1568403</v>
       </c>
       <c r="E5" t="n">
         <v>55164</v>
       </c>
       <c r="F5" t="n">
-        <v>24144</v>
+        <v>24151</v>
       </c>
       <c r="G5" t="n">
         <v>1.54</v>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>642730</v>
+        <v>642909</v>
       </c>
       <c r="E6" t="n">
         <v>50118</v>
       </c>
       <c r="F6" t="n">
-        <v>6671</v>
+        <v>6672</v>
       </c>
       <c r="G6" t="n">
         <v>1.04</v>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>556252</v>
+        <v>556352</v>
       </c>
       <c r="E8" t="n">
         <v>16782</v>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>418786</v>
+        <v>418914</v>
       </c>
       <c r="E9" t="n">
         <v>19113</v>
       </c>
       <c r="F9" t="n">
-        <v>26514</v>
+        <v>26524</v>
       </c>
       <c r="G9" t="n">
         <v>6.33</v>
@@ -5043,13 +5043,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>134495</v>
+        <v>134585</v>
       </c>
       <c r="E10" t="n">
         <v>17762</v>
       </c>
       <c r="F10" t="n">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="G10" t="n">
         <v>1.69</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38169</v>
+        <v>38307</v>
       </c>
       <c r="E11" t="n">
-        <v>14638</v>
+        <v>14728</v>
       </c>
       <c r="F11" t="n">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="G11" t="n">
         <v>1.76</v>
@@ -5131,16 +5131,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27269</v>
+        <v>27367</v>
       </c>
       <c r="E12" t="n">
-        <v>19472</v>
+        <v>19515</v>
       </c>
       <c r="F12" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22075</v>
+        <v>22096</v>
       </c>
       <c r="E15" t="n">
-        <v>18032</v>
+        <v>18045</v>
       </c>
       <c r="F15" t="n">
         <v>462</v>
@@ -5395,16 +5395,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11939</v>
+        <v>11961</v>
       </c>
       <c r="E18" t="n">
-        <v>10503</v>
+        <v>10522</v>
       </c>
       <c r="F18" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G18" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:40:13</t>
+          <t>Last Updated: 29-09-2026 23:44:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 28-09-2026)</t>
+          <t>MTD (01-09-2026 → 29-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>162298.54</v>
+        <v>162411.44</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>33074.62</v>
+        <v>34786.42</v>
       </c>
       <c r="D5" t="n">
-        <v>196029.88</v>
+        <v>206213.65</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>33074.62</v>
+        <v>34786.42</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>358328.42</v>
+        <v>368625.09</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 27-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 28-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>31214.84</v>
+        <v>33096.45</v>
       </c>
       <c r="D11" t="n">
-        <v>185009.56</v>
+        <v>196091.72</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>31214.84</v>
+        <v>33096.45</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>347308.1</v>
+        <v>358390.26</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>112.9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1859.78</v>
+        <v>1689.97</v>
       </c>
       <c r="D17" t="n">
-        <v>11020.32</v>
+        <v>10121.93</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1859.78</v>
+        <v>1689.97</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>11020.32</v>
+        <v>10234.83</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:40:45</t>
+          <t>Last Updated: 29-09-2026 23:45:00</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-28 | MTD-1: 2026-09-01 → 2026-09-27</t>
+          <t>MTD: 2026-09-01 → 2026-09-29 | MTD-1: 2026-09-01 → 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-28)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32490</v>
+        <v>39571</v>
       </c>
       <c r="C8" t="n">
-        <v>173142</v>
+        <v>211890</v>
       </c>
       <c r="D8" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="E8" t="n">
-        <v>5.33</v>
+        <v>5.35</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7180.19</v>
+        <v>8873.379999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-28)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -1694,19 +1694,19 @@
         <v>50118</v>
       </c>
       <c r="C14" t="n">
-        <v>643436</v>
+        <v>643786</v>
       </c>
       <c r="D14" t="n">
         <v>1.24</v>
       </c>
       <c r="E14" t="n">
-        <v>12.84</v>
+        <v>12.85</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>25894.43</v>
+        <v>25913.04</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-27)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28345</v>
+        <v>32517</v>
       </c>
       <c r="C20" t="n">
-        <v>150993</v>
+        <v>173359</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="E20" t="n">
         <v>5.33</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>6312.91</v>
+        <v>7186.34</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-27)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>49331</v>
+        <v>50118</v>
       </c>
       <c r="C26" t="n">
-        <v>618604</v>
+        <v>643725</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="E26" t="n">
-        <v>12.54</v>
+        <v>12.84</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>24901.93</v>
+        <v>25910.11</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4145</v>
+        <v>7054</v>
       </c>
       <c r="C32" t="n">
-        <v>22149</v>
+        <v>38531</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>867.28</v>
+        <v>1687.04</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>787</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>24832</v>
+        <v>61</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>992.5</v>
+        <v>2.93</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:41:26</t>
+          <t>Last Updated: 29-09-2026 23:45:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-28)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>130705</v>
+        <v>143467</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2816455</v>
+        <v>2945823</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>160811.33</v>
+        <v>168645.11</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>107779</v>
+        <v>108538</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3178959</v>
+        <v>3180290</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>162298.55</v>
+        <v>162411.44</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>238484</v>
+        <v>252005</v>
       </c>
       <c r="C7" t="n">
-        <v>5995414</v>
+        <v>6126113</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>323109.88</v>
+        <v>331056.55</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-28)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2732752</v>
+        <v>2808095</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>155074.02</v>
+        <v>160030.51</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83703</v>
+        <v>137728</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5737.31</v>
+        <v>8614.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-28)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2776365</v>
+        <v>2777620</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>150854.89</v>
+        <v>150960.72</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>402594</v>
+        <v>402670</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>11443.66</v>
+        <v>11450.72</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-27)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>130705</v>
+        <v>143467</v>
       </c>
       <c r="C38" t="n">
-        <v>43336</v>
+        <v>83846</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2798.7</v>
+        <v>5742.86</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2777,16 +2777,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>130705</v>
+        <v>143467</v>
       </c>
       <c r="C39" t="n">
-        <v>2658577</v>
+        <v>2733371</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>149937.2</v>
+        <v>155116.75</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>107779</v>
+        <v>108538</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>107779</v>
+        <v>108538</v>
       </c>
       <c r="C44" t="n">
         <v>2776365</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>93.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3158,14 +3158,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:42:04</t>
+          <t>Last Updated: 29-09-2026 23:46:17</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-28</t>
+          <t>MTD: 2026-09-01 → 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>38307</v>
+        <v>61459</v>
       </c>
       <c r="E5" t="n">
-        <v>83703</v>
+        <v>137728</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5737.31</v>
+        <v>8614.6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3417,7 +3417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:42:40</t>
+          <t>Last Updated: 29-09-2026 23:46:52</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:42:40</t>
+          <t>Last Updated: 29-09-2026 23:46:52</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:43:15</t>
+          <t>Last Updated: 29-09-2026 23:47:27</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 07:44:33</t>
+          <t>Last Updated: 29-09-2026 23:48:04</t>
         </is>
       </c>
     </row>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3178959</v>
+        <v>3180290</v>
       </c>
       <c r="E4" t="n">
-        <v>107779</v>
+        <v>108538</v>
       </c>
       <c r="F4" t="n">
-        <v>21301</v>
+        <v>21305</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
@@ -4823,16 +4823,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1568403</v>
+        <v>1626606</v>
       </c>
       <c r="E5" t="n">
-        <v>55164</v>
+        <v>56465</v>
       </c>
       <c r="F5" t="n">
-        <v>24151</v>
+        <v>24944</v>
       </c>
       <c r="G5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>642909</v>
+        <v>643263</v>
       </c>
       <c r="E6" t="n">
         <v>50118</v>
       </c>
       <c r="F6" t="n">
-        <v>6672</v>
+        <v>6676</v>
       </c>
       <c r="G6" t="n">
         <v>1.04</v>
@@ -4955,16 +4955,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>556352</v>
+        <v>573492</v>
       </c>
       <c r="E8" t="n">
-        <v>16782</v>
+        <v>17111</v>
       </c>
       <c r="F8" t="n">
-        <v>11913</v>
+        <v>12238</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>418914</v>
+        <v>435024</v>
       </c>
       <c r="E9" t="n">
-        <v>19113</v>
+        <v>19513</v>
       </c>
       <c r="F9" t="n">
-        <v>26524</v>
+        <v>27557</v>
       </c>
       <c r="G9" t="n">
         <v>6.33</v>
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>134585</v>
+        <v>150459</v>
       </c>
       <c r="E10" t="n">
-        <v>17762</v>
+        <v>18541</v>
       </c>
       <c r="F10" t="n">
-        <v>2270</v>
+        <v>2498</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5078,25 +5078,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>Activation_FirstPurchase_26Sep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38307</v>
+        <v>73690</v>
       </c>
       <c r="E11" t="n">
-        <v>14728</v>
+        <v>34736</v>
       </c>
       <c r="F11" t="n">
-        <v>673</v>
+        <v>1052</v>
       </c>
       <c r="G11" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5122,25 +5122,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27367</v>
+        <v>61151</v>
       </c>
       <c r="E12" t="n">
-        <v>19515</v>
+        <v>21030</v>
       </c>
       <c r="F12" t="n">
-        <v>628</v>
+        <v>992</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Retention_PurchasersNotReturning_26Sep</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25097</v>
+        <v>60774</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>27118</v>
       </c>
       <c r="F13" t="n">
-        <v>225</v>
+        <v>1331</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>2.19</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Activation_IntentButNotPurchased_26Sep</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22181</v>
+        <v>32579</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>14071</v>
       </c>
       <c r="F14" t="n">
-        <v>341</v>
+        <v>1277</v>
       </c>
       <c r="G14" t="n">
-        <v>1.54</v>
+        <v>3.92</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Activation_FirstPurchase_26Sep</t>
+          <t>Retention_PurchasersNotReturning_26Sep</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5263,16 +5263,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22096</v>
+        <v>25097</v>
       </c>
       <c r="E15" t="n">
-        <v>18045</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>462</v>
+        <v>225</v>
       </c>
       <c r="G15" t="n">
-        <v>2.09</v>
+        <v>0.9</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Retention_PurchasersReturning_26Sep</t>
+          <t>Activation_IntentButNotPurchased_26Sep</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5307,16 +5307,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19278</v>
+        <v>22181</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>221</v>
+        <v>341</v>
       </c>
       <c r="G16" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Activation_SearchIntentNotPurchased_26Sep</t>
+          <t>Retention_PurchasersReturning_26Sep</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5351,16 +5351,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16988</v>
+        <v>19278</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="G17" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>Activation_SearchIntentNotPurchased_26Sep</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5395,16 +5395,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11961</v>
+        <v>16988</v>
       </c>
       <c r="E18" t="n">
-        <v>10522</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>341</v>
+        <v>274</v>
       </c>
       <c r="G18" t="n">
-        <v>2.85</v>
+        <v>1.61</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:44:29</t>
+          <t>Last Updated: 30-09-2026 06:55:17</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>162411.44</v>
+        <v>164787.31</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>34786.42</v>
+        <v>34812.64</v>
       </c>
       <c r="D5" t="n">
-        <v>206213.65</v>
+        <v>206293.54</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>34786.42</v>
+        <v>34812.64</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>368625.09</v>
+        <v>371080.85</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>112.9</v>
+        <v>2488.77</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1689.97</v>
+        <v>1716.19</v>
       </c>
       <c r="D17" t="n">
-        <v>10121.93</v>
+        <v>10201.82</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1689.97</v>
+        <v>1716.19</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>10234.83</v>
+        <v>12690.59</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:45:00</t>
+          <t>Last Updated: 30-09-2026 06:55:47</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39571</v>
+        <v>39619</v>
       </c>
       <c r="C8" t="n">
-        <v>211890</v>
+        <v>212327</v>
       </c>
       <c r="D8" t="n">
         <v>2.06</v>
       </c>
       <c r="E8" t="n">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8873.379999999999</v>
+        <v>8899.610000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7054</v>
+        <v>7102</v>
       </c>
       <c r="C32" t="n">
-        <v>38531</v>
+        <v>38968</v>
       </c>
       <c r="D32" t="n">
         <v>-0.08</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1687.04</v>
+        <v>1713.27</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:45:40</t>
+          <t>Last Updated: 30-09-2026 06:56:27</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>143467</v>
+        <v>143544</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2945823</v>
+        <v>2946406</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>168645.11</v>
+        <v>168688.73</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2423,13 +2423,13 @@
         <v>108538</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3180290</v>
+        <v>3210239</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>162411.44</v>
+        <v>164787.31</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>252005</v>
+        <v>252082</v>
       </c>
       <c r="C7" t="n">
-        <v>6126113</v>
+        <v>6156645</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>331056.55</v>
+        <v>333476.04</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2808095</v>
+        <v>2808454</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>160030.51</v>
+        <v>160062.32</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>137728</v>
+        <v>137952</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8614.6</v>
+        <v>8626.41</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2777620</v>
+        <v>2805437</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>150960.72</v>
+        <v>153190.51</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>402670</v>
+        <v>404802</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>11450.72</v>
+        <v>11596.8</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>143467</v>
+        <v>143544</v>
       </c>
       <c r="C38" t="n">
         <v>83846</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>143467</v>
+        <v>143544</v>
       </c>
       <c r="C39" t="n">
         <v>2733371</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3158,7 +3158,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:46:17</t>
+          <t>Last Updated: 30-09-2026 06:57:03</t>
         </is>
       </c>
     </row>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61459</v>
+        <v>61580</v>
       </c>
       <c r="E5" t="n">
-        <v>137728</v>
+        <v>137952</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>8614.6</v>
+        <v>8626.41</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3324,12 +3324,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention Price Increase Agro Tools</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3358,12 +3358,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:46:52</t>
+          <t>Last Updated: 30-09-2026 06:57:38</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:46:52</t>
+          <t>Last Updated: 30-09-2026 06:57:38</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:47:27</t>
+          <t>Last Updated: 30-09-2026 06:58:13</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-09-2026 23:48:04</t>
+          <t>Last Updated: 30-09-2026 06:58:48</t>
         </is>
       </c>
     </row>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3180290</v>
+        <v>3210239</v>
       </c>
       <c r="E4" t="n">
         <v>108538</v>
       </c>
       <c r="F4" t="n">
-        <v>21305</v>
+        <v>21598</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
@@ -4823,13 +4823,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1626606</v>
+        <v>1626859</v>
       </c>
       <c r="E5" t="n">
         <v>56465</v>
       </c>
       <c r="F5" t="n">
-        <v>24944</v>
+        <v>24950</v>
       </c>
       <c r="G5" t="n">
         <v>1.53</v>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>573492</v>
+        <v>573598</v>
       </c>
       <c r="E8" t="n">
         <v>17111</v>
@@ -4999,16 +4999,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>435024</v>
+        <v>435337</v>
       </c>
       <c r="E9" t="n">
         <v>19513</v>
       </c>
       <c r="F9" t="n">
-        <v>27557</v>
+        <v>27579</v>
       </c>
       <c r="G9" t="n">
-        <v>6.33</v>
+        <v>6.34</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5043,13 +5043,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>150459</v>
+        <v>150761</v>
       </c>
       <c r="E10" t="n">
-        <v>18541</v>
+        <v>18589</v>
       </c>
       <c r="F10" t="n">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="G10" t="n">
         <v>1.66</v>
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73690</v>
+        <v>73959</v>
       </c>
       <c r="E11" t="n">
-        <v>34736</v>
+        <v>34737</v>
       </c>
       <c r="F11" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5131,13 +5131,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61151</v>
+        <v>61314</v>
       </c>
       <c r="E12" t="n">
         <v>21030</v>
       </c>
       <c r="F12" t="n">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="G12" t="n">
         <v>1.62</v>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60774</v>
+        <v>60950</v>
       </c>
       <c r="E13" t="n">
-        <v>27118</v>
+        <v>27175</v>
       </c>
       <c r="F13" t="n">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="G13" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32579</v>
+        <v>32627</v>
       </c>
       <c r="E14" t="n">
         <v>14071</v>
@@ -5228,7 +5228,7 @@
         <v>1277</v>
       </c>
       <c r="G14" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:55:17</t>
+          <t>Last Updated: 30-09-2026 23:37:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-09-2026 → 29-09-2026)</t>
+          <t>MTD (01-09-2026 → 30-09-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>164787.31</v>
+        <v>178432.16</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>34812.64</v>
+        <v>36515.15</v>
       </c>
       <c r="D5" t="n">
-        <v>206293.54</v>
+        <v>214524.72</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>34812.64</v>
+        <v>36515.15</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>371080.85</v>
+        <v>392956.88</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.88</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-09-2026 → 28-09-2026)</t>
+          <t>MTD-1 (01-09-2026 → 29-09-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>162298.54</v>
+        <v>164788.52</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>33096.45</v>
+        <v>34827.95</v>
       </c>
       <c r="D11" t="n">
-        <v>196091.72</v>
+        <v>206369.77</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>33096.45</v>
+        <v>34827.95</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>358390.26</v>
+        <v>371158.29</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.88</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2488.77</v>
+        <v>13643.64</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1716.19</v>
+        <v>1687.2</v>
       </c>
       <c r="D17" t="n">
-        <v>10201.82</v>
+        <v>8154.95</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1716.19</v>
+        <v>1687.2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12690.59</v>
+        <v>21798.59</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1434,14 +1434,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:55:47</t>
+          <t>Last Updated: 30-09-2026 23:38:13</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-29 | MTD-1: 2026-09-01 → 2026-09-28</t>
+          <t>MTD: 2026-09-01 → 2026-09-30 | MTD-1: 2026-09-01 → 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-09-01 → 2026-09-29)</t>
+          <t>KYC — MTD (2026-09-01 → 2026-09-30)</t>
         </is>
       </c>
     </row>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39619</v>
+        <v>44721</v>
       </c>
       <c r="C8" t="n">
-        <v>212327</v>
+        <v>250315</v>
       </c>
       <c r="D8" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="E8" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8899.610000000001</v>
+        <v>10602.11</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-09-01 → 2026-09-29)</t>
+          <t>First Txn — MTD (2026-09-01 → 2026-09-30)</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-09-01 → 2026-09-28)</t>
+          <t>KYC — MTD-1 (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32517</v>
+        <v>39688</v>
       </c>
       <c r="C20" t="n">
-        <v>173359</v>
+        <v>212747</v>
       </c>
       <c r="D20" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="E20" t="n">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>7186.34</v>
+        <v>8914.91</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-28)</t>
+          <t>First Txn — MTD-1 (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -1992,19 +1992,19 @@
         <v>50118</v>
       </c>
       <c r="C26" t="n">
-        <v>643725</v>
+        <v>643786</v>
       </c>
       <c r="D26" t="n">
         <v>1.24</v>
       </c>
       <c r="E26" t="n">
-        <v>12.84</v>
+        <v>12.85</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>25910.11</v>
+        <v>25913.04</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2132,22 +2132,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7102</v>
+        <v>5033</v>
       </c>
       <c r="C32" t="n">
-        <v>38968</v>
+        <v>37568</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1713.27</v>
+        <v>1687.2</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2340,14 +2340,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:56:27</t>
+          <t>Last Updated: 30-09-2026 23:38:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-09-01 → 2026-09-29)</t>
+          <t>Retention — MTD (2026-09-01 → 2026-09-30)</t>
         </is>
       </c>
     </row>
@@ -2395,16 +2395,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>143544</v>
+        <v>147414</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2946406</v>
+        <v>3054293</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>168688.73</v>
+        <v>175075.01</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>8</v>
@@ -2420,16 +2420,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>108538</v>
+        <v>114224</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3210239</v>
+        <v>3399947</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>164787.31</v>
+        <v>178432.16</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>8</v>
@@ -2445,16 +2445,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>252082</v>
+        <v>261638</v>
       </c>
       <c r="C7" t="n">
-        <v>6156645</v>
+        <v>6454240</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>333476.04</v>
+        <v>353507.17</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -2466,7 +2466,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-29)</t>
+          <t>Meta Ad Performance — MTD (2026-09-01 → 2026-09-30)</t>
         </is>
       </c>
     </row>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2808454</v>
+        <v>2881014</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>160062.32</v>
+        <v>164735.48</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>137952</v>
+        <v>173279</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8626.41</v>
+        <v>10339.53</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2564,7 +2564,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-29)</t>
+          <t>Google Ad Group Performance — MTD (2026-09-01 → 2026-09-30)</t>
         </is>
       </c>
     </row>
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2805437</v>
+        <v>2984014</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>153190.51</v>
+        <v>165915.05</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>404802</v>
+        <v>415933</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>11596.8</v>
+        <v>12517.11</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-09-01 → 2026-09-28)</t>
+          <t>MTD-1 (2026-09-01 → 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>143544</v>
+        <v>147414</v>
       </c>
       <c r="C38" t="n">
-        <v>83846</v>
+        <v>138165</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>5742.86</v>
+        <v>8637.030000000001</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2777,16 +2777,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>143544</v>
+        <v>147414</v>
       </c>
       <c r="C39" t="n">
-        <v>2733371</v>
+        <v>2809099</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>155116.75</v>
+        <v>160104.34</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>108538</v>
+        <v>114224</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2879,16 +2879,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>108538</v>
+        <v>114224</v>
       </c>
       <c r="C44" t="n">
-        <v>2776365</v>
+        <v>2805435</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>150854.89</v>
+        <v>153191.71</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>64.5</v>
+        <v>25.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>50.2</v>
+        <v>19.7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3158,14 +3158,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:57:03</t>
+          <t>Last Updated: 30-09-2026 23:39:30</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-09-01 → 2026-09-29</t>
+          <t>MTD: 2026-09-01 → 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61580</v>
+        <v>77812</v>
       </c>
       <c r="E5" t="n">
-        <v>137952</v>
+        <v>173279</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>8626.41</v>
+        <v>10339.53</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3417,7 +3417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:57:38</t>
+          <t>Last Updated: 30-09-2026 23:40:05</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:57:38</t>
+          <t>Last Updated: 30-09-2026 23:40:05</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:58:13</t>
+          <t>Last Updated: 30-09-2026 23:40:40</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-09-2026 06:58:48</t>
+          <t>Last Updated: 30-09-2026 23:41:16</t>
         </is>
       </c>
     </row>
@@ -4779,16 +4779,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3210239</v>
+        <v>3399947</v>
       </c>
       <c r="E4" t="n">
-        <v>108538</v>
+        <v>114224</v>
       </c>
       <c r="F4" t="n">
-        <v>21598</v>
+        <v>23059</v>
       </c>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -4823,13 +4823,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1626859</v>
+        <v>1682251</v>
       </c>
       <c r="E5" t="n">
-        <v>56465</v>
+        <v>57316</v>
       </c>
       <c r="F5" t="n">
-        <v>24950</v>
+        <v>25655</v>
       </c>
       <c r="G5" t="n">
         <v>1.53</v>
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>573598</v>
+        <v>590766</v>
       </c>
       <c r="E8" t="n">
-        <v>17111</v>
+        <v>17472</v>
       </c>
       <c r="F8" t="n">
-        <v>12238</v>
+        <v>12560</v>
       </c>
       <c r="G8" t="n">
         <v>2.13</v>
@@ -4999,16 +4999,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>435337</v>
+        <v>450229</v>
       </c>
       <c r="E9" t="n">
-        <v>19513</v>
+        <v>19727</v>
       </c>
       <c r="F9" t="n">
-        <v>27579</v>
+        <v>28585</v>
       </c>
       <c r="G9" t="n">
-        <v>6.34</v>
+        <v>6.35</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>150761</v>
+        <v>165310</v>
       </c>
       <c r="E10" t="n">
-        <v>18589</v>
+        <v>19049</v>
       </c>
       <c r="F10" t="n">
-        <v>2502</v>
+        <v>2718</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73959</v>
+        <v>106555</v>
       </c>
       <c r="E11" t="n">
-        <v>34737</v>
+        <v>39129</v>
       </c>
       <c r="F11" t="n">
-        <v>1053</v>
+        <v>1353</v>
       </c>
       <c r="G11" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5131,16 +5131,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61314</v>
+        <v>84742</v>
       </c>
       <c r="E12" t="n">
-        <v>21030</v>
+        <v>25672</v>
       </c>
       <c r="F12" t="n">
-        <v>995</v>
+        <v>1260</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60950</v>
+        <v>80325</v>
       </c>
       <c r="E13" t="n">
-        <v>27175</v>
+        <v>28997</v>
       </c>
       <c r="F13" t="n">
-        <v>1339</v>
+        <v>1733</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32627</v>
+        <v>48579</v>
       </c>
       <c r="E14" t="n">
-        <v>14071</v>
+        <v>14907</v>
       </c>
       <c r="F14" t="n">
-        <v>1277</v>
+        <v>1985</v>
       </c>
       <c r="G14" t="n">
-        <v>3.91</v>
+        <v>4.09</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Team Wise Cost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Onboarding_report" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="retention_brand_report" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="KAM_Brand_Report" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Inapp_Subcat_Report" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Inapp_Sale_Report" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Webengage_Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Webengage_Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Onboarding_report" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="retention_brand_report" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KAM_Brand_Report" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Inapp_Subcat_Report" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Inapp_Sale_Report" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Campaign_Performance_Report" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Prev_Month_Report" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 01-10-2026 06:55:23</t>
+          <t>Last Updated: 02-10-2026 00:04:33</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>184.49</v>
+        <v>6125.21</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>222.06</v>
+        <v>1536.78</v>
       </c>
       <c r="D5" t="n">
-        <v>376.42</v>
+        <v>7595.3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>222.06</v>
+        <v>1536.78</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>560.91</v>
+        <v>13720.51</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>184.49</v>
+        <v>6125.21</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>222.06</v>
+        <v>1536.78</v>
       </c>
       <c r="D11" t="n">
-        <v>376.42</v>
+        <v>7595.3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>222.06</v>
+        <v>1536.78</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>560.91</v>
+        <v>13720.51</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -825,93 +825,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="65" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Last Updated: 01-10-2026 06:55:54</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Last Updated: 01-10-2026 06:58:17</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>MTD: 2026-10-01 → 2026-09-30 | MTD-1: 2026-10-01 → 2026-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Note: Event numbers are from Apptrove</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Period: October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1. Channel Performance</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>KYC — MTD (2026-10-01 → 2026-09-30)</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>First Home Page View</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Cost Per KYC</t>
-        </is>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Push</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -925,27 +923,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>In-app</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -959,112 +944,69 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2. Team Engagement — Total</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-09-30)</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>First Purchase Success</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Cost Per TXN</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Marketing Retention</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1078,158 +1020,117 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2. Team Engagement — By Channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-09-29)</t>
-        </is>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>First Home Page View</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Cost Per KYC</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Push</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>In-app</t>
+        </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D19" t="n">
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1238,32 +1139,24 @@
       </c>
       <c r="F19" t="n">
         <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D20" t="n">
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1272,34 +1165,24 @@
       </c>
       <c r="F20" t="n">
         <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Push</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1309,432 +1192,468 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-09-29)</t>
-        </is>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>In-app</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>First Purchase Success</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Cost Per TXN</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>4. Journey Funnel — Classified</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Journey Category</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>5. WhatsApp Failure Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Failure Type</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>% of Total Failed</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>KYC — Change (MTD - MTD-1)</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DND Queue Drop</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>First Home Page View</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Cost Per KYC</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Frequency Capping Queue Drop</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Personalization Error</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Channel Not Available</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Invalid WhatsApp Number</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Message Format Error</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>First Txn — Change (MTD - MTD-1)</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Template Does Not Exist</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>First Purchase Success</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Cost Per TXN</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Throttling Error</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>User Blocked Messages</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>User Did Not Initiate Session</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>User Offline</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WSP Configuration Error</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WSP Quote Limit Reached</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Time Zone Elapsed</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Other Failures</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Failed</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>7. Push Engagement — Overall</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Impressions</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Clicks</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Dismisses</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dismiss Rate</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Total Conversions</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Conversion Rate</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>7. Push Engagement — By Campaign Type (One-time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Campaign Type</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1748,127 +1667,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="63" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 01-10-2026 06:56:31</t>
+          <t>Last Updated: 02-10-2026 00:05:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MTD: 2026-10-01 → 2026-10-01 | MTD-1: 2026-10-01 → 2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Retention — MTD (2026-10-01 → 2026-09-30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Note: Event numbers are from Apptrove</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>KYC — MTD (2026-10-01 → 2026-10-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>CTR (%)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>First Home Page View</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Cost Per KYC</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1882,165 +1767,762 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18240</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31497</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1536.77</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-09-30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-09-30)</t>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>CTR (%)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>First Purchase Success</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Cost Per TXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-09-30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>CTR (%)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>First Home Page View</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Cost Per KYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Ad Group</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-09-30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>CTR (%)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>First Purchase Success</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Cost Per TXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>KYC — Change (MTD - MTD-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>CTR (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>First Home Page View</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Cost Per KYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>18240</v>
+      </c>
+      <c r="C32" t="n">
+        <v>31497</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1536.77</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-09-29)</t>
+          <t>First Txn — Change (MTD - MTD-1)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>CTR (%)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>First Purchase Success</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Cost Per TXN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KAM Campaigns</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2049,10 +2531,8 @@
       <c r="C38" t="n">
         <v>0</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D38" t="n">
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2061,13 +2541,16 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Subcat</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2076,10 +2559,8 @@
       <c r="C39" t="n">
         <v>0</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D39" t="n">
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -2090,364 +2571,8 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>KAM Campaigns</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Subcat</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>% Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KAM Campaigns</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Subcat</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr"/>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>KAM Campaigns</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Subcat</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H39" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2461,16 +2586,823 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="63" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Last Updated: 02-10-2026 00:05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Retention — MTD (2026-10-01 → 2026-10-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t># Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>37803</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>110980</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5839.27</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>29822</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>91760</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6125.21</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>67625</v>
+      </c>
+      <c r="C7" t="n">
+        <v>202740</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11964.48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t># Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Catalogue_July_150_Top_Selling_Porducts_7July</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4553.25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Catalog_TopSellers</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>31936</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1286.02</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ad Group</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t># Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Category_Promotion</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>86814</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5727.55</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Product_Price</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4946</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>397.66</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>MTD-1 (2026-10-01 → 2026-09-30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>KAM Campaigns</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t># Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37803</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Subcat</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>37803</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KAM Campaigns</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t># Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>29822</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Subcat</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>29822</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>% Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KAM Campaigns</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t># Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Subcat</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>KAM Campaigns</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t># Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Subcat</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -2480,7 +3412,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 01-10-2026 06:57:07</t>
+          <t>Last Updated: 02-10-2026 00:06:20</t>
         </is>
       </c>
     </row>
@@ -2560,16 +3492,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1428</v>
+        <v>14161</v>
       </c>
       <c r="E5" t="n">
-        <v>1839</v>
+        <v>31936</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>88.38</v>
+        <v>1286.02</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2578,17 +3510,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Product 1 6June</t>
+          <t>Retention SasteKaSahiAddress Category 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -2612,12 +3544,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
+          <t>Retention SasteKaSahiAddress Video</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2646,12 +3578,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Retention SasteKaSahiAddress Video</t>
+          <t>Retention Price Increase Agro Tools</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2674,40 +3606,6 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Retention Price Increase Agro Tools</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>03-07-2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>08-07-2026</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2716,7 +3614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2739,7 +3637,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 01-10-2026 06:57:42</t>
+          <t>Last Updated: 02-10-2026 00:06:57</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3082,7 +3980,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 01-10-2026 06:57:42</t>
+          <t>Last Updated: 02-10-2026 00:06:57</t>
         </is>
       </c>
     </row>
@@ -3142,848 +4040,6 @@
       </c>
       <c r="F4" t="n">
         <v>21.69</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Last Updated: 01-10-2026 06:58:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Period: October 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>1. Channel Performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Push</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>In-app</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2. Team Engagement — Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2. Team Engagement — By Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Push</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>In-app</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Push</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>In-app</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>4. Journey Funnel — Classified</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Journey Category</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5. WhatsApp Failure Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Failure Type</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>% of Total Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DND Queue Drop</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Frequency Capping Queue Drop</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Personalization Error</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Channel Not Available</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Invalid WhatsApp Number</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Message Format Error</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Template Does Not Exist</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Throttling Error</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>User Blocked Messages</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>User Did Not Initiate Session</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>User Offline</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>WSP Configuration Error</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>WSP Quote Limit Reached</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Time Zone Elapsed</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Other Failures</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Total Failed</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>7. Push Engagement — Overall</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Total Impressions</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Total Clicks</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Total Dismisses</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Dismiss Rate</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Total Conversions</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Conversion Rate</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>7. Push Engagement — By Campaign Type (One-time)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Campaign Type</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -4004,7 +4060,7 @@
     <col width="63" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -4017,7 +4073,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 01-10-2026 06:58:52</t>
+          <t>Last Updated: 02-10-2026 00:08:08</t>
         </is>
       </c>
     </row>
@@ -4100,16 +4156,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1575</v>
+        <v>91760</v>
       </c>
       <c r="E4" t="n">
-        <v>114224</v>
+        <v>29822</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>626</v>
       </c>
       <c r="G4" t="n">
-        <v>1.14</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4135,25 +4191,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Dormant_Users_7July26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2903</v>
+        <v>60628</v>
       </c>
       <c r="E5" t="n">
-        <v>2129</v>
+        <v>19517</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>798</v>
       </c>
       <c r="G5" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4179,7 +4235,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Dormant_Users_7July26</t>
+          <t>Activation_FirstPurchase_26Sep</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4188,16 +4244,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2602</v>
+        <v>36824</v>
       </c>
       <c r="E6" t="n">
-        <v>2052</v>
+        <v>14085</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>301</v>
       </c>
       <c r="G6" t="n">
-        <v>1.27</v>
+        <v>0.82</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4223,25 +4279,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1073</v>
+        <v>21512</v>
       </c>
       <c r="E7" t="n">
-        <v>746</v>
+        <v>13243</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4267,7 +4323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4276,16 +4332,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1033</v>
+        <v>18935</v>
       </c>
       <c r="E8" t="n">
-        <v>804</v>
+        <v>8017</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>346</v>
       </c>
       <c r="G8" t="n">
-        <v>4.26</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4311,25 +4367,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>935</v>
+        <v>18416</v>
       </c>
       <c r="E9" t="n">
-        <v>783</v>
+        <v>5063</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>368</v>
       </c>
       <c r="G9" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4355,7 +4411,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4364,16 +4420,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>806</v>
+        <v>15841</v>
       </c>
       <c r="E10" t="n">
-        <v>628</v>
+        <v>6220</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>1043</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>6.58</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4399,7 +4455,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4408,16 +4464,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>656</v>
+        <v>13001</v>
       </c>
       <c r="E11" t="n">
-        <v>520</v>
+        <v>5206</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>480</v>
       </c>
       <c r="G11" t="n">
-        <v>7.16</v>
+        <v>3.69</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4443,25 +4499,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Activation_FirstPurchase_26Sep</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>528</v>
+        <v>9975</v>
       </c>
       <c r="E12" t="n">
-        <v>397</v>
+        <v>5023</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -4506,7 +4562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Previous Month Report — Last Updated: 01-10-2026 06:59:27</t>
+          <t>Previous Month Report — Last Updated: 02-10-2026 00:08:45</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178957.49</v>
+        <v>178958.62</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0</v>
@@ -4577,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>178957.49</v>
+        <v>178958.62</v>
       </c>
     </row>
     <row r="6">
@@ -4643,7 +4699,7 @@
         <v>36539.07</v>
       </c>
       <c r="D8" t="n">
-        <v>393572.43</v>
+        <v>393573.56</v>
       </c>
       <c r="E8" t="n">
         <v>2.88</v>
@@ -4652,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>430114.38</v>
+        <v>430115.51</v>
       </c>
     </row>
     <row r="9"/>
@@ -4754,16 +4810,16 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>44763</v>
+        <v>44776</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>250689</v>
+        <v>251070</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1.97</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
@@ -5016,7 +5072,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>147453</v>
+        <v>147473</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>3055363</v>
@@ -5041,16 +5097,16 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>114224</v>
+        <v>29822</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>3406154</v>
+        <v>3406171</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>178957.49</v>
+        <v>178958.62</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>8</v>
@@ -5066,16 +5122,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>261677</v>
+        <v>177295</v>
       </c>
       <c r="C29" t="n">
-        <v>6461517</v>
+        <v>6461534</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>354097.05</v>
+        <v>354098.18</v>
       </c>
       <c r="F29" t="n">
         <v>16</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Team Wise Cost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Webengage_Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Prev_Month_Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Onboarding_report" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="retention_brand_report" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="KAM_Brand_Report" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Inapp_Subcat_Report" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Inapp_Sale_Report" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Campaign_Performance_Report" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Prev_Month_Report" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Webengage_Analysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Campaign_Performance_Report" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 00:04:33</t>
+          <t>Last Updated: 02-10-2026 07:17:22</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6125.21</v>
+        <v>6960.53</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1536.78</v>
+        <v>1543.88</v>
       </c>
       <c r="D5" t="n">
-        <v>7595.3</v>
+        <v>7656.33</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1536.78</v>
+        <v>1543.88</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>13720.51</v>
+        <v>14616.86</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>6125.21</v>
+        <v>6960.53</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1536.78</v>
+        <v>1543.88</v>
       </c>
       <c r="D11" t="n">
-        <v>7595.3</v>
+        <v>7656.33</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1536.78</v>
+        <v>1543.88</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>13720.51</v>
+        <v>14616.86</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -825,835 +825,592 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Last Updated: 01-10-2026 06:58:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Period: October 2026</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Previous Month Report — Last Updated: 02-10-2026 00:08:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. TEAM WISE COST — September 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>1. Channel Performance</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Superstar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Voice AI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>178958.62</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>178958.62</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>36539.07</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>214614.94</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>251154.01</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Push</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>WhatsApp (Wati+WE)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>In-app</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>36539.07</v>
+      </c>
+      <c r="D8" t="n">
+        <v>393573.56</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2. Team Engagement — Total</t>
-        </is>
+        <v>2.88</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>430115.51</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2. ONBOARDING — September 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
+          <t>KYC — September 2026</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
+          <t>CTR (%)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>First Home Page View</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Cost Per KYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2. Team Engagement — By Channel</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>44776</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>251070</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>10626.03</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
+      <c r="B16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Push</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
+          <t>First TXN — September 2026</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marketing Onboarding</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>In-app</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CTR (%)</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>First Purchase Success</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Amount Spent</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Cost Per TXN</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>50118</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>643786</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>25913.04</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Push</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>In-app</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>4. Journey Funnel — Classified</t>
+      <c r="B22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Journey Category</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Delivered / Impr</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3. RETENTION — September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CTR (App/Impr%)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>App Traffic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t># Orders</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5. WhatsApp Failure Analysis</t>
-        </is>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>147473</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>3055363</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>175139.56</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Failure Type</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>% of Total Failed</t>
-        </is>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>29822</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>3406171</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>178958.62</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DND Queue Drop</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Frequency Capping Queue Drop</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Personalization Error</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Channel Not Available</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Invalid WhatsApp Number</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Message Format Error</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Template Does Not Exist</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Throttling Error</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>User Blocked Messages</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>User Did Not Initiate Session</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>User Offline</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>WSP Configuration Error</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>WSP Quote Limit Reached</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Time Zone Elapsed</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Other Failures</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Total Failed</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>7. Push Engagement — Overall</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Total Impressions</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Total Clicks</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Total Dismisses</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Dismiss Rate</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Total Conversions</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Conversion Rate</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>7. Push Engagement — By Campaign Type (One-time)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Campaign Type</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Conversions</t>
-        </is>
+        <v>177295</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6461534</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>354098.18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1683,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 00:05:04</t>
+          <t>Last Updated: 02-10-2026 07:17:53</t>
         </is>
       </c>
     </row>
@@ -1791,13 +1548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18240</v>
+        <v>18306</v>
       </c>
       <c r="C8" t="n">
-        <v>31497</v>
+        <v>31630</v>
       </c>
       <c r="D8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="E8" t="n">
         <v>1.73</v>
@@ -1806,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1536.77</v>
+        <v>1543.88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2393,13 +2150,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18240</v>
+        <v>18306</v>
       </c>
       <c r="C32" t="n">
-        <v>31497</v>
+        <v>31630</v>
       </c>
       <c r="D32" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="E32" t="n">
         <v>1.73</v>
@@ -2408,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1536.77</v>
+        <v>1543.88</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2601,7 +2358,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 00:05:43</t>
+          <t>Last Updated: 02-10-2026 07:18:32</t>
         </is>
       </c>
     </row>
@@ -2656,16 +2413,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>37803</v>
+        <v>38018</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>110980</v>
+        <v>111619</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5839.27</v>
+        <v>5884.79</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2684,13 +2441,13 @@
         <v>29822</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>91760</v>
+        <v>105397</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6125.21</v>
+        <v>6960.53</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2706,16 +2463,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67625</v>
+        <v>67840</v>
       </c>
       <c r="C7" t="n">
-        <v>202740</v>
+        <v>217016</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>11964.48</v>
+        <v>12845.32</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2780,13 +2537,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79044</v>
+        <v>79490</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4553.25</v>
+        <v>4585.3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2807,13 +2564,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31936</v>
+        <v>32129</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1286.02</v>
+        <v>1299.49</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2878,13 +2635,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>86814</v>
+        <v>99505</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>5727.55</v>
+        <v>6489.79</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2905,13 +2662,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4946</v>
+        <v>5892</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>397.66</v>
+        <v>470.74</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2984,7 +2741,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37803</v>
+        <v>38018</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3011,7 +2768,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>37803</v>
+        <v>38018</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3412,7 +3169,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 00:06:20</t>
+          <t>Last Updated: 02-10-2026 07:19:08</t>
         </is>
       </c>
     </row>
@@ -3492,16 +3249,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14161</v>
+        <v>14275</v>
       </c>
       <c r="E5" t="n">
-        <v>31936</v>
+        <v>32129</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1286.02</v>
+        <v>1299.49</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3637,7 +3394,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 00:06:57</t>
+          <t>Last Updated: 02-10-2026 07:19:43</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3737,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 00:06:57</t>
+          <t>Last Updated: 02-10-2026 07:19:43</t>
         </is>
       </c>
     </row>
@@ -4048,6 +3805,848 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Last Updated: 02-10-2026 07:20:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Period: October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1. Channel Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Push</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>In-app</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2. Team Engagement — Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2. Team Engagement — By Channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Push</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Marketing Onboarding</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>In-app</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Push</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Marketing Retention</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>In-app</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>4. Journey Funnel — Classified</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Journey Category</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Delivered / Impr</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>5. WhatsApp Failure Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Failure Type</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>% of Total Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DND Queue Drop</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Frequency Capping Queue Drop</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Personalization Error</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Channel Not Available</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Invalid WhatsApp Number</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Message Format Error</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Template Does Not Exist</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Throttling Error</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>User Blocked Messages</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>User Did Not Initiate Session</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>User Offline</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WSP Configuration Error</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WSP Quote Limit Reached</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Time Zone Elapsed</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Other Failures</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Failed</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>7. Push Engagement — Overall</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Impressions</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Clicks</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Dismisses</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dismiss Rate</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Total Conversions</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Conversion Rate</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>7. Push Engagement — By Campaign Type (One-time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Campaign Type</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Conversions</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4073,10 +4672,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 00:08:08</t>
-        </is>
-      </c>
-    </row>
+          <t>Last Updated: 02-10-2026 07:20:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -4156,16 +4756,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91760</v>
+        <v>105397</v>
       </c>
       <c r="E4" t="n">
         <v>29822</v>
       </c>
       <c r="F4" t="n">
-        <v>626</v>
+        <v>737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4200,13 +4800,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60628</v>
+        <v>60988</v>
       </c>
       <c r="E5" t="n">
-        <v>19517</v>
+        <v>19625</v>
       </c>
       <c r="F5" t="n">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="G5" t="n">
         <v>1.32</v>
@@ -4244,16 +4844,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36824</v>
+        <v>36992</v>
       </c>
       <c r="E6" t="n">
-        <v>14085</v>
+        <v>14151</v>
       </c>
       <c r="F6" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="G6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4288,10 +4888,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21512</v>
+        <v>21569</v>
       </c>
       <c r="E7" t="n">
-        <v>13243</v>
+        <v>13266</v>
       </c>
       <c r="F7" t="n">
         <v>293</v>
@@ -4332,16 +4932,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18935</v>
+        <v>19056</v>
       </c>
       <c r="E8" t="n">
-        <v>8017</v>
+        <v>8115</v>
       </c>
       <c r="F8" t="n">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4376,16 +4976,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18416</v>
+        <v>18502</v>
       </c>
       <c r="E9" t="n">
-        <v>5063</v>
+        <v>5064</v>
       </c>
       <c r="F9" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4420,16 +5020,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15841</v>
+        <v>15988</v>
       </c>
       <c r="E10" t="n">
-        <v>6220</v>
+        <v>6234</v>
       </c>
       <c r="F10" t="n">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="G10" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4464,13 +5064,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13001</v>
+        <v>13073</v>
       </c>
       <c r="E11" t="n">
-        <v>5206</v>
+        <v>5214</v>
       </c>
       <c r="F11" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G11" t="n">
         <v>3.69</v>
@@ -4508,16 +5108,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9975</v>
+        <v>10058</v>
       </c>
       <c r="E12" t="n">
-        <v>5023</v>
+        <v>5040</v>
       </c>
       <c r="F12" t="n">
         <v>133</v>
       </c>
       <c r="G12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -4532,611 +5132,6 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="61" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Previous Month Report — Last Updated: 02-10-2026 00:08:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1. TEAM WISE COST — September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Superstar</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Marketing Onboarding</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Marketing Retention</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Voice AI</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>178958.62</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>178958.62</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>36539.07</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>214614.94</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>251154.01</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>WhatsApp (Wati+WE)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>36539.07</v>
-      </c>
-      <c r="D8" t="n">
-        <v>393573.56</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>430115.51</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2. ONBOARDING — September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KYC — September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>First Home Page View</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Cost Per KYC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>44776</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>251070</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>10626.03</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>First TXN — September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>First Purchase Success</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Amount Spent</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Cost Per TXN</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>50118</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>643786</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>25913.04</v>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3. RETENTION — September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CTR (App/Impr%)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>App Traffic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t># Orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>147473</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>3055363</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>175139.56</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>29822</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>3406171</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>178958.62</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>177295</v>
-      </c>
-      <c r="C29" t="n">
-        <v>6461534</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>354098.18</v>
-      </c>
-      <c r="F29" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:17:22</t>
+          <t>Last Updated: 02-10-2026 23:30:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 01-10-2026)</t>
+          <t>MTD (01-10-2026 → 02-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6960.53</v>
+        <v>12847.74</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1543.88</v>
+        <v>3070.52</v>
       </c>
       <c r="D5" t="n">
-        <v>7656.33</v>
+        <v>14773.69</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1543.88</v>
+        <v>3070.52</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>14616.86</v>
+        <v>27621.43</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>6960.53</v>
+        <v>6961.21</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1543.88</v>
+        <v>1548.04</v>
       </c>
       <c r="D11" t="n">
-        <v>7656.33</v>
+        <v>7732.93</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1543.88</v>
+        <v>1548.04</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>14616.86</v>
+        <v>14694.14</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5886.53</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1522.48</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>7040.76</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>1522.48</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>12927.29</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:17:53</t>
+          <t>Last Updated: 02-10-2026 23:31:23</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-01 | MTD-1: 2026-10-01 → 2026-09-30</t>
+          <t>MTD: 2026-10-01 → 2026-10-02 | MTD-1: 2026-10-01 → 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-01)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18306</v>
+        <v>26694</v>
       </c>
       <c r="C8" t="n">
-        <v>31630</v>
+        <v>63983</v>
       </c>
       <c r="D8" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="E8" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1543.88</v>
+        <v>3070.53</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-01)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-09-30)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -1850,26 +1850,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>18391</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>31740</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.73</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1548.04</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1916,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-09-30)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -2150,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18306</v>
+        <v>8303</v>
       </c>
       <c r="C32" t="n">
-        <v>31630</v>
+        <v>32243</v>
       </c>
       <c r="D32" t="n">
-        <v>1.55</v>
+        <v>0.12</v>
       </c>
       <c r="E32" t="n">
-        <v>1.73</v>
+        <v>0.67</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1543.88</v>
+        <v>1522.49</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2358,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:18:32</t>
+          <t>Last Updated: 02-10-2026 23:32:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-01)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -2413,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>38018</v>
+        <v>49909</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>111619</v>
+        <v>213533</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5884.79</v>
+        <v>11305.72</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2438,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>29822</v>
+        <v>45300</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>105397</v>
+        <v>213261</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6960.53</v>
+        <v>12847.74</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2463,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67840</v>
+        <v>95209</v>
       </c>
       <c r="C7" t="n">
-        <v>217016</v>
+        <v>426794</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>12845.32</v>
+        <v>24153.46</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2484,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-01)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -2537,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79490</v>
+        <v>153036</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4585.3</v>
+        <v>8868.75</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2564,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32129</v>
+        <v>60497</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1299.49</v>
+        <v>2436.97</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2582,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-01)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>99505</v>
+        <v>200670</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>6489.79</v>
+        <v>12020.44</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2662,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5892</v>
+        <v>12591</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>470.74</v>
+        <v>827.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2680,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-09-30)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -2741,18 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38018</v>
+        <v>49909</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>32413</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1313.4</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2768,18 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38018</v>
+        <v>49909</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>80158</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>4630.83</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2845,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29822</v>
+        <v>45300</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2872,18 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29822</v>
+        <v>45300</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>99505</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>6490.47</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2958,20 +2948,16 @@
       <c r="B49" t="n">
         <v>0</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C49" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E49" t="n">
+        <v>85.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2993,20 +2979,16 @@
       <c r="B50" t="n">
         <v>0</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C50" t="n">
+        <v>90.90000000000001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E50" t="n">
+        <v>91.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3113,20 +3095,16 @@
       <c r="B55" t="n">
         <v>0</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C55" t="n">
+        <v>101.7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E55" t="n">
+        <v>85.2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3169,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:19:08</t>
+          <t>Last Updated: 02-10-2026 23:32:39</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-01</t>
+          <t>MTD: 2026-10-01 → 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -3249,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14275</v>
+        <v>27081</v>
       </c>
       <c r="E5" t="n">
-        <v>32129</v>
+        <v>60497</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1299.49</v>
+        <v>2436.97</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3394,7 +3372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:19:43</t>
+          <t>Last Updated: 02-10-2026 23:33:14</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3715,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:19:43</t>
+          <t>Last Updated: 02-10-2026 23:33:14</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3803,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:20:19</t>
+          <t>Last Updated: 02-10-2026 23:33:49</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4650,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 07:20:55</t>
+          <t>Last Updated: 02-10-2026 23:34:25</t>
         </is>
       </c>
     </row>
@@ -4756,16 +4734,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>105397</v>
+        <v>213261</v>
       </c>
       <c r="E4" t="n">
-        <v>29822</v>
+        <v>45300</v>
       </c>
       <c r="F4" t="n">
-        <v>737</v>
+        <v>1552</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4800,16 +4778,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60988</v>
+        <v>117869</v>
       </c>
       <c r="E5" t="n">
-        <v>19625</v>
+        <v>25395</v>
       </c>
       <c r="F5" t="n">
-        <v>806</v>
+        <v>1616</v>
       </c>
       <c r="G5" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4844,16 +4822,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36992</v>
+        <v>71185</v>
       </c>
       <c r="E6" t="n">
-        <v>14151</v>
+        <v>19262</v>
       </c>
       <c r="F6" t="n">
-        <v>308</v>
+        <v>609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4888,16 +4866,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21569</v>
+        <v>42764</v>
       </c>
       <c r="E7" t="n">
-        <v>13266</v>
+        <v>19272</v>
       </c>
       <c r="F7" t="n">
-        <v>293</v>
+        <v>613</v>
       </c>
       <c r="G7" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4932,16 +4910,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19056</v>
+        <v>37218</v>
       </c>
       <c r="E8" t="n">
-        <v>8115</v>
+        <v>11580</v>
       </c>
       <c r="F8" t="n">
-        <v>353</v>
+        <v>681</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4976,16 +4954,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18502</v>
+        <v>35167</v>
       </c>
       <c r="E9" t="n">
-        <v>5064</v>
+        <v>6300</v>
       </c>
       <c r="F9" t="n">
-        <v>372</v>
+        <v>684</v>
       </c>
       <c r="G9" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5020,13 +4998,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15988</v>
+        <v>31800</v>
       </c>
       <c r="E10" t="n">
-        <v>6234</v>
+        <v>8428</v>
       </c>
       <c r="F10" t="n">
-        <v>1053</v>
+        <v>2095</v>
       </c>
       <c r="G10" t="n">
         <v>6.59</v>
@@ -5064,16 +5042,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13073</v>
+        <v>23279</v>
       </c>
       <c r="E11" t="n">
-        <v>5214</v>
+        <v>6647</v>
       </c>
       <c r="F11" t="n">
-        <v>483</v>
+        <v>921</v>
       </c>
       <c r="G11" t="n">
-        <v>3.69</v>
+        <v>3.96</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5108,16 +5086,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10058</v>
+        <v>21219</v>
       </c>
       <c r="E12" t="n">
-        <v>5040</v>
+        <v>7452</v>
       </c>
       <c r="F12" t="n">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="G12" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:30:52</t>
+          <t>Last Updated: 03-10-2026 06:48:36</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>12847.74</v>
+        <v>14238.22</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>3070.52</v>
+        <v>3095.72</v>
       </c>
       <c r="D5" t="n">
-        <v>14773.69</v>
+        <v>14903.78</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3070.52</v>
+        <v>3095.72</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>27621.43</v>
+        <v>29142</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5886.53</v>
+        <v>7277.01</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1522.48</v>
+        <v>1547.68</v>
       </c>
       <c r="D17" t="n">
-        <v>7040.76</v>
+        <v>7170.85</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1522.48</v>
+        <v>1547.68</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12927.29</v>
+        <v>14447.86</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:31:23</t>
+          <t>Last Updated: 03-10-2026 06:49:07</t>
         </is>
       </c>
     </row>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26694</v>
+        <v>26791</v>
       </c>
       <c r="C8" t="n">
-        <v>63983</v>
+        <v>64353</v>
       </c>
       <c r="D8" t="n">
         <v>1.67</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3070.53</v>
+        <v>3095.72</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8303</v>
+        <v>8400</v>
       </c>
       <c r="C32" t="n">
-        <v>32243</v>
+        <v>32613</v>
       </c>
       <c r="D32" t="n">
         <v>0.12</v>
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1522.49</v>
+        <v>1547.68</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:32:03</t>
+          <t>Last Updated: 03-10-2026 06:49:46</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>49909</v>
+        <v>50154</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>213533</v>
+        <v>215129</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>11305.72</v>
+        <v>11402.3</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>45300</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>213261</v>
+        <v>240708</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12847.74</v>
+        <v>14238.22</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95209</v>
+        <v>95454</v>
       </c>
       <c r="C7" t="n">
-        <v>426794</v>
+        <v>455837</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>24153.46</v>
+        <v>25640.52</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>153036</v>
+        <v>154074</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8868.75</v>
+        <v>8941.23</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>60497</v>
+        <v>61055</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2436.97</v>
+        <v>2461.07</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>200670</v>
+        <v>225926</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>12020.44</v>
+        <v>13303.64</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12591</v>
+        <v>14782</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>827.3</v>
+        <v>934.58</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>49909</v>
+        <v>50154</v>
       </c>
       <c r="C38" t="n">
         <v>32413</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>49909</v>
+        <v>50154</v>
       </c>
       <c r="C39" t="n">
         <v>80158</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>86.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>85.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>91.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>101.7</v>
+        <v>127</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>85.2</v>
+        <v>105</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:32:39</t>
+          <t>Last Updated: 03-10-2026 06:50:23</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27081</v>
+        <v>27349</v>
       </c>
       <c r="E5" t="n">
-        <v>60497</v>
+        <v>61055</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2436.97</v>
+        <v>2461.07</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3372,7 +3372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:33:14</t>
+          <t>Last Updated: 03-10-2026 06:50:58</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:33:14</t>
+          <t>Last Updated: 03-10-2026 06:50:58</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:33:49</t>
+          <t>Last Updated: 03-10-2026 06:51:32</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 02-10-2026 23:34:25</t>
+          <t>Last Updated: 03-10-2026 06:52:08</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>213261</v>
+        <v>240708</v>
       </c>
       <c r="E4" t="n">
         <v>45300</v>
       </c>
       <c r="F4" t="n">
-        <v>1552</v>
+        <v>1743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>117869</v>
+        <v>118705</v>
       </c>
       <c r="E5" t="n">
-        <v>25395</v>
+        <v>25448</v>
       </c>
       <c r="F5" t="n">
-        <v>1616</v>
+        <v>1627</v>
       </c>
       <c r="G5" t="n">
         <v>1.37</v>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71185</v>
+        <v>71612</v>
       </c>
       <c r="E6" t="n">
-        <v>19262</v>
+        <v>19326</v>
       </c>
       <c r="F6" t="n">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="G6" t="n">
         <v>0.86</v>
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42764</v>
+        <v>42866</v>
       </c>
       <c r="E7" t="n">
-        <v>19272</v>
+        <v>19288</v>
       </c>
       <c r="F7" t="n">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G7" t="n">
         <v>1.43</v>
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37218</v>
+        <v>37555</v>
       </c>
       <c r="E8" t="n">
-        <v>11580</v>
+        <v>11722</v>
       </c>
       <c r="F8" t="n">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4954,16 +4954,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35167</v>
+        <v>35369</v>
       </c>
       <c r="E9" t="n">
-        <v>6300</v>
+        <v>6306</v>
       </c>
       <c r="F9" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="G9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4998,16 +4998,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31800</v>
+        <v>32039</v>
       </c>
       <c r="E10" t="n">
-        <v>8428</v>
+        <v>8476</v>
       </c>
       <c r="F10" t="n">
-        <v>2095</v>
+        <v>2113</v>
       </c>
       <c r="G10" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5042,16 +5042,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23279</v>
+        <v>23500</v>
       </c>
       <c r="E11" t="n">
-        <v>6647</v>
+        <v>6678</v>
       </c>
       <c r="F11" t="n">
-        <v>921</v>
+        <v>934</v>
       </c>
       <c r="G11" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5086,16 +5086,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21219</v>
+        <v>21485</v>
       </c>
       <c r="E12" t="n">
-        <v>7452</v>
+        <v>7503</v>
       </c>
       <c r="F12" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:48:36</t>
+          <t>Last Updated: 03-10-2026 22:08:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 02-10-2026)</t>
+          <t>MTD (01-10-2026 → 03-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>14238.22</v>
+        <v>19596.89</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>3095.72</v>
+        <v>5765.14</v>
       </c>
       <c r="D5" t="n">
-        <v>14903.78</v>
+        <v>21740.04</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3095.72</v>
+        <v>5765.14</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>29142</v>
+        <v>41336.93</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 01-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 02-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>6961.21</v>
+        <v>14241.15</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1548.04</v>
+        <v>4122.85</v>
       </c>
       <c r="D11" t="n">
-        <v>7732.93</v>
+        <v>14967.34</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1548.04</v>
+        <v>4122.85</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>14694.14</v>
+        <v>29208.49</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7277.01</v>
+        <v>5355.74</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1547.68</v>
+        <v>1642.29</v>
       </c>
       <c r="D17" t="n">
-        <v>7170.85</v>
+        <v>6772.7</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1547.68</v>
+        <v>1642.29</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14447.86</v>
+        <v>12128.44</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:49:07</t>
+          <t>Last Updated: 03-10-2026 22:08:49</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-02 | MTD-1: 2026-10-01 → 2026-10-01</t>
+          <t>MTD: 2026-10-01 → 2026-10-03 | MTD-1: 2026-10-01 → 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-02)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26791</v>
+        <v>10043</v>
       </c>
       <c r="C8" t="n">
-        <v>64353</v>
+        <v>36340</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4</v>
+        <v>3.62</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3095.72</v>
+        <v>3890.07</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-02)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-01)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18391</v>
+        <v>7519</v>
       </c>
       <c r="C20" t="n">
-        <v>31740</v>
+        <v>21604</v>
       </c>
       <c r="D20" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="E20" t="n">
-        <v>1.73</v>
+        <v>2.87</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1548.04</v>
+        <v>3100.64</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-01)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8400</v>
+        <v>2524</v>
       </c>
       <c r="C32" t="n">
-        <v>32613</v>
+        <v>14736</v>
       </c>
       <c r="D32" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E32" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1547.68</v>
+        <v>789.4299999999999</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2343,7 +2343,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="63" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:49:46</t>
+          <t>Last Updated: 03-10-2026 22:09:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-02)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>50154</v>
+        <v>58395</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>215129</v>
+        <v>304940</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>11402.3</v>
+        <v>16175.64</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>45300</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>240708</v>
+        <v>341318</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>14238.22</v>
+        <v>19596.89</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95454</v>
+        <v>103695</v>
       </c>
       <c r="C7" t="n">
-        <v>455837</v>
+        <v>646258</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>25640.52</v>
+        <v>35772.53</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-02)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>154074</v>
+        <v>215308</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8941.23</v>
+        <v>12504.26</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>61055</v>
+        <v>89632</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2461.07</v>
+        <v>3671.38</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-02)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>225926</v>
+        <v>319876</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>13303.64</v>
+        <v>18305.76</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14782</v>
+        <v>21442</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>934.58</v>
+        <v>1291.13</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-01)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>50154</v>
+        <v>58395</v>
       </c>
       <c r="C38" t="n">
-        <v>32413</v>
+        <v>61280</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1313.4</v>
+        <v>2470.73</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>50154</v>
+        <v>58395</v>
       </c>
       <c r="C39" t="n">
-        <v>80158</v>
+        <v>154662</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>4630.83</v>
+        <v>8981.620000000001</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>45300</v>
       </c>
       <c r="C44" t="n">
-        <v>99505</v>
+        <v>225921</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>6490.47</v>
+        <v>13306.57</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>88.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>87.40000000000001</v>
+        <v>48.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>92.2</v>
+        <v>39.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>93.09999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>127</v>
+        <v>41.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105</v>
+        <v>37.6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:50:23</t>
+          <t>Last Updated: 03-10-2026 22:10:06</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-02</t>
+          <t>MTD: 2026-10-01 → 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27349</v>
+        <v>41244</v>
       </c>
       <c r="E5" t="n">
-        <v>61055</v>
+        <v>89632</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2461.07</v>
+        <v>3671.38</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:50:58</t>
+          <t>Last Updated: 03-10-2026 22:10:41</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:50:58</t>
+          <t>Last Updated: 03-10-2026 22:10:41</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:51:32</t>
+          <t>Last Updated: 03-10-2026 22:11:15</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4650,7 +4650,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 06:52:08</t>
+          <t>Last Updated: 03-10-2026 22:11:53</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>240708</v>
+        <v>341318</v>
       </c>
       <c r="E4" t="n">
         <v>45300</v>
       </c>
       <c r="F4" t="n">
-        <v>1743</v>
+        <v>2355</v>
       </c>
       <c r="G4" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4778,16 +4778,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>118705</v>
+        <v>165929</v>
       </c>
       <c r="E5" t="n">
-        <v>25448</v>
+        <v>28681</v>
       </c>
       <c r="F5" t="n">
-        <v>1627</v>
+        <v>2345</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71612</v>
+        <v>97260</v>
       </c>
       <c r="E6" t="n">
-        <v>19326</v>
+        <v>22336</v>
       </c>
       <c r="F6" t="n">
-        <v>618</v>
+        <v>905</v>
       </c>
       <c r="G6" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4857,25 +4857,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42866</v>
+        <v>54117</v>
       </c>
       <c r="E7" t="n">
-        <v>19288</v>
+        <v>14439</v>
       </c>
       <c r="F7" t="n">
-        <v>615</v>
+        <v>985</v>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37555</v>
+        <v>49379</v>
       </c>
       <c r="E8" t="n">
-        <v>11722</v>
+        <v>7059</v>
       </c>
       <c r="F8" t="n">
-        <v>692</v>
+        <v>984</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4954,16 +4954,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35369</v>
+        <v>46982</v>
       </c>
       <c r="E9" t="n">
-        <v>6306</v>
+        <v>9774</v>
       </c>
       <c r="F9" t="n">
-        <v>687</v>
+        <v>3051</v>
       </c>
       <c r="G9" t="n">
-        <v>1.94</v>
+        <v>6.49</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4989,25 +4989,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32039</v>
+        <v>45483</v>
       </c>
       <c r="E10" t="n">
-        <v>8476</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2113</v>
+        <v>646</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>1.42</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5033,25 +5033,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>Onboarding_LoginSuccess_3Oct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23500</v>
+        <v>36667</v>
       </c>
       <c r="E11" t="n">
-        <v>6678</v>
+        <v>22889</v>
       </c>
       <c r="F11" t="n">
-        <v>934</v>
+        <v>537</v>
       </c>
       <c r="G11" t="n">
-        <v>3.97</v>
+        <v>1.46</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5086,16 +5086,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21485</v>
+        <v>36247</v>
       </c>
       <c r="E12" t="n">
-        <v>7503</v>
+        <v>10043</v>
       </c>
       <c r="F12" t="n">
-        <v>301</v>
+        <v>481</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5110,6 +5110,94 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Retention_ActivePurchasers_26Sep</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>35515</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8238</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1458</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4348</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2198</v>
+      </c>
+      <c r="F14" t="n">
+        <v>171</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:08:19</t>
+          <t>Last Updated: 04-10-2026 07:18:19</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>19596.89</v>
+        <v>21276.36</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5765.14</v>
+        <v>5901.52</v>
       </c>
       <c r="D5" t="n">
-        <v>21740.04</v>
+        <v>21963.82</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5765.14</v>
+        <v>5901.52</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>41336.93</v>
+        <v>43240.18</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5355.74</v>
+        <v>7035.21</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1642.29</v>
+        <v>1778.67</v>
       </c>
       <c r="D17" t="n">
-        <v>6772.7</v>
+        <v>6996.48</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1642.29</v>
+        <v>1778.67</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12128.44</v>
+        <v>14031.69</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:08:49</t>
+          <t>Last Updated: 04-10-2026 07:18:49</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10043</v>
+        <v>10437</v>
       </c>
       <c r="C8" t="n">
-        <v>36340</v>
+        <v>38096</v>
       </c>
       <c r="D8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="E8" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3890.07</v>
+        <v>3966.64</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>7519</v>
       </c>
       <c r="C20" t="n">
-        <v>21604</v>
+        <v>21605</v>
       </c>
       <c r="D20" t="n">
         <v>1.74</v>
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2524</v>
+        <v>2918</v>
       </c>
       <c r="C32" t="n">
-        <v>14736</v>
+        <v>16491</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="E32" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>789.4299999999999</v>
+        <v>866</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:09:29</t>
+          <t>Last Updated: 04-10-2026 07:19:29</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>58395</v>
+        <v>58908</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>304940</v>
+        <v>308455</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>16175.64</v>
+        <v>16301.19</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45300</v>
+        <v>54883</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>341318</v>
+        <v>376050</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>19596.89</v>
+        <v>21276.36</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103695</v>
+        <v>113791</v>
       </c>
       <c r="C7" t="n">
-        <v>646258</v>
+        <v>684505</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>35772.53</v>
+        <v>37577.55</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>215308</v>
+        <v>216680</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>12504.26</v>
+        <v>12551.55</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>89632</v>
+        <v>91775</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3671.38</v>
+        <v>3749.64</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>319876</v>
+        <v>351223</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>18305.76</v>
+        <v>19832.23</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21442</v>
+        <v>24827</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1291.13</v>
+        <v>1444.13</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>58395</v>
+        <v>58908</v>
       </c>
       <c r="C38" t="n">
         <v>61280</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>58395</v>
+        <v>58908</v>
       </c>
       <c r="C39" t="n">
         <v>154662</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>45300</v>
+        <v>54883</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>45300</v>
+        <v>54883</v>
       </c>
       <c r="C44" t="n">
         <v>225921</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>46.3</v>
+        <v>49.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>48.6</v>
+        <v>51.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>39.2</v>
+        <v>40.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>39.2</v>
+        <v>39.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>41.6</v>
+        <v>55.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>37.6</v>
+        <v>49</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:10:06</t>
+          <t>Last Updated: 04-10-2026 07:20:06</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41244</v>
+        <v>42043</v>
       </c>
       <c r="E5" t="n">
-        <v>89632</v>
+        <v>91775</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3671.38</v>
+        <v>3749.64</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3372,7 +3372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:10:41</t>
+          <t>Last Updated: 04-10-2026 07:20:41</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:10:41</t>
+          <t>Last Updated: 04-10-2026 07:20:41</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:11:15</t>
+          <t>Last Updated: 04-10-2026 07:21:16</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 03-10-2026 22:11:53</t>
+          <t>Last Updated: 04-10-2026 07:21:51</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>341318</v>
+        <v>376050</v>
       </c>
       <c r="E4" t="n">
-        <v>45300</v>
+        <v>54883</v>
       </c>
       <c r="F4" t="n">
-        <v>2355</v>
+        <v>2543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4778,16 +4778,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>165929</v>
+        <v>166969</v>
       </c>
       <c r="E5" t="n">
-        <v>28681</v>
+        <v>28766</v>
       </c>
       <c r="F5" t="n">
-        <v>2345</v>
+        <v>2367</v>
       </c>
       <c r="G5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>97260</v>
+        <v>98525</v>
       </c>
       <c r="E6" t="n">
-        <v>22336</v>
+        <v>22513</v>
       </c>
       <c r="F6" t="n">
-        <v>905</v>
+        <v>921</v>
       </c>
       <c r="G6" t="n">
         <v>0.93</v>
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54117</v>
+        <v>55673</v>
       </c>
       <c r="E7" t="n">
-        <v>14439</v>
+        <v>14772</v>
       </c>
       <c r="F7" t="n">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="G7" t="n">
         <v>1.82</v>
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49379</v>
+        <v>49711</v>
       </c>
       <c r="E8" t="n">
-        <v>7059</v>
+        <v>7076</v>
       </c>
       <c r="F8" t="n">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4954,16 +4954,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>46982</v>
+        <v>47903</v>
       </c>
       <c r="E9" t="n">
-        <v>9774</v>
+        <v>9827</v>
       </c>
       <c r="F9" t="n">
-        <v>3051</v>
+        <v>3116</v>
       </c>
       <c r="G9" t="n">
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Onboarding_LoginSuccess_3Oct</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5042,16 +5042,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36667</v>
+        <v>38093</v>
       </c>
       <c r="E11" t="n">
-        <v>22889</v>
+        <v>10437</v>
       </c>
       <c r="F11" t="n">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="G11" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>Onboarding_LoginSuccess_3Oct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5086,16 +5086,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36247</v>
+        <v>37606</v>
       </c>
       <c r="E12" t="n">
-        <v>10043</v>
+        <v>23480</v>
       </c>
       <c r="F12" t="n">
-        <v>481</v>
+        <v>568</v>
       </c>
       <c r="G12" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5130,16 +5130,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35515</v>
+        <v>36102</v>
       </c>
       <c r="E13" t="n">
-        <v>8238</v>
+        <v>8294</v>
       </c>
       <c r="F13" t="n">
-        <v>1458</v>
+        <v>1495</v>
       </c>
       <c r="G13" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4348</v>
+        <v>4485</v>
       </c>
       <c r="E14" t="n">
-        <v>2198</v>
+        <v>2235</v>
       </c>
       <c r="F14" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G14" t="n">
-        <v>3.93</v>
+        <v>4.06</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:18:19</t>
+          <t>Last Updated: 04-10-2026 22:28:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 03-10-2026)</t>
+          <t>MTD (01-10-2026 → 04-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>21276.36</v>
+        <v>25997.59</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5901.52</v>
+        <v>7071.08</v>
       </c>
       <c r="D5" t="n">
-        <v>21963.82</v>
+        <v>31646.52</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5901.52</v>
+        <v>7071.08</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>43240.18</v>
+        <v>57644.11</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 02-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 03-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>14241.15</v>
+        <v>21512.07</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4122.85</v>
+        <v>5908.14</v>
       </c>
       <c r="D11" t="n">
-        <v>14967.34</v>
+        <v>21964.67</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>4122.85</v>
+        <v>5908.14</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>29208.49</v>
+        <v>43476.74</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7035.21</v>
+        <v>4485.52</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1778.67</v>
+        <v>1162.94</v>
       </c>
       <c r="D17" t="n">
-        <v>6996.48</v>
+        <v>9681.85</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1778.67</v>
+        <v>1162.94</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14031.69</v>
+        <v>14167.37</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:18:49</t>
+          <t>Last Updated: 04-10-2026 22:29:03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-03 | MTD-1: 2026-10-01 → 2026-10-02</t>
+          <t>MTD: 2026-10-01 → 2026-10-04 | MTD-1: 2026-10-01 → 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-03)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10437</v>
+        <v>11741</v>
       </c>
       <c r="C8" t="n">
-        <v>38096</v>
+        <v>52468</v>
       </c>
       <c r="D8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="E8" t="n">
-        <v>3.65</v>
+        <v>4.47</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3966.64</v>
+        <v>4592.87</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-03)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-02)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7519</v>
+        <v>10470</v>
       </c>
       <c r="C20" t="n">
-        <v>21605</v>
+        <v>38267</v>
       </c>
       <c r="D20" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="E20" t="n">
-        <v>2.87</v>
+        <v>3.65</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3100.64</v>
+        <v>3971.22</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-02)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2918</v>
+        <v>1271</v>
       </c>
       <c r="C32" t="n">
-        <v>16491</v>
+        <v>14201</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="E32" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>866</v>
+        <v>621.65</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:19:29</t>
+          <t>Last Updated: 04-10-2026 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-03)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>58908</v>
+        <v>67473</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>308455</v>
+        <v>430779</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>16301.19</v>
+        <v>23153.49</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>54883</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>376050</v>
+        <v>468780</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>21276.36</v>
+        <v>25997.59</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113791</v>
+        <v>122356</v>
       </c>
       <c r="C7" t="n">
-        <v>684505</v>
+        <v>899559</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>37577.55</v>
+        <v>49151.08</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-03)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>216680</v>
+        <v>302799</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>12551.55</v>
+        <v>17850.71</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>91775</v>
+        <v>127980</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3749.64</v>
+        <v>5302.78</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-03)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>351223</v>
+        <v>435023</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>19832.23</v>
+        <v>24121.58</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24827</v>
+        <v>33757</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1444.13</v>
+        <v>1876.01</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-02)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-03)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>58908</v>
+        <v>67473</v>
       </c>
       <c r="C38" t="n">
-        <v>61280</v>
+        <v>91998</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2470.73</v>
+        <v>3749.64</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>58908</v>
+        <v>67473</v>
       </c>
       <c r="C39" t="n">
-        <v>154662</v>
+        <v>217045</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>8981.620000000001</v>
+        <v>12551.55</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>54883</v>
       </c>
       <c r="C44" t="n">
-        <v>225921</v>
+        <v>354947</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>13306.57</v>
+        <v>20042.48</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>49.8</v>
+        <v>39.1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>51.8</v>
+        <v>41.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>39.7</v>
+        <v>42.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>55.5</v>
+        <v>22.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>49</v>
+        <v>20.4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:20:06</t>
+          <t>Last Updated: 04-10-2026 22:30:20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-03</t>
+          <t>MTD: 2026-10-01 → 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42043</v>
+        <v>58706</v>
       </c>
       <c r="E5" t="n">
-        <v>91775</v>
+        <v>127980</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3749.64</v>
+        <v>5302.78</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:20:41</t>
+          <t>Last Updated: 04-10-2026 22:30:55</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:20:41</t>
+          <t>Last Updated: 04-10-2026 22:30:55</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:21:16</t>
+          <t>Last Updated: 04-10-2026 22:31:31</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 07:21:51</t>
+          <t>Last Updated: 04-10-2026 22:32:07</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>376050</v>
+        <v>468780</v>
       </c>
       <c r="E4" t="n">
         <v>54883</v>
       </c>
       <c r="F4" t="n">
-        <v>2543</v>
+        <v>3154</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4778,16 +4778,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>166969</v>
+        <v>234130</v>
       </c>
       <c r="E5" t="n">
-        <v>28766</v>
+        <v>32393</v>
       </c>
       <c r="F5" t="n">
-        <v>2367</v>
+        <v>3270</v>
       </c>
       <c r="G5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>98525</v>
+        <v>137091</v>
       </c>
       <c r="E6" t="n">
-        <v>22513</v>
+        <v>27056</v>
       </c>
       <c r="F6" t="n">
-        <v>921</v>
+        <v>1283</v>
       </c>
       <c r="G6" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4866,16 +4866,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55673</v>
+        <v>77104</v>
       </c>
       <c r="E7" t="n">
-        <v>14772</v>
+        <v>17060</v>
       </c>
       <c r="F7" t="n">
-        <v>1014</v>
+        <v>1375</v>
       </c>
       <c r="G7" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49711</v>
+        <v>68669</v>
       </c>
       <c r="E8" t="n">
-        <v>7076</v>
+        <v>8141</v>
       </c>
       <c r="F8" t="n">
-        <v>992</v>
+        <v>1387</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4954,13 +4954,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47903</v>
+        <v>58867</v>
       </c>
       <c r="E9" t="n">
-        <v>9827</v>
+        <v>10596</v>
       </c>
       <c r="F9" t="n">
-        <v>3116</v>
+        <v>3824</v>
       </c>
       <c r="G9" t="n">
         <v>6.5</v>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4998,16 +4998,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45483</v>
+        <v>52411</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>11741</v>
       </c>
       <c r="F10" t="n">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="G10" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5033,25 +5033,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38093</v>
+        <v>50876</v>
       </c>
       <c r="E11" t="n">
-        <v>10437</v>
+        <v>9879</v>
       </c>
       <c r="F11" t="n">
-        <v>509</v>
+        <v>2087</v>
       </c>
       <c r="G11" t="n">
-        <v>1.34</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5086,16 +5086,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>37606</v>
+        <v>48707</v>
       </c>
       <c r="E12" t="n">
-        <v>23480</v>
+        <v>28517</v>
       </c>
       <c r="F12" t="n">
-        <v>568</v>
+        <v>938</v>
       </c>
       <c r="G12" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5121,25 +5121,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36102</v>
+        <v>45483</v>
       </c>
       <c r="E13" t="n">
-        <v>8294</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1495</v>
+        <v>646</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14</v>
+        <v>1.42</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4485</v>
+        <v>19434</v>
       </c>
       <c r="E14" t="n">
-        <v>2235</v>
+        <v>5522</v>
       </c>
       <c r="F14" t="n">
-        <v>182</v>
+        <v>1113</v>
       </c>
       <c r="G14" t="n">
-        <v>4.06</v>
+        <v>5.73</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:28:32</t>
+          <t>Last Updated: 05-10-2026 06:37:12</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>25997.59</v>
+        <v>28350.39</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>7071.08</v>
+        <v>7137.61</v>
       </c>
       <c r="D5" t="n">
-        <v>31646.52</v>
+        <v>32106.92</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7071.08</v>
+        <v>7137.61</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>57644.11</v>
+        <v>60457.31</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4485.52</v>
+        <v>6838.32</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1162.94</v>
+        <v>1229.47</v>
       </c>
       <c r="D17" t="n">
-        <v>9681.85</v>
+        <v>10142.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1162.94</v>
+        <v>1229.47</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14167.37</v>
+        <v>16980.57</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:29:03</t>
+          <t>Last Updated: 05-10-2026 06:37:43</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11741</v>
+        <v>11835</v>
       </c>
       <c r="C8" t="n">
-        <v>52468</v>
+        <v>53389</v>
       </c>
       <c r="D8" t="n">
         <v>1.6</v>
       </c>
       <c r="E8" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4592.87</v>
+        <v>4636.67</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1853,13 +1853,13 @@
         <v>10470</v>
       </c>
       <c r="C20" t="n">
-        <v>38267</v>
+        <v>38269</v>
       </c>
       <c r="D20" t="n">
         <v>1.64</v>
       </c>
       <c r="E20" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1271</v>
+        <v>1365</v>
       </c>
       <c r="C32" t="n">
-        <v>14201</v>
+        <v>15120</v>
       </c>
       <c r="D32" t="n">
         <v>-0.04</v>
       </c>
       <c r="E32" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>621.65</v>
+        <v>665.45</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:29:43</t>
+          <t>Last Updated: 05-10-2026 06:38:21</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>67473</v>
+        <v>68019</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>430779</v>
+        <v>435754</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>23153.49</v>
+        <v>23428.69</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>54883</v>
+        <v>63358</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>468780</v>
+        <v>522183</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>25997.59</v>
+        <v>28350.39</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122356</v>
+        <v>131377</v>
       </c>
       <c r="C7" t="n">
-        <v>899559</v>
+        <v>957937</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>49151.08</v>
+        <v>51779.08</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>302799</v>
+        <v>305670</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>17850.71</v>
+        <v>18015.65</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>127980</v>
+        <v>130084</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5302.78</v>
+        <v>5413.04</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>435023</v>
+        <v>484099</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>24121.58</v>
+        <v>26267.48</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33757</v>
+        <v>38084</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1876.01</v>
+        <v>2082.91</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>67473</v>
+        <v>68019</v>
       </c>
       <c r="C38" t="n">
         <v>91998</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>67473</v>
+        <v>68019</v>
       </c>
       <c r="C39" t="n">
         <v>217045</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54883</v>
+        <v>63358</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>54883</v>
+        <v>63358</v>
       </c>
       <c r="C44" t="n">
         <v>354947</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>39.1</v>
+        <v>41.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>41.4</v>
+        <v>44.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>39.5</v>
+        <v>40.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>42.2</v>
+        <v>43.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>22.6</v>
+        <v>36.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>20.4</v>
+        <v>31.1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:30:20</t>
+          <t>Last Updated: 05-10-2026 06:38:57</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>58706</v>
+        <v>59495</v>
       </c>
       <c r="E5" t="n">
-        <v>127980</v>
+        <v>130084</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5302.78</v>
+        <v>5413.04</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3372,7 +3372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:30:55</t>
+          <t>Last Updated: 05-10-2026 06:39:31</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:30:55</t>
+          <t>Last Updated: 05-10-2026 06:39:31</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:31:31</t>
+          <t>Last Updated: 05-10-2026 06:40:06</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 04-10-2026 22:32:07</t>
+          <t>Last Updated: 05-10-2026 06:40:43</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>468780</v>
+        <v>522183</v>
       </c>
       <c r="E4" t="n">
-        <v>54883</v>
+        <v>63358</v>
       </c>
       <c r="F4" t="n">
-        <v>3154</v>
+        <v>3565</v>
       </c>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>234130</v>
+        <v>236597</v>
       </c>
       <c r="E5" t="n">
-        <v>32393</v>
+        <v>32568</v>
       </c>
       <c r="F5" t="n">
-        <v>3270</v>
+        <v>3314</v>
       </c>
       <c r="G5" t="n">
         <v>1.4</v>
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>137091</v>
+        <v>138730</v>
       </c>
       <c r="E6" t="n">
-        <v>27056</v>
+        <v>27417</v>
       </c>
       <c r="F6" t="n">
-        <v>1283</v>
+        <v>1313</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4866,16 +4866,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77104</v>
+        <v>78249</v>
       </c>
       <c r="E7" t="n">
-        <v>17060</v>
+        <v>17261</v>
       </c>
       <c r="F7" t="n">
-        <v>1375</v>
+        <v>1404</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68669</v>
+        <v>69073</v>
       </c>
       <c r="E8" t="n">
-        <v>8141</v>
+        <v>8225</v>
       </c>
       <c r="F8" t="n">
-        <v>1387</v>
+        <v>1406</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4954,16 +4954,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58867</v>
+        <v>59757</v>
       </c>
       <c r="E9" t="n">
-        <v>10596</v>
+        <v>10681</v>
       </c>
       <c r="F9" t="n">
-        <v>3824</v>
+        <v>3889</v>
       </c>
       <c r="G9" t="n">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4998,16 +4998,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52411</v>
+        <v>53383</v>
       </c>
       <c r="E10" t="n">
-        <v>11741</v>
+        <v>11835</v>
       </c>
       <c r="F10" t="n">
-        <v>675</v>
+        <v>698</v>
       </c>
       <c r="G10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5042,16 +5042,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>50876</v>
+        <v>51835</v>
       </c>
       <c r="E11" t="n">
-        <v>9879</v>
+        <v>9965</v>
       </c>
       <c r="F11" t="n">
-        <v>2087</v>
+        <v>2140</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5086,16 +5086,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48707</v>
+        <v>49230</v>
       </c>
       <c r="E12" t="n">
-        <v>28517</v>
+        <v>28998</v>
       </c>
       <c r="F12" t="n">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="G12" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19434</v>
+        <v>20154</v>
       </c>
       <c r="E14" t="n">
-        <v>5522</v>
+        <v>5631</v>
       </c>
       <c r="F14" t="n">
-        <v>1113</v>
+        <v>1172</v>
       </c>
       <c r="G14" t="n">
-        <v>5.73</v>
+        <v>5.82</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:37:12</t>
+          <t>Last Updated: 06-10-2026 07:55:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 04-10-2026)</t>
+          <t>MTD (01-10-2026 → 05-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>28350.39</v>
+        <v>35434.58</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>7137.61</v>
+        <v>8180.73</v>
       </c>
       <c r="D5" t="n">
-        <v>32106.92</v>
+        <v>40669.45</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7137.61</v>
+        <v>8180.73</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>60457.31</v>
+        <v>76104.03</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 03-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 04-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>21512.07</v>
+        <v>28354.87</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5908.14</v>
+        <v>7137.61</v>
       </c>
       <c r="D11" t="n">
-        <v>21964.67</v>
+        <v>32106.92</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5908.14</v>
+        <v>7137.61</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>43476.74</v>
+        <v>60461.79</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6838.32</v>
+        <v>7079.71</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1229.47</v>
+        <v>1043.12</v>
       </c>
       <c r="D17" t="n">
-        <v>10142.25</v>
+        <v>8562.530000000001</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1229.47</v>
+        <v>1043.12</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>16980.57</v>
+        <v>15642.24</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:37:43</t>
+          <t>Last Updated: 06-10-2026 07:55:34</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-04 | MTD-1: 2026-10-01 → 2026-10-03</t>
+          <t>MTD: 2026-10-01 → 2026-10-05 | MTD-1: 2026-10-01 → 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-04)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11835</v>
+        <v>12903</v>
       </c>
       <c r="C8" t="n">
-        <v>53389</v>
+        <v>66919</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="E8" t="n">
-        <v>4.51</v>
+        <v>5.19</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4636.67</v>
+        <v>5311.25</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-04)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-03)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10470</v>
+        <v>11878</v>
       </c>
       <c r="C20" t="n">
-        <v>38269</v>
+        <v>53597</v>
       </c>
       <c r="D20" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="E20" t="n">
-        <v>3.66</v>
+        <v>4.51</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3971.22</v>
+        <v>4636.67</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-03)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1365</v>
+        <v>1025</v>
       </c>
       <c r="C32" t="n">
-        <v>15120</v>
+        <v>13322</v>
       </c>
       <c r="D32" t="n">
         <v>-0.04</v>
       </c>
       <c r="E32" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>665.45</v>
+        <v>674.58</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:38:21</t>
+          <t>Last Updated: 06-10-2026 07:56:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-04)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68019</v>
+        <v>74166</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>435754</v>
+        <v>545772</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>23428.69</v>
+        <v>29468.68</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>63358</v>
+        <v>71375</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>522183</v>
+        <v>723517</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>28350.39</v>
+        <v>35434.58</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>131377</v>
+        <v>145541</v>
       </c>
       <c r="C7" t="n">
-        <v>957937</v>
+        <v>1269289</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>51779.08</v>
+        <v>64903.26</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-04)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>305670</v>
+        <v>380237</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>18015.65</v>
+        <v>22523.21</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>130084</v>
+        <v>165535</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5413.04</v>
+        <v>6945.47</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-04)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>484099</v>
+        <v>672642</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>26267.48</v>
+        <v>32791.87</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38084</v>
+        <v>50875</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2082.91</v>
+        <v>2642.71</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-03)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-04)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68019</v>
+        <v>74166</v>
       </c>
       <c r="C38" t="n">
-        <v>91998</v>
+        <v>130084</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3749.64</v>
+        <v>5413.04</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68019</v>
+        <v>74166</v>
       </c>
       <c r="C39" t="n">
-        <v>217045</v>
+        <v>305670</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>12551.55</v>
+        <v>18015.65</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63358</v>
+        <v>71375</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63358</v>
+        <v>71375</v>
       </c>
       <c r="C44" t="n">
-        <v>354947</v>
+        <v>484094</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>20042.48</v>
+        <v>26271.16</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>41.4</v>
+        <v>27.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>44.4</v>
+        <v>28.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>40.8</v>
+        <v>24.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>43.5</v>
+        <v>25</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>36.4</v>
+        <v>38.9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>31.1</v>
+        <v>24.8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:38:57</t>
+          <t>Last Updated: 06-10-2026 07:58:23</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-04</t>
+          <t>MTD: 2026-10-01 → 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -3227,120 +3227,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59495</v>
+        <v>76529</v>
       </c>
       <c r="E5" t="n">
-        <v>130084</v>
+        <v>165535</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5413.04</v>
+        <v>6945.47</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Retention SasteKaSahiAddress Category 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>08-07-2026</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Retention SasteKaSahiAddress Video</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>08-07-2026</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Retention Price Increase Agro Tools</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>08-07-2026</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3372,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:39:31</t>
+          <t>Last Updated: 06-10-2026 07:59:25</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:39:31</t>
+          <t>Last Updated: 06-10-2026 07:59:25</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:40:06</t>
+          <t>Last Updated: 06-10-2026 08:00:00</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 05-10-2026 06:40:43</t>
+          <t>Last Updated: 06-10-2026 08:00:38</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>522183</v>
+        <v>723517</v>
       </c>
       <c r="E4" t="n">
-        <v>63358</v>
+        <v>71375</v>
       </c>
       <c r="F4" t="n">
-        <v>3565</v>
+        <v>4235</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4778,16 +4676,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>236597</v>
+        <v>294624</v>
       </c>
       <c r="E5" t="n">
-        <v>32568</v>
+        <v>34475</v>
       </c>
       <c r="F5" t="n">
-        <v>3314</v>
+        <v>4040</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4822,13 +4720,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>138730</v>
+        <v>173759</v>
       </c>
       <c r="E6" t="n">
-        <v>27417</v>
+        <v>30415</v>
       </c>
       <c r="F6" t="n">
-        <v>1313</v>
+        <v>1648</v>
       </c>
       <c r="G6" t="n">
         <v>0.95</v>
@@ -4866,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78249</v>
+        <v>100341</v>
       </c>
       <c r="E7" t="n">
-        <v>17261</v>
+        <v>19856</v>
       </c>
       <c r="F7" t="n">
-        <v>1404</v>
+        <v>1733</v>
       </c>
       <c r="G7" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4910,13 +4808,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69073</v>
+        <v>85613</v>
       </c>
       <c r="E8" t="n">
-        <v>8225</v>
+        <v>8844</v>
       </c>
       <c r="F8" t="n">
-        <v>1406</v>
+        <v>1750</v>
       </c>
       <c r="G8" t="n">
         <v>2.04</v>
@@ -4954,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59757</v>
+        <v>72676</v>
       </c>
       <c r="E9" t="n">
-        <v>10681</v>
+        <v>11501</v>
       </c>
       <c r="F9" t="n">
-        <v>3889</v>
+        <v>4735</v>
       </c>
       <c r="G9" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4998,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53383</v>
+        <v>66704</v>
       </c>
       <c r="E10" t="n">
-        <v>11835</v>
+        <v>12903</v>
       </c>
       <c r="F10" t="n">
-        <v>698</v>
+        <v>850</v>
       </c>
       <c r="G10" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5042,16 +4940,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51835</v>
+        <v>65194</v>
       </c>
       <c r="E11" t="n">
-        <v>9965</v>
+        <v>10991</v>
       </c>
       <c r="F11" t="n">
-        <v>2140</v>
+        <v>2616</v>
       </c>
       <c r="G11" t="n">
-        <v>4.13</v>
+        <v>4.01</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -5086,16 +4984,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49230</v>
+        <v>57831</v>
       </c>
       <c r="E12" t="n">
-        <v>28998</v>
+        <v>32637</v>
       </c>
       <c r="F12" t="n">
-        <v>965</v>
+        <v>1253</v>
       </c>
       <c r="G12" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5174,16 +5072,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20154</v>
+        <v>31775</v>
       </c>
       <c r="E14" t="n">
-        <v>5631</v>
+        <v>6895</v>
       </c>
       <c r="F14" t="n">
-        <v>1172</v>
+        <v>1919</v>
       </c>
       <c r="G14" t="n">
-        <v>5.82</v>
+        <v>6.04</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 07:55:03</t>
+          <t>Last Updated: 07-10-2026 00:05:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 05-10-2026)</t>
+          <t>MTD (01-10-2026 → 06-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>35434.58</v>
+        <v>41041.85</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8180.73</v>
+        <v>8419.77</v>
       </c>
       <c r="D5" t="n">
-        <v>40669.45</v>
+        <v>52309.69</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8180.73</v>
+        <v>8419.77</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>76104.03</v>
+        <v>93351.53999999999</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 04-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 05-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>28354.87</v>
+        <v>35860.94</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>7137.61</v>
+        <v>8180.73</v>
       </c>
       <c r="D11" t="n">
-        <v>32106.92</v>
+        <v>40669.45</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>7137.61</v>
+        <v>8180.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>60461.79</v>
+        <v>76530.39</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7079.71</v>
+        <v>5180.91</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1043.12</v>
+        <v>239.04</v>
       </c>
       <c r="D17" t="n">
-        <v>8562.530000000001</v>
+        <v>11640.24</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1043.12</v>
+        <v>239.04</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15642.24</v>
+        <v>16821.15</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 07:55:34</t>
+          <t>Last Updated: 07-10-2026 00:05:50</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-05 | MTD-1: 2026-10-01 → 2026-10-04</t>
+          <t>MTD: 2026-10-01 → 2026-10-06 | MTD-1: 2026-10-01 → 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-05)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12903</v>
+        <v>13321</v>
       </c>
       <c r="C8" t="n">
-        <v>66919</v>
+        <v>72299</v>
       </c>
       <c r="D8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="E8" t="n">
-        <v>5.19</v>
+        <v>5.43</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5311.25</v>
+        <v>5540.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-05)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-04)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11878</v>
+        <v>12915</v>
       </c>
       <c r="C20" t="n">
-        <v>53597</v>
+        <v>67029</v>
       </c>
       <c r="D20" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="E20" t="n">
-        <v>4.51</v>
+        <v>5.19</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4636.67</v>
+        <v>5311.25</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-04)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1025</v>
+        <v>406</v>
       </c>
       <c r="C32" t="n">
-        <v>13322</v>
+        <v>5270</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E32" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>674.58</v>
+        <v>229.65</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 07:56:15</t>
+          <t>Last Updated: 07-10-2026 00:06:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-05)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>74166</v>
+        <v>79974</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>545772</v>
+        <v>651484</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>29468.68</v>
+        <v>35686.74</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>71375</v>
+        <v>77732</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>723517</v>
+        <v>880490</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>35434.58</v>
+        <v>41041.86</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>145541</v>
+        <v>157706</v>
       </c>
       <c r="C7" t="n">
-        <v>1269289</v>
+        <v>1531974</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>64903.26</v>
+        <v>76728.60000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-05)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>380237</v>
+        <v>448526</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>22523.21</v>
+        <v>26879.13</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>165535</v>
+        <v>202958</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>6945.47</v>
+        <v>8807.610000000001</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-05)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>672642</v>
+        <v>820542</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>32791.87</v>
+        <v>38067.94</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50875</v>
+        <v>59948</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2642.71</v>
+        <v>2973.92</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-04)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-05)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>74166</v>
+        <v>79974</v>
       </c>
       <c r="C38" t="n">
-        <v>130084</v>
+        <v>165535</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>5413.04</v>
+        <v>6945.47</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>74166</v>
+        <v>79974</v>
       </c>
       <c r="C39" t="n">
-        <v>305670</v>
+        <v>380237</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>18015.65</v>
+        <v>22523.21</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>71375</v>
+        <v>77732</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>71375</v>
+        <v>77732</v>
       </c>
       <c r="C44" t="n">
-        <v>484094</v>
+        <v>672875</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>26271.16</v>
+        <v>33182.97</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>27.3</v>
+        <v>22.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>24.4</v>
+        <v>18</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>19.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>38.9</v>
+        <v>21.9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>24.8</v>
+        <v>14.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 07:58:23</t>
+          <t>Last Updated: 07-10-2026 00:07:07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-05</t>
+          <t>MTD: 2026-10-01 → 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>76529</v>
+        <v>94191</v>
       </c>
       <c r="E5" t="n">
-        <v>165535</v>
+        <v>202958</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6945.47</v>
+        <v>8807.610000000001</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 07:59:25</t>
+          <t>Last Updated: 07-10-2026 00:07:43</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 07:59:25</t>
+          <t>Last Updated: 07-10-2026 00:07:43</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 08:00:00</t>
+          <t>Last Updated: 07-10-2026 00:08:18</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 06-10-2026 08:00:38</t>
+          <t>Last Updated: 07-10-2026 00:08:55</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>723517</v>
+        <v>880490</v>
       </c>
       <c r="E4" t="n">
-        <v>71375</v>
+        <v>77732</v>
       </c>
       <c r="F4" t="n">
-        <v>4235</v>
+        <v>4944</v>
       </c>
       <c r="G4" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>294624</v>
+        <v>347958</v>
       </c>
       <c r="E5" t="n">
-        <v>34475</v>
+        <v>36444</v>
       </c>
       <c r="F5" t="n">
-        <v>4040</v>
+        <v>4742</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>173759</v>
+        <v>257459</v>
       </c>
       <c r="E6" t="n">
-        <v>30415</v>
+        <v>53186</v>
       </c>
       <c r="F6" t="n">
-        <v>1648</v>
+        <v>2507</v>
       </c>
       <c r="G6" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100341</v>
+        <v>123386</v>
       </c>
       <c r="E7" t="n">
-        <v>19856</v>
+        <v>22057</v>
       </c>
       <c r="F7" t="n">
-        <v>1733</v>
+        <v>2086</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85613</v>
+        <v>100568</v>
       </c>
       <c r="E8" t="n">
-        <v>8844</v>
+        <v>9638</v>
       </c>
       <c r="F8" t="n">
-        <v>1750</v>
+        <v>2029</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72676</v>
+        <v>87787</v>
       </c>
       <c r="E9" t="n">
-        <v>11501</v>
+        <v>12248</v>
       </c>
       <c r="F9" t="n">
-        <v>4735</v>
+        <v>5690</v>
       </c>
       <c r="G9" t="n">
-        <v>6.52</v>
+        <v>6.48</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4887,25 +4887,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66704</v>
+        <v>79572</v>
       </c>
       <c r="E10" t="n">
-        <v>12903</v>
+        <v>11835</v>
       </c>
       <c r="F10" t="n">
-        <v>850</v>
+        <v>3287</v>
       </c>
       <c r="G10" t="n">
-        <v>1.27</v>
+        <v>4.13</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4931,25 +4931,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65194</v>
+        <v>71974</v>
       </c>
       <c r="E11" t="n">
-        <v>10991</v>
+        <v>13321</v>
       </c>
       <c r="F11" t="n">
-        <v>2616</v>
+        <v>908</v>
       </c>
       <c r="G11" t="n">
-        <v>4.01</v>
+        <v>1.26</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>57831</v>
+        <v>58047</v>
       </c>
       <c r="E12" t="n">
-        <v>32637</v>
+        <v>32648</v>
       </c>
       <c r="F12" t="n">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="G12" t="n">
         <v>2.17</v>
@@ -5072,16 +5072,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31775</v>
+        <v>40861</v>
       </c>
       <c r="E14" t="n">
-        <v>6895</v>
+        <v>7640</v>
       </c>
       <c r="F14" t="n">
-        <v>1919</v>
+        <v>2463</v>
       </c>
       <c r="G14" t="n">
-        <v>6.04</v>
+        <v>6.03</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5096,6 +5096,50 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Retargeting_HighIntent_6Oct</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4959</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2626</v>
+      </c>
+      <c r="F15" t="n">
+        <v>121</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:05:19</t>
+          <t>Last Updated: 07-10-2026 07:14:06</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>41041.85</v>
+        <v>43272.74</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8419.77</v>
+        <v>8420.790000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>52309.69</v>
+        <v>52410.26</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8419.77</v>
+        <v>8420.790000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>93351.53999999999</v>
+        <v>95683</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5180.91</v>
+        <v>7411.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>239.04</v>
+        <v>240.06</v>
       </c>
       <c r="D17" t="n">
-        <v>11640.24</v>
+        <v>11740.81</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>239.04</v>
+        <v>240.06</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>16821.15</v>
+        <v>19152.61</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:05:50</t>
+          <t>Last Updated: 07-10-2026 07:14:37</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>13321</v>
       </c>
       <c r="C8" t="n">
-        <v>72299</v>
+        <v>72319</v>
       </c>
       <c r="D8" t="n">
         <v>1.55</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5540.9</v>
+        <v>5541.87</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>406</v>
       </c>
       <c r="C32" t="n">
-        <v>5270</v>
+        <v>5290</v>
       </c>
       <c r="D32" t="n">
         <v>-0.02</v>
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>229.65</v>
+        <v>230.62</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:06:31</t>
+          <t>Last Updated: 07-10-2026 07:15:16</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>79974</v>
+        <v>80024</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>651484</v>
+        <v>652175</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35686.74</v>
+        <v>35738.98</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>77732</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>880490</v>
+        <v>942285</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>41041.86</v>
+        <v>43272.74</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157706</v>
+        <v>157756</v>
       </c>
       <c r="C7" t="n">
-        <v>1531974</v>
+        <v>1594460</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>76728.60000000001</v>
+        <v>79011.72</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>448526</v>
+        <v>448949</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>26879.13</v>
+        <v>26913.02</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>202958</v>
+        <v>203226</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8807.610000000001</v>
+        <v>8825.959999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>820542</v>
+        <v>878590</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>38067.94</v>
+        <v>40177.28</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>59948</v>
+        <v>63695</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2973.92</v>
+        <v>3095.46</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>79974</v>
+        <v>80024</v>
       </c>
       <c r="C38" t="n">
         <v>165535</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79974</v>
+        <v>80024</v>
       </c>
       <c r="C39" t="n">
         <v>380237</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>21.9</v>
+        <v>30.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>14.7</v>
+        <v>21.1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:07:07</t>
+          <t>Last Updated: 07-10-2026 07:15:52</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>94191</v>
+        <v>94338</v>
       </c>
       <c r="E5" t="n">
-        <v>202958</v>
+        <v>203226</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>8807.610000000001</v>
+        <v>8825.959999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:07:43</t>
+          <t>Last Updated: 07-10-2026 07:16:28</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:07:43</t>
+          <t>Last Updated: 07-10-2026 07:16:28</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:08:18</t>
+          <t>Last Updated: 07-10-2026 07:17:02</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 00:08:55</t>
+          <t>Last Updated: 07-10-2026 07:17:40</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>880490</v>
+        <v>942285</v>
       </c>
       <c r="E4" t="n">
         <v>77732</v>
       </c>
       <c r="F4" t="n">
-        <v>4944</v>
+        <v>5171</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>347958</v>
+        <v>348274</v>
       </c>
       <c r="E5" t="n">
-        <v>36444</v>
+        <v>36456</v>
       </c>
       <c r="F5" t="n">
-        <v>4742</v>
+        <v>4746</v>
       </c>
       <c r="G5" t="n">
         <v>1.36</v>
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>257459</v>
+        <v>257965</v>
       </c>
       <c r="E6" t="n">
-        <v>53186</v>
+        <v>53454</v>
       </c>
       <c r="F6" t="n">
-        <v>2507</v>
+        <v>2518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>123386</v>
+        <v>123542</v>
       </c>
       <c r="E7" t="n">
-        <v>22057</v>
+        <v>22084</v>
       </c>
       <c r="F7" t="n">
         <v>2086</v>
@@ -4808,13 +4808,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>100568</v>
+        <v>100675</v>
       </c>
       <c r="E8" t="n">
-        <v>9638</v>
+        <v>9649</v>
       </c>
       <c r="F8" t="n">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="G8" t="n">
         <v>2.02</v>
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>87787</v>
+        <v>87892</v>
       </c>
       <c r="E9" t="n">
-        <v>12248</v>
+        <v>12261</v>
       </c>
       <c r="F9" t="n">
-        <v>5690</v>
+        <v>5694</v>
       </c>
       <c r="G9" t="n">
         <v>6.48</v>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79572</v>
+        <v>79684</v>
       </c>
       <c r="E10" t="n">
-        <v>11835</v>
+        <v>11836</v>
       </c>
       <c r="F10" t="n">
-        <v>3287</v>
+        <v>3294</v>
       </c>
       <c r="G10" t="n">
         <v>4.13</v>
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>71974</v>
+        <v>71994</v>
       </c>
       <c r="E11" t="n">
         <v>13321</v>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="E12" t="n">
         <v>32648</v>
@@ -5072,16 +5072,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40861</v>
+        <v>40931</v>
       </c>
       <c r="E14" t="n">
-        <v>7640</v>
+        <v>7660</v>
       </c>
       <c r="F14" t="n">
-        <v>2463</v>
+        <v>2472</v>
       </c>
       <c r="G14" t="n">
-        <v>6.03</v>
+        <v>6.04</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4959</v>
+        <v>5013</v>
       </c>
       <c r="E15" t="n">
-        <v>2626</v>
+        <v>2665</v>
       </c>
       <c r="F15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:14:06</t>
+          <t>Last Updated: 08-10-2026 00:34:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 06-10-2026)</t>
+          <t>MTD (01-10-2026 → 07-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>43272.74</v>
+        <v>49256.54</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8420.790000000001</v>
+        <v>8421.74</v>
       </c>
       <c r="D5" t="n">
-        <v>52410.26</v>
+        <v>66713.87</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8420.790000000001</v>
+        <v>8421.74</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>95683</v>
+        <v>115970.41</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 05-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 06-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>35860.94</v>
+        <v>43282.85</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8180.73</v>
+        <v>8420.790000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>40669.45</v>
+        <v>52410.26</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8180.73</v>
+        <v>8420.790000000001</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>76530.39</v>
+        <v>95693.11</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7411.8</v>
+        <v>5973.69</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>240.06</v>
+        <v>0.95</v>
       </c>
       <c r="D17" t="n">
-        <v>11740.81</v>
+        <v>14303.61</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>240.06</v>
+        <v>0.95</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>19152.61</v>
+        <v>20277.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:14:37</t>
+          <t>Last Updated: 08-10-2026 00:35:26</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-06 | MTD-1: 2026-10-01 → 2026-10-05</t>
+          <t>MTD: 2026-10-01 → 2026-10-07 | MTD-1: 2026-10-01 → 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-06)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>13321</v>
       </c>
       <c r="C8" t="n">
-        <v>72319</v>
+        <v>72327</v>
       </c>
       <c r="D8" t="n">
         <v>1.55</v>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-06)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-05)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12915</v>
+        <v>13321</v>
       </c>
       <c r="C20" t="n">
-        <v>67029</v>
+        <v>72327</v>
       </c>
       <c r="D20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="E20" t="n">
-        <v>5.19</v>
+        <v>5.43</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5311.25</v>
+        <v>5541.87</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-05)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -2146,22 +2146,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>5290</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>230.62</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:15:16</t>
+          <t>Last Updated: 08-10-2026 00:36:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-06)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>80024</v>
+        <v>89389</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>652175</v>
+        <v>781171</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35738.98</v>
+        <v>42773.09</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>77732</v>
+        <v>83047</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>942285</v>
+        <v>1099428</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>43272.74</v>
+        <v>49256.54</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157756</v>
+        <v>172436</v>
       </c>
       <c r="C7" t="n">
-        <v>1594460</v>
+        <v>1880599</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>79011.72</v>
+        <v>92029.63</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-06)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>448949</v>
+        <v>531794</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>26913.02</v>
+        <v>31906.16</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>203226</v>
+        <v>249377</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8825.959999999999</v>
+        <v>10866.93</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-06)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>878590</v>
+        <v>1026008</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>40177.28</v>
+        <v>45822.98</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63695</v>
+        <v>73420</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3095.46</v>
+        <v>3433.56</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-05)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>80024</v>
+        <v>89389</v>
       </c>
       <c r="C38" t="n">
-        <v>165535</v>
+        <v>203226</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>6945.47</v>
+        <v>8825.959999999999</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>80024</v>
+        <v>89389</v>
       </c>
       <c r="C39" t="n">
-        <v>380237</v>
+        <v>448949</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>22523.21</v>
+        <v>26913.02</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77732</v>
+        <v>83047</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>77732</v>
+        <v>83047</v>
       </c>
       <c r="C44" t="n">
-        <v>672875</v>
+        <v>878328</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>33182.97</v>
+        <v>40186.67</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>27.1</v>
+        <v>23.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>19.5</v>
+        <v>18.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>30.6</v>
+        <v>16.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>21.1</v>
+        <v>14</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3134,10 +3134,10 @@
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:15:52</t>
+          <t>Last Updated: 08-10-2026 00:36:42</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-06</t>
+          <t>MTD: 2026-10-01 → 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>94338</v>
+        <v>114952</v>
       </c>
       <c r="E5" t="n">
-        <v>203226</v>
+        <v>249377</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>8825.959999999999</v>
+        <v>10866.93</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:16:28</t>
+          <t>Last Updated: 08-10-2026 00:37:18</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:16:28</t>
+          <t>Last Updated: 08-10-2026 00:37:18</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:17:02</t>
+          <t>Last Updated: 08-10-2026 00:37:54</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 07-10-2026 07:17:40</t>
+          <t>Last Updated: 08-10-2026 00:38:31</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>942285</v>
+        <v>1099428</v>
       </c>
       <c r="E4" t="n">
-        <v>77732</v>
+        <v>83047</v>
       </c>
       <c r="F4" t="n">
-        <v>5171</v>
+        <v>5795</v>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Dormant_Users_7July26</t>
+          <t>Activation_FirstPurchase_26Sep</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>348274</v>
+        <v>430949</v>
       </c>
       <c r="E5" t="n">
-        <v>36456</v>
+        <v>85648</v>
       </c>
       <c r="F5" t="n">
-        <v>4746</v>
+        <v>3799</v>
       </c>
       <c r="G5" t="n">
-        <v>1.36</v>
+        <v>0.88</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Activation_FirstPurchase_26Sep</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Dormant_Users_7July26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>257965</v>
+        <v>413172</v>
       </c>
       <c r="E6" t="n">
-        <v>53454</v>
+        <v>39818</v>
       </c>
       <c r="F6" t="n">
-        <v>2518</v>
+        <v>5445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.98</v>
+        <v>1.32</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>123542</v>
+        <v>152755</v>
       </c>
       <c r="E7" t="n">
-        <v>22084</v>
+        <v>25995</v>
       </c>
       <c r="F7" t="n">
-        <v>2086</v>
+        <v>2439</v>
       </c>
       <c r="G7" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>100675</v>
+        <v>118622</v>
       </c>
       <c r="E8" t="n">
-        <v>9649</v>
+        <v>10595</v>
       </c>
       <c r="F8" t="n">
-        <v>2034</v>
+        <v>2336</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>87892</v>
+        <v>106622</v>
       </c>
       <c r="E9" t="n">
-        <v>12261</v>
+        <v>13050</v>
       </c>
       <c r="F9" t="n">
-        <v>5694</v>
+        <v>6811</v>
       </c>
       <c r="G9" t="n">
-        <v>6.48</v>
+        <v>6.39</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79684</v>
+        <v>96622</v>
       </c>
       <c r="E10" t="n">
-        <v>11836</v>
+        <v>12981</v>
       </c>
       <c r="F10" t="n">
-        <v>3294</v>
+        <v>3925</v>
       </c>
       <c r="G10" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58048</v>
+        <v>58073</v>
       </c>
       <c r="E12" t="n">
         <v>32648</v>
       </c>
       <c r="F12" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="G12" t="n">
         <v>2.17</v>
@@ -5019,25 +5019,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45483</v>
+        <v>52967</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>9207</v>
       </c>
       <c r="F13" t="n">
-        <v>646</v>
+        <v>3181</v>
       </c>
       <c r="G13" t="n">
-        <v>1.42</v>
+        <v>6.01</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5063,25 +5063,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity_Catalog_3Oct</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40931</v>
+        <v>45483</v>
       </c>
       <c r="E14" t="n">
-        <v>7660</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2472</v>
+        <v>646</v>
       </c>
       <c r="G14" t="n">
-        <v>6.04</v>
+        <v>1.42</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5013</v>
+        <v>15052</v>
       </c>
       <c r="E15" t="n">
-        <v>2665</v>
+        <v>4938</v>
       </c>
       <c r="F15" t="n">
-        <v>122</v>
+        <v>292</v>
       </c>
       <c r="G15" t="n">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:34:55</t>
+          <t>Last Updated: 08-10-2026 07:40:47</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>49256.54</v>
+        <v>51538.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.74</v>
       </c>
       <c r="D5" t="n">
-        <v>66713.87</v>
+        <v>66799.41</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.74</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>115970.41</v>
+        <v>118337.58</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5973.69</v>
+        <v>8255.32</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0.95</v>
       </c>
       <c r="D17" t="n">
-        <v>14303.61</v>
+        <v>14389.15</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0.95</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20277.3</v>
+        <v>22644.47</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:35:26</t>
+          <t>Last Updated: 08-10-2026 07:41:17</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:36:05</t>
+          <t>Last Updated: 08-10-2026 07:42:00</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>89389</v>
+        <v>89424</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>781171</v>
+        <v>781846</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>42773.09</v>
+        <v>42822.91</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>83047</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1099428</v>
+        <v>1160420</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>49256.54</v>
+        <v>51538.16</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172436</v>
+        <v>172471</v>
       </c>
       <c r="C7" t="n">
-        <v>1880599</v>
+        <v>1942266</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>92029.63</v>
+        <v>94361.07000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>531794</v>
+        <v>532215</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>31906.16</v>
+        <v>31940.5</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>249377</v>
+        <v>249631</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>10866.93</v>
+        <v>10882.41</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1026008</v>
+        <v>1082682</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>45822.98</v>
+        <v>47970.66</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>73420</v>
+        <v>77738</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3433.56</v>
+        <v>3567.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>89389</v>
+        <v>89424</v>
       </c>
       <c r="C38" t="n">
         <v>203226</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>89389</v>
+        <v>89424</v>
       </c>
       <c r="C39" t="n">
         <v>448949</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>16.8</v>
+        <v>23.3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>14</v>
+        <v>19.4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:36:42</t>
+          <t>Last Updated: 08-10-2026 07:42:37</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>114952</v>
+        <v>115060</v>
       </c>
       <c r="E5" t="n">
-        <v>249377</v>
+        <v>249631</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>10866.93</v>
+        <v>10882.41</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:37:18</t>
+          <t>Last Updated: 08-10-2026 07:43:13</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:37:18</t>
+          <t>Last Updated: 08-10-2026 07:43:13</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:37:54</t>
+          <t>Last Updated: 08-10-2026 07:43:48</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 00:38:31</t>
+          <t>Last Updated: 08-10-2026 07:44:24</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1099428</v>
+        <v>1160420</v>
       </c>
       <c r="E4" t="n">
         <v>83047</v>
       </c>
       <c r="F4" t="n">
-        <v>5795</v>
+        <v>6021</v>
       </c>
       <c r="G4" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>430949</v>
+        <v>431425</v>
       </c>
       <c r="E5" t="n">
-        <v>85648</v>
+        <v>85670</v>
       </c>
       <c r="F5" t="n">
-        <v>3799</v>
+        <v>3801</v>
       </c>
       <c r="G5" t="n">
         <v>0.88</v>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>413172</v>
+        <v>413462</v>
       </c>
       <c r="E6" t="n">
-        <v>39818</v>
+        <v>39828</v>
       </c>
       <c r="F6" t="n">
         <v>5445</v>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>152755</v>
+        <v>152912</v>
       </c>
       <c r="E7" t="n">
-        <v>25995</v>
+        <v>26009</v>
       </c>
       <c r="F7" t="n">
-        <v>2439</v>
+        <v>2442</v>
       </c>
       <c r="G7" t="n">
         <v>1.6</v>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118622</v>
+        <v>118753</v>
       </c>
       <c r="E8" t="n">
-        <v>10595</v>
+        <v>10606</v>
       </c>
       <c r="F8" t="n">
         <v>2336</v>
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106622</v>
+        <v>106724</v>
       </c>
       <c r="E9" t="n">
-        <v>13050</v>
+        <v>13068</v>
       </c>
       <c r="F9" t="n">
-        <v>6811</v>
+        <v>6816</v>
       </c>
       <c r="G9" t="n">
         <v>6.39</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96622</v>
+        <v>96719</v>
       </c>
       <c r="E10" t="n">
         <v>12981</v>
@@ -5028,13 +5028,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>52967</v>
+        <v>53039</v>
       </c>
       <c r="E13" t="n">
-        <v>9207</v>
+        <v>9216</v>
       </c>
       <c r="F13" t="n">
-        <v>3181</v>
+        <v>3185</v>
       </c>
       <c r="G13" t="n">
         <v>6.01</v>
@@ -5116,13 +5116,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15052</v>
+        <v>15112</v>
       </c>
       <c r="E15" t="n">
-        <v>4938</v>
+        <v>4945</v>
       </c>
       <c r="F15" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G15" t="n">
         <v>1.94</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:40:47</t>
+          <t>Last Updated: 09-10-2026 00:30:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 07-10-2026)</t>
+          <t>MTD (01-10-2026 → 08-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>51538.17</v>
+        <v>55919.97</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.74</v>
       </c>
       <c r="D5" t="n">
-        <v>66799.41</v>
+        <v>80374.32000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.74</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>118337.58</v>
+        <v>136294.29</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 06-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 07-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>43282.85</v>
+        <v>51540.08</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8420.790000000001</v>
+        <v>8421.74</v>
       </c>
       <c r="D11" t="n">
-        <v>52410.26</v>
+        <v>66799.41</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8420.790000000001</v>
+        <v>8421.74</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>95693.11</v>
+        <v>118339.49</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8255.32</v>
+        <v>4379.89</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14389.15</v>
+        <v>13574.91</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22644.47</v>
+        <v>17954.8</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:41:17</t>
+          <t>Last Updated: 09-10-2026 00:30:58</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-07 | MTD-1: 2026-10-01 → 2026-10-06</t>
+          <t>MTD: 2026-10-01 → 2026-10-08 | MTD-1: 2026-10-01 → 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-07)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>13321</v>
       </c>
       <c r="C8" t="n">
-        <v>72327</v>
+        <v>72328</v>
       </c>
       <c r="D8" t="n">
         <v>1.55</v>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-07)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-06)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         <v>13321</v>
       </c>
       <c r="C20" t="n">
-        <v>72327</v>
+        <v>72328</v>
       </c>
       <c r="D20" t="n">
         <v>1.55</v>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-06)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:42:00</t>
+          <t>Last Updated: 09-10-2026 00:31:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-07)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>89424</v>
+        <v>94294</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>781846</v>
+        <v>900820</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>42822.91</v>
+        <v>49836.7</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>83047</v>
+        <v>86545</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1160420</v>
+        <v>1259194</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>51538.16</v>
+        <v>55919.97</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172471</v>
+        <v>180839</v>
       </c>
       <c r="C7" t="n">
-        <v>1942266</v>
+        <v>2160014</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>94361.07000000001</v>
+        <v>105756.67</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-07)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>532215</v>
+        <v>607506</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>31940.5</v>
+        <v>36884.91</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>249631</v>
+        <v>293314</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>10882.41</v>
+        <v>12951.79</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-07)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1082682</v>
+        <v>1176167</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>47970.66</v>
+        <v>52130.52</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>77738</v>
+        <v>83027</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3567.5</v>
+        <v>3789.45</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-06)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>89424</v>
+        <v>94294</v>
       </c>
       <c r="C38" t="n">
-        <v>203226</v>
+        <v>249631</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>8825.959999999999</v>
+        <v>10882.41</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>89424</v>
+        <v>94294</v>
       </c>
       <c r="C39" t="n">
-        <v>448949</v>
+        <v>532215</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>26913.02</v>
+        <v>31940.5</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>83047</v>
+        <v>86545</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>83047</v>
+        <v>86545</v>
       </c>
       <c r="C44" t="n">
-        <v>878328</v>
+        <v>1082681</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>40186.67</v>
+        <v>47972.58</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>22.8</v>
+        <v>17.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>23.3</v>
+        <v>19</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>18.5</v>
+        <v>14.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>18.7</v>
+        <v>15.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>23.3</v>
+        <v>8.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>19.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:42:37</t>
+          <t>Last Updated: 09-10-2026 00:32:12</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-07</t>
+          <t>MTD: 2026-10-01 → 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>115060</v>
+        <v>133936</v>
       </c>
       <c r="E5" t="n">
-        <v>249631</v>
+        <v>293314</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>10882.41</v>
+        <v>12951.79</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:43:13</t>
+          <t>Last Updated: 09-10-2026 00:32:46</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:43:13</t>
+          <t>Last Updated: 09-10-2026 00:32:46</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:43:48</t>
+          <t>Last Updated: 09-10-2026 00:33:23</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 08-10-2026 07:44:24</t>
+          <t>Last Updated: 09-10-2026 00:33:59</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1160420</v>
+        <v>1259194</v>
       </c>
       <c r="E4" t="n">
-        <v>83047</v>
+        <v>86545</v>
       </c>
       <c r="F4" t="n">
-        <v>6021</v>
+        <v>6892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>431425</v>
+        <v>564252</v>
       </c>
       <c r="E5" t="n">
-        <v>85670</v>
+        <v>93572</v>
       </c>
       <c r="F5" t="n">
-        <v>3801</v>
+        <v>4648</v>
       </c>
       <c r="G5" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>413462</v>
+        <v>471721</v>
       </c>
       <c r="E6" t="n">
-        <v>39828</v>
+        <v>41329</v>
       </c>
       <c r="F6" t="n">
-        <v>5445</v>
+        <v>6057</v>
       </c>
       <c r="G6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>152912</v>
+        <v>179866</v>
       </c>
       <c r="E7" t="n">
-        <v>26009</v>
+        <v>27917</v>
       </c>
       <c r="F7" t="n">
-        <v>2442</v>
+        <v>2737</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118753</v>
+        <v>135785</v>
       </c>
       <c r="E8" t="n">
-        <v>10606</v>
+        <v>11135</v>
       </c>
       <c r="F8" t="n">
-        <v>2336</v>
+        <v>2600</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106724</v>
+        <v>124489</v>
       </c>
       <c r="E9" t="n">
-        <v>13068</v>
+        <v>13675</v>
       </c>
       <c r="F9" t="n">
-        <v>6816</v>
+        <v>7852</v>
       </c>
       <c r="G9" t="n">
-        <v>6.39</v>
+        <v>6.31</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96719</v>
+        <v>113448</v>
       </c>
       <c r="E10" t="n">
-        <v>12981</v>
+        <v>13913</v>
       </c>
       <c r="F10" t="n">
-        <v>3925</v>
+        <v>4453</v>
       </c>
       <c r="G10" t="n">
-        <v>4.06</v>
+        <v>3.93</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4975,25 +4975,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Onboarding_LoginSuccess_3Oct</t>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58073</v>
+        <v>65266</v>
       </c>
       <c r="E12" t="n">
-        <v>32648</v>
+        <v>10162</v>
       </c>
       <c r="F12" t="n">
-        <v>1261</v>
+        <v>3896</v>
       </c>
       <c r="G12" t="n">
-        <v>2.17</v>
+        <v>5.97</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity_Catalog_3Oct</t>
+          <t>Onboarding_LoginSuccess_3Oct</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53039</v>
+        <v>58073</v>
       </c>
       <c r="E13" t="n">
-        <v>9216</v>
+        <v>32648</v>
       </c>
       <c r="F13" t="n">
-        <v>3185</v>
+        <v>1261</v>
       </c>
       <c r="G13" t="n">
-        <v>6.01</v>
+        <v>2.17</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15112</v>
+        <v>24840</v>
       </c>
       <c r="E15" t="n">
-        <v>4945</v>
+        <v>6050</v>
       </c>
       <c r="F15" t="n">
-        <v>293</v>
+        <v>449</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:30:27</t>
+          <t>Last Updated: 09-10-2026 07:54:15</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>55919.97</v>
+        <v>57659.41</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.74</v>
       </c>
       <c r="D5" t="n">
-        <v>80374.32000000001</v>
+        <v>80455.71000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.74</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>136294.29</v>
+        <v>138115.12</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4379.89</v>
+        <v>6119.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13574.91</v>
+        <v>13656.3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>17954.8</v>
+        <v>19775.63</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:30:58</t>
+          <t>Last Updated: 09-10-2026 07:54:46</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:31:36</t>
+          <t>Last Updated: 09-10-2026 07:55:27</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>94294</v>
+        <v>94308</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>900820</v>
+        <v>901401</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>49836.7</v>
+        <v>49879.19</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>86545</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1259194</v>
+        <v>1292227</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>55919.97</v>
+        <v>57659.41</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>180839</v>
+        <v>180853</v>
       </c>
       <c r="C7" t="n">
-        <v>2160014</v>
+        <v>2193628</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>105756.67</v>
+        <v>107538.6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>607506</v>
+        <v>607858</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36884.91</v>
+        <v>36909.8</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>293314</v>
+        <v>293543</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>12951.79</v>
+        <v>12969.39</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1176167</v>
+        <v>1207109</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>52130.52</v>
+        <v>53763.04</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>83027</v>
+        <v>85118</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3789.45</v>
+        <v>3896.37</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>94294</v>
+        <v>94308</v>
       </c>
       <c r="C38" t="n">
         <v>249631</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>94294</v>
+        <v>94308</v>
       </c>
       <c r="C39" t="n">
         <v>532215</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>8.699999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:32:12</t>
+          <t>Last Updated: 09-10-2026 07:56:03</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>133936</v>
+        <v>134005</v>
       </c>
       <c r="E5" t="n">
-        <v>293314</v>
+        <v>293543</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>12951.79</v>
+        <v>12969.39</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:32:46</t>
+          <t>Last Updated: 09-10-2026 07:56:39</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:32:46</t>
+          <t>Last Updated: 09-10-2026 07:56:39</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:33:23</t>
+          <t>Last Updated: 09-10-2026 07:57:14</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 00:33:59</t>
+          <t>Last Updated: 09-10-2026 07:57:51</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1259194</v>
+        <v>1292227</v>
       </c>
       <c r="E4" t="n">
         <v>86545</v>
       </c>
       <c r="F4" t="n">
-        <v>6892</v>
+        <v>7295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>564252</v>
+        <v>564701</v>
       </c>
       <c r="E5" t="n">
-        <v>93572</v>
+        <v>93579</v>
       </c>
       <c r="F5" t="n">
-        <v>4648</v>
+        <v>4650</v>
       </c>
       <c r="G5" t="n">
         <v>0.82</v>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>471721</v>
+        <v>472000</v>
       </c>
       <c r="E6" t="n">
-        <v>41329</v>
+        <v>41335</v>
       </c>
       <c r="F6" t="n">
-        <v>6057</v>
+        <v>6060</v>
       </c>
       <c r="G6" t="n">
         <v>1.28</v>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>179866</v>
+        <v>180003</v>
       </c>
       <c r="E7" t="n">
-        <v>27917</v>
+        <v>27923</v>
       </c>
       <c r="F7" t="n">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="G7" t="n">
         <v>1.52</v>
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>135785</v>
+        <v>135858</v>
       </c>
       <c r="E8" t="n">
-        <v>11135</v>
+        <v>11137</v>
       </c>
       <c r="F8" t="n">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>124489</v>
+        <v>124585</v>
       </c>
       <c r="E9" t="n">
-        <v>13675</v>
+        <v>13692</v>
       </c>
       <c r="F9" t="n">
-        <v>7852</v>
+        <v>7855</v>
       </c>
       <c r="G9" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>113448</v>
+        <v>113540</v>
       </c>
       <c r="E10" t="n">
         <v>13913</v>
       </c>
       <c r="F10" t="n">
-        <v>4453</v>
+        <v>4458</v>
       </c>
       <c r="G10" t="n">
         <v>3.93</v>
@@ -4984,16 +4984,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65266</v>
+        <v>65334</v>
       </c>
       <c r="E12" t="n">
-        <v>10162</v>
+        <v>10183</v>
       </c>
       <c r="F12" t="n">
-        <v>3896</v>
+        <v>3897</v>
       </c>
       <c r="G12" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5116,13 +5116,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24840</v>
+        <v>24902</v>
       </c>
       <c r="E15" t="n">
-        <v>6050</v>
+        <v>6066</v>
       </c>
       <c r="F15" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G15" t="n">
         <v>1.81</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:54:15</t>
+          <t>Last Updated: 10-10-2026 00:00:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 08-10-2026)</t>
+          <t>MTD (01-10-2026 → 09-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>57659.41</v>
+        <v>61617.04</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.74</v>
       </c>
       <c r="D5" t="n">
-        <v>80455.71000000001</v>
+        <v>94342.06</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.74</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>138115.12</v>
+        <v>155959.1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 07-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 08-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>51540.08</v>
+        <v>57661.07</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>8421.74</v>
       </c>
       <c r="D11" t="n">
-        <v>66799.41</v>
+        <v>80548.58</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8421.74</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>118339.49</v>
+        <v>138209.65</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6119.33</v>
+        <v>3955.97</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13656.3</v>
+        <v>13793.48</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>19775.63</v>
+        <v>17749.45</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:54:46</t>
+          <t>Last Updated: 10-10-2026 00:00:44</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-08 | MTD-1: 2026-10-01 → 2026-10-07</t>
+          <t>MTD: 2026-10-01 → 2026-10-09 | MTD-1: 2026-10-01 → 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-08)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-08)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-07)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-07)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:55:27</t>
+          <t>Last Updated: 10-10-2026 00:01:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-08)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>94308</v>
+        <v>98518</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>901401</v>
+        <v>999789</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>49879.19</v>
+        <v>56490.37</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>86545</v>
+        <v>90577</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1292227</v>
+        <v>1382219</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>57659.41</v>
+        <v>61617.03</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>180853</v>
+        <v>189095</v>
       </c>
       <c r="C7" t="n">
-        <v>2193628</v>
+        <v>2382008</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>107538.6</v>
+        <v>118107.4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-08)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>607858</v>
+        <v>667148</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36909.8</v>
+        <v>40927.8</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>293543</v>
+        <v>332641</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>12969.39</v>
+        <v>15562.57</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-08)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1207109</v>
+        <v>1292315</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>53763.04</v>
+        <v>57518.27</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>85118</v>
+        <v>89904</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3896.37</v>
+        <v>4098.76</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-07)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>94308</v>
+        <v>98518</v>
       </c>
       <c r="C38" t="n">
-        <v>249631</v>
+        <v>293865</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>10882.41</v>
+        <v>12985.61</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>94308</v>
+        <v>98518</v>
       </c>
       <c r="C39" t="n">
-        <v>532215</v>
+        <v>608394</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>31940.5</v>
+        <v>36945.17</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>86545</v>
+        <v>90577</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>86545</v>
+        <v>90577</v>
       </c>
       <c r="C44" t="n">
-        <v>1082681</v>
+        <v>1207082</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>47972.58</v>
+        <v>53764.52</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>17.6</v>
+        <v>13.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>14.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15.6</v>
+        <v>10.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>11.5</v>
+        <v>7.1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12.1</v>
+        <v>7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:56:03</t>
+          <t>Last Updated: 10-10-2026 00:02:02</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-08</t>
+          <t>MTD: 2026-10-01 → 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>134005</v>
+        <v>153246</v>
       </c>
       <c r="E5" t="n">
-        <v>293543</v>
+        <v>332641</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>12969.39</v>
+        <v>15562.57</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:56:39</t>
+          <t>Last Updated: 10-10-2026 00:02:37</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:56:39</t>
+          <t>Last Updated: 10-10-2026 00:02:37</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:57:14</t>
+          <t>Last Updated: 10-10-2026 00:03:13</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
     <col width="63" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 09-10-2026 07:57:51</t>
+          <t>Last Updated: 10-10-2026 00:03:49</t>
         </is>
       </c>
     </row>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1292227</v>
+        <v>1382219</v>
       </c>
       <c r="E4" t="n">
-        <v>86545</v>
+        <v>90577</v>
       </c>
       <c r="F4" t="n">
-        <v>7295</v>
+        <v>7737</v>
       </c>
       <c r="G4" t="n">
         <v>0.5600000000000001</v>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>564701</v>
+        <v>667352</v>
       </c>
       <c r="E5" t="n">
-        <v>93579</v>
+        <v>103662</v>
       </c>
       <c r="F5" t="n">
-        <v>4650</v>
+        <v>5398</v>
       </c>
       <c r="G5" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>472000</v>
+        <v>517391</v>
       </c>
       <c r="E6" t="n">
-        <v>41335</v>
+        <v>42456</v>
       </c>
       <c r="F6" t="n">
-        <v>6060</v>
+        <v>6545</v>
       </c>
       <c r="G6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>180003</v>
+        <v>199160</v>
       </c>
       <c r="E7" t="n">
-        <v>27923</v>
+        <v>29189</v>
       </c>
       <c r="F7" t="n">
-        <v>2738</v>
+        <v>2939</v>
       </c>
       <c r="G7" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>135858</v>
+        <v>149757</v>
       </c>
       <c r="E8" t="n">
-        <v>11137</v>
+        <v>11689</v>
       </c>
       <c r="F8" t="n">
-        <v>2604</v>
+        <v>2836</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>124585</v>
+        <v>137487</v>
       </c>
       <c r="E9" t="n">
-        <v>13692</v>
+        <v>13933</v>
       </c>
       <c r="F9" t="n">
-        <v>7855</v>
+        <v>8565</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>6.23</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>113540</v>
+        <v>133481</v>
       </c>
       <c r="E10" t="n">
-        <v>13913</v>
+        <v>15184</v>
       </c>
       <c r="F10" t="n">
-        <v>4458</v>
+        <v>5155</v>
       </c>
       <c r="G10" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4931,25 +4931,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>71994</v>
+        <v>74357</v>
       </c>
       <c r="E11" t="n">
-        <v>13321</v>
+        <v>10886</v>
       </c>
       <c r="F11" t="n">
-        <v>908</v>
+        <v>4422</v>
       </c>
       <c r="G11" t="n">
-        <v>1.26</v>
+        <v>5.95</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4975,25 +4975,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity_Catalog_3Oct</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65334</v>
+        <v>71994</v>
       </c>
       <c r="E12" t="n">
-        <v>10183</v>
+        <v>13321</v>
       </c>
       <c r="F12" t="n">
-        <v>3897</v>
+        <v>908</v>
       </c>
       <c r="G12" t="n">
-        <v>5.96</v>
+        <v>1.26</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5063,25 +5063,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>Retargeting_HighIntent_6Oct</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45483</v>
+        <v>52414</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>17538</v>
       </c>
       <c r="F14" t="n">
-        <v>646</v>
+        <v>1980</v>
       </c>
       <c r="G14" t="n">
-        <v>1.42</v>
+        <v>3.78</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5107,25 +5107,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Retargeting_HighIntent_6Oct</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24902</v>
+        <v>45483</v>
       </c>
       <c r="E15" t="n">
-        <v>6066</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>450</v>
+        <v>646</v>
       </c>
       <c r="G15" t="n">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:00:13</t>
+          <t>Last Updated: 10-10-2026 07:22:50</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>61617.04</v>
+        <v>64314.91</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.74</v>
       </c>
       <c r="D5" t="n">
-        <v>94342.06</v>
+        <v>94453.10000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.74</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>155959.1</v>
+        <v>158768.01</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3955.97</v>
+        <v>6653.84</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13793.48</v>
+        <v>13904.52</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>17749.45</v>
+        <v>20558.36</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:00:44</t>
+          <t>Last Updated: 10-10-2026 07:23:21</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:01:25</t>
+          <t>Last Updated: 10-10-2026 07:24:02</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>98518</v>
+        <v>98547</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>999789</v>
+        <v>1000511</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>56490.37</v>
+        <v>56545.3</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>90577</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1382219</v>
+        <v>1447809</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>61617.03</v>
+        <v>64314.9</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>189095</v>
+        <v>189124</v>
       </c>
       <c r="C7" t="n">
-        <v>2382008</v>
+        <v>2448320</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>118107.4</v>
+        <v>120860.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>667148</v>
+        <v>667611</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>40927.8</v>
+        <v>40966.85</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>332641</v>
+        <v>332900</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>15562.57</v>
+        <v>15578.45</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1292315</v>
+        <v>1354346</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>57518.27</v>
+        <v>60060.94</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>89904</v>
+        <v>93463</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4098.76</v>
+        <v>4253.96</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>98518</v>
+        <v>98547</v>
       </c>
       <c r="C38" t="n">
         <v>293865</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>98518</v>
+        <v>98547</v>
       </c>
       <c r="C39" t="n">
         <v>608394</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7.1</v>
+        <v>12.2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>11.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:02:02</t>
+          <t>Last Updated: 10-10-2026 07:24:39</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>153246</v>
+        <v>153381</v>
       </c>
       <c r="E5" t="n">
-        <v>332641</v>
+        <v>332900</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>15562.57</v>
+        <v>15578.45</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:02:37</t>
+          <t>Last Updated: 10-10-2026 07:25:15</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:02:37</t>
+          <t>Last Updated: 10-10-2026 07:25:15</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:03:13</t>
+          <t>Last Updated: 10-10-2026 07:25:51</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 00:03:49</t>
+          <t>Last Updated: 10-10-2026 07:26:27</t>
         </is>
       </c>
     </row>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1382219</v>
+        <v>1447809</v>
       </c>
       <c r="E4" t="n">
         <v>90577</v>
       </c>
       <c r="F4" t="n">
-        <v>7737</v>
+        <v>8056</v>
       </c>
       <c r="G4" t="n">
         <v>0.5600000000000001</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>667352</v>
+        <v>668082</v>
       </c>
       <c r="E5" t="n">
-        <v>103662</v>
+        <v>103676</v>
       </c>
       <c r="F5" t="n">
-        <v>5398</v>
+        <v>5414</v>
       </c>
       <c r="G5" t="n">
         <v>0.8100000000000001</v>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>517391</v>
+        <v>517718</v>
       </c>
       <c r="E6" t="n">
-        <v>42456</v>
+        <v>42459</v>
       </c>
       <c r="F6" t="n">
-        <v>6545</v>
+        <v>6553</v>
       </c>
       <c r="G6" t="n">
         <v>1.27</v>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>199160</v>
+        <v>199302</v>
       </c>
       <c r="E7" t="n">
-        <v>29189</v>
+        <v>29192</v>
       </c>
       <c r="F7" t="n">
-        <v>2939</v>
+        <v>2941</v>
       </c>
       <c r="G7" t="n">
         <v>1.48</v>
@@ -4808,13 +4808,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>149757</v>
+        <v>149893</v>
       </c>
       <c r="E8" t="n">
-        <v>11689</v>
+        <v>11699</v>
       </c>
       <c r="F8" t="n">
-        <v>2836</v>
+        <v>2840</v>
       </c>
       <c r="G8" t="n">
         <v>1.89</v>
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>137487</v>
+        <v>137589</v>
       </c>
       <c r="E9" t="n">
-        <v>13933</v>
+        <v>13935</v>
       </c>
       <c r="F9" t="n">
-        <v>8565</v>
+        <v>8573</v>
       </c>
       <c r="G9" t="n">
         <v>6.23</v>
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>133481</v>
+        <v>133598</v>
       </c>
       <c r="E10" t="n">
-        <v>15184</v>
+        <v>15197</v>
       </c>
       <c r="F10" t="n">
-        <v>5155</v>
+        <v>5171</v>
       </c>
       <c r="G10" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4940,13 +4940,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74357</v>
+        <v>74426</v>
       </c>
       <c r="E11" t="n">
-        <v>10886</v>
+        <v>10888</v>
       </c>
       <c r="F11" t="n">
-        <v>4422</v>
+        <v>4429</v>
       </c>
       <c r="G11" t="n">
         <v>5.95</v>
@@ -5072,16 +5072,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>52414</v>
+        <v>52615</v>
       </c>
       <c r="E14" t="n">
-        <v>17538</v>
+        <v>17580</v>
       </c>
       <c r="F14" t="n">
-        <v>1980</v>
+        <v>1997</v>
       </c>
       <c r="G14" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:22:50</t>
+          <t>Last Updated: 10-10-2026 22:58:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 09-10-2026)</t>
+          <t>MTD (01-10-2026 → 10-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>64314.91</v>
+        <v>69730.55</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8421.74</v>
+        <v>8421.75</v>
       </c>
       <c r="D5" t="n">
-        <v>94453.10000000001</v>
+        <v>110637.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8421.74</v>
+        <v>8421.75</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>158768.01</v>
+        <v>180368.3</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 08-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 09-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>57661.07</v>
+        <v>64321.04</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>8421.74</v>
       </c>
       <c r="D11" t="n">
-        <v>80548.58</v>
+        <v>94580.39999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8421.74</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>138209.65</v>
+        <v>158901.44</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6653.84</v>
+        <v>5409.51</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D17" t="n">
-        <v>13904.52</v>
+        <v>16057.35</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20558.36</v>
+        <v>21466.86</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:23:21</t>
+          <t>Last Updated: 10-10-2026 22:58:56</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-09 | MTD-1: 2026-10-01 → 2026-10-08</t>
+          <t>MTD: 2026-10-01 → 2026-10-10 | MTD-1: 2026-10-01 → 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-09)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-09)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-08)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-08)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:24:02</t>
+          <t>Last Updated: 10-10-2026 22:59:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-09)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>98547</v>
+        <v>103138</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1000511</v>
+        <v>1104732</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>56545.3</v>
+        <v>63835.75</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>90577</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1447809</v>
+        <v>1568006</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>64314.9</v>
+        <v>69730.55</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>189124</v>
+        <v>193715</v>
       </c>
       <c r="C7" t="n">
-        <v>2448320</v>
+        <v>2672738</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>120860.2</v>
+        <v>133566.3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-09)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>667611</v>
+        <v>727275</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>40966.85</v>
+        <v>45231.88</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>332900</v>
+        <v>377457</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>15578.45</v>
+        <v>18603.87</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-09)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1354346</v>
+        <v>1467893</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>60060.94</v>
+        <v>65171.13</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>93463</v>
+        <v>100113</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4253.96</v>
+        <v>4559.42</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-08)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-09)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>98547</v>
+        <v>103138</v>
       </c>
       <c r="C38" t="n">
-        <v>293865</v>
+        <v>333255</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>12985.61</v>
+        <v>15607.46</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>98547</v>
+        <v>103138</v>
       </c>
       <c r="C39" t="n">
-        <v>608394</v>
+        <v>668165</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>36945.17</v>
+        <v>41010</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>90577</v>
       </c>
       <c r="C44" t="n">
-        <v>1207082</v>
+        <v>1354335</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>53764.52</v>
+        <v>60067.08</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>12.2</v>
+        <v>8.4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>11.7</v>
+        <v>8.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:24:39</t>
+          <t>Last Updated: 10-10-2026 23:00:12</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-09</t>
+          <t>MTD: 2026-10-01 → 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>153381</v>
+        <v>174752</v>
       </c>
       <c r="E5" t="n">
-        <v>332900</v>
+        <v>377457</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>15578.45</v>
+        <v>18603.87</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:25:15</t>
+          <t>Last Updated: 10-10-2026 23:00:48</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:25:15</t>
+          <t>Last Updated: 10-10-2026 23:00:48</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:25:51</t>
+          <t>Last Updated: 10-10-2026 23:01:24</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 07:26:27</t>
+          <t>Last Updated: 10-10-2026 23:02:00</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1447809</v>
+        <v>1568006</v>
       </c>
       <c r="E4" t="n">
         <v>90577</v>
       </c>
       <c r="F4" t="n">
-        <v>8056</v>
+        <v>8637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>668082</v>
+        <v>782920</v>
       </c>
       <c r="E5" t="n">
-        <v>103676</v>
+        <v>114314</v>
       </c>
       <c r="F5" t="n">
-        <v>5414</v>
+        <v>6304</v>
       </c>
       <c r="G5" t="n">
         <v>0.8100000000000001</v>
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>517718</v>
+        <v>563920</v>
       </c>
       <c r="E6" t="n">
-        <v>42459</v>
+        <v>43646</v>
       </c>
       <c r="F6" t="n">
-        <v>6553</v>
+        <v>7048</v>
       </c>
       <c r="G6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>199302</v>
+        <v>222691</v>
       </c>
       <c r="E7" t="n">
-        <v>29192</v>
+        <v>30985</v>
       </c>
       <c r="F7" t="n">
-        <v>2941</v>
+        <v>3214</v>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>149893</v>
+        <v>163355</v>
       </c>
       <c r="E8" t="n">
-        <v>11699</v>
+        <v>12237</v>
       </c>
       <c r="F8" t="n">
-        <v>2840</v>
+        <v>3050</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>137589</v>
+        <v>154766</v>
       </c>
       <c r="E9" t="n">
-        <v>13935</v>
+        <v>16270</v>
       </c>
       <c r="F9" t="n">
-        <v>8573</v>
+        <v>5871</v>
       </c>
       <c r="G9" t="n">
-        <v>6.23</v>
+        <v>3.79</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>133598</v>
+        <v>153703</v>
       </c>
       <c r="E10" t="n">
-        <v>15197</v>
+        <v>14326</v>
       </c>
       <c r="F10" t="n">
-        <v>5171</v>
+        <v>9509</v>
       </c>
       <c r="G10" t="n">
-        <v>3.87</v>
+        <v>6.19</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity_Catalog_3Oct</t>
+          <t>Retargeting_HighIntent_6Oct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74426</v>
+        <v>101934</v>
       </c>
       <c r="E11" t="n">
-        <v>10888</v>
+        <v>28991</v>
       </c>
       <c r="F11" t="n">
-        <v>4429</v>
+        <v>4236</v>
       </c>
       <c r="G11" t="n">
-        <v>5.95</v>
+        <v>4.16</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4975,25 +4975,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71994</v>
+        <v>85216</v>
       </c>
       <c r="E12" t="n">
-        <v>13321</v>
+        <v>11814</v>
       </c>
       <c r="F12" t="n">
-        <v>908</v>
+        <v>5045</v>
       </c>
       <c r="G12" t="n">
-        <v>1.26</v>
+        <v>5.92</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Onboarding_LoginSuccess_3Oct</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5028,16 +5028,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58073</v>
+        <v>71994</v>
       </c>
       <c r="E13" t="n">
-        <v>32648</v>
+        <v>13321</v>
       </c>
       <c r="F13" t="n">
-        <v>1261</v>
+        <v>908</v>
       </c>
       <c r="G13" t="n">
-        <v>2.17</v>
+        <v>1.26</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5063,25 +5063,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Retargeting_HighIntent_6Oct</t>
+          <t>Onboarding_LoginSuccess_3Oct</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>52615</v>
+        <v>58075</v>
       </c>
       <c r="E14" t="n">
-        <v>17580</v>
+        <v>32648</v>
       </c>
       <c r="F14" t="n">
-        <v>1997</v>
+        <v>1261</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>2.17</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 22:58:26</t>
+          <t>Last Updated: 11-10-2026 06:38:31</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>69730.55</v>
+        <v>72104.49000000001</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.75</v>
       </c>
       <c r="D5" t="n">
-        <v>110637.75</v>
+        <v>111238.76</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.75</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>180368.3</v>
+        <v>183343.25</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5409.51</v>
+        <v>7783.45</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0.01</v>
       </c>
       <c r="D17" t="n">
-        <v>16057.35</v>
+        <v>16658.36</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0.01</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>21466.86</v>
+        <v>24441.81</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 22:58:56</t>
+          <t>Last Updated: 11-10-2026 06:39:02</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 22:59:36</t>
+          <t>Last Updated: 11-10-2026 06:39:41</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>103138</v>
+        <v>103250</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1104732</v>
+        <v>1107922</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>63835.75</v>
+        <v>64045.61</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>90577</v>
+        <v>95153</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1568006</v>
+        <v>1624909</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>69730.55</v>
+        <v>72104.5</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>193715</v>
+        <v>198403</v>
       </c>
       <c r="C7" t="n">
-        <v>2672738</v>
+        <v>2732831</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>133566.3</v>
+        <v>136150.11</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>727275</v>
+        <v>729292</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>45231.88</v>
+        <v>45377.01</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>377457</v>
+        <v>378630</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>18603.87</v>
+        <v>18668.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1467893</v>
+        <v>1521410</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>65171.13</v>
+        <v>67399.74000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100113</v>
+        <v>103499</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4559.42</v>
+        <v>4704.76</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>103138</v>
+        <v>103250</v>
       </c>
       <c r="C38" t="n">
         <v>333255</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>103138</v>
+        <v>103250</v>
       </c>
       <c r="C39" t="n">
         <v>668165</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>90577</v>
+        <v>95153</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>90577</v>
+        <v>95153</v>
       </c>
       <c r="C44" t="n">
         <v>1354335</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>8.4</v>
+        <v>12.3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>8.5</v>
+        <v>12.2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 23:00:12</t>
+          <t>Last Updated: 11-10-2026 06:40:19</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>174752</v>
+        <v>175147</v>
       </c>
       <c r="E5" t="n">
-        <v>377457</v>
+        <v>378630</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>18603.87</v>
+        <v>18668.6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 23:00:48</t>
+          <t>Last Updated: 11-10-2026 06:40:54</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 23:00:48</t>
+          <t>Last Updated: 11-10-2026 06:40:54</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 23:01:24</t>
+          <t>Last Updated: 11-10-2026 06:41:29</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 10-10-2026 23:02:00</t>
+          <t>Last Updated: 11-10-2026 06:42:04</t>
         </is>
       </c>
     </row>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1568006</v>
+        <v>1624909</v>
       </c>
       <c r="E4" t="n">
-        <v>90577</v>
+        <v>95153</v>
       </c>
       <c r="F4" t="n">
-        <v>8637</v>
+        <v>8883</v>
       </c>
       <c r="G4" t="n">
         <v>0.55</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>782920</v>
+        <v>788981</v>
       </c>
       <c r="E5" t="n">
-        <v>114314</v>
+        <v>114865</v>
       </c>
       <c r="F5" t="n">
-        <v>6304</v>
+        <v>6360</v>
       </c>
       <c r="G5" t="n">
         <v>0.8100000000000001</v>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>563920</v>
+        <v>565505</v>
       </c>
       <c r="E6" t="n">
-        <v>43646</v>
+        <v>43676</v>
       </c>
       <c r="F6" t="n">
-        <v>7048</v>
+        <v>7079</v>
       </c>
       <c r="G6" t="n">
         <v>1.25</v>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>222691</v>
+        <v>223380</v>
       </c>
       <c r="E7" t="n">
-        <v>30985</v>
+        <v>31028</v>
       </c>
       <c r="F7" t="n">
-        <v>3214</v>
+        <v>3232</v>
       </c>
       <c r="G7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4808,13 +4808,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>163355</v>
+        <v>163787</v>
       </c>
       <c r="E8" t="n">
-        <v>12237</v>
+        <v>12261</v>
       </c>
       <c r="F8" t="n">
-        <v>3050</v>
+        <v>3070</v>
       </c>
       <c r="G8" t="n">
         <v>1.87</v>
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>154766</v>
+        <v>155250</v>
       </c>
       <c r="E9" t="n">
-        <v>16270</v>
+        <v>16285</v>
       </c>
       <c r="F9" t="n">
-        <v>5871</v>
+        <v>5888</v>
       </c>
       <c r="G9" t="n">
         <v>3.79</v>
@@ -4896,13 +4896,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>153703</v>
+        <v>154350</v>
       </c>
       <c r="E10" t="n">
-        <v>14326</v>
+        <v>14358</v>
       </c>
       <c r="F10" t="n">
-        <v>9509</v>
+        <v>9557</v>
       </c>
       <c r="G10" t="n">
         <v>6.19</v>
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>101934</v>
+        <v>103456</v>
       </c>
       <c r="E11" t="n">
-        <v>28991</v>
+        <v>29248</v>
       </c>
       <c r="F11" t="n">
-        <v>4236</v>
+        <v>4318</v>
       </c>
       <c r="G11" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85216</v>
+        <v>85684</v>
       </c>
       <c r="E12" t="n">
-        <v>11814</v>
+        <v>11863</v>
       </c>
       <c r="F12" t="n">
-        <v>5045</v>
+        <v>5072</v>
       </c>
       <c r="G12" t="n">
         <v>5.92</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:38:31</t>
+          <t>Last Updated: 11-10-2026 23:17:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 10-10-2026)</t>
+          <t>MTD (01-10-2026 → 11-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>72104.49000000001</v>
+        <v>77420.2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.75</v>
       </c>
       <c r="D5" t="n">
-        <v>111238.76</v>
+        <v>130274.34</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.75</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>183343.25</v>
+        <v>207694.54</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 09-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 10-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>64321.04</v>
+        <v>72105.13</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8421.74</v>
+        <v>8421.75</v>
       </c>
       <c r="D11" t="n">
-        <v>94580.39999999999</v>
+        <v>111332.56</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8421.74</v>
+        <v>8421.75</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>158901.44</v>
+        <v>183437.69</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7783.45</v>
+        <v>5315.07</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>16658.36</v>
+        <v>18941.78</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>24441.81</v>
+        <v>24256.85</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:39:02</t>
+          <t>Last Updated: 11-10-2026 23:17:55</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-10 | MTD-1: 2026-10-01 → 2026-10-09</t>
+          <t>MTD: 2026-10-01 → 2026-10-11 | MTD-1: 2026-10-01 → 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-10)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-10)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-09)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-09)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:39:41</t>
+          <t>Last Updated: 11-10-2026 23:18:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-10)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>103250</v>
+        <v>106279</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1107922</v>
+        <v>1231397</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>64045.61</v>
+        <v>73440.42999999999</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>95153</v>
+        <v>98817</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1624909</v>
+        <v>1749817</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>72104.5</v>
+        <v>77420.2</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>198403</v>
+        <v>205096</v>
       </c>
       <c r="C7" t="n">
-        <v>2732831</v>
+        <v>2981214</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>136150.11</v>
+        <v>150860.63</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-10)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>729292</v>
+        <v>801056</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>45377.01</v>
+        <v>50878.85</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>378630</v>
+        <v>430341</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>18668.6</v>
+        <v>22561.58</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-10)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1521410</v>
+        <v>1636455</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>67399.74000000001</v>
+        <v>72310.05</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>103499</v>
+        <v>113362</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4704.76</v>
+        <v>5110.15</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-09)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-10)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>103250</v>
+        <v>106279</v>
       </c>
       <c r="C38" t="n">
-        <v>333255</v>
+        <v>378970</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>15607.46</v>
+        <v>18685.08</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>103250</v>
+        <v>106279</v>
       </c>
       <c r="C39" t="n">
-        <v>668165</v>
+        <v>729859</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>41010</v>
+        <v>45398.58</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>95153</v>
+        <v>98817</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>95153</v>
+        <v>98817</v>
       </c>
       <c r="C44" t="n">
-        <v>1354335</v>
+        <v>1521395</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>60067.08</v>
+        <v>67400.21000000001</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19.6</v>
+        <v>20.7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>12.3</v>
+        <v>7.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12.2</v>
+        <v>7.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3147,14 +3147,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:40:19</t>
+          <t>Last Updated: 11-10-2026 23:19:11</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-10</t>
+          <t>MTD: 2026-10-01 → 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>175147</v>
+        <v>197026</v>
       </c>
       <c r="E5" t="n">
-        <v>378630</v>
+        <v>430341</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>18668.6</v>
+        <v>22561.58</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:40:54</t>
+          <t>Last Updated: 11-10-2026 23:19:47</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:40:54</t>
+          <t>Last Updated: 11-10-2026 23:19:47</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:41:29</t>
+          <t>Last Updated: 11-10-2026 23:20:22</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 06:42:04</t>
+          <t>Last Updated: 11-10-2026 23:20:58</t>
         </is>
       </c>
     </row>
@@ -4632,16 +4632,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1624909</v>
+        <v>1749817</v>
       </c>
       <c r="E4" t="n">
-        <v>95153</v>
+        <v>98817</v>
       </c>
       <c r="F4" t="n">
-        <v>8883</v>
+        <v>9495</v>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>788981</v>
+        <v>931890</v>
       </c>
       <c r="E5" t="n">
-        <v>114865</v>
+        <v>124010</v>
       </c>
       <c r="F5" t="n">
-        <v>6360</v>
+        <v>7326</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>565505</v>
+        <v>620394</v>
       </c>
       <c r="E6" t="n">
-        <v>43676</v>
+        <v>44522</v>
       </c>
       <c r="F6" t="n">
-        <v>7079</v>
+        <v>7653</v>
       </c>
       <c r="G6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4764,16 +4764,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223380</v>
+        <v>245402</v>
       </c>
       <c r="E7" t="n">
-        <v>31028</v>
+        <v>31959</v>
       </c>
       <c r="F7" t="n">
-        <v>3232</v>
+        <v>3462</v>
       </c>
       <c r="G7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>163787</v>
+        <v>184939</v>
       </c>
       <c r="E8" t="n">
-        <v>12261</v>
+        <v>17026</v>
       </c>
       <c r="F8" t="n">
-        <v>3070</v>
+        <v>6740</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>3.64</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4852,16 +4852,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>155250</v>
+        <v>180662</v>
       </c>
       <c r="E9" t="n">
-        <v>16285</v>
+        <v>12772</v>
       </c>
       <c r="F9" t="n">
-        <v>5888</v>
+        <v>3377</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79</v>
+        <v>1.87</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154350</v>
+        <v>166744</v>
       </c>
       <c r="E10" t="n">
-        <v>14358</v>
+        <v>14564</v>
       </c>
       <c r="F10" t="n">
-        <v>9557</v>
+        <v>10228</v>
       </c>
       <c r="G10" t="n">
-        <v>6.19</v>
+        <v>6.13</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>103456</v>
+        <v>146917</v>
       </c>
       <c r="E11" t="n">
-        <v>29248</v>
+        <v>34681</v>
       </c>
       <c r="F11" t="n">
-        <v>4318</v>
+        <v>6232</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17</v>
+        <v>4.24</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4984,16 +4984,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>85684</v>
+        <v>96453</v>
       </c>
       <c r="E12" t="n">
-        <v>11863</v>
+        <v>12484</v>
       </c>
       <c r="F12" t="n">
-        <v>5072</v>
+        <v>5656</v>
       </c>
       <c r="G12" t="n">
-        <v>5.92</v>
+        <v>5.86</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58075</v>
+        <v>58076</v>
       </c>
       <c r="E14" t="n">
         <v>32648</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:17:24</t>
+          <t>Last Updated: 12-10-2026 07:00:50</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>77420.2</v>
+        <v>79391.57000000001</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8421.75</v>
       </c>
       <c r="D5" t="n">
-        <v>130274.34</v>
+        <v>130646.7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8421.75</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>207694.54</v>
+        <v>210038.27</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5315.07</v>
+        <v>7286.44</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>18941.78</v>
+        <v>19314.14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>24256.85</v>
+        <v>26600.58</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:17:55</t>
+          <t>Last Updated: 12-10-2026 07:01:21</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:18:34</t>
+          <t>Last Updated: 12-10-2026 07:02:01</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>106279</v>
+        <v>106341</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1231397</v>
+        <v>1232934</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>73440.42999999999</v>
+        <v>73574.44</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>98817</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1749817</v>
+        <v>1798196</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>77420.2</v>
+        <v>79391.58</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>205096</v>
+        <v>205158</v>
       </c>
       <c r="C7" t="n">
-        <v>2981214</v>
+        <v>3031130</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>150860.63</v>
+        <v>152966.02</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>801056</v>
+        <v>801518</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>50878.85</v>
+        <v>50921.61</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>430341</v>
+        <v>431416</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22561.58</v>
+        <v>22652.83</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1636455</v>
+        <v>1682165</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>72310.05</v>
+        <v>74169.07000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>113362</v>
+        <v>116031</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>5110.15</v>
+        <v>5222.51</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>106279</v>
+        <v>106341</v>
       </c>
       <c r="C38" t="n">
         <v>378970</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106279</v>
+        <v>106341</v>
       </c>
       <c r="C39" t="n">
         <v>729859</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7.6</v>
+        <v>10.6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:19:11</t>
+          <t>Last Updated: 12-10-2026 07:02:38</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3227,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>197026</v>
+        <v>197362</v>
       </c>
       <c r="E5" t="n">
-        <v>430341</v>
+        <v>431416</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>22561.58</v>
+        <v>22652.83</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:19:47</t>
+          <t>Last Updated: 12-10-2026 07:03:14</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:19:47</t>
+          <t>Last Updated: 12-10-2026 07:03:14</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:20:22</t>
+          <t>Last Updated: 12-10-2026 07:03:50</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 11-10-2026 23:20:58</t>
+          <t>Last Updated: 12-10-2026 07:04:26</t>
         </is>
       </c>
     </row>
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1749817</v>
+        <v>1798196</v>
       </c>
       <c r="E4" t="n">
         <v>98817</v>
       </c>
       <c r="F4" t="n">
-        <v>9495</v>
+        <v>9688</v>
       </c>
       <c r="G4" t="n">
         <v>0.54</v>
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>931890</v>
+        <v>934737</v>
       </c>
       <c r="E5" t="n">
-        <v>124010</v>
+        <v>124082</v>
       </c>
       <c r="F5" t="n">
-        <v>7326</v>
+        <v>7375</v>
       </c>
       <c r="G5" t="n">
         <v>0.79</v>
@@ -4720,13 +4720,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>620394</v>
+        <v>620774</v>
       </c>
       <c r="E6" t="n">
         <v>44522</v>
       </c>
       <c r="F6" t="n">
-        <v>7653</v>
+        <v>7664</v>
       </c>
       <c r="G6" t="n">
         <v>1.23</v>
@@ -4764,13 +4764,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>245402</v>
+        <v>245841</v>
       </c>
       <c r="E7" t="n">
-        <v>31959</v>
+        <v>32009</v>
       </c>
       <c r="F7" t="n">
-        <v>3462</v>
+        <v>3470</v>
       </c>
       <c r="G7" t="n">
         <v>1.41</v>
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>184939</v>
+        <v>185575</v>
       </c>
       <c r="E8" t="n">
         <v>17026</v>
       </c>
       <c r="F8" t="n">
-        <v>6740</v>
+        <v>6779</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>180662</v>
+        <v>180744</v>
       </c>
       <c r="E9" t="n">
-        <v>12772</v>
+        <v>12784</v>
       </c>
       <c r="F9" t="n">
-        <v>3377</v>
+        <v>3386</v>
       </c>
       <c r="G9" t="n">
         <v>1.87</v>
@@ -4896,16 +4896,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>166744</v>
+        <v>167001</v>
       </c>
       <c r="E10" t="n">
-        <v>14564</v>
+        <v>14592</v>
       </c>
       <c r="F10" t="n">
-        <v>10228</v>
+        <v>10250</v>
       </c>
       <c r="G10" t="n">
-        <v>6.13</v>
+        <v>6.14</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>146917</v>
+        <v>147864</v>
       </c>
       <c r="E11" t="n">
-        <v>34681</v>
+        <v>34780</v>
       </c>
       <c r="F11" t="n">
-        <v>6232</v>
+        <v>6333</v>
       </c>
       <c r="G11" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4984,16 +4984,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>96453</v>
+        <v>96716</v>
       </c>
       <c r="E12" t="n">
-        <v>12484</v>
+        <v>12504</v>
       </c>
       <c r="F12" t="n">
-        <v>5656</v>
+        <v>5703</v>
       </c>
       <c r="G12" t="n">
-        <v>5.86</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:00:50</t>
+          <t>Last Updated: 13-10-2026 02:55:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 11-10-2026)</t>
+          <t>MTD (01-10-2026 → 12-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>79391.57000000001</v>
+        <v>91181.97</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8421.75</v>
+        <v>8470.709999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>130646.7</v>
+        <v>146150.39</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8421.75</v>
+        <v>8470.709999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>210038.27</v>
+        <v>237332.36</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 10-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 11-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>72105.13</v>
+        <v>86680.92999999999</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>8421.75</v>
       </c>
       <c r="D11" t="n">
-        <v>111332.56</v>
+        <v>130646.7</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8421.75</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>183437.69</v>
+        <v>217327.63</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7286.44</v>
+        <v>4501.04</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>48.96</v>
       </c>
       <c r="D17" t="n">
-        <v>19314.14</v>
+        <v>15503.69</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>48.96</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26600.58</v>
+        <v>20004.73</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:01:21</t>
+          <t>Last Updated: 13-10-2026 02:55:43</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-11 | MTD-1: 2026-10-01 → 2026-10-10</t>
+          <t>MTD: 2026-10-01 → 2026-10-12 | MTD-1: 2026-10-01 → 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-11)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-11)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-10)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-10)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:02:01</t>
+          <t>Last Updated: 13-10-2026 02:56:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-11)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>106341</v>
+        <v>109016</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1232934</v>
+        <v>1332138</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>73574.44</v>
+        <v>81089.82000000001</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>98817</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1798196</v>
+        <v>1799189</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>79391.58</v>
+        <v>79487.35000000001</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>205158</v>
+        <v>109016</v>
       </c>
       <c r="C7" t="n">
-        <v>3031130</v>
+        <v>3131327</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>152966.02</v>
+        <v>160577.17</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-11)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>801518</v>
+        <v>859399</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>50921.61</v>
+        <v>55477.19</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>431416</v>
+        <v>472739</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22652.83</v>
+        <v>25612.63</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-11)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1682165</v>
+        <v>1683103</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>74169.07000000001</v>
+        <v>74259.31</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>116031</v>
+        <v>116086</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>5222.51</v>
+        <v>5228.04</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-10)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-11)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>106341</v>
+        <v>109016</v>
       </c>
       <c r="C38" t="n">
-        <v>378970</v>
+        <v>431416</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>18685.08</v>
+        <v>22652.83</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106341</v>
+        <v>109016</v>
       </c>
       <c r="C39" t="n">
-        <v>729859</v>
+        <v>801518</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>45398.58</v>
+        <v>50921.61</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>98817</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>98817</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1521395</v>
+        <v>1682165</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>67400.21000000001</v>
+        <v>74169.07000000001</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>21.2</v>
+        <v>13.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>12.2</v>
+        <v>8.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3057,8 +3057,10 @@
           <t>Brand</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3092,11 +3094,13 @@
           <t>Subcat</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C55" t="n">
-        <v>10.6</v>
+        <v>0.1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3104,7 +3108,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3147,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:02:38</t>
+          <t>Last Updated: 13-10-2026 02:57:00</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-11</t>
+          <t>MTD: 2026-10-01 → 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>197362</v>
+        <v>217458</v>
       </c>
       <c r="E5" t="n">
-        <v>431416</v>
+        <v>472739</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>22652.83</v>
+        <v>25612.63</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3270,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:03:14</t>
+          <t>Last Updated: 13-10-2026 02:57:35</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:03:14</t>
+          <t>Last Updated: 13-10-2026 02:57:35</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:03:50</t>
+          <t>Last Updated: 13-10-2026 02:58:11</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4548,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 12-10-2026 07:04:26</t>
+          <t>Last Updated: 13-10-2026 02:58:48</t>
         </is>
       </c>
     </row>
@@ -4632,13 +4636,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1798196</v>
+        <v>1799189</v>
       </c>
       <c r="E4" t="n">
-        <v>98817</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9688</v>
+        <v>9701</v>
       </c>
       <c r="G4" t="n">
         <v>0.54</v>
@@ -4662,12 +4666,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Activation_FirstPurchase_26Sep</t>
+          <t>UAC_Purchase_6Oct</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4676,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>934737</v>
+        <v>284434</v>
       </c>
       <c r="E5" t="n">
-        <v>124082</v>
+        <v>100908</v>
       </c>
       <c r="F5" t="n">
-        <v>7375</v>
+        <v>1266</v>
       </c>
       <c r="G5" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4706,12 +4710,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Dormant_Users_7July26</t>
+          <t>UAC_LoginSuccess_12Oct</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4720,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>620774</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>44522</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>7664</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4755,7 +4759,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>Activation_FirstPurchase_26Sep</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4764,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>245841</v>
+        <v>1036522</v>
       </c>
       <c r="E7" t="n">
-        <v>32009</v>
+        <v>130607</v>
       </c>
       <c r="F7" t="n">
-        <v>3470</v>
+        <v>8220</v>
       </c>
       <c r="G7" t="n">
-        <v>1.41</v>
+        <v>0.79</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4799,7 +4803,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Dormant_Users_7July26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4808,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>185575</v>
+        <v>664133</v>
       </c>
       <c r="E8" t="n">
-        <v>17026</v>
+        <v>45523</v>
       </c>
       <c r="F8" t="n">
-        <v>6779</v>
+        <v>8292</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4843,7 +4847,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4852,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>180744</v>
+        <v>263084</v>
       </c>
       <c r="E9" t="n">
-        <v>12784</v>
+        <v>32909</v>
       </c>
       <c r="F9" t="n">
-        <v>3386</v>
+        <v>3715</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4887,7 +4891,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4896,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>167001</v>
+        <v>209655</v>
       </c>
       <c r="E10" t="n">
-        <v>14592</v>
+        <v>17450</v>
       </c>
       <c r="F10" t="n">
-        <v>10250</v>
+        <v>7561</v>
       </c>
       <c r="G10" t="n">
-        <v>6.14</v>
+        <v>3.61</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4931,7 +4935,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retargeting_HighIntent_6Oct</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4940,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>147864</v>
+        <v>195266</v>
       </c>
       <c r="E11" t="n">
-        <v>34780</v>
+        <v>13134</v>
       </c>
       <c r="F11" t="n">
-        <v>6333</v>
+        <v>3687</v>
       </c>
       <c r="G11" t="n">
-        <v>4.28</v>
+        <v>1.89</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4975,7 +4979,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity_Catalog_3Oct</t>
+          <t>Retargeting_HighIntent_6Oct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4984,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>96716</v>
+        <v>186366</v>
       </c>
       <c r="E12" t="n">
-        <v>12504</v>
+        <v>38631</v>
       </c>
       <c r="F12" t="n">
-        <v>5703</v>
+        <v>8287</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>4.45</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5019,25 +5023,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>71994</v>
+        <v>178071</v>
       </c>
       <c r="E13" t="n">
-        <v>13321</v>
+        <v>14933</v>
       </c>
       <c r="F13" t="n">
-        <v>908</v>
+        <v>10867</v>
       </c>
       <c r="G13" t="n">
-        <v>1.26</v>
+        <v>6.1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5063,25 +5067,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Onboarding_LoginSuccess_3Oct</t>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58076</v>
+        <v>105716</v>
       </c>
       <c r="E14" t="n">
-        <v>32648</v>
+        <v>13151</v>
       </c>
       <c r="F14" t="n">
-        <v>1261</v>
+        <v>6248</v>
       </c>
       <c r="G14" t="n">
-        <v>2.17</v>
+        <v>5.91</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5107,39 +5111,171 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>71994</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13321</v>
+      </c>
+      <c r="F15" t="n">
+        <v>908</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Onboarding_LoginSuccess_3Oct</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>59058</v>
+      </c>
+      <c r="E16" t="n">
+        <v>33328</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1298</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D17" t="n">
         <v>45483</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>646</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G17" t="n">
         <v>1.42</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>General_Tools_12Oct</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Retention</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6202</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3082</v>
+      </c>
+      <c r="F18" t="n">
+        <v>108</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:55:12</t>
+          <t>Last Updated: 13-10-2026 08:38:24</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8470.709999999999</v>
+        <v>8471.110000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>146150.39</v>
+        <v>146288.59</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8470.709999999999</v>
+        <v>8471.110000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>237332.36</v>
+        <v>237470.56</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>48.96</v>
+        <v>49.36</v>
       </c>
       <c r="D17" t="n">
-        <v>15503.69</v>
+        <v>15641.89</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>48.96</v>
+        <v>49.36</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20004.73</v>
+        <v>20142.93</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:55:43</t>
+          <t>Last Updated: 13-10-2026 08:38:55</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:56:23</t>
+          <t>Last Updated: 13-10-2026 08:39:33</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>109016</v>
+        <v>109030</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1332138</v>
+        <v>1332883</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>81089.82000000001</v>
+        <v>81162.07000000001</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109016</v>
+        <v>109030</v>
       </c>
       <c r="C7" t="n">
-        <v>3131327</v>
+        <v>3132072</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>160577.17</v>
+        <v>160649.42</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>859399</v>
+        <v>859854</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>55477.19</v>
+        <v>55521.65</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>472739</v>
+        <v>473029</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>25612.63</v>
+        <v>25640.42</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>109016</v>
+        <v>109030</v>
       </c>
       <c r="C38" t="n">
         <v>431416</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>109016</v>
+        <v>109030</v>
       </c>
       <c r="C39" t="n">
         <v>801518</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:57:00</t>
+          <t>Last Updated: 13-10-2026 08:40:09</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>217458</v>
+        <v>217556</v>
       </c>
       <c r="E5" t="n">
-        <v>472739</v>
+        <v>473029</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>25612.63</v>
+        <v>25640.42</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:57:35</t>
+          <t>Last Updated: 13-10-2026 08:40:43</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:57:35</t>
+          <t>Last Updated: 13-10-2026 08:40:43</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:58:11</t>
+          <t>Last Updated: 13-10-2026 08:41:18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 02:58:48</t>
+          <t>Last Updated: 13-10-2026 08:41:54</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1036522</v>
+        <v>1037005</v>
       </c>
       <c r="E7" t="n">
-        <v>130607</v>
+        <v>130609</v>
       </c>
       <c r="F7" t="n">
-        <v>8220</v>
+        <v>8228</v>
       </c>
       <c r="G7" t="n">
         <v>0.79</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>664133</v>
+        <v>664476</v>
       </c>
       <c r="E8" t="n">
-        <v>45523</v>
+        <v>45524</v>
       </c>
       <c r="F8" t="n">
-        <v>8292</v>
+        <v>8302</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>263084</v>
+        <v>263211</v>
       </c>
       <c r="E9" t="n">
         <v>32909</v>
       </c>
       <c r="F9" t="n">
-        <v>3715</v>
+        <v>3719</v>
       </c>
       <c r="G9" t="n">
         <v>1.41</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>209655</v>
+        <v>209818</v>
       </c>
       <c r="E10" t="n">
         <v>17450</v>
       </c>
       <c r="F10" t="n">
-        <v>7561</v>
+        <v>7570</v>
       </c>
       <c r="G10" t="n">
         <v>3.61</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>195266</v>
+        <v>195378</v>
       </c>
       <c r="E11" t="n">
-        <v>13134</v>
+        <v>13147</v>
       </c>
       <c r="F11" t="n">
-        <v>3687</v>
+        <v>3689</v>
       </c>
       <c r="G11" t="n">
         <v>1.89</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>186366</v>
+        <v>186651</v>
       </c>
       <c r="E12" t="n">
-        <v>38631</v>
+        <v>38734</v>
       </c>
       <c r="F12" t="n">
-        <v>8287</v>
+        <v>8298</v>
       </c>
       <c r="G12" t="n">
         <v>4.45</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>178071</v>
+        <v>178146</v>
       </c>
       <c r="E13" t="n">
         <v>14933</v>
       </c>
       <c r="F13" t="n">
-        <v>10867</v>
+        <v>10870</v>
       </c>
       <c r="G13" t="n">
         <v>6.1</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>105716</v>
+        <v>105779</v>
       </c>
       <c r="E14" t="n">
         <v>13151</v>
       </c>
       <c r="F14" t="n">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="G14" t="n">
         <v>5.91</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59058</v>
+        <v>59066</v>
       </c>
       <c r="E16" t="n">
         <v>33328</v>
@@ -5252,16 +5252,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6202</v>
+        <v>6251</v>
       </c>
       <c r="E18" t="n">
-        <v>3082</v>
+        <v>3098</v>
       </c>
       <c r="F18" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:38:24</t>
+          <t>Last Updated: 14-10-2026 00:59:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 12-10-2026)</t>
+          <t>MTD (01-10-2026 → 13-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>91181.97</v>
+        <v>93567.58</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8471.110000000001</v>
+        <v>8487.41</v>
       </c>
       <c r="D5" t="n">
-        <v>146288.59</v>
+        <v>166167.73</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8471.110000000001</v>
+        <v>8487.41</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>237470.56</v>
+        <v>259735.31</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 11-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 12-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>86680.92999999999</v>
+        <v>91181.97</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8421.75</v>
+        <v>8471.110000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>130646.7</v>
+        <v>146288.59</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8421.75</v>
+        <v>8471.110000000001</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>217327.63</v>
+        <v>237470.56</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4501.04</v>
+        <v>2385.61</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>49.36</v>
+        <v>16.3</v>
       </c>
       <c r="D17" t="n">
-        <v>15641.89</v>
+        <v>19879.14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>49.36</v>
+        <v>16.3</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20142.93</v>
+        <v>22264.75</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:38:55</t>
+          <t>Last Updated: 14-10-2026 01:00:27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-12 | MTD-1: 2026-10-01 → 2026-10-11</t>
+          <t>MTD: 2026-10-01 → 2026-10-13 | MTD-1: 2026-10-01 → 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-12)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-12)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-11)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-11)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:39:33</t>
+          <t>Last Updated: 14-10-2026 01:01:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-12)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>109030</v>
+        <v>113229</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1332883</v>
+        <v>1441989</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>81162.07000000001</v>
+        <v>89358.71000000001</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109030</v>
+        <v>113229</v>
       </c>
       <c r="C7" t="n">
-        <v>3132072</v>
+        <v>3241178</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>160649.42</v>
+        <v>168846.06</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-12)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>859854</v>
+        <v>922774</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>55521.65</v>
+        <v>60410.88</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>473029</v>
+        <v>519215</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>25640.42</v>
+        <v>28947.83</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-12)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-11)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-12)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>109030</v>
+        <v>113229</v>
       </c>
       <c r="C38" t="n">
-        <v>431416</v>
+        <v>473029</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>22652.83</v>
+        <v>25640.42</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>109030</v>
+        <v>113229</v>
       </c>
       <c r="C39" t="n">
-        <v>801518</v>
+        <v>859854</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>50921.61</v>
+        <v>55521.65</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1682165</v>
+        <v>1683103</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>74169.07000000001</v>
+        <v>74259.31</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:40:09</t>
+          <t>Last Updated: 14-10-2026 01:01:45</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-12</t>
+          <t>MTD: 2026-10-01 → 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>217556</v>
+        <v>239488</v>
       </c>
       <c r="E5" t="n">
-        <v>473029</v>
+        <v>519215</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>25640.42</v>
+        <v>28947.83</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:40:43</t>
+          <t>Last Updated: 14-10-2026 01:02:21</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:40:43</t>
+          <t>Last Updated: 14-10-2026 01:02:21</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:41:18</t>
+          <t>Last Updated: 14-10-2026 01:02:56</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 13-10-2026 08:41:54</t>
+          <t>Last Updated: 14-10-2026 01:03:32</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>284434</v>
+        <v>284640</v>
       </c>
       <c r="E5" t="n">
-        <v>100908</v>
+        <v>100913</v>
       </c>
       <c r="F5" t="n">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="G5" t="n">
         <v>0.45</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>61131</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>23101</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1037005</v>
+        <v>1198878</v>
       </c>
       <c r="E7" t="n">
-        <v>130609</v>
+        <v>140949</v>
       </c>
       <c r="F7" t="n">
-        <v>8228</v>
+        <v>9540</v>
       </c>
       <c r="G7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>664476</v>
+        <v>713090</v>
       </c>
       <c r="E8" t="n">
-        <v>45524</v>
+        <v>46983</v>
       </c>
       <c r="F8" t="n">
-        <v>8302</v>
+        <v>8934</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>263211</v>
+        <v>284118</v>
       </c>
       <c r="E9" t="n">
-        <v>32909</v>
+        <v>34765</v>
       </c>
       <c r="F9" t="n">
-        <v>3719</v>
+        <v>3977</v>
       </c>
       <c r="G9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>209818</v>
+        <v>235097</v>
       </c>
       <c r="E10" t="n">
-        <v>17450</v>
+        <v>17920</v>
       </c>
       <c r="F10" t="n">
-        <v>7570</v>
+        <v>8436</v>
       </c>
       <c r="G10" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>Retargeting_HighIntent_6Oct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>195378</v>
+        <v>226216</v>
       </c>
       <c r="E11" t="n">
-        <v>13147</v>
+        <v>41431</v>
       </c>
       <c r="F11" t="n">
-        <v>3689</v>
+        <v>10218</v>
       </c>
       <c r="G11" t="n">
-        <v>1.89</v>
+        <v>4.52</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Retargeting_HighIntent_6Oct</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>186651</v>
+        <v>209684</v>
       </c>
       <c r="E12" t="n">
-        <v>38734</v>
+        <v>13561</v>
       </c>
       <c r="F12" t="n">
-        <v>8298</v>
+        <v>3951</v>
       </c>
       <c r="G12" t="n">
-        <v>4.45</v>
+        <v>1.88</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>178146</v>
+        <v>190786</v>
       </c>
       <c r="E13" t="n">
-        <v>14933</v>
+        <v>15089</v>
       </c>
       <c r="F13" t="n">
-        <v>10870</v>
+        <v>11611</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>105779</v>
+        <v>116583</v>
       </c>
       <c r="E14" t="n">
-        <v>13151</v>
+        <v>13763</v>
       </c>
       <c r="F14" t="n">
-        <v>6252</v>
+        <v>6877</v>
       </c>
       <c r="G14" t="n">
-        <v>5.91</v>
+        <v>5.9</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59066</v>
+        <v>59445</v>
       </c>
       <c r="E16" t="n">
-        <v>33328</v>
+        <v>33513</v>
       </c>
       <c r="F16" t="n">
-        <v>1298</v>
+        <v>1313</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5252,16 +5252,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6251</v>
+        <v>19613</v>
       </c>
       <c r="E18" t="n">
-        <v>3098</v>
+        <v>6224</v>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
+        <v>310</v>
       </c>
       <c r="G18" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 00:59:57</t>
+          <t>Last Updated: 14-10-2026 06:50:47</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>93567.58</v>
+        <v>93684.28999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8487.41</v>
       </c>
       <c r="D5" t="n">
-        <v>166167.73</v>
+        <v>166259.9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8487.41</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>259735.31</v>
+        <v>259944.19</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2385.61</v>
+        <v>2502.32</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>16.3</v>
       </c>
       <c r="D17" t="n">
-        <v>19879.14</v>
+        <v>19971.31</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>16.3</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22264.75</v>
+        <v>22473.63</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 01:00:27</t>
+          <t>Last Updated: 14-10-2026 06:51:18</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 01:01:08</t>
+          <t>Last Updated: 14-10-2026 06:51:58</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>113229</v>
+        <v>113321</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1441989</v>
+        <v>1442421</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>89358.71000000001</v>
+        <v>89405.97</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113229</v>
+        <v>113321</v>
       </c>
       <c r="C7" t="n">
-        <v>3241178</v>
+        <v>3241610</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>168846.06</v>
+        <v>168893.32</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>922774</v>
+        <v>923015</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>60410.88</v>
+        <v>60435.07</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>519215</v>
+        <v>519406</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>28947.83</v>
+        <v>28970.9</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113229</v>
+        <v>113321</v>
       </c>
       <c r="C38" t="n">
         <v>473029</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>113229</v>
+        <v>113321</v>
       </c>
       <c r="C39" t="n">
         <v>859854</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 01:01:45</t>
+          <t>Last Updated: 14-10-2026 06:52:36</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>239488</v>
+        <v>239604</v>
       </c>
       <c r="E5" t="n">
-        <v>519215</v>
+        <v>519406</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>28947.83</v>
+        <v>28970.9</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 01:02:21</t>
+          <t>Last Updated: 14-10-2026 06:53:11</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 01:02:21</t>
+          <t>Last Updated: 14-10-2026 06:53:11</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 01:02:56</t>
+          <t>Last Updated: 14-10-2026 06:53:47</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 01:03:32</t>
+          <t>Last Updated: 14-10-2026 06:54:25</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>284640</v>
+        <v>285717</v>
       </c>
       <c r="E5" t="n">
         <v>100913</v>
       </c>
       <c r="F5" t="n">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="G5" t="n">
         <v>0.45</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61131</v>
+        <v>61126</v>
       </c>
       <c r="E6" t="n">
         <v>23101</v>
       </c>
       <c r="F6" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G6" t="n">
         <v>1.31</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1198878</v>
+        <v>1199226</v>
       </c>
       <c r="E7" t="n">
-        <v>140949</v>
+        <v>140953</v>
       </c>
       <c r="F7" t="n">
-        <v>9540</v>
+        <v>9545</v>
       </c>
       <c r="G7" t="n">
         <v>0.8</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>713090</v>
+        <v>713274</v>
       </c>
       <c r="E8" t="n">
-        <v>46983</v>
+        <v>46984</v>
       </c>
       <c r="F8" t="n">
-        <v>8934</v>
+        <v>8937</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>284118</v>
+        <v>284184</v>
       </c>
       <c r="E9" t="n">
-        <v>34765</v>
+        <v>34856</v>
       </c>
       <c r="F9" t="n">
         <v>3977</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>235097</v>
+        <v>235222</v>
       </c>
       <c r="E10" t="n">
         <v>17920</v>
       </c>
       <c r="F10" t="n">
-        <v>8436</v>
+        <v>8441</v>
       </c>
       <c r="G10" t="n">
         <v>3.59</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>226216</v>
+        <v>226367</v>
       </c>
       <c r="E11" t="n">
-        <v>41431</v>
+        <v>41484</v>
       </c>
       <c r="F11" t="n">
-        <v>10218</v>
+        <v>10228</v>
       </c>
       <c r="G11" t="n">
         <v>4.52</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>209684</v>
+        <v>209741</v>
       </c>
       <c r="E12" t="n">
         <v>13561</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>190786</v>
+        <v>190840</v>
       </c>
       <c r="E13" t="n">
         <v>15089</v>
       </c>
       <c r="F13" t="n">
-        <v>11611</v>
+        <v>11613</v>
       </c>
       <c r="G13" t="n">
         <v>6.09</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>116583</v>
+        <v>116641</v>
       </c>
       <c r="E14" t="n">
-        <v>13763</v>
+        <v>13767</v>
       </c>
       <c r="F14" t="n">
-        <v>6877</v>
+        <v>6882</v>
       </c>
       <c r="G14" t="n">
         <v>5.9</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19613</v>
+        <v>19645</v>
       </c>
       <c r="E18" t="n">
-        <v>6224</v>
+        <v>6227</v>
       </c>
       <c r="F18" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G18" t="n">
         <v>1.58</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:50:47</t>
+          <t>Last Updated: 14-10-2026 23:00:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 13-10-2026)</t>
+          <t>MTD (01-10-2026 → 14-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>93684.28999999999</v>
+        <v>97164.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8487.41</v>
+        <v>8493.469999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>166259.9</v>
+        <v>188244.51</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8487.41</v>
+        <v>8493.469999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>259944.19</v>
+        <v>285408.68</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 12-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 13-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>91181.97</v>
+        <v>93684.63</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8471.110000000001</v>
+        <v>8487.469999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>146288.59</v>
+        <v>166462.65</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8471.110000000001</v>
+        <v>8487.469999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>237470.56</v>
+        <v>260147.28</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2502.32</v>
+        <v>3479.54</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.3</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>19971.31</v>
+        <v>21781.86</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>16.3</v>
+        <v>6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22473.63</v>
+        <v>25261.4</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:51:18</t>
+          <t>Last Updated: 14-10-2026 23:01:21</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-13 | MTD-1: 2026-10-01 → 2026-10-12</t>
+          <t>MTD: 2026-10-01 → 2026-10-14 | MTD-1: 2026-10-01 → 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-13)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-13)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-12)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-12)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:51:58</t>
+          <t>Last Updated: 14-10-2026 23:02:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-13)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>113321</v>
+        <v>115483</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1442421</v>
+        <v>1539311</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>89405.97</v>
+        <v>96555.91</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113321</v>
+        <v>115483</v>
       </c>
       <c r="C7" t="n">
-        <v>3241610</v>
+        <v>3338500</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>168893.32</v>
+        <v>176043.26</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-13)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>923015</v>
+        <v>983284</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>60435.07</v>
+        <v>64984.96</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>519406</v>
+        <v>556027</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>28970.9</v>
+        <v>31570.95</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-13)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-12)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113321</v>
+        <v>115483</v>
       </c>
       <c r="C38" t="n">
-        <v>473029</v>
+        <v>519904</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>25640.42</v>
+        <v>29018.87</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>113321</v>
+        <v>115483</v>
       </c>
       <c r="C39" t="n">
-        <v>859854</v>
+        <v>923735</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>55521.65</v>
+        <v>60494.76</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:52:36</t>
+          <t>Last Updated: 14-10-2026 23:02:38</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-13</t>
+          <t>MTD: 2026-10-01 → 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>239604</v>
+        <v>256624</v>
       </c>
       <c r="E5" t="n">
-        <v>519406</v>
+        <v>556027</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>28970.9</v>
+        <v>31570.95</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:53:11</t>
+          <t>Last Updated: 14-10-2026 23:03:13</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:53:11</t>
+          <t>Last Updated: 14-10-2026 23:03:13</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:53:47</t>
+          <t>Last Updated: 14-10-2026 23:03:49</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 06:54:25</t>
+          <t>Last Updated: 14-10-2026 23:04:25</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>285717</v>
+        <v>320871</v>
       </c>
       <c r="E5" t="n">
-        <v>100913</v>
+        <v>104356</v>
       </c>
       <c r="F5" t="n">
-        <v>1280</v>
+        <v>1588</v>
       </c>
       <c r="G5" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61126</v>
+        <v>85937</v>
       </c>
       <c r="E6" t="n">
-        <v>23101</v>
+        <v>31463</v>
       </c>
       <c r="F6" t="n">
-        <v>799</v>
+        <v>1201</v>
       </c>
       <c r="G6" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1199226</v>
+        <v>1346297</v>
       </c>
       <c r="E7" t="n">
-        <v>140953</v>
+        <v>148182</v>
       </c>
       <c r="F7" t="n">
-        <v>9545</v>
+        <v>10553</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>713274</v>
+        <v>759444</v>
       </c>
       <c r="E8" t="n">
-        <v>46984</v>
+        <v>47875</v>
       </c>
       <c r="F8" t="n">
-        <v>8937</v>
+        <v>9477</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>284184</v>
+        <v>300354</v>
       </c>
       <c r="E9" t="n">
-        <v>34856</v>
+        <v>35333</v>
       </c>
       <c r="F9" t="n">
-        <v>3977</v>
+        <v>4146</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>Retargeting_HighIntent_6Oct</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>235222</v>
+        <v>262134</v>
       </c>
       <c r="E10" t="n">
-        <v>17920</v>
+        <v>43303</v>
       </c>
       <c r="F10" t="n">
-        <v>8441</v>
+        <v>11867</v>
       </c>
       <c r="G10" t="n">
-        <v>3.59</v>
+        <v>4.53</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retargeting_HighIntent_6Oct</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>226367</v>
+        <v>255673</v>
       </c>
       <c r="E11" t="n">
-        <v>41484</v>
+        <v>18140</v>
       </c>
       <c r="F11" t="n">
-        <v>10228</v>
+        <v>9028</v>
       </c>
       <c r="G11" t="n">
-        <v>4.52</v>
+        <v>3.53</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>209741</v>
+        <v>223840</v>
       </c>
       <c r="E12" t="n">
-        <v>13561</v>
+        <v>14156</v>
       </c>
       <c r="F12" t="n">
-        <v>3951</v>
+        <v>4178</v>
       </c>
       <c r="G12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>190840</v>
+        <v>202484</v>
       </c>
       <c r="E13" t="n">
-        <v>15089</v>
+        <v>15282</v>
       </c>
       <c r="F13" t="n">
-        <v>11613</v>
+        <v>12213</v>
       </c>
       <c r="G13" t="n">
-        <v>6.09</v>
+        <v>6.03</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>116641</v>
+        <v>126485</v>
       </c>
       <c r="E14" t="n">
-        <v>13767</v>
+        <v>14299</v>
       </c>
       <c r="F14" t="n">
-        <v>6882</v>
+        <v>7443</v>
       </c>
       <c r="G14" t="n">
-        <v>5.9</v>
+        <v>5.88</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5155,25 +5155,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Onboarding_LoginSuccess_3Oct</t>
+          <t>General_PushUnreachable_12Oct</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59445</v>
+        <v>64411</v>
       </c>
       <c r="E16" t="n">
-        <v>33513</v>
+        <v>23064</v>
       </c>
       <c r="F16" t="n">
-        <v>1313</v>
+        <v>1340</v>
       </c>
       <c r="G16" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>Onboarding_LoginSuccess_3Oct</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45483</v>
+        <v>59649</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>33568</v>
       </c>
       <c r="F17" t="n">
-        <v>646</v>
+        <v>1322</v>
       </c>
       <c r="G17" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5243,39 +5243,83 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>45483</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>646</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>General_Tools_12Oct</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>19645</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6227</v>
-      </c>
-      <c r="F18" t="n">
-        <v>311</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="D19" t="n">
+        <v>32201</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7845</v>
+      </c>
+      <c r="F19" t="n">
+        <v>569</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:00:50</t>
+          <t>Last Updated: 15-10-2026 06:12:30</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>97164.17</v>
+        <v>97347.06</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8493.469999999999</v>
+        <v>8493.68</v>
       </c>
       <c r="D5" t="n">
-        <v>188244.51</v>
+        <v>188912.93</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8493.469999999999</v>
+        <v>8493.68</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>285408.68</v>
+        <v>286259.99</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3479.54</v>
+        <v>3662.43</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="D17" t="n">
-        <v>21781.86</v>
+        <v>22450.28</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>25261.4</v>
+        <v>26112.71</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:01:21</t>
+          <t>Last Updated: 15-10-2026 06:13:00</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:02:01</t>
+          <t>Last Updated: 15-10-2026 06:13:39</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>115483</v>
+        <v>115615</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1539311</v>
+        <v>1542961</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>96555.91</v>
+        <v>96858.31</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115483</v>
+        <v>115615</v>
       </c>
       <c r="C7" t="n">
-        <v>3338500</v>
+        <v>3342150</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>176043.26</v>
+        <v>176345.66</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>983284</v>
+        <v>985441</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>64984.96</v>
+        <v>65172.3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>556027</v>
+        <v>557520</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>31570.95</v>
+        <v>31686.01</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>115483</v>
+        <v>115615</v>
       </c>
       <c r="C38" t="n">
         <v>519904</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>115483</v>
+        <v>115615</v>
       </c>
       <c r="C39" t="n">
         <v>923735</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:02:38</t>
+          <t>Last Updated: 15-10-2026 06:14:14</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>256624</v>
+        <v>257207</v>
       </c>
       <c r="E5" t="n">
-        <v>556027</v>
+        <v>557520</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>31570.95</v>
+        <v>31686.01</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:03:13</t>
+          <t>Last Updated: 15-10-2026 06:14:49</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:03:13</t>
+          <t>Last Updated: 15-10-2026 06:14:49</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:03:49</t>
+          <t>Last Updated: 15-10-2026 06:15:24</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 14-10-2026 23:04:25</t>
+          <t>Last Updated: 15-10-2026 06:16:02</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>320871</v>
+        <v>323463</v>
       </c>
       <c r="E5" t="n">
         <v>104356</v>
       </c>
       <c r="F5" t="n">
-        <v>1588</v>
+        <v>1610</v>
       </c>
       <c r="G5" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>85937</v>
+        <v>86022</v>
       </c>
       <c r="E6" t="n">
         <v>31463</v>
       </c>
       <c r="F6" t="n">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="G6" t="n">
         <v>1.4</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1346297</v>
+        <v>1350693</v>
       </c>
       <c r="E7" t="n">
-        <v>148182</v>
+        <v>148186</v>
       </c>
       <c r="F7" t="n">
-        <v>10553</v>
+        <v>10585</v>
       </c>
       <c r="G7" t="n">
         <v>0.78</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>759444</v>
+        <v>761018</v>
       </c>
       <c r="E8" t="n">
-        <v>47875</v>
+        <v>47921</v>
       </c>
       <c r="F8" t="n">
-        <v>9477</v>
+        <v>9499</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>300354</v>
+        <v>301065</v>
       </c>
       <c r="E9" t="n">
-        <v>35333</v>
+        <v>35346</v>
       </c>
       <c r="F9" t="n">
-        <v>4146</v>
+        <v>4151</v>
       </c>
       <c r="G9" t="n">
         <v>1.38</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>262134</v>
+        <v>263452</v>
       </c>
       <c r="E10" t="n">
-        <v>43303</v>
+        <v>43306</v>
       </c>
       <c r="F10" t="n">
-        <v>11867</v>
+        <v>11924</v>
       </c>
       <c r="G10" t="n">
         <v>4.53</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>255673</v>
+        <v>256455</v>
       </c>
       <c r="E11" t="n">
-        <v>18140</v>
+        <v>18143</v>
       </c>
       <c r="F11" t="n">
-        <v>9028</v>
+        <v>9045</v>
       </c>
       <c r="G11" t="n">
         <v>3.53</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>223840</v>
+        <v>224423</v>
       </c>
       <c r="E12" t="n">
-        <v>14156</v>
+        <v>14206</v>
       </c>
       <c r="F12" t="n">
-        <v>4178</v>
+        <v>4191</v>
       </c>
       <c r="G12" t="n">
         <v>1.87</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>202484</v>
+        <v>202788</v>
       </c>
       <c r="E13" t="n">
-        <v>15282</v>
+        <v>15290</v>
       </c>
       <c r="F13" t="n">
-        <v>12213</v>
+        <v>12221</v>
       </c>
       <c r="G13" t="n">
         <v>6.03</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>126485</v>
+        <v>126773</v>
       </c>
       <c r="E14" t="n">
-        <v>14299</v>
+        <v>14310</v>
       </c>
       <c r="F14" t="n">
-        <v>7443</v>
+        <v>7462</v>
       </c>
       <c r="G14" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64411</v>
+        <v>64803</v>
       </c>
       <c r="E16" t="n">
-        <v>23064</v>
+        <v>23136</v>
       </c>
       <c r="F16" t="n">
-        <v>1340</v>
+        <v>1361</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59649</v>
+        <v>59659</v>
       </c>
       <c r="E17" t="n">
         <v>33568</v>
@@ -5296,13 +5296,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32201</v>
+        <v>32433</v>
       </c>
       <c r="E19" t="n">
-        <v>7845</v>
+        <v>7949</v>
       </c>
       <c r="F19" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="G19" t="n">
         <v>1.77</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:12:30</t>
+          <t>Last Updated: 15-10-2026 22:48:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 14-10-2026)</t>
+          <t>MTD (01-10-2026 → 15-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>97347.06</v>
+        <v>101398.07</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8493.68</v>
+        <v>8500.73</v>
       </c>
       <c r="D5" t="n">
-        <v>188912.93</v>
+        <v>210622.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8493.68</v>
+        <v>8500.73</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>286259.99</v>
+        <v>312020.87</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 13-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 14-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>93684.63</v>
+        <v>97343.89</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8487.469999999999</v>
+        <v>8493.68</v>
       </c>
       <c r="D11" t="n">
-        <v>166462.65</v>
+        <v>189158.16</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8487.469999999999</v>
+        <v>8493.68</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>260147.28</v>
+        <v>286502.05</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3662.43</v>
+        <v>4054.18</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>6.21</v>
+        <v>7.05</v>
       </c>
       <c r="D17" t="n">
-        <v>22450.28</v>
+        <v>21464.64</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>6.21</v>
+        <v>7.05</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26112.71</v>
+        <v>25518.82</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:13:00</t>
+          <t>Last Updated: 15-10-2026 22:49:20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-14 | MTD-1: 2026-10-01 → 2026-10-13</t>
+          <t>MTD: 2026-10-01 → 2026-10-15 | MTD-1: 2026-10-01 → 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-14)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-14)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-13)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-13)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:13:39</t>
+          <t>Last Updated: 15-10-2026 22:49:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-14)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>115615</v>
+        <v>118362</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1542961</v>
+        <v>1642938</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>96858.31</v>
+        <v>103990.46</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115615</v>
+        <v>118362</v>
       </c>
       <c r="C7" t="n">
-        <v>3342150</v>
+        <v>3442127</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>176345.66</v>
+        <v>183477.81</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-14)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>985441</v>
+        <v>1036182</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>65172.3</v>
+        <v>68606.2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>557520</v>
+        <v>606756</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>31686.01</v>
+        <v>35384.26</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-14)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-13)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-14)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>115615</v>
+        <v>118362</v>
       </c>
       <c r="C38" t="n">
-        <v>519904</v>
+        <v>557903</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>29018.87</v>
+        <v>31724.29</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>115615</v>
+        <v>118362</v>
       </c>
       <c r="C39" t="n">
-        <v>923735</v>
+        <v>986183</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>60494.76</v>
+        <v>65232.55</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7.7</v>
+        <v>5.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:14:14</t>
+          <t>Last Updated: 15-10-2026 22:50:36</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-14</t>
+          <t>MTD: 2026-10-01 → 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>257207</v>
+        <v>277818</v>
       </c>
       <c r="E5" t="n">
-        <v>557520</v>
+        <v>606756</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>31686.01</v>
+        <v>35384.26</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:14:49</t>
+          <t>Last Updated: 15-10-2026 22:51:11</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:14:49</t>
+          <t>Last Updated: 15-10-2026 22:51:11</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:15:24</t>
+          <t>Last Updated: 15-10-2026 22:51:46</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 06:16:02</t>
+          <t>Last Updated: 15-10-2026 22:52:22</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>323463</v>
+        <v>374477</v>
       </c>
       <c r="E5" t="n">
         <v>104356</v>
       </c>
       <c r="F5" t="n">
-        <v>1610</v>
+        <v>2029</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>86022</v>
+        <v>111237</v>
       </c>
       <c r="E6" t="n">
         <v>31463</v>
       </c>
       <c r="F6" t="n">
-        <v>1203</v>
+        <v>1605</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1350693</v>
+        <v>1484058</v>
       </c>
       <c r="E7" t="n">
-        <v>148186</v>
+        <v>151309</v>
       </c>
       <c r="F7" t="n">
-        <v>10585</v>
+        <v>11419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>761018</v>
+        <v>807669</v>
       </c>
       <c r="E8" t="n">
-        <v>47921</v>
+        <v>49165</v>
       </c>
       <c r="F8" t="n">
-        <v>9499</v>
+        <v>10048</v>
       </c>
       <c r="G8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>301065</v>
+        <v>322272</v>
       </c>
       <c r="E9" t="n">
-        <v>35346</v>
+        <v>36240</v>
       </c>
       <c r="F9" t="n">
-        <v>4151</v>
+        <v>4370</v>
       </c>
       <c r="G9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>263452</v>
+        <v>304967</v>
       </c>
       <c r="E10" t="n">
-        <v>43306</v>
+        <v>45184</v>
       </c>
       <c r="F10" t="n">
-        <v>11924</v>
+        <v>13948</v>
       </c>
       <c r="G10" t="n">
-        <v>4.53</v>
+        <v>4.57</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>256455</v>
+        <v>284484</v>
       </c>
       <c r="E11" t="n">
-        <v>18143</v>
+        <v>18663</v>
       </c>
       <c r="F11" t="n">
-        <v>9045</v>
+        <v>9786</v>
       </c>
       <c r="G11" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>224423</v>
+        <v>228513</v>
       </c>
       <c r="E12" t="n">
-        <v>14206</v>
+        <v>14294</v>
       </c>
       <c r="F12" t="n">
-        <v>4191</v>
+        <v>4246</v>
       </c>
       <c r="G12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>202788</v>
+        <v>216013</v>
       </c>
       <c r="E13" t="n">
-        <v>15290</v>
+        <v>15430</v>
       </c>
       <c r="F13" t="n">
-        <v>12221</v>
+        <v>12933</v>
       </c>
       <c r="G13" t="n">
-        <v>6.03</v>
+        <v>5.99</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>126773</v>
+        <v>138203</v>
       </c>
       <c r="E14" t="n">
-        <v>14310</v>
+        <v>14720</v>
       </c>
       <c r="F14" t="n">
-        <v>7462</v>
+        <v>8172</v>
       </c>
       <c r="G14" t="n">
-        <v>5.89</v>
+        <v>5.91</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5111,25 +5111,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>General_PushUnreachable_12Oct</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>71994</v>
+        <v>124066</v>
       </c>
       <c r="E15" t="n">
-        <v>13321</v>
+        <v>30388</v>
       </c>
       <c r="F15" t="n">
-        <v>908</v>
+        <v>2288</v>
       </c>
       <c r="G15" t="n">
-        <v>1.26</v>
+        <v>1.84</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5155,25 +5155,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>General_PushUnreachable_12Oct</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64803</v>
+        <v>71994</v>
       </c>
       <c r="E16" t="n">
-        <v>23136</v>
+        <v>13321</v>
       </c>
       <c r="F16" t="n">
-        <v>1361</v>
+        <v>908</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59659</v>
+        <v>59785</v>
       </c>
       <c r="E17" t="n">
-        <v>33568</v>
+        <v>33713</v>
       </c>
       <c r="F17" t="n">
-        <v>1322</v>
+        <v>1333</v>
       </c>
       <c r="G17" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5296,16 +5296,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32433</v>
+        <v>43884</v>
       </c>
       <c r="E19" t="n">
-        <v>7949</v>
+        <v>8948</v>
       </c>
       <c r="F19" t="n">
-        <v>575</v>
+        <v>851</v>
       </c>
       <c r="G19" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:48:49</t>
+          <t>Last Updated: 16-10-2026 06:04:35</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>101398.07</v>
+        <v>102135.81</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8500.73</v>
+        <v>8500.84</v>
       </c>
       <c r="D5" t="n">
-        <v>210622.8</v>
+        <v>211557.42</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8500.73</v>
+        <v>8500.84</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>312020.87</v>
+        <v>313693.23</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4054.18</v>
+        <v>4791.92</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>7.05</v>
+        <v>7.16</v>
       </c>
       <c r="D17" t="n">
-        <v>21464.64</v>
+        <v>22399.26</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7.05</v>
+        <v>7.16</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>25518.82</v>
+        <v>27191.18</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:49:20</t>
+          <t>Last Updated: 16-10-2026 06:05:05</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:49:59</t>
+          <t>Last Updated: 16-10-2026 06:05:45</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>118362</v>
+        <v>118425</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1642938</v>
+        <v>1646244</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>103990.46</v>
+        <v>104230.53</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118362</v>
+        <v>118425</v>
       </c>
       <c r="C7" t="n">
-        <v>3442127</v>
+        <v>3445433</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>183477.81</v>
+        <v>183717.88</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1036182</v>
+        <v>1037621</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>68606.2</v>
+        <v>68702.89</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>606756</v>
+        <v>608623</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>35384.26</v>
+        <v>35527.64</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>118362</v>
+        <v>118425</v>
       </c>
       <c r="C38" t="n">
         <v>557903</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>118362</v>
+        <v>118425</v>
       </c>
       <c r="C39" t="n">
         <v>986183</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:50:36</t>
+          <t>Last Updated: 16-10-2026 06:06:20</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>277818</v>
+        <v>278382</v>
       </c>
       <c r="E5" t="n">
-        <v>606756</v>
+        <v>608623</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>35384.26</v>
+        <v>35527.64</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:51:11</t>
+          <t>Last Updated: 16-10-2026 06:06:56</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:51:11</t>
+          <t>Last Updated: 16-10-2026 06:06:56</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:51:46</t>
+          <t>Last Updated: 16-10-2026 06:07:31</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 15-10-2026 22:52:22</t>
+          <t>Last Updated: 16-10-2026 06:08:07</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>374477</v>
+        <v>389112</v>
       </c>
       <c r="E5" t="n">
-        <v>104356</v>
+        <v>108870</v>
       </c>
       <c r="F5" t="n">
-        <v>2029</v>
+        <v>2138</v>
       </c>
       <c r="G5" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>111237</v>
+        <v>111440</v>
       </c>
       <c r="E6" t="n">
-        <v>31463</v>
+        <v>39632</v>
       </c>
       <c r="F6" t="n">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="G6" t="n">
         <v>1.44</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1484058</v>
+        <v>1488525</v>
       </c>
       <c r="E7" t="n">
-        <v>151309</v>
+        <v>151474</v>
       </c>
       <c r="F7" t="n">
-        <v>11419</v>
+        <v>11460</v>
       </c>
       <c r="G7" t="n">
         <v>0.77</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>807669</v>
+        <v>809092</v>
       </c>
       <c r="E8" t="n">
-        <v>49165</v>
+        <v>49193</v>
       </c>
       <c r="F8" t="n">
-        <v>10048</v>
+        <v>10066</v>
       </c>
       <c r="G8" t="n">
         <v>1.24</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>322272</v>
+        <v>323108</v>
       </c>
       <c r="E9" t="n">
-        <v>36240</v>
+        <v>36271</v>
       </c>
       <c r="F9" t="n">
-        <v>4370</v>
+        <v>4384</v>
       </c>
       <c r="G9" t="n">
         <v>1.36</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>304967</v>
+        <v>306369</v>
       </c>
       <c r="E10" t="n">
-        <v>45184</v>
+        <v>45291</v>
       </c>
       <c r="F10" t="n">
-        <v>13948</v>
+        <v>14013</v>
       </c>
       <c r="G10" t="n">
         <v>4.57</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>284484</v>
+        <v>285515</v>
       </c>
       <c r="E11" t="n">
-        <v>18663</v>
+        <v>18667</v>
       </c>
       <c r="F11" t="n">
-        <v>9786</v>
+        <v>9817</v>
       </c>
       <c r="G11" t="n">
         <v>3.44</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>228513</v>
+        <v>228529</v>
       </c>
       <c r="E12" t="n">
         <v>14294</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>216013</v>
+        <v>216543</v>
       </c>
       <c r="E13" t="n">
-        <v>15430</v>
+        <v>15468</v>
       </c>
       <c r="F13" t="n">
-        <v>12933</v>
+        <v>12966</v>
       </c>
       <c r="G13" t="n">
         <v>5.99</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>138203</v>
+        <v>138550</v>
       </c>
       <c r="E14" t="n">
-        <v>14720</v>
+        <v>14737</v>
       </c>
       <c r="F14" t="n">
-        <v>8172</v>
+        <v>8190</v>
       </c>
       <c r="G14" t="n">
         <v>5.91</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>124066</v>
+        <v>128870</v>
       </c>
       <c r="E15" t="n">
-        <v>30388</v>
+        <v>31134</v>
       </c>
       <c r="F15" t="n">
-        <v>2288</v>
+        <v>2382</v>
       </c>
       <c r="G15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59785</v>
+        <v>59791</v>
       </c>
       <c r="E17" t="n">
         <v>33713</v>
       </c>
       <c r="F17" t="n">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="G17" t="n">
         <v>2.23</v>
@@ -5296,16 +5296,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43884</v>
+        <v>44229</v>
       </c>
       <c r="E19" t="n">
-        <v>8948</v>
+        <v>8959</v>
       </c>
       <c r="F19" t="n">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="G19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:04:35</t>
+          <t>Last Updated: 16-10-2026 22:24:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 15-10-2026)</t>
+          <t>MTD (01-10-2026 → 16-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>102135.81</v>
+        <v>106360.31</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8500.84</v>
+        <v>8505.57</v>
       </c>
       <c r="D5" t="n">
-        <v>211557.42</v>
+        <v>233636.79</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8500.84</v>
+        <v>8505.57</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>313693.23</v>
+        <v>339997.1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 14-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 15-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>97343.89</v>
+        <v>102139.02</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8493.68</v>
+        <v>8500.84</v>
       </c>
       <c r="D11" t="n">
-        <v>189158.16</v>
+        <v>211800.97</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8493.68</v>
+        <v>8500.84</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>286502.05</v>
+        <v>313939.99</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4791.92</v>
+        <v>4221.29</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>7.16</v>
+        <v>4.73</v>
       </c>
       <c r="D17" t="n">
-        <v>22399.26</v>
+        <v>21835.82</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7.16</v>
+        <v>4.73</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27191.18</v>
+        <v>26057.11</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:05:05</t>
+          <t>Last Updated: 16-10-2026 22:24:54</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-15 | MTD-1: 2026-10-01 → 2026-10-14</t>
+          <t>MTD: 2026-10-01 → 2026-10-16 | MTD-1: 2026-10-01 → 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-15)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-15)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-14)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-14)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:05:45</t>
+          <t>Last Updated: 16-10-2026 22:25:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-15)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>118425</v>
+        <v>121228</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1646244</v>
+        <v>1734496</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>104230.53</v>
+        <v>110559.68</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118425</v>
+        <v>121228</v>
       </c>
       <c r="C7" t="n">
-        <v>3445433</v>
+        <v>3533685</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>183717.88</v>
+        <v>190047.03</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-15)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1037621</v>
+        <v>1081962</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>68702.89</v>
+        <v>71574.95</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>608623</v>
+        <v>652534</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>35527.64</v>
+        <v>38984.73</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-15)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-14)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>118425</v>
+        <v>121228</v>
       </c>
       <c r="C38" t="n">
-        <v>557903</v>
+        <v>609171</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>31724.29</v>
+        <v>35579.54</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>118425</v>
+        <v>121228</v>
       </c>
       <c r="C39" t="n">
-        <v>986183</v>
+        <v>1038141</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>65232.55</v>
+        <v>68736.67999999999</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:06:20</t>
+          <t>Last Updated: 16-10-2026 22:26:12</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-15</t>
+          <t>MTD: 2026-10-01 → 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>278382</v>
+        <v>297036</v>
       </c>
       <c r="E5" t="n">
-        <v>608623</v>
+        <v>652534</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>35527.64</v>
+        <v>38984.73</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:06:56</t>
+          <t>Last Updated: 16-10-2026 22:26:49</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:06:56</t>
+          <t>Last Updated: 16-10-2026 22:26:49</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:07:31</t>
+          <t>Last Updated: 16-10-2026 22:27:24</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 06:08:07</t>
+          <t>Last Updated: 16-10-2026 22:28:00</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>389112</v>
+        <v>450631</v>
       </c>
       <c r="E5" t="n">
         <v>108870</v>
       </c>
       <c r="F5" t="n">
-        <v>2138</v>
+        <v>2488</v>
       </c>
       <c r="G5" t="n">
         <v>0.55</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>111440</v>
+        <v>134793</v>
       </c>
       <c r="E6" t="n">
         <v>39632</v>
       </c>
       <c r="F6" t="n">
-        <v>1606</v>
+        <v>1974</v>
       </c>
       <c r="G6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1488525</v>
+        <v>1621791</v>
       </c>
       <c r="E7" t="n">
-        <v>151474</v>
+        <v>157890</v>
       </c>
       <c r="F7" t="n">
-        <v>11460</v>
+        <v>12216</v>
       </c>
       <c r="G7" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>809092</v>
+        <v>853432</v>
       </c>
       <c r="E8" t="n">
-        <v>49193</v>
+        <v>50360</v>
       </c>
       <c r="F8" t="n">
-        <v>10066</v>
+        <v>10621</v>
       </c>
       <c r="G8" t="n">
         <v>1.24</v>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>Retargeting_HighIntent_6Oct</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>323108</v>
+        <v>352647</v>
       </c>
       <c r="E9" t="n">
-        <v>36271</v>
+        <v>47552</v>
       </c>
       <c r="F9" t="n">
-        <v>4384</v>
+        <v>16431</v>
       </c>
       <c r="G9" t="n">
-        <v>1.36</v>
+        <v>4.66</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retargeting_HighIntent_6Oct</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>306369</v>
+        <v>342507</v>
       </c>
       <c r="E10" t="n">
-        <v>45291</v>
+        <v>36996</v>
       </c>
       <c r="F10" t="n">
-        <v>14013</v>
+        <v>4579</v>
       </c>
       <c r="G10" t="n">
-        <v>4.57</v>
+        <v>1.34</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>285515</v>
+        <v>310027</v>
       </c>
       <c r="E11" t="n">
-        <v>18667</v>
+        <v>19584</v>
       </c>
       <c r="F11" t="n">
-        <v>9817</v>
+        <v>10410</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>228529</v>
+        <v>228530</v>
       </c>
       <c r="E12" t="n">
         <v>14294</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>216543</v>
+        <v>228334</v>
       </c>
       <c r="E13" t="n">
-        <v>15468</v>
+        <v>15535</v>
       </c>
       <c r="F13" t="n">
-        <v>12966</v>
+        <v>13708</v>
       </c>
       <c r="G13" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity_Catalog_3Oct</t>
+          <t>General_PushUnreachable_12Oct</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>138550</v>
+        <v>187784</v>
       </c>
       <c r="E14" t="n">
-        <v>14737</v>
+        <v>35101</v>
       </c>
       <c r="F14" t="n">
-        <v>8190</v>
+        <v>3312</v>
       </c>
       <c r="G14" t="n">
-        <v>5.91</v>
+        <v>1.76</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General_PushUnreachable_12Oct</t>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>128870</v>
+        <v>149336</v>
       </c>
       <c r="E15" t="n">
-        <v>31134</v>
+        <v>15132</v>
       </c>
       <c r="F15" t="n">
-        <v>2382</v>
+        <v>8888</v>
       </c>
       <c r="G15" t="n">
-        <v>1.85</v>
+        <v>5.95</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59791</v>
+        <v>59899</v>
       </c>
       <c r="E17" t="n">
-        <v>33713</v>
+        <v>33787</v>
       </c>
       <c r="F17" t="n">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="G17" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5243,25 +5243,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_3P_3Aug</t>
+          <t>General_Tools_12Oct</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45483</v>
+        <v>53198</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>9544</v>
       </c>
       <c r="F18" t="n">
-        <v>646</v>
+        <v>1055</v>
       </c>
       <c r="G18" t="n">
-        <v>1.42</v>
+        <v>1.98</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>General_Tools_12Oct</t>
+          <t>AR_Onboarding_Install_3P_3Aug</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>44229</v>
+        <v>45483</v>
       </c>
       <c r="E19" t="n">
-        <v>8959</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>855</v>
+        <v>646</v>
       </c>
       <c r="G19" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:24:23</t>
+          <t>Last Updated: 17-10-2026 06:11:12</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>106360.31</v>
+        <v>107149.91</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8505.57</v>
+        <v>8505.82</v>
       </c>
       <c r="D5" t="n">
-        <v>233636.79</v>
+        <v>234665.26</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8505.57</v>
+        <v>8505.82</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>339997.1</v>
+        <v>341815.17</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4221.29</v>
+        <v>5010.89</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>4.73</v>
+        <v>4.98</v>
       </c>
       <c r="D17" t="n">
-        <v>21835.82</v>
+        <v>22864.29</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4.73</v>
+        <v>4.98</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>26057.11</v>
+        <v>27875.18</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:24:54</t>
+          <t>Last Updated: 17-10-2026 06:11:43</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:25:35</t>
+          <t>Last Updated: 17-10-2026 06:12:22</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>121228</v>
+        <v>121524</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1734496</v>
+        <v>1737314</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>110559.68</v>
+        <v>110776.36</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121228</v>
+        <v>121524</v>
       </c>
       <c r="C7" t="n">
-        <v>3533685</v>
+        <v>3536503</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>190047.03</v>
+        <v>190263.71</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1081962</v>
+        <v>1082721</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>71574.95</v>
+        <v>71632.67999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>652534</v>
+        <v>654593</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>38984.73</v>
+        <v>39143.68</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>121228</v>
+        <v>121524</v>
       </c>
       <c r="C38" t="n">
         <v>609171</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>121228</v>
+        <v>121524</v>
       </c>
       <c r="C39" t="n">
         <v>1038141</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,15 +2980,15 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
         <v>4.2</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>4.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:26:12</t>
+          <t>Last Updated: 17-10-2026 06:12:58</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>297036</v>
+        <v>297870</v>
       </c>
       <c r="E5" t="n">
-        <v>652534</v>
+        <v>654593</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>38984.73</v>
+        <v>39143.68</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:26:49</t>
+          <t>Last Updated: 17-10-2026 06:13:34</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:26:49</t>
+          <t>Last Updated: 17-10-2026 06:13:34</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:27:24</t>
+          <t>Last Updated: 17-10-2026 06:14:09</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 16-10-2026 22:28:00</t>
+          <t>Last Updated: 17-10-2026 06:14:45</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>450631</v>
+        <v>465035</v>
       </c>
       <c r="E5" t="n">
-        <v>108870</v>
+        <v>112579</v>
       </c>
       <c r="F5" t="n">
-        <v>2488</v>
+        <v>2571</v>
       </c>
       <c r="G5" t="n">
         <v>0.55</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>134793</v>
+        <v>135360</v>
       </c>
       <c r="E6" t="n">
-        <v>39632</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="n">
-        <v>1974</v>
+        <v>1985</v>
       </c>
       <c r="G6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1621791</v>
+        <v>1626422</v>
       </c>
       <c r="E7" t="n">
-        <v>157890</v>
+        <v>158040</v>
       </c>
       <c r="F7" t="n">
-        <v>12216</v>
+        <v>12257</v>
       </c>
       <c r="G7" t="n">
         <v>0.75</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>853432</v>
+        <v>854191</v>
       </c>
       <c r="E8" t="n">
-        <v>50360</v>
+        <v>50443</v>
       </c>
       <c r="F8" t="n">
-        <v>10621</v>
+        <v>10636</v>
       </c>
       <c r="G8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>352647</v>
+        <v>354537</v>
       </c>
       <c r="E9" t="n">
-        <v>47552</v>
+        <v>47660</v>
       </c>
       <c r="F9" t="n">
-        <v>16431</v>
+        <v>16519</v>
       </c>
       <c r="G9" t="n">
         <v>4.66</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>342507</v>
+        <v>343733</v>
       </c>
       <c r="E10" t="n">
-        <v>36996</v>
+        <v>37059</v>
       </c>
       <c r="F10" t="n">
-        <v>4579</v>
+        <v>4597</v>
       </c>
       <c r="G10" t="n">
         <v>1.34</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>310027</v>
+        <v>310860</v>
       </c>
       <c r="E11" t="n">
-        <v>19584</v>
+        <v>19728</v>
       </c>
       <c r="F11" t="n">
-        <v>10410</v>
+        <v>10435</v>
       </c>
       <c r="G11" t="n">
         <v>3.36</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>228530</v>
+        <v>228977</v>
       </c>
       <c r="E12" t="n">
-        <v>14294</v>
+        <v>15535</v>
       </c>
       <c r="F12" t="n">
-        <v>4246</v>
+        <v>13740</v>
       </c>
       <c r="G12" t="n">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>228334</v>
+        <v>228530</v>
       </c>
       <c r="E13" t="n">
-        <v>15535</v>
+        <v>14294</v>
       </c>
       <c r="F13" t="n">
-        <v>13708</v>
+        <v>4246</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>187784</v>
+        <v>193655</v>
       </c>
       <c r="E14" t="n">
-        <v>35101</v>
+        <v>35793</v>
       </c>
       <c r="F14" t="n">
-        <v>3312</v>
+        <v>3394</v>
       </c>
       <c r="G14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>149336</v>
+        <v>149730</v>
       </c>
       <c r="E15" t="n">
-        <v>15132</v>
+        <v>15133</v>
       </c>
       <c r="F15" t="n">
-        <v>8888</v>
+        <v>8917</v>
       </c>
       <c r="G15" t="n">
-        <v>5.95</v>
+        <v>5.96</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59899</v>
+        <v>59908</v>
       </c>
       <c r="E17" t="n">
         <v>33787</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53198</v>
+        <v>53647</v>
       </c>
       <c r="E18" t="n">
-        <v>9544</v>
+        <v>9585</v>
       </c>
       <c r="F18" t="n">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="G18" t="n">
         <v>1.98</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:11:12</t>
+          <t>Last Updated: 17-10-2026 21:22:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 16-10-2026)</t>
+          <t>MTD (01-10-2026 → 17-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>107149.91</v>
+        <v>111217.28</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8505.82</v>
+        <v>8514.75</v>
       </c>
       <c r="D5" t="n">
-        <v>234665.26</v>
+        <v>250043.33</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8505.82</v>
+        <v>8514.75</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>341815.17</v>
+        <v>361260.61</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 15-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 16-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>102139.02</v>
+        <v>107151.41</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8500.84</v>
+        <v>8505.91</v>
       </c>
       <c r="D11" t="n">
-        <v>211800.97</v>
+        <v>234895.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8500.84</v>
+        <v>8505.91</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>313939.99</v>
+        <v>342046.81</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5010.89</v>
+        <v>4065.87</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>4.98</v>
+        <v>8.84</v>
       </c>
       <c r="D17" t="n">
-        <v>22864.29</v>
+        <v>15147.93</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4.98</v>
+        <v>8.84</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>27875.18</v>
+        <v>19213.8</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:11:43</t>
+          <t>Last Updated: 17-10-2026 21:22:31</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-16 | MTD-1: 2026-10-01 → 2026-10-15</t>
+          <t>MTD: 2026-10-01 → 2026-10-17 | MTD-1: 2026-10-01 → 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-16)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-16)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-15)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-15)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:12:22</t>
+          <t>Last Updated: 17-10-2026 21:23:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-16)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>121524</v>
+        <v>123799</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1737314</v>
+        <v>1803795</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>110776.36</v>
+        <v>115516.64</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121524</v>
+        <v>123799</v>
       </c>
       <c r="C7" t="n">
-        <v>3536503</v>
+        <v>3602984</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>190263.71</v>
+        <v>195003.99</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-16)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1082721</v>
+        <v>1116949</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>71632.67999999999</v>
+        <v>73874.36</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>654593</v>
+        <v>686846</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>39143.68</v>
+        <v>41642.28</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-16)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-15)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>121524</v>
+        <v>123799</v>
       </c>
       <c r="C38" t="n">
-        <v>609171</v>
+        <v>655185</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>35579.54</v>
+        <v>39183.12</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>121524</v>
+        <v>123799</v>
       </c>
       <c r="C39" t="n">
-        <v>1038141</v>
+        <v>1083121</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>68736.67999999999</v>
+        <v>71658.3</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:12:58</t>
+          <t>Last Updated: 17-10-2026 21:23:48</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-16</t>
+          <t>MTD: 2026-10-01 → 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>297870</v>
+        <v>313847</v>
       </c>
       <c r="E5" t="n">
-        <v>654593</v>
+        <v>686846</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>39143.68</v>
+        <v>41642.28</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:13:34</t>
+          <t>Last Updated: 17-10-2026 21:24:25</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:13:34</t>
+          <t>Last Updated: 17-10-2026 21:24:25</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:14:09</t>
+          <t>Last Updated: 17-10-2026 21:25:00</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 06:14:45</t>
+          <t>Last Updated: 17-10-2026 21:25:37</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>465035</v>
+        <v>542215</v>
       </c>
       <c r="E5" t="n">
         <v>112579</v>
       </c>
       <c r="F5" t="n">
-        <v>2571</v>
+        <v>2954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>135360</v>
+        <v>165537</v>
       </c>
       <c r="E6" t="n">
         <v>46321</v>
       </c>
       <c r="F6" t="n">
-        <v>1985</v>
+        <v>2439</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1626422</v>
+        <v>1717762</v>
       </c>
       <c r="E7" t="n">
-        <v>158040</v>
+        <v>161555</v>
       </c>
       <c r="F7" t="n">
-        <v>12257</v>
+        <v>12936</v>
       </c>
       <c r="G7" t="n">
         <v>0.75</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>854191</v>
+        <v>888419</v>
       </c>
       <c r="E8" t="n">
-        <v>50443</v>
+        <v>50971</v>
       </c>
       <c r="F8" t="n">
-        <v>10636</v>
+        <v>11123</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>354537</v>
+        <v>385927</v>
       </c>
       <c r="E9" t="n">
-        <v>47660</v>
+        <v>48561</v>
       </c>
       <c r="F9" t="n">
-        <v>16519</v>
+        <v>18298</v>
       </c>
       <c r="G9" t="n">
-        <v>4.66</v>
+        <v>4.74</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>343733</v>
+        <v>358593</v>
       </c>
       <c r="E10" t="n">
-        <v>37059</v>
+        <v>37880</v>
       </c>
       <c r="F10" t="n">
-        <v>4597</v>
+        <v>4814</v>
       </c>
       <c r="G10" t="n">
         <v>1.34</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>310860</v>
+        <v>328253</v>
       </c>
       <c r="E11" t="n">
-        <v>19728</v>
+        <v>20651</v>
       </c>
       <c r="F11" t="n">
-        <v>10435</v>
+        <v>10880</v>
       </c>
       <c r="G11" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>228977</v>
+        <v>238188</v>
       </c>
       <c r="E12" t="n">
-        <v>15535</v>
+        <v>15691</v>
       </c>
       <c r="F12" t="n">
-        <v>13740</v>
+        <v>14385</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
         <v>228530</v>
       </c>
       <c r="E13" t="n">
-        <v>14294</v>
+        <v>14297</v>
       </c>
       <c r="F13" t="n">
         <v>4246</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>193655</v>
+        <v>219464</v>
       </c>
       <c r="E14" t="n">
-        <v>35793</v>
+        <v>37805</v>
       </c>
       <c r="F14" t="n">
-        <v>3394</v>
+        <v>3804</v>
       </c>
       <c r="G14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>149730</v>
+        <v>157548</v>
       </c>
       <c r="E15" t="n">
-        <v>15133</v>
+        <v>15434</v>
       </c>
       <c r="F15" t="n">
-        <v>8917</v>
+        <v>9458</v>
       </c>
       <c r="G15" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5199,25 +5199,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Onboarding_LoginSuccess_3Oct</t>
+          <t>General_Tools_12Oct</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59908</v>
+        <v>60488</v>
       </c>
       <c r="E17" t="n">
-        <v>33787</v>
+        <v>9820</v>
       </c>
       <c r="F17" t="n">
-        <v>1339</v>
+        <v>1241</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5243,25 +5243,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General_Tools_12Oct</t>
+          <t>Onboarding_LoginSuccess_3Oct</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53647</v>
+        <v>60111</v>
       </c>
       <c r="E18" t="n">
-        <v>9585</v>
+        <v>33876</v>
       </c>
       <c r="F18" t="n">
-        <v>1062</v>
+        <v>1344</v>
       </c>
       <c r="G18" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:22:01</t>
+          <t>Last Updated: 18-10-2026 05:40:34</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>111217.28</v>
+        <v>112325.92</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8514.75</v>
+        <v>8515.33</v>
       </c>
       <c r="D5" t="n">
-        <v>250043.33</v>
+        <v>251029.18</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8514.75</v>
+        <v>8515.33</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>361260.61</v>
+        <v>363355.1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4065.87</v>
+        <v>5174.51</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>8.84</v>
+        <v>9.42</v>
       </c>
       <c r="D17" t="n">
-        <v>15147.93</v>
+        <v>16133.78</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>8.84</v>
+        <v>9.42</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>19213.8</v>
+        <v>21308.29</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:22:31</t>
+          <t>Last Updated: 18-10-2026 05:41:05</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:23:12</t>
+          <t>Last Updated: 18-10-2026 05:41:43</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>123799</v>
+        <v>124165</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1803795</v>
+        <v>1807604</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>115516.64</v>
+        <v>115722.02</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123799</v>
+        <v>124165</v>
       </c>
       <c r="C7" t="n">
-        <v>3602984</v>
+        <v>3606793</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>195003.99</v>
+        <v>195209.37</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1116949</v>
+        <v>1118969</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>73874.36</v>
+        <v>73974.25</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>686846</v>
+        <v>688635</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>41642.28</v>
+        <v>41747.77</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>123799</v>
+        <v>124165</v>
       </c>
       <c r="C38" t="n">
         <v>655185</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>123799</v>
+        <v>124165</v>
       </c>
       <c r="C39" t="n">
         <v>1083121</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:23:48</t>
+          <t>Last Updated: 18-10-2026 05:42:19</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>313847</v>
+        <v>314543</v>
       </c>
       <c r="E5" t="n">
-        <v>686846</v>
+        <v>688635</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>41642.28</v>
+        <v>41747.77</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:24:25</t>
+          <t>Last Updated: 18-10-2026 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:24:25</t>
+          <t>Last Updated: 18-10-2026 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:25:00</t>
+          <t>Last Updated: 18-10-2026 05:43:29</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 17-10-2026 21:25:37</t>
+          <t>Last Updated: 18-10-2026 05:44:04</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>542215</v>
+        <v>566430</v>
       </c>
       <c r="E5" t="n">
-        <v>112579</v>
+        <v>115800</v>
       </c>
       <c r="F5" t="n">
-        <v>2954</v>
+        <v>3124</v>
       </c>
       <c r="G5" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>165537</v>
+        <v>165795</v>
       </c>
       <c r="E6" t="n">
-        <v>46321</v>
+        <v>52742</v>
       </c>
       <c r="F6" t="n">
-        <v>2439</v>
+        <v>2444</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1717762</v>
+        <v>1729865</v>
       </c>
       <c r="E7" t="n">
-        <v>161555</v>
+        <v>161625</v>
       </c>
       <c r="F7" t="n">
-        <v>12936</v>
+        <v>13032</v>
       </c>
       <c r="G7" t="n">
         <v>0.75</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>888419</v>
+        <v>890439</v>
       </c>
       <c r="E8" t="n">
-        <v>50971</v>
+        <v>51161</v>
       </c>
       <c r="F8" t="n">
-        <v>11123</v>
+        <v>11159</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>385927</v>
+        <v>387911</v>
       </c>
       <c r="E9" t="n">
-        <v>48561</v>
+        <v>48914</v>
       </c>
       <c r="F9" t="n">
-        <v>18298</v>
+        <v>18412</v>
       </c>
       <c r="G9" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>358593</v>
+        <v>359541</v>
       </c>
       <c r="E10" t="n">
-        <v>37880</v>
+        <v>37997</v>
       </c>
       <c r="F10" t="n">
-        <v>4814</v>
+        <v>4826</v>
       </c>
       <c r="G10" t="n">
         <v>1.34</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>328253</v>
+        <v>329094</v>
       </c>
       <c r="E11" t="n">
-        <v>20651</v>
+        <v>20710</v>
       </c>
       <c r="F11" t="n">
-        <v>10880</v>
+        <v>10907</v>
       </c>
       <c r="G11" t="n">
         <v>3.31</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>238188</v>
+        <v>239104</v>
       </c>
       <c r="E12" t="n">
-        <v>15691</v>
+        <v>15711</v>
       </c>
       <c r="F12" t="n">
-        <v>14385</v>
+        <v>14449</v>
       </c>
       <c r="G12" t="n">
         <v>6.04</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>219464</v>
+        <v>219611</v>
       </c>
       <c r="E14" t="n">
-        <v>37805</v>
+        <v>37812</v>
       </c>
       <c r="F14" t="n">
-        <v>3804</v>
+        <v>3808</v>
       </c>
       <c r="G14" t="n">
         <v>1.73</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>157548</v>
+        <v>158172</v>
       </c>
       <c r="E15" t="n">
-        <v>15434</v>
+        <v>15518</v>
       </c>
       <c r="F15" t="n">
-        <v>9458</v>
+        <v>9499</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60488</v>
+        <v>61107</v>
       </c>
       <c r="E17" t="n">
-        <v>9820</v>
+        <v>9858</v>
       </c>
       <c r="F17" t="n">
-        <v>1241</v>
+        <v>1257</v>
       </c>
       <c r="G17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60111</v>
+        <v>60127</v>
       </c>
       <c r="E18" t="n">
         <v>33876</v>
       </c>
       <c r="F18" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="G18" t="n">
         <v>2.24</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:40:34</t>
+          <t>Last Updated: 18-10-2026 21:36:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 17-10-2026)</t>
+          <t>MTD (01-10-2026 → 18-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>112325.92</v>
+        <v>116176.13</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8515.33</v>
+        <v>8525.67</v>
       </c>
       <c r="D5" t="n">
-        <v>251029.18</v>
+        <v>269550.13</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8515.33</v>
+        <v>8525.67</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>363355.1</v>
+        <v>385726.26</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 16-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 17-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>107151.41</v>
+        <v>112327.61</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8505.91</v>
+        <v>8515.360000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>234895.4</v>
+        <v>251059.06</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8505.91</v>
+        <v>8515.360000000001</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>342046.81</v>
+        <v>363386.67</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5174.51</v>
+        <v>3848.52</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>9.42</v>
+        <v>10.31</v>
       </c>
       <c r="D17" t="n">
-        <v>16133.78</v>
+        <v>18491.07</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>9.42</v>
+        <v>10.31</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>21308.29</v>
+        <v>22339.59</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:41:05</t>
+          <t>Last Updated: 18-10-2026 21:37:10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-17 | MTD-1: 2026-10-01 → 2026-10-16</t>
+          <t>MTD: 2026-10-01 → 2026-10-18 | MTD-1: 2026-10-01 → 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-17)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-17)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-16)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-16)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:41:43</t>
+          <t>Last Updated: 18-10-2026 21:37:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-17)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>124165</v>
+        <v>126221</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1807604</v>
+        <v>1891571</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>115722.02</v>
+        <v>121255.38</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124165</v>
+        <v>126221</v>
       </c>
       <c r="C7" t="n">
-        <v>3606793</v>
+        <v>3690760</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>195209.37</v>
+        <v>200742.73</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-17)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1118969</v>
+        <v>1168330</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>73974.25</v>
+        <v>76887.55</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>688635</v>
+        <v>723241</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>41747.77</v>
+        <v>44367.83</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-17)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-16)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-17)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>124165</v>
+        <v>126221</v>
       </c>
       <c r="C38" t="n">
-        <v>655185</v>
+        <v>689011</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>39183.12</v>
+        <v>41747.77</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>124165</v>
+        <v>126221</v>
       </c>
       <c r="C39" t="n">
-        <v>1083121</v>
+        <v>1119222</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>71658.3</v>
+        <v>73974.25</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:42:19</t>
+          <t>Last Updated: 18-10-2026 21:38:27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-17</t>
+          <t>MTD: 2026-10-01 → 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>314543</v>
+        <v>330756</v>
       </c>
       <c r="E5" t="n">
-        <v>688635</v>
+        <v>723241</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>41747.77</v>
+        <v>44367.83</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:42:54</t>
+          <t>Last Updated: 18-10-2026 21:39:02</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:42:54</t>
+          <t>Last Updated: 18-10-2026 21:39:02</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:43:29</t>
+          <t>Last Updated: 18-10-2026 21:39:38</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 05:44:04</t>
+          <t>Last Updated: 18-10-2026 21:40:13</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>566430</v>
+        <v>650483</v>
       </c>
       <c r="E5" t="n">
         <v>115800</v>
       </c>
       <c r="F5" t="n">
-        <v>3124</v>
+        <v>3426</v>
       </c>
       <c r="G5" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>165795</v>
+        <v>193258</v>
       </c>
       <c r="E6" t="n">
         <v>52742</v>
       </c>
       <c r="F6" t="n">
-        <v>2444</v>
+        <v>2891</v>
       </c>
       <c r="G6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1729865</v>
+        <v>1854285</v>
       </c>
       <c r="E7" t="n">
-        <v>161625</v>
+        <v>165002</v>
       </c>
       <c r="F7" t="n">
-        <v>13032</v>
+        <v>13825</v>
       </c>
       <c r="G7" t="n">
         <v>0.75</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>890439</v>
+        <v>939800</v>
       </c>
       <c r="E8" t="n">
-        <v>51161</v>
+        <v>51908</v>
       </c>
       <c r="F8" t="n">
-        <v>11159</v>
+        <v>11712</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>387911</v>
+        <v>432596</v>
       </c>
       <c r="E9" t="n">
-        <v>48914</v>
+        <v>50586</v>
       </c>
       <c r="F9" t="n">
-        <v>18412</v>
+        <v>20726</v>
       </c>
       <c r="G9" t="n">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>359541</v>
+        <v>373880</v>
       </c>
       <c r="E10" t="n">
-        <v>37997</v>
+        <v>38526</v>
       </c>
       <c r="F10" t="n">
-        <v>4826</v>
+        <v>4956</v>
       </c>
       <c r="G10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>329094</v>
+        <v>349361</v>
       </c>
       <c r="E11" t="n">
-        <v>20710</v>
+        <v>21490</v>
       </c>
       <c r="F11" t="n">
-        <v>10907</v>
+        <v>11403</v>
       </c>
       <c r="G11" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
+          <t>General_PushUnreachable_12Oct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>239104</v>
+        <v>261987</v>
       </c>
       <c r="E12" t="n">
-        <v>15711</v>
+        <v>39124</v>
       </c>
       <c r="F12" t="n">
-        <v>14449</v>
+        <v>4304</v>
       </c>
       <c r="G12" t="n">
-        <v>6.04</v>
+        <v>1.64</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>PPV_Sensitivity50_Catalogue_3Sept26 - Copy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>228530</v>
+        <v>247359</v>
       </c>
       <c r="E13" t="n">
-        <v>14297</v>
+        <v>15920</v>
       </c>
       <c r="F13" t="n">
-        <v>4246</v>
+        <v>15019</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>6.07</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General_PushUnreachable_12Oct</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>219611</v>
+        <v>228530</v>
       </c>
       <c r="E14" t="n">
-        <v>37812</v>
+        <v>14297</v>
       </c>
       <c r="F14" t="n">
-        <v>3808</v>
+        <v>4246</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>158172</v>
+        <v>166188</v>
       </c>
       <c r="E15" t="n">
-        <v>15518</v>
+        <v>15922</v>
       </c>
       <c r="F15" t="n">
-        <v>9499</v>
+        <v>10085</v>
       </c>
       <c r="G15" t="n">
-        <v>6.01</v>
+        <v>6.07</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61107</v>
+        <v>69913</v>
       </c>
       <c r="E17" t="n">
-        <v>9858</v>
+        <v>10270</v>
       </c>
       <c r="F17" t="n">
-        <v>1257</v>
+        <v>1473</v>
       </c>
       <c r="G17" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60127</v>
+        <v>60323</v>
       </c>
       <c r="E18" t="n">
-        <v>33876</v>
+        <v>33960</v>
       </c>
       <c r="F18" t="n">
-        <v>1345</v>
+        <v>1354</v>
       </c>
       <c r="G18" t="n">
         <v>2.24</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:36:39</t>
+          <t>Last Updated: 19-10-2026 05:52:05</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>116176.13</v>
+        <v>117357.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8525.67</v>
+        <v>8526.83</v>
       </c>
       <c r="D5" t="n">
-        <v>269550.13</v>
+        <v>271670.53</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8525.67</v>
+        <v>8526.83</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>385726.26</v>
+        <v>389027.7</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3848.52</v>
+        <v>5029.56</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.31</v>
+        <v>11.47</v>
       </c>
       <c r="D17" t="n">
-        <v>18491.07</v>
+        <v>20611.47</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>10.31</v>
+        <v>11.47</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22339.59</v>
+        <v>25641.03</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:37:10</t>
+          <t>Last Updated: 19-10-2026 05:52:36</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:37:50</t>
+          <t>Last Updated: 19-10-2026 05:53:15</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>126221</v>
+        <v>126366</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1891571</v>
+        <v>1901173</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>121255.38</v>
+        <v>122027.66</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>126221</v>
+        <v>126366</v>
       </c>
       <c r="C7" t="n">
-        <v>3690760</v>
+        <v>3700362</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>200742.73</v>
+        <v>201515.01</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1168330</v>
+        <v>1173699</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>76887.55</v>
+        <v>77234.61</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>723241</v>
+        <v>727474</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>44367.83</v>
+        <v>44793.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>126221</v>
+        <v>126366</v>
       </c>
       <c r="C38" t="n">
         <v>689011</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>126221</v>
+        <v>126366</v>
       </c>
       <c r="C39" t="n">
         <v>1119222</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,15 +2980,15 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
         <v>4.4</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>3.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:38:27</t>
+          <t>Last Updated: 19-10-2026 05:53:53</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>330756</v>
+        <v>332436</v>
       </c>
       <c r="E5" t="n">
-        <v>723241</v>
+        <v>727474</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>44367.83</v>
+        <v>44793.05</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:39:02</t>
+          <t>Last Updated: 19-10-2026 05:54:28</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:39:02</t>
+          <t>Last Updated: 19-10-2026 05:54:28</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:39:38</t>
+          <t>Last Updated: 19-10-2026 05:55:04</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 18-10-2026 21:40:13</t>
+          <t>Last Updated: 19-10-2026 05:55:42</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>650483</v>
+        <v>679551</v>
       </c>
       <c r="E5" t="n">
-        <v>115800</v>
+        <v>118851</v>
       </c>
       <c r="F5" t="n">
-        <v>3426</v>
+        <v>3568</v>
       </c>
       <c r="G5" t="n">
         <v>0.53</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>193258</v>
+        <v>196244</v>
       </c>
       <c r="E6" t="n">
-        <v>52742</v>
+        <v>58225</v>
       </c>
       <c r="F6" t="n">
-        <v>2891</v>
+        <v>2965</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1854285</v>
+        <v>1861001</v>
       </c>
       <c r="E7" t="n">
-        <v>165002</v>
+        <v>165531</v>
       </c>
       <c r="F7" t="n">
-        <v>13825</v>
+        <v>13887</v>
       </c>
       <c r="G7" t="n">
         <v>0.75</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>939800</v>
+        <v>945169</v>
       </c>
       <c r="E8" t="n">
-        <v>51908</v>
+        <v>51909</v>
       </c>
       <c r="F8" t="n">
-        <v>11712</v>
+        <v>11783</v>
       </c>
       <c r="G8" t="n">
         <v>1.25</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>432596</v>
+        <v>437232</v>
       </c>
       <c r="E9" t="n">
-        <v>50586</v>
+        <v>50729</v>
       </c>
       <c r="F9" t="n">
-        <v>20726</v>
+        <v>20936</v>
       </c>
       <c r="G9" t="n">
         <v>4.79</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>373880</v>
+        <v>375566</v>
       </c>
       <c r="E10" t="n">
-        <v>38526</v>
+        <v>38528</v>
       </c>
       <c r="F10" t="n">
-        <v>4956</v>
+        <v>4973</v>
       </c>
       <c r="G10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>349361</v>
+        <v>351908</v>
       </c>
       <c r="E11" t="n">
-        <v>21490</v>
+        <v>21632</v>
       </c>
       <c r="F11" t="n">
-        <v>11403</v>
+        <v>11472</v>
       </c>
       <c r="G11" t="n">
         <v>3.26</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>261987</v>
+        <v>267323</v>
       </c>
       <c r="E12" t="n">
-        <v>39124</v>
+        <v>39204</v>
       </c>
       <c r="F12" t="n">
-        <v>4304</v>
+        <v>4378</v>
       </c>
       <c r="G12" t="n">
         <v>1.64</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>247359</v>
+        <v>248483</v>
       </c>
       <c r="E13" t="n">
-        <v>15920</v>
+        <v>15933</v>
       </c>
       <c r="F13" t="n">
-        <v>15019</v>
+        <v>15091</v>
       </c>
       <c r="G13" t="n">
         <v>6.07</v>
@@ -5120,13 +5120,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>166188</v>
+        <v>167263</v>
       </c>
       <c r="E15" t="n">
-        <v>15922</v>
+        <v>15971</v>
       </c>
       <c r="F15" t="n">
-        <v>10085</v>
+        <v>10157</v>
       </c>
       <c r="G15" t="n">
         <v>6.07</v>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69913</v>
+        <v>71011</v>
       </c>
       <c r="E17" t="n">
-        <v>10270</v>
+        <v>10394</v>
       </c>
       <c r="F17" t="n">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="G17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5252,16 +5252,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60323</v>
+        <v>60352</v>
       </c>
       <c r="E18" t="n">
         <v>33960</v>
       </c>
       <c r="F18" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:52:05</t>
+          <t>Last Updated: 20-10-2026 00:21:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 18-10-2026)</t>
+          <t>MTD (01-10-2026 → 19-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>117357.17</v>
+        <v>119551.16</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8526.83</v>
+        <v>8536.23</v>
       </c>
       <c r="D5" t="n">
-        <v>271670.53</v>
+        <v>292774.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8526.83</v>
+        <v>8536.23</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>389027.7</v>
+        <v>412325.76</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 17-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 18-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>112327.61</v>
+        <v>117358.71</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8515.360000000001</v>
+        <v>8526.83</v>
       </c>
       <c r="D11" t="n">
-        <v>251059.06</v>
+        <v>271670.53</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8515.360000000001</v>
+        <v>8526.83</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>363386.67</v>
+        <v>389029.24</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5029.56</v>
+        <v>2192.45</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>11.47</v>
+        <v>9.4</v>
       </c>
       <c r="D17" t="n">
-        <v>20611.47</v>
+        <v>21104.07</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.47</v>
+        <v>9.4</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>25641.03</v>
+        <v>23296.52</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:52:36</t>
+          <t>Last Updated: 20-10-2026 00:21:32</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-18 | MTD-1: 2026-10-01 → 2026-10-17</t>
+          <t>MTD: 2026-10-01 → 2026-10-19 | MTD-1: 2026-10-01 → 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-18)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-18)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-17)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-17)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:53:15</t>
+          <t>Last Updated: 20-10-2026 00:22:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-18)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>126366</v>
+        <v>129242</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1901173</v>
+        <v>2001316</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>122027.66</v>
+        <v>128548.39</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>126366</v>
+        <v>129242</v>
       </c>
       <c r="C7" t="n">
-        <v>3700362</v>
+        <v>3800505</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>201515.01</v>
+        <v>208035.74</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-18)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1173699</v>
+        <v>1225763</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>77234.61</v>
+        <v>80270.35000000001</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>727474</v>
+        <v>775553</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>44793.05</v>
+        <v>48278.04</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-18)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-17)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-18)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>126366</v>
+        <v>129242</v>
       </c>
       <c r="C38" t="n">
-        <v>689011</v>
+        <v>727474</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>41747.77</v>
+        <v>44793.05</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>126366</v>
+        <v>129242</v>
       </c>
       <c r="C39" t="n">
-        <v>1119222</v>
+        <v>1173699</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>73974.25</v>
+        <v>77234.61</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:53:53</t>
+          <t>Last Updated: 20-10-2026 00:22:47</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-18</t>
+          <t>MTD: 2026-10-01 → 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>332436</v>
+        <v>352882</v>
       </c>
       <c r="E5" t="n">
-        <v>727474</v>
+        <v>775553</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>44793.05</v>
+        <v>48278.04</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:54:28</t>
+          <t>Last Updated: 20-10-2026 00:23:21</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:54:28</t>
+          <t>Last Updated: 20-10-2026 00:23:21</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:55:04</t>
+          <t>Last Updated: 20-10-2026 00:23:56</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 19-10-2026 05:55:42</t>
+          <t>Last Updated: 20-10-2026 00:24:33</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>679551</v>
+        <v>749259</v>
       </c>
       <c r="E5" t="n">
-        <v>118851</v>
+        <v>120683</v>
       </c>
       <c r="F5" t="n">
-        <v>3568</v>
+        <v>3779</v>
       </c>
       <c r="G5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>196244</v>
+        <v>212670</v>
       </c>
       <c r="E6" t="n">
-        <v>58225</v>
+        <v>60447</v>
       </c>
       <c r="F6" t="n">
-        <v>2965</v>
+        <v>3260</v>
       </c>
       <c r="G6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1861001</v>
+        <v>1996531</v>
       </c>
       <c r="E7" t="n">
-        <v>165531</v>
+        <v>170156</v>
       </c>
       <c r="F7" t="n">
-        <v>13887</v>
+        <v>14731</v>
       </c>
       <c r="G7" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>945169</v>
+        <v>997233</v>
       </c>
       <c r="E8" t="n">
-        <v>51909</v>
+        <v>52681</v>
       </c>
       <c r="F8" t="n">
-        <v>11783</v>
+        <v>12313</v>
       </c>
       <c r="G8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>437232</v>
+        <v>484595</v>
       </c>
       <c r="E9" t="n">
-        <v>50729</v>
+        <v>52532</v>
       </c>
       <c r="F9" t="n">
-        <v>20936</v>
+        <v>23005</v>
       </c>
       <c r="G9" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>375566</v>
+        <v>399163</v>
       </c>
       <c r="E10" t="n">
-        <v>38528</v>
+        <v>39688</v>
       </c>
       <c r="F10" t="n">
-        <v>4973</v>
+        <v>5199</v>
       </c>
       <c r="G10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>351908</v>
+        <v>376390</v>
       </c>
       <c r="E11" t="n">
-        <v>21632</v>
+        <v>22576</v>
       </c>
       <c r="F11" t="n">
-        <v>11472</v>
+        <v>11968</v>
       </c>
       <c r="G11" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>267323</v>
+        <v>315011</v>
       </c>
       <c r="E12" t="n">
-        <v>39204</v>
+        <v>40703</v>
       </c>
       <c r="F12" t="n">
-        <v>4378</v>
+        <v>4889</v>
       </c>
       <c r="G12" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>248483</v>
+        <v>259155</v>
       </c>
       <c r="E13" t="n">
-        <v>15933</v>
+        <v>16042</v>
       </c>
       <c r="F13" t="n">
-        <v>15091</v>
+        <v>15716</v>
       </c>
       <c r="G13" t="n">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>167263</v>
+        <v>177753</v>
       </c>
       <c r="E15" t="n">
-        <v>15971</v>
+        <v>16483</v>
       </c>
       <c r="F15" t="n">
-        <v>10157</v>
+        <v>10832</v>
       </c>
       <c r="G15" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5155,25 +5155,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AR_Onboarding_Install_1P_18Sept26</t>
+          <t>General_Tools_12Oct</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Retention</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>71994</v>
+        <v>84156</v>
       </c>
       <c r="E16" t="n">
-        <v>13321</v>
+        <v>11035</v>
       </c>
       <c r="F16" t="n">
-        <v>908</v>
+        <v>1773</v>
       </c>
       <c r="G16" t="n">
-        <v>1.26</v>
+        <v>2.11</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5199,25 +5199,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>General_Tools_12Oct</t>
+          <t>AR_Onboarding_Install_1P_18Sept26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Retention</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71011</v>
+        <v>71994</v>
       </c>
       <c r="E17" t="n">
-        <v>10394</v>
+        <v>13321</v>
       </c>
       <c r="F17" t="n">
-        <v>1493</v>
+        <v>908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -5252,16 +5252,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60352</v>
+        <v>60553</v>
       </c>
       <c r="E18" t="n">
-        <v>33960</v>
+        <v>34128</v>
       </c>
       <c r="F18" t="n">
-        <v>1357</v>
+        <v>1368</v>
       </c>
       <c r="G18" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:21:01</t>
+          <t>Last Updated: 20-10-2026 06:42:06</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>119551.16</v>
+        <v>119729.55</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8536.23</v>
       </c>
       <c r="D5" t="n">
-        <v>292774.6</v>
+        <v>292901.46</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8536.23</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>412325.76</v>
+        <v>412631.01</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2192.45</v>
+        <v>2370.84</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>9.4</v>
       </c>
       <c r="D17" t="n">
-        <v>21104.07</v>
+        <v>21230.93</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>9.4</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>23296.52</v>
+        <v>23601.77</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:21:32</t>
+          <t>Last Updated: 20-10-2026 06:42:37</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:22:11</t>
+          <t>Last Updated: 20-10-2026 06:43:22</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>129242</v>
+        <v>129312</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2001316</v>
+        <v>2001717</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>128548.39</v>
+        <v>128581.43</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129242</v>
+        <v>129312</v>
       </c>
       <c r="C7" t="n">
-        <v>3800505</v>
+        <v>3800906</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>208035.74</v>
+        <v>208068.78</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1225763</v>
+        <v>1225977</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>80270.35000000001</v>
+        <v>80286.53999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>775553</v>
+        <v>775740</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>48278.04</v>
+        <v>48294.89</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>129242</v>
+        <v>129312</v>
       </c>
       <c r="C38" t="n">
         <v>727474</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>129242</v>
+        <v>129312</v>
       </c>
       <c r="C39" t="n">
         <v>1173699</v>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:22:47</t>
+          <t>Last Updated: 20-10-2026 06:44:01</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>352882</v>
+        <v>353019</v>
       </c>
       <c r="E5" t="n">
-        <v>775553</v>
+        <v>775740</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>48278.04</v>
+        <v>48294.89</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:23:21</t>
+          <t>Last Updated: 20-10-2026 06:44:38</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:23:21</t>
+          <t>Last Updated: 20-10-2026 06:44:38</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:23:56</t>
+          <t>Last Updated: 20-10-2026 06:45:15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 00:24:33</t>
+          <t>Last Updated: 20-10-2026 06:45:53</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>749259</v>
+        <v>755592</v>
       </c>
       <c r="E5" t="n">
         <v>120683</v>
       </c>
       <c r="F5" t="n">
-        <v>3779</v>
+        <v>3811</v>
       </c>
       <c r="G5" t="n">
         <v>0.5</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1996531</v>
+        <v>1997147</v>
       </c>
       <c r="E7" t="n">
-        <v>170156</v>
+        <v>170300</v>
       </c>
       <c r="F7" t="n">
-        <v>14731</v>
+        <v>14733</v>
       </c>
       <c r="G7" t="n">
         <v>0.74</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>997233</v>
+        <v>997447</v>
       </c>
       <c r="E8" t="n">
-        <v>52681</v>
+        <v>52684</v>
       </c>
       <c r="F8" t="n">
-        <v>12313</v>
+        <v>12320</v>
       </c>
       <c r="G8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>484595</v>
+        <v>484768</v>
       </c>
       <c r="E9" t="n">
-        <v>52532</v>
+        <v>52550</v>
       </c>
       <c r="F9" t="n">
-        <v>23005</v>
+        <v>23010</v>
       </c>
       <c r="G9" t="n">
         <v>4.75</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>399163</v>
+        <v>399236</v>
       </c>
       <c r="E10" t="n">
-        <v>39688</v>
+        <v>39714</v>
       </c>
       <c r="F10" t="n">
-        <v>5199</v>
+        <v>5201</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>376390</v>
+        <v>376504</v>
       </c>
       <c r="E11" t="n">
-        <v>22576</v>
+        <v>22617</v>
       </c>
       <c r="F11" t="n">
         <v>11968</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>315011</v>
+        <v>315229</v>
       </c>
       <c r="E12" t="n">
-        <v>40703</v>
+        <v>40784</v>
       </c>
       <c r="F12" t="n">
-        <v>4889</v>
+        <v>4891</v>
       </c>
       <c r="G12" t="n">
         <v>1.55</v>
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>259155</v>
+        <v>259190</v>
       </c>
       <c r="E13" t="n">
         <v>16042</v>
@@ -5120,13 +5120,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>177753</v>
+        <v>177795</v>
       </c>
       <c r="E15" t="n">
         <v>16483</v>
       </c>
       <c r="F15" t="n">
-        <v>10832</v>
+        <v>10834</v>
       </c>
       <c r="G15" t="n">
         <v>6.09</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>84156</v>
+        <v>84205</v>
       </c>
       <c r="E16" t="n">
-        <v>11035</v>
+        <v>11052</v>
       </c>
       <c r="F16" t="n">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="G16" t="n">
         <v>2.11</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:42:06</t>
+          <t>Last Updated: 20-10-2026 22:58:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 19-10-2026)</t>
+          <t>MTD (01-10-2026 → 20-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>119729.55</v>
+        <v>121231.52</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8536.23</v>
+        <v>8538.92</v>
       </c>
       <c r="D5" t="n">
-        <v>292901.46</v>
+        <v>311191.33</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8536.23</v>
+        <v>8538.92</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>412631.01</v>
+        <v>432422.85</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 18-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 19-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>117358.71</v>
+        <v>119730.18</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8526.83</v>
+        <v>8536.309999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>271670.53</v>
+        <v>293170.53</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8526.83</v>
+        <v>8536.309999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>389029.24</v>
+        <v>412900.71</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2370.84</v>
+        <v>1501.34</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>9.4</v>
+        <v>2.61</v>
       </c>
       <c r="D17" t="n">
-        <v>21230.93</v>
+        <v>18020.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>9.4</v>
+        <v>2.61</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>23601.77</v>
+        <v>19522.14</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:42:37</t>
+          <t>Last Updated: 20-10-2026 22:59:08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-19 | MTD-1: 2026-10-01 → 2026-10-18</t>
+          <t>MTD: 2026-10-01 → 2026-10-20 | MTD-1: 2026-10-01 → 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-19)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-19)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-18)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-18)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:43:22</t>
+          <t>Last Updated: 20-10-2026 22:59:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-19)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>129312</v>
+        <v>131895</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2001717</v>
+        <v>2092677</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>128581.43</v>
+        <v>134736.71</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129312</v>
+        <v>131895</v>
       </c>
       <c r="C7" t="n">
-        <v>3800906</v>
+        <v>3891866</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>208068.78</v>
+        <v>214224.06</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-19)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1225977</v>
+        <v>1274686</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>80286.53999999999</v>
+        <v>83235.19</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>775740</v>
+        <v>817991</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>48294.89</v>
+        <v>51501.52</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-19)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-18)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>129312</v>
+        <v>131895</v>
       </c>
       <c r="C38" t="n">
-        <v>727474</v>
+        <v>776369</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>44793.05</v>
+        <v>48320.89</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>129312</v>
+        <v>131895</v>
       </c>
       <c r="C39" t="n">
-        <v>1173699</v>
+        <v>1226522</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>77234.61</v>
+        <v>80315.25</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,15 +2949,15 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
         <v>6.6</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>7.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:44:01</t>
+          <t>Last Updated: 20-10-2026 23:00:24</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-19</t>
+          <t>MTD: 2026-10-01 → 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>353019</v>
+        <v>371861</v>
       </c>
       <c r="E5" t="n">
-        <v>775740</v>
+        <v>817991</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>48294.89</v>
+        <v>51501.52</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:44:38</t>
+          <t>Last Updated: 20-10-2026 23:00:59</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:44:38</t>
+          <t>Last Updated: 20-10-2026 23:00:59</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:45:15</t>
+          <t>Last Updated: 20-10-2026 23:01:36</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 06:45:53</t>
+          <t>Last Updated: 20-10-2026 23:02:12</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>755592</v>
+        <v>815551</v>
       </c>
       <c r="E5" t="n">
         <v>120683</v>
       </c>
       <c r="F5" t="n">
-        <v>3811</v>
+        <v>3964</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>212670</v>
+        <v>214534</v>
       </c>
       <c r="E6" t="n">
         <v>60447</v>
       </c>
       <c r="F6" t="n">
-        <v>3260</v>
+        <v>3271</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1997147</v>
+        <v>2121584</v>
       </c>
       <c r="E7" t="n">
-        <v>170300</v>
+        <v>175191</v>
       </c>
       <c r="F7" t="n">
-        <v>14733</v>
+        <v>15410</v>
       </c>
       <c r="G7" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>997447</v>
+        <v>1046156</v>
       </c>
       <c r="E8" t="n">
-        <v>52684</v>
+        <v>53220</v>
       </c>
       <c r="F8" t="n">
-        <v>12320</v>
+        <v>12885</v>
       </c>
       <c r="G8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>484768</v>
+        <v>530711</v>
       </c>
       <c r="E9" t="n">
-        <v>52550</v>
+        <v>54478</v>
       </c>
       <c r="F9" t="n">
-        <v>23010</v>
+        <v>24972</v>
       </c>
       <c r="G9" t="n">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>399236</v>
+        <v>420270</v>
       </c>
       <c r="E10" t="n">
-        <v>39714</v>
+        <v>41066</v>
       </c>
       <c r="F10" t="n">
-        <v>5201</v>
+        <v>5429</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>376504</v>
+        <v>397721</v>
       </c>
       <c r="E11" t="n">
-        <v>22617</v>
+        <v>23321</v>
       </c>
       <c r="F11" t="n">
-        <v>11968</v>
+        <v>12380</v>
       </c>
       <c r="G11" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>315229</v>
+        <v>364874</v>
       </c>
       <c r="E12" t="n">
-        <v>40784</v>
+        <v>42532</v>
       </c>
       <c r="F12" t="n">
-        <v>4891</v>
+        <v>5362</v>
       </c>
       <c r="G12" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>259190</v>
+        <v>269101</v>
       </c>
       <c r="E13" t="n">
-        <v>16042</v>
+        <v>16076</v>
       </c>
       <c r="F13" t="n">
-        <v>15716</v>
+        <v>16349</v>
       </c>
       <c r="G13" t="n">
-        <v>6.06</v>
+        <v>6.08</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>177795</v>
+        <v>186974</v>
       </c>
       <c r="E15" t="n">
-        <v>16483</v>
+        <v>16756</v>
       </c>
       <c r="F15" t="n">
-        <v>10834</v>
+        <v>11342</v>
       </c>
       <c r="G15" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>84205</v>
+        <v>94369</v>
       </c>
       <c r="E16" t="n">
-        <v>11052</v>
+        <v>11655</v>
       </c>
       <c r="F16" t="n">
-        <v>1776</v>
+        <v>2024</v>
       </c>
       <c r="G16" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60553</v>
+        <v>60623</v>
       </c>
       <c r="E18" t="n">
-        <v>34128</v>
+        <v>34152</v>
       </c>
       <c r="F18" t="n">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="G18" t="n">
         <v>2.26</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 22:58:37</t>
+          <t>Last Updated: 21-10-2026 06:15:39</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>121231.52</v>
+        <v>121776.1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8538.92</v>
+        <v>8538.98</v>
       </c>
       <c r="D5" t="n">
-        <v>311191.33</v>
+        <v>311816.08</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8538.92</v>
+        <v>8538.98</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>432422.85</v>
+        <v>433592.18</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1501.34</v>
+        <v>2045.92</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="D17" t="n">
-        <v>18020.8</v>
+        <v>18645.55</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>19522.14</v>
+        <v>20691.47</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 22:59:08</t>
+          <t>Last Updated: 21-10-2026 06:16:09</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 22:59:48</t>
+          <t>Last Updated: 21-10-2026 06:16:48</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>131895</v>
+        <v>131975</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2092677</v>
+        <v>2095613</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>134736.71</v>
+        <v>134937.31</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>131895</v>
+        <v>131975</v>
       </c>
       <c r="C7" t="n">
-        <v>3891866</v>
+        <v>3894802</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>214224.06</v>
+        <v>214424.66</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1274686</v>
+        <v>1276346</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>83235.19</v>
+        <v>83329.42999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>817991</v>
+        <v>819267</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>51501.52</v>
+        <v>51607.88</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>131895</v>
+        <v>131975</v>
       </c>
       <c r="C38" t="n">
         <v>776369</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>131895</v>
+        <v>131975</v>
       </c>
       <c r="C39" t="n">
         <v>1226522</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 23:00:24</t>
+          <t>Last Updated: 21-10-2026 06:17:23</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>371861</v>
+        <v>372356</v>
       </c>
       <c r="E5" t="n">
-        <v>817991</v>
+        <v>819267</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>51501.52</v>
+        <v>51607.88</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 23:00:59</t>
+          <t>Last Updated: 21-10-2026 06:17:58</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 23:00:59</t>
+          <t>Last Updated: 21-10-2026 06:17:58</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 23:01:36</t>
+          <t>Last Updated: 21-10-2026 06:18:33</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 20-10-2026 23:02:12</t>
+          <t>Last Updated: 21-10-2026 06:19:09</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>815551</v>
+        <v>832864</v>
       </c>
       <c r="E5" t="n">
-        <v>120683</v>
+        <v>122267</v>
       </c>
       <c r="F5" t="n">
-        <v>3964</v>
+        <v>4021</v>
       </c>
       <c r="G5" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>214534</v>
+        <v>215608</v>
       </c>
       <c r="E6" t="n">
-        <v>60447</v>
+        <v>61082</v>
       </c>
       <c r="F6" t="n">
-        <v>3271</v>
+        <v>3281</v>
       </c>
       <c r="G6" t="n">
         <v>1.52</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2121584</v>
+        <v>2125169</v>
       </c>
       <c r="E7" t="n">
-        <v>175191</v>
+        <v>175196</v>
       </c>
       <c r="F7" t="n">
-        <v>15410</v>
+        <v>15432</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1046156</v>
+        <v>1047816</v>
       </c>
       <c r="E8" t="n">
         <v>53220</v>
       </c>
       <c r="F8" t="n">
-        <v>12885</v>
+        <v>12906</v>
       </c>
       <c r="G8" t="n">
         <v>1.23</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>530711</v>
+        <v>531963</v>
       </c>
       <c r="E9" t="n">
-        <v>54478</v>
+        <v>54726</v>
       </c>
       <c r="F9" t="n">
-        <v>24972</v>
+        <v>25021</v>
       </c>
       <c r="G9" t="n">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>420270</v>
+        <v>420852</v>
       </c>
       <c r="E10" t="n">
-        <v>41066</v>
+        <v>41088</v>
       </c>
       <c r="F10" t="n">
-        <v>5429</v>
+        <v>5436</v>
       </c>
       <c r="G10" t="n">
         <v>1.29</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>397721</v>
+        <v>398415</v>
       </c>
       <c r="E11" t="n">
-        <v>23321</v>
+        <v>23372</v>
       </c>
       <c r="F11" t="n">
-        <v>12380</v>
+        <v>12395</v>
       </c>
       <c r="G11" t="n">
         <v>3.11</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>364874</v>
+        <v>367444</v>
       </c>
       <c r="E12" t="n">
-        <v>42532</v>
+        <v>42613</v>
       </c>
       <c r="F12" t="n">
-        <v>5362</v>
+        <v>5383</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>269101</v>
+        <v>269345</v>
       </c>
       <c r="E13" t="n">
         <v>16076</v>
       </c>
       <c r="F13" t="n">
-        <v>16349</v>
+        <v>16367</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>186974</v>
+        <v>187306</v>
       </c>
       <c r="E15" t="n">
-        <v>16756</v>
+        <v>16779</v>
       </c>
       <c r="F15" t="n">
-        <v>11342</v>
+        <v>11355</v>
       </c>
       <c r="G15" t="n">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>94369</v>
+        <v>94640</v>
       </c>
       <c r="E16" t="n">
-        <v>11655</v>
+        <v>11694</v>
       </c>
       <c r="F16" t="n">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="G16" t="n">
         <v>2.14</v>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60623</v>
+        <v>60625</v>
       </c>
       <c r="E18" t="n">
         <v>34152</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:15:39</t>
+          <t>Last Updated: 21-10-2026 23:05:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 20-10-2026)</t>
+          <t>MTD (01-10-2026 → 21-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>121776.1</v>
+        <v>123152.63</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8538.98</v>
+        <v>8541.93</v>
       </c>
       <c r="D5" t="n">
-        <v>311816.08</v>
+        <v>332583.46</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8538.98</v>
+        <v>8541.93</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>433592.18</v>
+        <v>455736.09</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 19-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 20-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>119730.18</v>
+        <v>121777.21</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8536.309999999999</v>
+        <v>8538.98</v>
       </c>
       <c r="D11" t="n">
-        <v>293170.53</v>
+        <v>312046.44</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8536.309999999999</v>
+        <v>8538.98</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>412900.71</v>
+        <v>433823.65</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2045.92</v>
+        <v>1375.42</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="D17" t="n">
-        <v>18645.55</v>
+        <v>20537.02</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>20691.47</v>
+        <v>21912.44</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:16:09</t>
+          <t>Last Updated: 21-10-2026 23:06:25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-20 | MTD-1: 2026-10-01 → 2026-10-19</t>
+          <t>MTD: 2026-10-01 → 2026-10-21 | MTD-1: 2026-10-01 → 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-20)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-20)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-19)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-19)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:16:48</t>
+          <t>Last Updated: 21-10-2026 23:07:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-20)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>131975</v>
+        <v>134411</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2095613</v>
+        <v>2189208</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>134937.31</v>
+        <v>141384.47</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>131975</v>
+        <v>134411</v>
       </c>
       <c r="C7" t="n">
-        <v>3894802</v>
+        <v>3988397</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>214424.66</v>
+        <v>220871.82</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-20)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1276346</v>
+        <v>1326618</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>83329.42999999999</v>
+        <v>86363.14</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>819267</v>
+        <v>862590</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>51607.88</v>
+        <v>55021.33</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-20)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-19)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>131975</v>
+        <v>134411</v>
       </c>
       <c r="C38" t="n">
-        <v>776369</v>
+        <v>820184</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>48320.89</v>
+        <v>51657.11</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>131975</v>
+        <v>134411</v>
       </c>
       <c r="C39" t="n">
-        <v>1226522</v>
+        <v>1276953</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>80315.25</v>
+        <v>83366.59</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:17:23</t>
+          <t>Last Updated: 21-10-2026 23:07:44</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-20</t>
+          <t>MTD: 2026-10-01 → 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>372356</v>
+        <v>390521</v>
       </c>
       <c r="E5" t="n">
-        <v>819267</v>
+        <v>862590</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>51607.88</v>
+        <v>55021.33</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:17:58</t>
+          <t>Last Updated: 21-10-2026 23:08:21</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:17:58</t>
+          <t>Last Updated: 21-10-2026 23:08:21</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:18:33</t>
+          <t>Last Updated: 21-10-2026 23:08:56</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 06:19:09</t>
+          <t>Last Updated: 21-10-2026 23:09:32</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>832864</v>
+        <v>884597</v>
       </c>
       <c r="E5" t="n">
-        <v>122267</v>
+        <v>123421</v>
       </c>
       <c r="F5" t="n">
-        <v>4021</v>
+        <v>4173</v>
       </c>
       <c r="G5" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>215608</v>
+        <v>217559</v>
       </c>
       <c r="E6" t="n">
-        <v>61082</v>
+        <v>61675</v>
       </c>
       <c r="F6" t="n">
-        <v>3281</v>
+        <v>3303</v>
       </c>
       <c r="G6" t="n">
         <v>1.52</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2125169</v>
+        <v>2249852</v>
       </c>
       <c r="E7" t="n">
-        <v>175196</v>
+        <v>180375</v>
       </c>
       <c r="F7" t="n">
-        <v>15432</v>
+        <v>16331</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1047816</v>
+        <v>1098088</v>
       </c>
       <c r="E8" t="n">
-        <v>53220</v>
+        <v>54144</v>
       </c>
       <c r="F8" t="n">
-        <v>12906</v>
+        <v>13442</v>
       </c>
       <c r="G8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>531963</v>
+        <v>578420</v>
       </c>
       <c r="E9" t="n">
-        <v>54726</v>
+        <v>58097</v>
       </c>
       <c r="F9" t="n">
-        <v>25021</v>
+        <v>26875</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>420852</v>
+        <v>440507</v>
       </c>
       <c r="E10" t="n">
-        <v>41088</v>
+        <v>41669</v>
       </c>
       <c r="F10" t="n">
-        <v>5436</v>
+        <v>5615</v>
       </c>
       <c r="G10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>398415</v>
+        <v>422083</v>
       </c>
       <c r="E11" t="n">
-        <v>23372</v>
+        <v>24305</v>
       </c>
       <c r="F11" t="n">
-        <v>12395</v>
+        <v>12841</v>
       </c>
       <c r="G11" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>367444</v>
+        <v>419177</v>
       </c>
       <c r="E12" t="n">
-        <v>42613</v>
+        <v>43908</v>
       </c>
       <c r="F12" t="n">
-        <v>5383</v>
+        <v>5888</v>
       </c>
       <c r="G12" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>269345</v>
+        <v>280879</v>
       </c>
       <c r="E13" t="n">
-        <v>16076</v>
+        <v>16213</v>
       </c>
       <c r="F13" t="n">
-        <v>16367</v>
+        <v>17074</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>187306</v>
+        <v>198483</v>
       </c>
       <c r="E15" t="n">
-        <v>16779</v>
+        <v>17420</v>
       </c>
       <c r="F15" t="n">
-        <v>11355</v>
+        <v>12002</v>
       </c>
       <c r="G15" t="n">
-        <v>6.06</v>
+        <v>6.05</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>94640</v>
+        <v>106607</v>
       </c>
       <c r="E16" t="n">
-        <v>11694</v>
+        <v>12282</v>
       </c>
       <c r="F16" t="n">
-        <v>2028</v>
+        <v>2272</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60625</v>
+        <v>60677</v>
       </c>
       <c r="E18" t="n">
-        <v>34152</v>
+        <v>34164</v>
       </c>
       <c r="F18" t="n">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="G18" t="n">
         <v>2.26</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:05:55</t>
+          <t>Last Updated: 22-10-2026 06:19:56</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>123152.63</v>
+        <v>123687.45</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>8541.93</v>
       </c>
       <c r="D5" t="n">
-        <v>332583.46</v>
+        <v>333106.13</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8541.93</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>455736.09</v>
+        <v>456793.58</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1375.42</v>
+        <v>1910.24</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>2.95</v>
       </c>
       <c r="D17" t="n">
-        <v>20537.02</v>
+        <v>21059.69</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>2.95</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>21912.44</v>
+        <v>22969.93</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:06:25</t>
+          <t>Last Updated: 22-10-2026 06:20:27</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:07:06</t>
+          <t>Last Updated: 22-10-2026 06:21:06</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>134411</v>
+        <v>134462</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2189208</v>
+        <v>2191600</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>141384.47</v>
+        <v>141568.71</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134411</v>
+        <v>134462</v>
       </c>
       <c r="C7" t="n">
-        <v>3988397</v>
+        <v>3990789</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>220871.82</v>
+        <v>221056.06</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1326618</v>
+        <v>1327565</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>86363.14</v>
+        <v>86422.14</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>862590</v>
+        <v>864035</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>55021.33</v>
+        <v>55146.57</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>134411</v>
+        <v>134462</v>
       </c>
       <c r="C38" t="n">
         <v>820184</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>134411</v>
+        <v>134462</v>
       </c>
       <c r="C39" t="n">
         <v>1276953</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:07:44</t>
+          <t>Last Updated: 22-10-2026 06:21:43</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>390521</v>
+        <v>391120</v>
       </c>
       <c r="E5" t="n">
-        <v>862590</v>
+        <v>864035</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>55021.33</v>
+        <v>55146.57</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:08:21</t>
+          <t>Last Updated: 22-10-2026 06:22:19</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:08:21</t>
+          <t>Last Updated: 22-10-2026 06:22:19</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:08:56</t>
+          <t>Last Updated: 22-10-2026 06:22:54</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 21-10-2026 23:09:32</t>
+          <t>Last Updated: 22-10-2026 06:23:30</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>884597</v>
+        <v>899809</v>
       </c>
       <c r="E5" t="n">
         <v>123421</v>
       </c>
       <c r="F5" t="n">
-        <v>4173</v>
+        <v>4235</v>
       </c>
       <c r="G5" t="n">
         <v>0.47</v>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>217559</v>
+        <v>219236</v>
       </c>
       <c r="E6" t="n">
         <v>61675</v>
       </c>
       <c r="F6" t="n">
-        <v>3303</v>
+        <v>3319</v>
       </c>
       <c r="G6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2249852</v>
+        <v>2252979</v>
       </c>
       <c r="E7" t="n">
-        <v>180375</v>
+        <v>180561</v>
       </c>
       <c r="F7" t="n">
-        <v>16331</v>
+        <v>16351</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1098088</v>
+        <v>1099035</v>
       </c>
       <c r="E8" t="n">
         <v>54144</v>
       </c>
       <c r="F8" t="n">
-        <v>13442</v>
+        <v>13450</v>
       </c>
       <c r="G8" t="n">
         <v>1.22</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>578420</v>
+        <v>579543</v>
       </c>
       <c r="E9" t="n">
-        <v>58097</v>
+        <v>58144</v>
       </c>
       <c r="F9" t="n">
-        <v>26875</v>
+        <v>26923</v>
       </c>
       <c r="G9" t="n">
         <v>4.65</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>440507</v>
+        <v>441198</v>
       </c>
       <c r="E10" t="n">
-        <v>41669</v>
+        <v>41681</v>
       </c>
       <c r="F10" t="n">
-        <v>5615</v>
+        <v>5622</v>
       </c>
       <c r="G10" t="n">
         <v>1.27</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>422083</v>
+        <v>422837</v>
       </c>
       <c r="E11" t="n">
-        <v>24305</v>
+        <v>24340</v>
       </c>
       <c r="F11" t="n">
-        <v>12841</v>
+        <v>12863</v>
       </c>
       <c r="G11" t="n">
         <v>3.04</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>419177</v>
+        <v>420996</v>
       </c>
       <c r="E12" t="n">
-        <v>43908</v>
+        <v>43964</v>
       </c>
       <c r="F12" t="n">
-        <v>5888</v>
+        <v>5910</v>
       </c>
       <c r="G12" t="n">
         <v>1.4</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>280879</v>
+        <v>281180</v>
       </c>
       <c r="E13" t="n">
         <v>16213</v>
       </c>
       <c r="F13" t="n">
-        <v>17074</v>
+        <v>17085</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5120,13 +5120,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>198483</v>
+        <v>198761</v>
       </c>
       <c r="E15" t="n">
         <v>17420</v>
       </c>
       <c r="F15" t="n">
-        <v>12002</v>
+        <v>12023</v>
       </c>
       <c r="G15" t="n">
         <v>6.05</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>106607</v>
+        <v>106928</v>
       </c>
       <c r="E16" t="n">
-        <v>12282</v>
+        <v>12292</v>
       </c>
       <c r="F16" t="n">
-        <v>2272</v>
+        <v>2278</v>
       </c>
       <c r="G16" t="n">
         <v>2.13</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:19:56</t>
+          <t>Last Updated: 22-10-2026 23:01:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 21-10-2026)</t>
+          <t>MTD (01-10-2026 → 22-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>123687.45</v>
+        <v>124516.9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8541.93</v>
+        <v>8553.18</v>
       </c>
       <c r="D5" t="n">
-        <v>333106.13</v>
+        <v>351950.31</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8541.93</v>
+        <v>8553.18</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>456793.58</v>
+        <v>476467.21</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 20-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 21-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>121777.21</v>
+        <v>123687.83</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8538.98</v>
+        <v>8541.93</v>
       </c>
       <c r="D11" t="n">
-        <v>312046.44</v>
+        <v>335564.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8538.98</v>
+        <v>8541.93</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>433823.65</v>
+        <v>459252.63</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1910.24</v>
+        <v>829.0700000000001</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.95</v>
+        <v>11.25</v>
       </c>
       <c r="D17" t="n">
-        <v>21059.69</v>
+        <v>16385.51</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2.95</v>
+        <v>11.25</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22969.93</v>
+        <v>17214.58</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:20:27</t>
+          <t>Last Updated: 22-10-2026 23:02:29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-21 | MTD-1: 2026-10-01 → 2026-10-20</t>
+          <t>MTD: 2026-10-01 → 2026-10-22 | MTD-1: 2026-10-01 → 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-21)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-21)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-20)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-20)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:21:06</t>
+          <t>Last Updated: 22-10-2026 23:03:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-21)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>134462</v>
+        <v>137293</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2191600</v>
+        <v>2294150</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>141568.71</v>
+        <v>148041.04</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134462</v>
+        <v>137293</v>
       </c>
       <c r="C7" t="n">
-        <v>3990789</v>
+        <v>4093339</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>221056.06</v>
+        <v>227528.39</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-21)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1327565</v>
+        <v>1383181</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>86422.14</v>
+        <v>89437.89</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>864035</v>
+        <v>910969</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>55146.57</v>
+        <v>58603.15</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-21)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-20)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>134462</v>
+        <v>137293</v>
       </c>
       <c r="C38" t="n">
-        <v>820184</v>
+        <v>865060</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>51657.11</v>
+        <v>55205.53</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>134462</v>
+        <v>137293</v>
       </c>
       <c r="C39" t="n">
-        <v>1276953</v>
+        <v>1328124</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>83366.59</v>
+        <v>86459.69</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:21:43</t>
+          <t>Last Updated: 22-10-2026 23:03:45</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-21</t>
+          <t>MTD: 2026-10-01 → 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>391120</v>
+        <v>410331</v>
       </c>
       <c r="E5" t="n">
-        <v>864035</v>
+        <v>910969</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>55146.57</v>
+        <v>58603.15</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:22:19</t>
+          <t>Last Updated: 22-10-2026 23:04:20</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:22:19</t>
+          <t>Last Updated: 22-10-2026 23:04:20</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:22:54</t>
+          <t>Last Updated: 22-10-2026 23:04:54</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 06:23:30</t>
+          <t>Last Updated: 22-10-2026 23:05:29</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>899809</v>
+        <v>924860</v>
       </c>
       <c r="E5" t="n">
-        <v>123421</v>
+        <v>124091</v>
       </c>
       <c r="F5" t="n">
-        <v>4235</v>
+        <v>4310</v>
       </c>
       <c r="G5" t="n">
         <v>0.47</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>219236</v>
+        <v>221103</v>
       </c>
       <c r="E6" t="n">
-        <v>61675</v>
+        <v>62230</v>
       </c>
       <c r="F6" t="n">
-        <v>3319</v>
+        <v>3341</v>
       </c>
       <c r="G6" t="n">
         <v>1.51</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2252979</v>
+        <v>2348278</v>
       </c>
       <c r="E7" t="n">
-        <v>180561</v>
+        <v>184256</v>
       </c>
       <c r="F7" t="n">
-        <v>16351</v>
+        <v>17010</v>
       </c>
       <c r="G7" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1099035</v>
+        <v>1154651</v>
       </c>
       <c r="E8" t="n">
-        <v>54144</v>
+        <v>55791</v>
       </c>
       <c r="F8" t="n">
-        <v>13450</v>
+        <v>13979</v>
       </c>
       <c r="G8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>579543</v>
+        <v>623957</v>
       </c>
       <c r="E9" t="n">
-        <v>58144</v>
+        <v>60249</v>
       </c>
       <c r="F9" t="n">
-        <v>26923</v>
+        <v>28913</v>
       </c>
       <c r="G9" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>General_PushUnreachable_12Oct</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>441198</v>
+        <v>459900</v>
       </c>
       <c r="E10" t="n">
-        <v>41681</v>
+        <v>44790</v>
       </c>
       <c r="F10" t="n">
-        <v>5622</v>
+        <v>6252</v>
       </c>
       <c r="G10" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>422837</v>
+        <v>458634</v>
       </c>
       <c r="E11" t="n">
-        <v>24340</v>
+        <v>41934</v>
       </c>
       <c r="F11" t="n">
-        <v>12863</v>
+        <v>5793</v>
       </c>
       <c r="G11" t="n">
-        <v>3.04</v>
+        <v>1.26</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>General_PushUnreachable_12Oct</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>420996</v>
+        <v>452335</v>
       </c>
       <c r="E12" t="n">
-        <v>43964</v>
+        <v>25333</v>
       </c>
       <c r="F12" t="n">
-        <v>5910</v>
+        <v>13350</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>2.95</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>281180</v>
+        <v>294530</v>
       </c>
       <c r="E13" t="n">
-        <v>16213</v>
+        <v>16317</v>
       </c>
       <c r="F13" t="n">
-        <v>17085</v>
+        <v>17907</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>198761</v>
+        <v>214122</v>
       </c>
       <c r="E15" t="n">
-        <v>17420</v>
+        <v>18316</v>
       </c>
       <c r="F15" t="n">
-        <v>12023</v>
+        <v>12831</v>
       </c>
       <c r="G15" t="n">
-        <v>6.05</v>
+        <v>5.99</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>106928</v>
+        <v>122076</v>
       </c>
       <c r="E16" t="n">
-        <v>12292</v>
+        <v>13179</v>
       </c>
       <c r="F16" t="n">
-        <v>2278</v>
+        <v>2512</v>
       </c>
       <c r="G16" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5252,16 +5252,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60677</v>
+        <v>60825</v>
       </c>
       <c r="E18" t="n">
-        <v>34164</v>
+        <v>34273</v>
       </c>
       <c r="F18" t="n">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="G18" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:01:58</t>
+          <t>Last Updated: 23-10-2026 06:19:04</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>124516.9</v>
+        <v>124783.94</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8553.18</v>
+        <v>8554.129999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>351950.31</v>
+        <v>352359.45</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8553.18</v>
+        <v>8554.129999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>476467.21</v>
+        <v>477143.39</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>829.0700000000001</v>
+        <v>1096.11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D17" t="n">
-        <v>16385.51</v>
+        <v>16794.65</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>17214.58</v>
+        <v>17890.76</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:02:29</t>
+          <t>Last Updated: 23-10-2026 06:19:35</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:03:08</t>
+          <t>Last Updated: 23-10-2026 06:20:14</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>137293</v>
+        <v>137470</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2294150</v>
+        <v>2296032</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>148041.04</v>
+        <v>148177.57</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>137293</v>
+        <v>137470</v>
       </c>
       <c r="C7" t="n">
-        <v>4093339</v>
+        <v>4095221</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>227528.39</v>
+        <v>227664.92</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1383181</v>
+        <v>1383450</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>89437.89</v>
+        <v>89458.03</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>910969</v>
+        <v>912582</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>58603.15</v>
+        <v>58719.54</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>137293</v>
+        <v>137470</v>
       </c>
       <c r="C38" t="n">
         <v>865060</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>137293</v>
+        <v>137470</v>
       </c>
       <c r="C39" t="n">
         <v>1328124</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:03:45</t>
+          <t>Last Updated: 23-10-2026 06:20:50</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>410331</v>
+        <v>411091</v>
       </c>
       <c r="E5" t="n">
-        <v>910969</v>
+        <v>912582</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>58603.15</v>
+        <v>58719.54</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:04:20</t>
+          <t>Last Updated: 23-10-2026 06:21:26</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:04:20</t>
+          <t>Last Updated: 23-10-2026 06:21:26</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:04:54</t>
+          <t>Last Updated: 23-10-2026 06:22:00</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 22-10-2026 23:05:29</t>
+          <t>Last Updated: 23-10-2026 06:22:36</t>
         </is>
       </c>
     </row>
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>924860</v>
+        <v>931903</v>
       </c>
       <c r="E5" t="n">
         <v>124091</v>
       </c>
       <c r="F5" t="n">
-        <v>4310</v>
+        <v>4329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>221103</v>
+        <v>222383</v>
       </c>
       <c r="E6" t="n">
         <v>62230</v>
       </c>
       <c r="F6" t="n">
-        <v>3341</v>
+        <v>3349</v>
       </c>
       <c r="G6" t="n">
         <v>1.51</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2348278</v>
+        <v>2348901</v>
       </c>
       <c r="E7" t="n">
-        <v>184256</v>
+        <v>184599</v>
       </c>
       <c r="F7" t="n">
-        <v>17010</v>
+        <v>17019</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1154651</v>
+        <v>1154920</v>
       </c>
       <c r="E8" t="n">
         <v>55791</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>623957</v>
+        <v>625394</v>
       </c>
       <c r="E9" t="n">
-        <v>60249</v>
+        <v>60511</v>
       </c>
       <c r="F9" t="n">
-        <v>28913</v>
+        <v>28982</v>
       </c>
       <c r="G9" t="n">
         <v>4.63</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>459900</v>
+        <v>460896</v>
       </c>
       <c r="E10" t="n">
         <v>44790</v>
       </c>
       <c r="F10" t="n">
-        <v>6252</v>
+        <v>6264</v>
       </c>
       <c r="G10" t="n">
         <v>1.36</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>458634</v>
+        <v>459252</v>
       </c>
       <c r="E11" t="n">
-        <v>41934</v>
+        <v>42029</v>
       </c>
       <c r="F11" t="n">
-        <v>5793</v>
+        <v>5802</v>
       </c>
       <c r="G11" t="n">
         <v>1.26</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>452335</v>
+        <v>453330</v>
       </c>
       <c r="E12" t="n">
-        <v>25333</v>
+        <v>25353</v>
       </c>
       <c r="F12" t="n">
-        <v>13350</v>
+        <v>13374</v>
       </c>
       <c r="G12" t="n">
         <v>2.95</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>294530</v>
+        <v>294848</v>
       </c>
       <c r="E13" t="n">
         <v>16317</v>
       </c>
       <c r="F13" t="n">
-        <v>17907</v>
+        <v>17937</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5120,13 +5120,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>214122</v>
+        <v>214479</v>
       </c>
       <c r="E15" t="n">
-        <v>18316</v>
+        <v>18341</v>
       </c>
       <c r="F15" t="n">
-        <v>12831</v>
+        <v>12848</v>
       </c>
       <c r="G15" t="n">
         <v>5.99</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>122076</v>
+        <v>122419</v>
       </c>
       <c r="E16" t="n">
-        <v>13179</v>
+        <v>13192</v>
       </c>
       <c r="F16" t="n">
-        <v>2512</v>
+        <v>2520</v>
       </c>
       <c r="G16" t="n">
         <v>2.06</v>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60825</v>
+        <v>60839</v>
       </c>
       <c r="E18" t="n">
         <v>34273</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:19:04</t>
+          <t>Last Updated: 23-10-2026 22:54:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 22-10-2026)</t>
+          <t>MTD (01-10-2026 → 23-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>124783.94</v>
+        <v>125422.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8554.129999999999</v>
+        <v>8561.4</v>
       </c>
       <c r="D5" t="n">
-        <v>352359.45</v>
+        <v>367622.14</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8554.129999999999</v>
+        <v>8561.4</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>477143.39</v>
+        <v>493044.64</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 21-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 22-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>123687.83</v>
+        <v>124783.97</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8541.93</v>
+        <v>8554.129999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>335564.8</v>
+        <v>352562.05</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8541.93</v>
+        <v>8554.129999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>459252.63</v>
+        <v>477346.02</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1096.11</v>
+        <v>638.53</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>12.2</v>
+        <v>7.27</v>
       </c>
       <c r="D17" t="n">
-        <v>16794.65</v>
+        <v>15060.09</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>12.2</v>
+        <v>7.27</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>17890.76</v>
+        <v>15698.62</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:19:35</t>
+          <t>Last Updated: 23-10-2026 22:55:24</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-22 | MTD-1: 2026-10-01 → 2026-10-21</t>
+          <t>MTD: 2026-10-01 → 2026-10-23 | MTD-1: 2026-10-01 → 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-22)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-22)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-21)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-21)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:20:14</t>
+          <t>Last Updated: 23-10-2026 22:56:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-22)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>137470</v>
+        <v>139761</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2296032</v>
+        <v>2396747</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>148177.57</v>
+        <v>154268.05</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>137470</v>
+        <v>139761</v>
       </c>
       <c r="C7" t="n">
-        <v>4095221</v>
+        <v>4195936</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>227664.92</v>
+        <v>233755.4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-22)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1383450</v>
+        <v>1432955</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>89458.03</v>
+        <v>92044.21000000001</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>912582</v>
+        <v>963792</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>58719.54</v>
+        <v>62223.84</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-22)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-21)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>137470</v>
+        <v>139761</v>
       </c>
       <c r="C38" t="n">
-        <v>865060</v>
+        <v>913484</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>55205.53</v>
+        <v>58772</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>137470</v>
+        <v>139761</v>
       </c>
       <c r="C39" t="n">
-        <v>1328124</v>
+        <v>1383928</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>86459.69</v>
+        <v>89483.34</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:20:50</t>
+          <t>Last Updated: 23-10-2026 22:56:41</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-22</t>
+          <t>MTD: 2026-10-01 → 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>411091</v>
+        <v>431242</v>
       </c>
       <c r="E5" t="n">
-        <v>912582</v>
+        <v>963792</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>58719.54</v>
+        <v>62223.84</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:21:26</t>
+          <t>Last Updated: 23-10-2026 22:57:17</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:21:26</t>
+          <t>Last Updated: 23-10-2026 22:57:17</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:22:00</t>
+          <t>Last Updated: 23-10-2026 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 06:22:36</t>
+          <t>Last Updated: 23-10-2026 22:58:30</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>931903</v>
+        <v>954543</v>
       </c>
       <c r="E5" t="n">
         <v>124091</v>
       </c>
       <c r="F5" t="n">
-        <v>4329</v>
+        <v>4367</v>
       </c>
       <c r="G5" t="n">
         <v>0.46</v>
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>222383</v>
+        <v>223578</v>
       </c>
       <c r="E6" t="n">
         <v>62230</v>
       </c>
       <c r="F6" t="n">
-        <v>3349</v>
+        <v>3366</v>
       </c>
       <c r="G6" t="n">
         <v>1.51</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2348901</v>
+        <v>2381975</v>
       </c>
       <c r="E7" t="n">
-        <v>184599</v>
+        <v>187774</v>
       </c>
       <c r="F7" t="n">
-        <v>17019</v>
+        <v>17214</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1154920</v>
+        <v>1204425</v>
       </c>
       <c r="E8" t="n">
-        <v>55791</v>
+        <v>56798</v>
       </c>
       <c r="F8" t="n">
-        <v>13979</v>
+        <v>14421</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>625394</v>
+        <v>682800</v>
       </c>
       <c r="E9" t="n">
-        <v>60511</v>
+        <v>62817</v>
       </c>
       <c r="F9" t="n">
-        <v>28982</v>
+        <v>31483</v>
       </c>
       <c r="G9" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>460896</v>
+        <v>491515</v>
       </c>
       <c r="E10" t="n">
-        <v>44790</v>
+        <v>45086</v>
       </c>
       <c r="F10" t="n">
-        <v>6264</v>
+        <v>6542</v>
       </c>
       <c r="G10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>459252</v>
+        <v>483467</v>
       </c>
       <c r="E11" t="n">
-        <v>42029</v>
+        <v>26064</v>
       </c>
       <c r="F11" t="n">
-        <v>5802</v>
+        <v>13866</v>
       </c>
       <c r="G11" t="n">
-        <v>1.26</v>
+        <v>2.87</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>453330</v>
+        <v>480325</v>
       </c>
       <c r="E12" t="n">
-        <v>25353</v>
+        <v>42628</v>
       </c>
       <c r="F12" t="n">
-        <v>13374</v>
+        <v>6001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>294848</v>
+        <v>307316</v>
       </c>
       <c r="E13" t="n">
-        <v>16317</v>
+        <v>16396</v>
       </c>
       <c r="F13" t="n">
-        <v>17937</v>
+        <v>18671</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>214479</v>
+        <v>228497</v>
       </c>
       <c r="E15" t="n">
-        <v>18341</v>
+        <v>18799</v>
       </c>
       <c r="F15" t="n">
-        <v>12848</v>
+        <v>13610</v>
       </c>
       <c r="G15" t="n">
-        <v>5.99</v>
+        <v>5.96</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>122419</v>
+        <v>134832</v>
       </c>
       <c r="E16" t="n">
-        <v>13192</v>
+        <v>13614</v>
       </c>
       <c r="F16" t="n">
-        <v>2520</v>
+        <v>2732</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60839</v>
+        <v>60912</v>
       </c>
       <c r="E18" t="n">
-        <v>34273</v>
+        <v>34276</v>
       </c>
       <c r="F18" t="n">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="G18" t="n">
         <v>2.27</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:54:53</t>
+          <t>Last Updated: 24-10-2026 06:25:49</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8561.4</v>
+        <v>8561.620000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>367622.14</v>
+        <v>368065.16</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8561.4</v>
+        <v>8561.620000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>493044.64</v>
+        <v>493487.66</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>7.27</v>
+        <v>7.49</v>
       </c>
       <c r="D17" t="n">
-        <v>15060.09</v>
+        <v>15503.11</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7.27</v>
+        <v>7.49</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15698.62</v>
+        <v>16141.64</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:55:24</t>
+          <t>Last Updated: 24-10-2026 06:26:20</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:56:04</t>
+          <t>Last Updated: 24-10-2026 06:26:59</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>139761</v>
+        <v>139900</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2396747</v>
+        <v>2399499</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>154268.05</v>
+        <v>154448.78</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>139761</v>
+        <v>139900</v>
       </c>
       <c r="C7" t="n">
-        <v>4195936</v>
+        <v>4198688</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>233755.4</v>
+        <v>233936.13</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1432955</v>
+        <v>1434446</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>92044.21000000001</v>
+        <v>92121.00999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>963792</v>
+        <v>965053</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>62223.84</v>
+        <v>62327.77</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>139761</v>
+        <v>139900</v>
       </c>
       <c r="C38" t="n">
         <v>913484</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>139761</v>
+        <v>139900</v>
       </c>
       <c r="C39" t="n">
         <v>1383928</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:56:41</t>
+          <t>Last Updated: 24-10-2026 06:27:35</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>431242</v>
+        <v>431793</v>
       </c>
       <c r="E5" t="n">
-        <v>963792</v>
+        <v>965053</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>62223.84</v>
+        <v>62327.77</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:57:17</t>
+          <t>Last Updated: 24-10-2026 06:28:10</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:57:17</t>
+          <t>Last Updated: 24-10-2026 06:28:10</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:57:54</t>
+          <t>Last Updated: 24-10-2026 06:28:45</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 23-10-2026 22:58:30</t>
+          <t>Last Updated: 24-10-2026 06:29:21</t>
         </is>
       </c>
     </row>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>954543</v>
+        <v>954542</v>
       </c>
       <c r="E5" t="n">
-        <v>124091</v>
+        <v>124509</v>
       </c>
       <c r="F5" t="n">
         <v>4367</v>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>223578</v>
+        <v>223577</v>
       </c>
       <c r="E6" t="n">
-        <v>62230</v>
+        <v>62497</v>
       </c>
       <c r="F6" t="n">
         <v>3366</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2381975</v>
+        <v>2382648</v>
       </c>
       <c r="E7" t="n">
-        <v>187774</v>
+        <v>187803</v>
       </c>
       <c r="F7" t="n">
-        <v>17214</v>
+        <v>17221</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1204425</v>
+        <v>1205916</v>
       </c>
       <c r="E8" t="n">
-        <v>56798</v>
+        <v>56830</v>
       </c>
       <c r="F8" t="n">
-        <v>14421</v>
+        <v>14438</v>
       </c>
       <c r="G8" t="n">
         <v>1.2</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>682800</v>
+        <v>684053</v>
       </c>
       <c r="E9" t="n">
-        <v>62817</v>
+        <v>62912</v>
       </c>
       <c r="F9" t="n">
-        <v>31483</v>
+        <v>31515</v>
       </c>
       <c r="G9" t="n">
         <v>4.61</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>491515</v>
+        <v>492430</v>
       </c>
       <c r="E10" t="n">
-        <v>45086</v>
+        <v>45189</v>
       </c>
       <c r="F10" t="n">
-        <v>6542</v>
+        <v>6551</v>
       </c>
       <c r="G10" t="n">
         <v>1.33</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>483467</v>
+        <v>484276</v>
       </c>
       <c r="E11" t="n">
-        <v>26064</v>
+        <v>26142</v>
       </c>
       <c r="F11" t="n">
-        <v>13866</v>
+        <v>13895</v>
       </c>
       <c r="G11" t="n">
         <v>2.87</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>480325</v>
+        <v>480777</v>
       </c>
       <c r="E12" t="n">
-        <v>42628</v>
+        <v>42631</v>
       </c>
       <c r="F12" t="n">
-        <v>6001</v>
+        <v>6006</v>
       </c>
       <c r="G12" t="n">
         <v>1.25</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>307316</v>
+        <v>307660</v>
       </c>
       <c r="E13" t="n">
-        <v>16396</v>
+        <v>16439</v>
       </c>
       <c r="F13" t="n">
-        <v>18671</v>
+        <v>18694</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
+          <t>PPV_Sensitivity_Catalog_3Oct</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>228530</v>
+        <v>228893</v>
       </c>
       <c r="E14" t="n">
-        <v>14297</v>
+        <v>18842</v>
       </c>
       <c r="F14" t="n">
-        <v>4246</v>
+        <v>13636</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>5.96</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PPV_Sensitivity_Catalog_3Oct</t>
+          <t>AR_Retention_Catalogue_Purchased_Once_Add_to_cart_7July26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>228497</v>
+        <v>228530</v>
       </c>
       <c r="E15" t="n">
-        <v>18799</v>
+        <v>14297</v>
       </c>
       <c r="F15" t="n">
-        <v>13610</v>
+        <v>4246</v>
       </c>
       <c r="G15" t="n">
-        <v>5.96</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>134832</v>
+        <v>135205</v>
       </c>
       <c r="E16" t="n">
-        <v>13614</v>
+        <v>13633</v>
       </c>
       <c r="F16" t="n">
-        <v>2732</v>
+        <v>2742</v>
       </c>
       <c r="G16" t="n">
         <v>2.03</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60912</v>
+        <v>60915</v>
       </c>
       <c r="E18" t="n">
-        <v>34276</v>
+        <v>34306</v>
       </c>
       <c r="F18" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="G18" t="n">
         <v>2.27</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:25:49</t>
+          <t>Last Updated: 24-10-2026 21:42:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 23-10-2026)</t>
+          <t>MTD (01-10-2026 → 24-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>8561.620000000001</v>
+        <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>368065.16</v>
+        <v>380707.41</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8561.620000000001</v>
+        <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>493487.66</v>
+        <v>506129.91</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 22-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 23-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>124783.97</v>
+        <v>125422.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8554.129999999999</v>
+        <v>8562.030000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>352562.05</v>
+        <v>368237.61</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8554.129999999999</v>
+        <v>8562.030000000001</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>477346.02</v>
+        <v>493660.11</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>638.53</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>7.49</v>
+        <v>1.31</v>
       </c>
       <c r="D17" t="n">
-        <v>15503.11</v>
+        <v>12469.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7.49</v>
+        <v>1.31</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>16141.64</v>
+        <v>12469.8</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:26:20</t>
+          <t>Last Updated: 24-10-2026 21:43:14</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-23 | MTD-1: 2026-10-01 → 2026-10-22</t>
+          <t>MTD: 2026-10-01 → 2026-10-24 | MTD-1: 2026-10-01 → 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-23)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-23)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-22)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-22)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:26:59</t>
+          <t>Last Updated: 24-10-2026 21:43:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-23)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>139900</v>
+        <v>142083</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2399499</v>
+        <v>2487309</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>154448.78</v>
+        <v>159809.01</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>139900</v>
+        <v>142083</v>
       </c>
       <c r="C7" t="n">
-        <v>4198688</v>
+        <v>4286498</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>233936.13</v>
+        <v>239296.36</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-23)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1434446</v>
+        <v>1480775</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>92121.00999999999</v>
+        <v>94446.5</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>965053</v>
+        <v>1006534</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>62327.77</v>
+        <v>65362.51</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-23)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-22)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-23)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>139900</v>
+        <v>142083</v>
       </c>
       <c r="C38" t="n">
-        <v>913484</v>
+        <v>965950</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>58772</v>
+        <v>62372.12</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>139900</v>
+        <v>142083</v>
       </c>
       <c r="C39" t="n">
-        <v>1383928</v>
+        <v>1434876</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>89483.34</v>
+        <v>92145</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:27:35</t>
+          <t>Last Updated: 24-10-2026 21:44:31</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-23</t>
+          <t>MTD: 2026-10-01 → 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>431793</v>
+        <v>449925</v>
       </c>
       <c r="E5" t="n">
-        <v>965053</v>
+        <v>1006534</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>62327.77</v>
+        <v>65362.51</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:28:10</t>
+          <t>Last Updated: 24-10-2026 21:45:06</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:28:10</t>
+          <t>Last Updated: 24-10-2026 21:45:06</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:28:45</t>
+          <t>Last Updated: 24-10-2026 21:45:41</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 06:29:21</t>
+          <t>Last Updated: 24-10-2026 21:46:17</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2382648</v>
+        <v>2411749</v>
       </c>
       <c r="E7" t="n">
-        <v>187803</v>
+        <v>190296</v>
       </c>
       <c r="F7" t="n">
-        <v>17221</v>
+        <v>17414</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1205916</v>
+        <v>1252245</v>
       </c>
       <c r="E8" t="n">
-        <v>56830</v>
+        <v>57669</v>
       </c>
       <c r="F8" t="n">
-        <v>14438</v>
+        <v>14859</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>684053</v>
+        <v>729427</v>
       </c>
       <c r="E9" t="n">
-        <v>62912</v>
+        <v>64176</v>
       </c>
       <c r="F9" t="n">
-        <v>31515</v>
+        <v>33373</v>
       </c>
       <c r="G9" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>492430</v>
+        <v>512045</v>
       </c>
       <c r="E10" t="n">
-        <v>45189</v>
+        <v>45463</v>
       </c>
       <c r="F10" t="n">
-        <v>6551</v>
+        <v>6755</v>
       </c>
       <c r="G10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>484276</v>
+        <v>508538</v>
       </c>
       <c r="E11" t="n">
-        <v>26142</v>
+        <v>26985</v>
       </c>
       <c r="F11" t="n">
-        <v>13895</v>
+        <v>14278</v>
       </c>
       <c r="G11" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>480777</v>
+        <v>497996</v>
       </c>
       <c r="E12" t="n">
-        <v>42631</v>
+        <v>43139</v>
       </c>
       <c r="F12" t="n">
-        <v>6006</v>
+        <v>6143</v>
       </c>
       <c r="G12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>307660</v>
+        <v>318656</v>
       </c>
       <c r="E13" t="n">
-        <v>16439</v>
+        <v>16579</v>
       </c>
       <c r="F13" t="n">
-        <v>18694</v>
+        <v>19349</v>
       </c>
       <c r="G13" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>228893</v>
+        <v>241520</v>
       </c>
       <c r="E14" t="n">
-        <v>18842</v>
+        <v>19318</v>
       </c>
       <c r="F14" t="n">
-        <v>13636</v>
+        <v>14267</v>
       </c>
       <c r="G14" t="n">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>135205</v>
+        <v>147457</v>
       </c>
       <c r="E16" t="n">
-        <v>13633</v>
+        <v>14092</v>
       </c>
       <c r="F16" t="n">
-        <v>2742</v>
+        <v>2949</v>
       </c>
       <c r="G16" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60915</v>
+        <v>60933</v>
       </c>
       <c r="E18" t="n">
         <v>34306</v>
       </c>
       <c r="F18" t="n">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="G18" t="n">
         <v>2.27</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:42:43</t>
+          <t>Last Updated: 25-10-2026 05:58:20</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>380707.41</v>
+        <v>381643.09</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>506129.91</v>
+        <v>507065.59</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>1.31</v>
       </c>
       <c r="D17" t="n">
-        <v>12469.8</v>
+        <v>13405.48</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>1.31</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12469.8</v>
+        <v>13405.48</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:43:14</t>
+          <t>Last Updated: 25-10-2026 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:43:54</t>
+          <t>Last Updated: 25-10-2026 05:59:31</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>142083</v>
+        <v>142339</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2487309</v>
+        <v>2493571</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>159809.01</v>
+        <v>160191.69</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142083</v>
+        <v>142339</v>
       </c>
       <c r="C7" t="n">
-        <v>4286498</v>
+        <v>4292760</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>239296.36</v>
+        <v>239679.04</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1480775</v>
+        <v>1483804</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>94446.5</v>
+        <v>94583.55</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1006534</v>
+        <v>1009767</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>65362.51</v>
+        <v>65608.14</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>142083</v>
+        <v>142339</v>
       </c>
       <c r="C38" t="n">
         <v>965950</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>142083</v>
+        <v>142339</v>
       </c>
       <c r="C39" t="n">
         <v>1434876</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:44:31</t>
+          <t>Last Updated: 25-10-2026 06:00:07</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>449925</v>
+        <v>451199</v>
       </c>
       <c r="E5" t="n">
-        <v>1006534</v>
+        <v>1009767</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>65362.51</v>
+        <v>65608.14</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:45:06</t>
+          <t>Last Updated: 25-10-2026 06:00:43</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:45:06</t>
+          <t>Last Updated: 25-10-2026 06:00:43</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:45:41</t>
+          <t>Last Updated: 25-10-2026 06:01:19</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 24-10-2026 21:46:17</t>
+          <t>Last Updated: 25-10-2026 06:01:55</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
         <v>954542</v>
       </c>
       <c r="E5" t="n">
-        <v>124509</v>
+        <v>124507</v>
       </c>
       <c r="F5" t="n">
         <v>4367</v>
@@ -4727,7 +4727,7 @@
         <v>223577</v>
       </c>
       <c r="E6" t="n">
-        <v>62497</v>
+        <v>62490</v>
       </c>
       <c r="F6" t="n">
         <v>3366</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2411749</v>
+        <v>2413110</v>
       </c>
       <c r="E7" t="n">
-        <v>190296</v>
+        <v>190336</v>
       </c>
       <c r="F7" t="n">
-        <v>17414</v>
+        <v>17430</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1252245</v>
+        <v>1255274</v>
       </c>
       <c r="E8" t="n">
-        <v>57669</v>
+        <v>57774</v>
       </c>
       <c r="F8" t="n">
-        <v>14859</v>
+        <v>14905</v>
       </c>
       <c r="G8" t="n">
         <v>1.19</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>729427</v>
+        <v>733370</v>
       </c>
       <c r="E9" t="n">
-        <v>64176</v>
+        <v>64225</v>
       </c>
       <c r="F9" t="n">
-        <v>33373</v>
+        <v>33574</v>
       </c>
       <c r="G9" t="n">
         <v>4.58</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>512045</v>
+        <v>513195</v>
       </c>
       <c r="E10" t="n">
-        <v>45463</v>
+        <v>45466</v>
       </c>
       <c r="F10" t="n">
-        <v>6755</v>
+        <v>6771</v>
       </c>
       <c r="G10" t="n">
         <v>1.32</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>508538</v>
+        <v>510261</v>
       </c>
       <c r="E11" t="n">
-        <v>26985</v>
+        <v>27085</v>
       </c>
       <c r="F11" t="n">
-        <v>14278</v>
+        <v>14321</v>
       </c>
       <c r="G11" t="n">
         <v>2.81</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>497996</v>
+        <v>499506</v>
       </c>
       <c r="E12" t="n">
-        <v>43139</v>
+        <v>43186</v>
       </c>
       <c r="F12" t="n">
-        <v>6143</v>
+        <v>6152</v>
       </c>
       <c r="G12" t="n">
         <v>1.23</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>318656</v>
+        <v>319626</v>
       </c>
       <c r="E13" t="n">
         <v>16579</v>
       </c>
       <c r="F13" t="n">
-        <v>19349</v>
+        <v>19425</v>
       </c>
       <c r="G13" t="n">
-        <v>6.07</v>
+        <v>6.08</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>241520</v>
+        <v>242507</v>
       </c>
       <c r="E14" t="n">
-        <v>19318</v>
+        <v>19405</v>
       </c>
       <c r="F14" t="n">
-        <v>14267</v>
+        <v>14342</v>
       </c>
       <c r="G14" t="n">
         <v>5.91</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>147457</v>
+        <v>148569</v>
       </c>
       <c r="E16" t="n">
-        <v>14092</v>
+        <v>14171</v>
       </c>
       <c r="F16" t="n">
-        <v>2949</v>
+        <v>2985</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 05:58:20</t>
+          <t>Last Updated: 25-10-2026 22:14:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 24-10-2026)</t>
+          <t>MTD (01-10-2026 → 25-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>381643.09</v>
+        <v>397494.34</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>507065.59</v>
+        <v>522916.84</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 23-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 24-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8562.030000000001</v>
+        <v>8563.34</v>
       </c>
       <c r="D11" t="n">
-        <v>368237.61</v>
+        <v>381665.69</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>8562.030000000001</v>
+        <v>8563.34</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>493660.11</v>
+        <v>507088.19</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -758,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13405.48</v>
+        <v>15828.65</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13405.48</v>
+        <v>15828.65</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 05:58:51</t>
+          <t>Last Updated: 25-10-2026 22:14:46</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-24 | MTD-1: 2026-10-01 → 2026-10-23</t>
+          <t>MTD: 2026-10-01 → 2026-10-25 | MTD-1: 2026-10-01 → 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-24)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-24)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-23)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-23)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 05:59:31</t>
+          <t>Last Updated: 25-10-2026 22:15:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-24)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>142339</v>
+        <v>145263</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2493571</v>
+        <v>2598961</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>160191.69</v>
+        <v>166702.18</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142339</v>
+        <v>145263</v>
       </c>
       <c r="C7" t="n">
-        <v>4292760</v>
+        <v>4398150</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>239679.04</v>
+        <v>246189.53</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-24)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1483804</v>
+        <v>1545902</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>94583.55</v>
+        <v>97729.89</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1009767</v>
+        <v>1053059</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>65608.14</v>
+        <v>68972.28999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-24)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-23)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-24)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>142339</v>
+        <v>145263</v>
       </c>
       <c r="C38" t="n">
-        <v>965950</v>
+        <v>1010629</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>62372.12</v>
+        <v>65614.71000000001</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>142339</v>
+        <v>145263</v>
       </c>
       <c r="C39" t="n">
-        <v>1434876</v>
+        <v>1484180</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>92145</v>
+        <v>94585.53</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 06:00:07</t>
+          <t>Last Updated: 25-10-2026 22:16:03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-24</t>
+          <t>MTD: 2026-10-01 → 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>451199</v>
+        <v>470858</v>
       </c>
       <c r="E5" t="n">
-        <v>1009767</v>
+        <v>1053059</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>65608.14</v>
+        <v>68972.28999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 06:00:43</t>
+          <t>Last Updated: 25-10-2026 22:16:37</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 06:00:43</t>
+          <t>Last Updated: 25-10-2026 22:16:37</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 06:01:19</t>
+          <t>Last Updated: 25-10-2026 22:17:13</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 06:01:55</t>
+          <t>Last Updated: 25-10-2026 22:17:50</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2413110</v>
+        <v>2440779</v>
       </c>
       <c r="E7" t="n">
-        <v>190336</v>
+        <v>194047</v>
       </c>
       <c r="F7" t="n">
-        <v>17430</v>
+        <v>17636</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1255274</v>
+        <v>1317372</v>
       </c>
       <c r="E8" t="n">
-        <v>57774</v>
+        <v>58812</v>
       </c>
       <c r="F8" t="n">
-        <v>14905</v>
+        <v>15648</v>
       </c>
       <c r="G8" t="n">
         <v>1.19</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>733370</v>
+        <v>807568</v>
       </c>
       <c r="E9" t="n">
-        <v>64225</v>
+        <v>68252</v>
       </c>
       <c r="F9" t="n">
-        <v>33574</v>
+        <v>36435</v>
       </c>
       <c r="G9" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General_PushUnreachable_12Oct</t>
+          <t>Retention_ActivePurchasers_26Sep</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>513195</v>
+        <v>534213</v>
       </c>
       <c r="E10" t="n">
-        <v>45466</v>
+        <v>28011</v>
       </c>
       <c r="F10" t="n">
-        <v>6771</v>
+        <v>14707</v>
       </c>
       <c r="G10" t="n">
-        <v>1.32</v>
+        <v>2.75</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retention_ActivePurchasers_26Sep</t>
+          <t>General_PushUnreachable_12Oct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>510261</v>
+        <v>528416</v>
       </c>
       <c r="E11" t="n">
-        <v>27085</v>
+        <v>45612</v>
       </c>
       <c r="F11" t="n">
-        <v>14321</v>
+        <v>6921</v>
       </c>
       <c r="G11" t="n">
-        <v>2.81</v>
+        <v>1.31</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>499506</v>
+        <v>518846</v>
       </c>
       <c r="E12" t="n">
-        <v>43186</v>
+        <v>44143</v>
       </c>
       <c r="F12" t="n">
-        <v>6152</v>
+        <v>6294</v>
       </c>
       <c r="G12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>319626</v>
+        <v>330112</v>
       </c>
       <c r="E13" t="n">
-        <v>16579</v>
+        <v>16656</v>
       </c>
       <c r="F13" t="n">
-        <v>19425</v>
+        <v>20057</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>242507</v>
+        <v>255045</v>
       </c>
       <c r="E14" t="n">
-        <v>19405</v>
+        <v>20049</v>
       </c>
       <c r="F14" t="n">
-        <v>14342</v>
+        <v>15055</v>
       </c>
       <c r="G14" t="n">
-        <v>5.91</v>
+        <v>5.9</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>148569</v>
+        <v>160064</v>
       </c>
       <c r="E16" t="n">
-        <v>14171</v>
+        <v>15039</v>
       </c>
       <c r="F16" t="n">
-        <v>2985</v>
+        <v>3180</v>
       </c>
       <c r="G16" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:14:15</t>
+          <t>Last Updated: 26-10-2026 06:03:27</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>397494.34</v>
+        <v>398423.98</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>522916.84</v>
+        <v>523846.48</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15828.65</v>
+        <v>16758.29</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15828.65</v>
+        <v>16758.29</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:14:46</t>
+          <t>Last Updated: 26-10-2026 06:03:58</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:15:25</t>
+          <t>Last Updated: 26-10-2026 06:04:39</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>145263</v>
+        <v>145462</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2598961</v>
+        <v>2604811</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>166702.18</v>
+        <v>167115.73</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>145263</v>
+        <v>145462</v>
       </c>
       <c r="C7" t="n">
-        <v>4398150</v>
+        <v>4404000</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>246189.53</v>
+        <v>246603.08</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1545902</v>
+        <v>1549118</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>97729.89</v>
+        <v>97891.05</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1053059</v>
+        <v>1055693</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>68972.28999999999</v>
+        <v>69224.67999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>145263</v>
+        <v>145462</v>
       </c>
       <c r="C38" t="n">
         <v>1010629</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>145263</v>
+        <v>145462</v>
       </c>
       <c r="C39" t="n">
         <v>1484180</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:16:03</t>
+          <t>Last Updated: 26-10-2026 06:05:17</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>470858</v>
+        <v>471888</v>
       </c>
       <c r="E5" t="n">
-        <v>1053059</v>
+        <v>1055693</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>68972.28999999999</v>
+        <v>69224.67999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:16:37</t>
+          <t>Last Updated: 26-10-2026 06:05:53</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:16:37</t>
+          <t>Last Updated: 26-10-2026 06:05:53</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:17:13</t>
+          <t>Last Updated: 26-10-2026 06:06:30</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 25-10-2026 22:17:50</t>
+          <t>Last Updated: 26-10-2026 06:07:08</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
         <v>954542</v>
       </c>
       <c r="E5" t="n">
-        <v>124507</v>
+        <v>124509</v>
       </c>
       <c r="F5" t="n">
         <v>4367</v>
@@ -4727,7 +4727,7 @@
         <v>223577</v>
       </c>
       <c r="E6" t="n">
-        <v>62490</v>
+        <v>62485</v>
       </c>
       <c r="F6" t="n">
         <v>3366</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2440779</v>
+        <v>2441997</v>
       </c>
       <c r="E7" t="n">
-        <v>194047</v>
+        <v>194205</v>
       </c>
       <c r="F7" t="n">
-        <v>17636</v>
+        <v>17642</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1317372</v>
+        <v>1320588</v>
       </c>
       <c r="E8" t="n">
-        <v>58812</v>
+        <v>58851</v>
       </c>
       <c r="F8" t="n">
-        <v>15648</v>
+        <v>15695</v>
       </c>
       <c r="G8" t="n">
         <v>1.19</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>807568</v>
+        <v>811009</v>
       </c>
       <c r="E9" t="n">
-        <v>68252</v>
+        <v>68375</v>
       </c>
       <c r="F9" t="n">
-        <v>36435</v>
+        <v>36609</v>
       </c>
       <c r="G9" t="n">
         <v>4.51</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>534213</v>
+        <v>535820</v>
       </c>
       <c r="E10" t="n">
-        <v>28011</v>
+        <v>28087</v>
       </c>
       <c r="F10" t="n">
-        <v>14707</v>
+        <v>14734</v>
       </c>
       <c r="G10" t="n">
         <v>2.75</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>528416</v>
+        <v>529066</v>
       </c>
       <c r="E11" t="n">
-        <v>45612</v>
+        <v>45615</v>
       </c>
       <c r="F11" t="n">
-        <v>6921</v>
+        <v>6926</v>
       </c>
       <c r="G11" t="n">
         <v>1.31</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>518846</v>
+        <v>519873</v>
       </c>
       <c r="E12" t="n">
-        <v>44143</v>
+        <v>44227</v>
       </c>
       <c r="F12" t="n">
-        <v>6294</v>
+        <v>6300</v>
       </c>
       <c r="G12" t="n">
         <v>1.21</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>330112</v>
+        <v>330790</v>
       </c>
       <c r="E13" t="n">
-        <v>16656</v>
+        <v>16665</v>
       </c>
       <c r="F13" t="n">
-        <v>20057</v>
+        <v>20112</v>
       </c>
       <c r="G13" t="n">
         <v>6.08</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>255045</v>
+        <v>255799</v>
       </c>
       <c r="E14" t="n">
-        <v>20049</v>
+        <v>20071</v>
       </c>
       <c r="F14" t="n">
-        <v>15055</v>
+        <v>15098</v>
       </c>
       <c r="G14" t="n">
         <v>5.9</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>160064</v>
+        <v>160806</v>
       </c>
       <c r="E16" t="n">
-        <v>15039</v>
+        <v>15129</v>
       </c>
       <c r="F16" t="n">
-        <v>3180</v>
+        <v>3190</v>
       </c>
       <c r="G16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:03:27</t>
+          <t>Last Updated: 27-10-2026 00:22:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 25-10-2026)</t>
+          <t>MTD (01-10-2026 → 26-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>398423.98</v>
+        <v>412576.71</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>523846.48</v>
+        <v>537999.21</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 24-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 25-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
         <v>8563.34</v>
       </c>
       <c r="D11" t="n">
-        <v>381665.69</v>
+        <v>398423.98</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8563.34</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>507088.19</v>
+        <v>523846.48</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>16758.29</v>
+        <v>14152.73</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>16758.29</v>
+        <v>14152.73</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:03:58</t>
+          <t>Last Updated: 27-10-2026 00:22:51</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-25 | MTD-1: 2026-10-01 → 2026-10-24</t>
+          <t>MTD: 2026-10-01 → 2026-10-26 | MTD-1: 2026-10-01 → 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-25)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-25)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-24)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-24)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:04:39</t>
+          <t>Last Updated: 27-10-2026 00:23:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-25)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>145462</v>
+        <v>147459</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2604811</v>
+        <v>2706635</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>167115.73</v>
+        <v>173238.48</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>145462</v>
+        <v>147459</v>
       </c>
       <c r="C7" t="n">
-        <v>4404000</v>
+        <v>4505824</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>246603.08</v>
+        <v>252725.83</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-25)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1549118</v>
+        <v>1604326</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>97891.05</v>
+        <v>100714.91</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1055693</v>
+        <v>1102309</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>69224.67999999999</v>
+        <v>72523.57000000001</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-25)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-24)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>145462</v>
+        <v>147459</v>
       </c>
       <c r="C38" t="n">
-        <v>1010629</v>
+        <v>1055693</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>65614.71000000001</v>
+        <v>69224.67999999999</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>145462</v>
+        <v>147459</v>
       </c>
       <c r="C39" t="n">
-        <v>1484180</v>
+        <v>1549118</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>94585.53</v>
+        <v>97891.05</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:05:17</t>
+          <t>Last Updated: 27-10-2026 00:24:07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-25</t>
+          <t>MTD: 2026-10-01 → 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>471888</v>
+        <v>490970</v>
       </c>
       <c r="E5" t="n">
-        <v>1055693</v>
+        <v>1102309</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>69224.67999999999</v>
+        <v>72523.57000000001</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:05:53</t>
+          <t>Last Updated: 27-10-2026 00:24:43</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:05:53</t>
+          <t>Last Updated: 27-10-2026 00:24:43</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:06:30</t>
+          <t>Last Updated: 27-10-2026 00:25:17</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 26-10-2026 06:07:08</t>
+          <t>Last Updated: 27-10-2026 00:25:53</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
         <v>954542</v>
       </c>
       <c r="E5" t="n">
-        <v>124509</v>
+        <v>124496</v>
       </c>
       <c r="F5" t="n">
         <v>4367</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2441997</v>
+        <v>2468757</v>
       </c>
       <c r="E7" t="n">
-        <v>194205</v>
+        <v>196536</v>
       </c>
       <c r="F7" t="n">
-        <v>17642</v>
+        <v>17850</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1320588</v>
+        <v>1375796</v>
       </c>
       <c r="E8" t="n">
-        <v>58851</v>
+        <v>59603</v>
       </c>
       <c r="F8" t="n">
-        <v>15695</v>
+        <v>16287</v>
       </c>
       <c r="G8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>811009</v>
+        <v>887464</v>
       </c>
       <c r="E9" t="n">
-        <v>68375</v>
+        <v>71200</v>
       </c>
       <c r="F9" t="n">
-        <v>36609</v>
+        <v>39789</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>535820</v>
+        <v>561410</v>
       </c>
       <c r="E10" t="n">
-        <v>28087</v>
+        <v>28740</v>
       </c>
       <c r="F10" t="n">
-        <v>14734</v>
+        <v>15186</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>General_PushUnreachable_12Oct</t>
+          <t>Retention_DormantPurchasers_26Sep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>529066</v>
+        <v>540899</v>
       </c>
       <c r="E11" t="n">
-        <v>45615</v>
+        <v>44819</v>
       </c>
       <c r="F11" t="n">
-        <v>6926</v>
+        <v>6475</v>
       </c>
       <c r="G11" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Retention_DormantPurchasers_26Sep</t>
+          <t>General_PushUnreachable_12Oct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>519873</v>
+        <v>539749</v>
       </c>
       <c r="E12" t="n">
-        <v>44227</v>
+        <v>45626</v>
       </c>
       <c r="F12" t="n">
-        <v>6300</v>
+        <v>7002</v>
       </c>
       <c r="G12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>330790</v>
+        <v>341750</v>
       </c>
       <c r="E13" t="n">
-        <v>16665</v>
+        <v>16675</v>
       </c>
       <c r="F13" t="n">
-        <v>20112</v>
+        <v>20695</v>
       </c>
       <c r="G13" t="n">
-        <v>6.08</v>
+        <v>6.06</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>255799</v>
+        <v>266378</v>
       </c>
       <c r="E14" t="n">
-        <v>20071</v>
+        <v>20611</v>
       </c>
       <c r="F14" t="n">
-        <v>15098</v>
+        <v>15624</v>
       </c>
       <c r="G14" t="n">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>160806</v>
+        <v>173200</v>
       </c>
       <c r="E16" t="n">
-        <v>15129</v>
+        <v>15779</v>
       </c>
       <c r="F16" t="n">
-        <v>3190</v>
+        <v>3414</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:22:20</t>
+          <t>Last Updated: 27-10-2026 07:06:27</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>412576.71</v>
+        <v>412663.14</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>537999.21</v>
+        <v>538085.64</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14152.73</v>
+        <v>14239.16</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14152.73</v>
+        <v>14239.16</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:22:51</t>
+          <t>Last Updated: 27-10-2026 07:06:57</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:23:31</t>
+          <t>Last Updated: 27-10-2026 07:07:37</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>147459</v>
+        <v>147477</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2706635</v>
+        <v>2707180</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>173238.48</v>
+        <v>173287.79</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>147459</v>
+        <v>147477</v>
       </c>
       <c r="C7" t="n">
-        <v>4505824</v>
+        <v>4506369</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>252725.83</v>
+        <v>252775.14</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1604326</v>
+        <v>1604558</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>100714.91</v>
+        <v>100727.42</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1102309</v>
+        <v>1102622</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>72523.57000000001</v>
+        <v>72560.37</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>147459</v>
+        <v>147477</v>
       </c>
       <c r="C38" t="n">
         <v>1055693</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>147459</v>
+        <v>147477</v>
       </c>
       <c r="C39" t="n">
         <v>1549118</v>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:24:07</t>
+          <t>Last Updated: 27-10-2026 07:08:13</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>490970</v>
+        <v>491168</v>
       </c>
       <c r="E5" t="n">
-        <v>1102309</v>
+        <v>1102622</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>72523.57000000001</v>
+        <v>72560.37</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:24:43</t>
+          <t>Last Updated: 27-10-2026 07:08:48</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:24:43</t>
+          <t>Last Updated: 27-10-2026 07:08:48</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:25:17</t>
+          <t>Last Updated: 27-10-2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 00:25:53</t>
+          <t>Last Updated: 27-10-2026 07:10:02</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2468757</v>
+        <v>2468918</v>
       </c>
       <c r="E7" t="n">
-        <v>196536</v>
+        <v>196542</v>
       </c>
       <c r="F7" t="n">
-        <v>17850</v>
+        <v>17851</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1375796</v>
+        <v>1376028</v>
       </c>
       <c r="E8" t="n">
         <v>59603</v>
       </c>
       <c r="F8" t="n">
-        <v>16287</v>
+        <v>16290</v>
       </c>
       <c r="G8" t="n">
         <v>1.18</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>887464</v>
+        <v>887710</v>
       </c>
       <c r="E9" t="n">
         <v>71200</v>
       </c>
       <c r="F9" t="n">
-        <v>39789</v>
+        <v>39810</v>
       </c>
       <c r="G9" t="n">
         <v>4.48</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>561410</v>
+        <v>561628</v>
       </c>
       <c r="E10" t="n">
-        <v>28740</v>
+        <v>28747</v>
       </c>
       <c r="F10" t="n">
-        <v>15186</v>
+        <v>15188</v>
       </c>
       <c r="G10" t="n">
         <v>2.7</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>540899</v>
+        <v>540994</v>
       </c>
       <c r="E11" t="n">
-        <v>44819</v>
+        <v>44830</v>
       </c>
       <c r="F11" t="n">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="G11" t="n">
         <v>1.2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>539749</v>
+        <v>539769</v>
       </c>
       <c r="E12" t="n">
         <v>45626</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>341750</v>
+        <v>341809</v>
       </c>
       <c r="E13" t="n">
         <v>16675</v>
       </c>
       <c r="F13" t="n">
-        <v>20695</v>
+        <v>20700</v>
       </c>
       <c r="G13" t="n">
         <v>6.06</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>266378</v>
+        <v>266438</v>
       </c>
       <c r="E14" t="n">
-        <v>20611</v>
+        <v>20613</v>
       </c>
       <c r="F14" t="n">
-        <v>15624</v>
+        <v>15626</v>
       </c>
       <c r="G14" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>173200</v>
+        <v>173242</v>
       </c>
       <c r="E16" t="n">
-        <v>15779</v>
+        <v>15786</v>
       </c>
       <c r="F16" t="n">
         <v>3414</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:06:27</t>
+          <t>Last Updated: 27-10-2026 23:42:58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 26-10-2026)</t>
+          <t>MTD (01-10-2026 → 27-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>412663.14</v>
+        <v>425601.22</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>538085.64</v>
+        <v>551023.72</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 25-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 26-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
         <v>8563.34</v>
       </c>
       <c r="D11" t="n">
-        <v>398423.98</v>
+        <v>412798.22</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8563.34</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>523846.48</v>
+        <v>538220.72</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14239.16</v>
+        <v>12803</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14239.16</v>
+        <v>12803</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:06:57</t>
+          <t>Last Updated: 27-10-2026 23:43:29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-26 | MTD-1: 2026-10-01 → 2026-10-25</t>
+          <t>MTD: 2026-10-01 → 2026-10-27 | MTD-1: 2026-10-01 → 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-26)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-26)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-25)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-25)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:07:37</t>
+          <t>Last Updated: 27-10-2026 23:44:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-26)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>147477</v>
+        <v>149326</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2707180</v>
+        <v>2799919</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>173287.79</v>
+        <v>179183.96</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>147477</v>
+        <v>149326</v>
       </c>
       <c r="C7" t="n">
-        <v>4506369</v>
+        <v>4599108</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>252775.14</v>
+        <v>258671.31</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-26)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1604558</v>
+        <v>1653999</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>100727.42</v>
+        <v>103318.85</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1102622</v>
+        <v>1145920</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>72560.37</v>
+        <v>75865.11</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-26)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-25)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-26)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>147477</v>
+        <v>149326</v>
       </c>
       <c r="C38" t="n">
-        <v>1055693</v>
+        <v>1103548</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>69224.67999999999</v>
+        <v>72605.32000000001</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>147477</v>
+        <v>149326</v>
       </c>
       <c r="C39" t="n">
-        <v>1549118</v>
+        <v>1605097</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>97891.05</v>
+        <v>100756.67</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:08:13</t>
+          <t>Last Updated: 27-10-2026 23:44:51</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-26</t>
+          <t>MTD: 2026-10-01 → 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>491168</v>
+        <v>510184</v>
       </c>
       <c r="E5" t="n">
-        <v>1102622</v>
+        <v>1145920</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>72560.37</v>
+        <v>75865.11</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:08:48</t>
+          <t>Last Updated: 27-10-2026 23:45:27</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:08:48</t>
+          <t>Last Updated: 27-10-2026 23:45:27</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:09:23</t>
+          <t>Last Updated: 27-10-2026 23:46:02</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 07:10:02</t>
+          <t>Last Updated: 27-10-2026 23:46:38</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
         <v>954542</v>
       </c>
       <c r="E5" t="n">
-        <v>124496</v>
+        <v>124505</v>
       </c>
       <c r="F5" t="n">
         <v>4367</v>
@@ -4727,7 +4727,7 @@
         <v>223577</v>
       </c>
       <c r="E6" t="n">
-        <v>62485</v>
+        <v>62491</v>
       </c>
       <c r="F6" t="n">
         <v>3366</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2468918</v>
+        <v>2500678</v>
       </c>
       <c r="E7" t="n">
-        <v>196542</v>
+        <v>198746</v>
       </c>
       <c r="F7" t="n">
-        <v>17851</v>
+        <v>18109</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1376028</v>
+        <v>1425469</v>
       </c>
       <c r="E8" t="n">
-        <v>59603</v>
+        <v>60434</v>
       </c>
       <c r="F8" t="n">
-        <v>16290</v>
+        <v>16948</v>
       </c>
       <c r="G8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>887710</v>
+        <v>933305</v>
       </c>
       <c r="E9" t="n">
-        <v>71200</v>
+        <v>71860</v>
       </c>
       <c r="F9" t="n">
-        <v>39810</v>
+        <v>41996</v>
       </c>
       <c r="G9" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>561628</v>
+        <v>590109</v>
       </c>
       <c r="E10" t="n">
-        <v>28747</v>
+        <v>29295</v>
       </c>
       <c r="F10" t="n">
-        <v>15188</v>
+        <v>15625</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>540994</v>
+        <v>555811</v>
       </c>
       <c r="E11" t="n">
-        <v>44830</v>
+        <v>45300</v>
       </c>
       <c r="F11" t="n">
-        <v>6478</v>
+        <v>6646</v>
       </c>
       <c r="G11" t="n">
         <v>1.2</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>539769</v>
+        <v>548460</v>
       </c>
       <c r="E12" t="n">
-        <v>45626</v>
+        <v>45634</v>
       </c>
       <c r="F12" t="n">
-        <v>7002</v>
+        <v>7083</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>341809</v>
+        <v>353843</v>
       </c>
       <c r="E13" t="n">
-        <v>16675</v>
+        <v>16789</v>
       </c>
       <c r="F13" t="n">
-        <v>20700</v>
+        <v>21376</v>
       </c>
       <c r="G13" t="n">
-        <v>6.06</v>
+        <v>6.04</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>266438</v>
+        <v>278420</v>
       </c>
       <c r="E14" t="n">
-        <v>20613</v>
+        <v>21002</v>
       </c>
       <c r="F14" t="n">
-        <v>15626</v>
+        <v>16267</v>
       </c>
       <c r="G14" t="n">
-        <v>5.86</v>
+        <v>5.84</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>173242</v>
+        <v>182745</v>
       </c>
       <c r="E16" t="n">
-        <v>15786</v>
+        <v>16111</v>
       </c>
       <c r="F16" t="n">
-        <v>3414</v>
+        <v>3618</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:42:58</t>
+          <t>Last Updated: 28-10-2026 07:04:02</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>425601.22</v>
+        <v>425782.29</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>551023.72</v>
+        <v>551204.79</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12803</v>
+        <v>12984.07</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12803</v>
+        <v>12984.07</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:43:29</t>
+          <t>Last Updated: 28-10-2026 07:04:33</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:44:14</t>
+          <t>Last Updated: 28-10-2026 07:05:12</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>149326</v>
+        <v>149386</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2799919</v>
+        <v>2801156</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>179183.96</v>
+        <v>179274.83</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149326</v>
+        <v>149386</v>
       </c>
       <c r="C7" t="n">
-        <v>4599108</v>
+        <v>4600345</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>258671.31</v>
+        <v>258762.18</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1653999</v>
+        <v>1654564</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>103318.85</v>
+        <v>103350.15</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1145920</v>
+        <v>1146592</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>75865.11</v>
+        <v>75924.67999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>149326</v>
+        <v>149386</v>
       </c>
       <c r="C38" t="n">
         <v>1103548</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>149326</v>
+        <v>149386</v>
       </c>
       <c r="C39" t="n">
         <v>1605097</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:44:51</t>
+          <t>Last Updated: 28-10-2026 07:05:48</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>510184</v>
+        <v>510608</v>
       </c>
       <c r="E5" t="n">
-        <v>1145920</v>
+        <v>1146592</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>75865.11</v>
+        <v>75924.67999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:45:27</t>
+          <t>Last Updated: 28-10-2026 07:06:24</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:45:27</t>
+          <t>Last Updated: 28-10-2026 07:06:24</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:46:02</t>
+          <t>Last Updated: 28-10-2026 07:06:58</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 27-10-2026 23:46:38</t>
+          <t>Last Updated: 28-10-2026 07:07:33</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2500678</v>
+        <v>2500978</v>
       </c>
       <c r="E7" t="n">
-        <v>198746</v>
+        <v>198761</v>
       </c>
       <c r="F7" t="n">
-        <v>18109</v>
+        <v>18112</v>
       </c>
       <c r="G7" t="n">
         <v>0.72</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1425469</v>
+        <v>1426034</v>
       </c>
       <c r="E8" t="n">
         <v>60434</v>
       </c>
       <c r="F8" t="n">
-        <v>16948</v>
+        <v>16955</v>
       </c>
       <c r="G8" t="n">
         <v>1.19</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>933305</v>
+        <v>933782</v>
       </c>
       <c r="E9" t="n">
         <v>71860</v>
       </c>
       <c r="F9" t="n">
-        <v>41996</v>
+        <v>42024</v>
       </c>
       <c r="G9" t="n">
         <v>4.5</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>590109</v>
+        <v>590588</v>
       </c>
       <c r="E10" t="n">
-        <v>29295</v>
+        <v>29338</v>
       </c>
       <c r="F10" t="n">
-        <v>15625</v>
+        <v>15631</v>
       </c>
       <c r="G10" t="n">
         <v>2.65</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>555811</v>
+        <v>556004</v>
       </c>
       <c r="E11" t="n">
-        <v>45300</v>
+        <v>45317</v>
       </c>
       <c r="F11" t="n">
-        <v>6646</v>
+        <v>6651</v>
       </c>
       <c r="G11" t="n">
         <v>1.2</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>548460</v>
+        <v>548564</v>
       </c>
       <c r="E12" t="n">
         <v>45634</v>
       </c>
       <c r="F12" t="n">
-        <v>7083</v>
+        <v>7086</v>
       </c>
       <c r="G12" t="n">
         <v>1.29</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>353843</v>
+        <v>353958</v>
       </c>
       <c r="E13" t="n">
         <v>16789</v>
       </c>
       <c r="F13" t="n">
-        <v>21376</v>
+        <v>21377</v>
       </c>
       <c r="G13" t="n">
         <v>6.04</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>278420</v>
+        <v>278533</v>
       </c>
       <c r="E14" t="n">
         <v>21002</v>
       </c>
       <c r="F14" t="n">
-        <v>16267</v>
+        <v>16274</v>
       </c>
       <c r="G14" t="n">
         <v>5.84</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>182745</v>
+        <v>182883</v>
       </c>
       <c r="E16" t="n">
-        <v>16111</v>
+        <v>16130</v>
       </c>
       <c r="F16" t="n">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="G16" t="n">
         <v>1.98</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:04:02</t>
+          <t>Last Updated: 28-10-2026 23:59:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 27-10-2026)</t>
+          <t>MTD (01-10-2026 → 28-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>425782.29</v>
+        <v>440330.71</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>551204.79</v>
+        <v>565753.21</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 26-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 27-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
         <v>8563.34</v>
       </c>
       <c r="D11" t="n">
-        <v>412798.22</v>
+        <v>425943.99</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8563.34</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>538220.72</v>
+        <v>551366.49</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12984.07</v>
+        <v>14386.72</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12984.07</v>
+        <v>14386.72</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:04:33</t>
+          <t>Last Updated: 28-10-2026 23:59:40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-27 | MTD-1: 2026-10-01 → 2026-10-26</t>
+          <t>MTD: 2026-10-01 → 2026-10-28 | MTD-1: 2026-10-01 → 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-27)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-27)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-26)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-26)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:05:12</t>
+          <t>Last Updated: 29-10-2026 00:00:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-27)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>149386</v>
+        <v>151381</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2801156</v>
+        <v>2895900</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>179274.83</v>
+        <v>185907.86</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149386</v>
+        <v>151381</v>
       </c>
       <c r="C7" t="n">
-        <v>4600345</v>
+        <v>4695089</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>258762.18</v>
+        <v>265395.21</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-27)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1654564</v>
+        <v>1700808</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>103350.15</v>
+        <v>106171.18</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1146592</v>
+        <v>1195092</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>75924.67999999999</v>
+        <v>79736.67999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-27)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-26)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-27)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>149386</v>
+        <v>151381</v>
       </c>
       <c r="C38" t="n">
-        <v>1103548</v>
+        <v>1147661</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>72605.32000000001</v>
+        <v>75978.49000000001</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>149386</v>
+        <v>151381</v>
       </c>
       <c r="C39" t="n">
-        <v>1605097</v>
+        <v>1655067</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>100756.67</v>
+        <v>103378.81</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:05:48</t>
+          <t>Last Updated: 29-10-2026 00:00:58</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-27</t>
+          <t>MTD: 2026-10-01 → 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>510608</v>
+        <v>531720</v>
       </c>
       <c r="E5" t="n">
-        <v>1146592</v>
+        <v>1195092</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>75924.67999999999</v>
+        <v>79736.67999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:06:24</t>
+          <t>Last Updated: 29-10-2026 00:01:32</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:06:24</t>
+          <t>Last Updated: 29-10-2026 00:01:32</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:06:58</t>
+          <t>Last Updated: 29-10-2026 00:02:07</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 07:07:33</t>
+          <t>Last Updated: 29-10-2026 00:02:42</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
         <v>954542</v>
       </c>
       <c r="E5" t="n">
-        <v>124505</v>
+        <v>124504</v>
       </c>
       <c r="F5" t="n">
         <v>4367</v>
@@ -4768,16 +4768,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2500978</v>
+        <v>2539013</v>
       </c>
       <c r="E7" t="n">
-        <v>198761</v>
+        <v>201419</v>
       </c>
       <c r="F7" t="n">
-        <v>18112</v>
+        <v>18452</v>
       </c>
       <c r="G7" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1426034</v>
+        <v>1472278</v>
       </c>
       <c r="E8" t="n">
-        <v>60434</v>
+        <v>60864</v>
       </c>
       <c r="F8" t="n">
-        <v>16955</v>
+        <v>17564</v>
       </c>
       <c r="G8" t="n">
         <v>1.19</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>933782</v>
+        <v>983490</v>
       </c>
       <c r="E9" t="n">
-        <v>71860</v>
+        <v>72691</v>
       </c>
       <c r="F9" t="n">
-        <v>42024</v>
+        <v>44367</v>
       </c>
       <c r="G9" t="n">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>590588</v>
+        <v>620190</v>
       </c>
       <c r="E10" t="n">
-        <v>29338</v>
+        <v>30192</v>
       </c>
       <c r="F10" t="n">
-        <v>15631</v>
+        <v>16149</v>
       </c>
       <c r="G10" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>556004</v>
+        <v>574902</v>
       </c>
       <c r="E11" t="n">
-        <v>45317</v>
+        <v>46028</v>
       </c>
       <c r="F11" t="n">
-        <v>6651</v>
+        <v>6865</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>548564</v>
+        <v>556230</v>
       </c>
       <c r="E12" t="n">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="F12" t="n">
-        <v>7086</v>
+        <v>7149</v>
       </c>
       <c r="G12" t="n">
         <v>1.29</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>353958</v>
+        <v>363747</v>
       </c>
       <c r="E13" t="n">
-        <v>16789</v>
+        <v>16815</v>
       </c>
       <c r="F13" t="n">
-        <v>21377</v>
+        <v>21933</v>
       </c>
       <c r="G13" t="n">
-        <v>6.04</v>
+        <v>6.03</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>278533</v>
+        <v>289434</v>
       </c>
       <c r="E14" t="n">
-        <v>21002</v>
+        <v>21281</v>
       </c>
       <c r="F14" t="n">
-        <v>16274</v>
+        <v>16875</v>
       </c>
       <c r="G14" t="n">
-        <v>5.84</v>
+        <v>5.83</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>182883</v>
+        <v>193413</v>
       </c>
       <c r="E16" t="n">
-        <v>16130</v>
+        <v>16535</v>
       </c>
       <c r="F16" t="n">
-        <v>3619</v>
+        <v>3880</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 23:59:09</t>
+          <t>Last Updated: 29-10-2026 07:26:43</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>440330.71</v>
+        <v>440468.62</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>565753.21</v>
+        <v>565891.12</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14386.72</v>
+        <v>14524.63</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14386.72</v>
+        <v>14524.63</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 28-10-2026 23:59:40</t>
+          <t>Last Updated: 29-10-2026 07:27:14</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 00:00:19</t>
+          <t>Last Updated: 29-10-2026 07:27:53</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>151381</v>
+        <v>151482</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2895900</v>
+        <v>2896852</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>185907.86</v>
+        <v>185981.62</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>151381</v>
+        <v>151482</v>
       </c>
       <c r="C7" t="n">
-        <v>4695089</v>
+        <v>4696041</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>265395.21</v>
+        <v>265468.97</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1700808</v>
+        <v>1701157</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>106171.18</v>
+        <v>106194.06</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1195092</v>
+        <v>1195695</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>79736.67999999999</v>
+        <v>79787.56</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>151381</v>
+        <v>151482</v>
       </c>
       <c r="C38" t="n">
         <v>1147661</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>151381</v>
+        <v>151482</v>
       </c>
       <c r="C39" t="n">
         <v>1655067</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 00:00:58</t>
+          <t>Last Updated: 29-10-2026 07:28:29</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>531720</v>
+        <v>532119</v>
       </c>
       <c r="E5" t="n">
-        <v>1195092</v>
+        <v>1195695</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>79736.67999999999</v>
+        <v>79787.56</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 00:01:32</t>
+          <t>Last Updated: 29-10-2026 07:29:04</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 00:01:32</t>
+          <t>Last Updated: 29-10-2026 07:29:04</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 00:02:07</t>
+          <t>Last Updated: 29-10-2026 07:29:39</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 00:02:42</t>
+          <t>Last Updated: 29-10-2026 07:30:15</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2539013</v>
+        <v>2539310</v>
       </c>
       <c r="E7" t="n">
-        <v>201419</v>
+        <v>201440</v>
       </c>
       <c r="F7" t="n">
-        <v>18452</v>
+        <v>18455</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1472278</v>
+        <v>1472627</v>
       </c>
       <c r="E8" t="n">
-        <v>60864</v>
+        <v>60866</v>
       </c>
       <c r="F8" t="n">
-        <v>17564</v>
+        <v>17565</v>
       </c>
       <c r="G8" t="n">
         <v>1.19</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>983490</v>
+        <v>983845</v>
       </c>
       <c r="E9" t="n">
         <v>72691</v>
       </c>
       <c r="F9" t="n">
-        <v>44367</v>
+        <v>44384</v>
       </c>
       <c r="G9" t="n">
         <v>4.51</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>620190</v>
+        <v>620559</v>
       </c>
       <c r="E10" t="n">
-        <v>30192</v>
+        <v>30216</v>
       </c>
       <c r="F10" t="n">
-        <v>16149</v>
+        <v>16153</v>
       </c>
       <c r="G10" t="n">
         <v>2.6</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>574902</v>
+        <v>575136</v>
       </c>
       <c r="E11" t="n">
-        <v>46028</v>
+        <v>46106</v>
       </c>
       <c r="F11" t="n">
-        <v>6865</v>
+        <v>6867</v>
       </c>
       <c r="G11" t="n">
         <v>1.19</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>556230</v>
+        <v>556280</v>
       </c>
       <c r="E12" t="n">
         <v>45638</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>363747</v>
+        <v>363819</v>
       </c>
       <c r="E13" t="n">
         <v>16815</v>
       </c>
       <c r="F13" t="n">
-        <v>21933</v>
+        <v>21934</v>
       </c>
       <c r="G13" t="n">
         <v>6.03</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>289434</v>
+        <v>289504</v>
       </c>
       <c r="E14" t="n">
         <v>21281</v>
       </c>
       <c r="F14" t="n">
-        <v>16875</v>
+        <v>16878</v>
       </c>
       <c r="G14" t="n">
         <v>5.83</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>193413</v>
+        <v>193499</v>
       </c>
       <c r="E16" t="n">
-        <v>16535</v>
+        <v>16542</v>
       </c>
       <c r="F16" t="n">
-        <v>3880</v>
+        <v>3882</v>
       </c>
       <c r="G16" t="n">
         <v>2.01</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:26:43</t>
+          <t>Last Updated: 30-10-2026 00:09:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 28-10-2026)</t>
+          <t>MTD (01-10-2026 → 29-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>440468.62</v>
+        <v>455847.43</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>565891.12</v>
+        <v>581269.9300000001</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 27-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 28-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
         <v>8563.34</v>
       </c>
       <c r="D11" t="n">
-        <v>425943.99</v>
+        <v>440468.62</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8563.34</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>551366.49</v>
+        <v>565891.12</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14524.63</v>
+        <v>15378.81</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14524.63</v>
+        <v>15378.81</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:27:14</t>
+          <t>Last Updated: 30-10-2026 00:09:49</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-28 | MTD-1: 2026-10-01 → 2026-10-27</t>
+          <t>MTD: 2026-10-01 → 2026-10-29 | MTD-1: 2026-10-01 → 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-28)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-28)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-27)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-27)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:27:53</t>
+          <t>Last Updated: 30-10-2026 00:10:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-28)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>151482</v>
+        <v>154334</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2896852</v>
+        <v>3003791</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>185981.62</v>
+        <v>193502.62</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>151482</v>
+        <v>154334</v>
       </c>
       <c r="C7" t="n">
-        <v>4696041</v>
+        <v>4802980</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>265468.97</v>
+        <v>272989.97</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-28)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1701157</v>
+        <v>1753980</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>106194.06</v>
+        <v>109241.07</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1195695</v>
+        <v>1249811</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>79787.56</v>
+        <v>84261.55</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-28)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-27)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-28)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>151482</v>
+        <v>154334</v>
       </c>
       <c r="C38" t="n">
-        <v>1147661</v>
+        <v>1195695</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>75978.49000000001</v>
+        <v>79787.56</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>151482</v>
+        <v>154334</v>
       </c>
       <c r="C39" t="n">
-        <v>1655067</v>
+        <v>1701157</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>103378.81</v>
+        <v>106194.06</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:28:29</t>
+          <t>Last Updated: 30-10-2026 00:11:06</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-28</t>
+          <t>MTD: 2026-10-01 → 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>532119</v>
+        <v>554550</v>
       </c>
       <c r="E5" t="n">
-        <v>1195695</v>
+        <v>1249811</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>79787.56</v>
+        <v>84261.55</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:29:04</t>
+          <t>Last Updated: 30-10-2026 00:11:41</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:29:04</t>
+          <t>Last Updated: 30-10-2026 00:11:41</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:29:39</t>
+          <t>Last Updated: 30-10-2026 00:12:16</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 29-10-2026 07:30:15</t>
+          <t>Last Updated: 30-10-2026 00:12:52</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
         <v>954542</v>
       </c>
       <c r="E5" t="n">
-        <v>124504</v>
+        <v>124503</v>
       </c>
       <c r="F5" t="n">
         <v>4367</v>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2539310</v>
+        <v>2583836</v>
       </c>
       <c r="E7" t="n">
-        <v>201440</v>
+        <v>204399</v>
       </c>
       <c r="F7" t="n">
-        <v>18455</v>
+        <v>18858</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1472627</v>
+        <v>1525450</v>
       </c>
       <c r="E8" t="n">
-        <v>60866</v>
+        <v>62141</v>
       </c>
       <c r="F8" t="n">
-        <v>17565</v>
+        <v>18237</v>
       </c>
       <c r="G8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>983845</v>
+        <v>1031407</v>
       </c>
       <c r="E9" t="n">
-        <v>72691</v>
+        <v>73388</v>
       </c>
       <c r="F9" t="n">
-        <v>44384</v>
+        <v>46523</v>
       </c>
       <c r="G9" t="n">
         <v>4.51</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>620559</v>
+        <v>655982</v>
       </c>
       <c r="E10" t="n">
-        <v>30216</v>
+        <v>30748</v>
       </c>
       <c r="F10" t="n">
-        <v>16153</v>
+        <v>16667</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>575136</v>
+        <v>593829</v>
       </c>
       <c r="E11" t="n">
-        <v>46106</v>
+        <v>47148</v>
       </c>
       <c r="F11" t="n">
-        <v>6867</v>
+        <v>7074</v>
       </c>
       <c r="G11" t="n">
         <v>1.19</v>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>556280</v>
+        <v>562079</v>
       </c>
       <c r="E12" t="n">
-        <v>45638</v>
+        <v>45723</v>
       </c>
       <c r="F12" t="n">
-        <v>7149</v>
+        <v>7222</v>
       </c>
       <c r="G12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>363819</v>
+        <v>372162</v>
       </c>
       <c r="E13" t="n">
-        <v>16815</v>
+        <v>16908</v>
       </c>
       <c r="F13" t="n">
-        <v>21934</v>
+        <v>22379</v>
       </c>
       <c r="G13" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>289504</v>
+        <v>300864</v>
       </c>
       <c r="E14" t="n">
-        <v>21281</v>
+        <v>21528</v>
       </c>
       <c r="F14" t="n">
-        <v>16878</v>
+        <v>17440</v>
       </c>
       <c r="G14" t="n">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>193499</v>
+        <v>205550</v>
       </c>
       <c r="E16" t="n">
-        <v>16542</v>
+        <v>17112</v>
       </c>
       <c r="F16" t="n">
-        <v>3882</v>
+        <v>4125</v>
       </c>
       <c r="G16" t="n">
         <v>2.01</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:09:18</t>
+          <t>Last Updated: 30-10-2026 07:36:23</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>455847.43</v>
+        <v>455992.03</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>581269.9300000001</v>
+        <v>581414.53</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15378.81</v>
+        <v>15523.41</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15378.81</v>
+        <v>15523.41</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:09:49</t>
+          <t>Last Updated: 30-10-2026 07:36:53</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:10:29</t>
+          <t>Last Updated: 30-10-2026 07:37:33</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>154334</v>
+        <v>154409</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3003791</v>
+        <v>3004740</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>193502.62</v>
+        <v>193585.81</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>154334</v>
+        <v>154409</v>
       </c>
       <c r="C7" t="n">
-        <v>4802980</v>
+        <v>4803929</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>272989.97</v>
+        <v>273073.16</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1753980</v>
+        <v>1754258</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>109241.07</v>
+        <v>109258.73</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1249811</v>
+        <v>1250482</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>84261.55</v>
+        <v>84327.08</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>154334</v>
+        <v>154409</v>
       </c>
       <c r="C38" t="n">
         <v>1195695</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>154334</v>
+        <v>154409</v>
       </c>
       <c r="C39" t="n">
         <v>1701157</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:11:06</t>
+          <t>Last Updated: 30-10-2026 07:38:09</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>554550</v>
+        <v>554975</v>
       </c>
       <c r="E5" t="n">
-        <v>1249811</v>
+        <v>1250482</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>84261.55</v>
+        <v>84327.08</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:11:41</t>
+          <t>Last Updated: 30-10-2026 07:38:45</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:11:41</t>
+          <t>Last Updated: 30-10-2026 07:38:45</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:12:16</t>
+          <t>Last Updated: 30-10-2026 07:39:20</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 00:12:52</t>
+          <t>Last Updated: 30-10-2026 07:39:56</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2583836</v>
+        <v>2584174</v>
       </c>
       <c r="E7" t="n">
-        <v>204399</v>
+        <v>204411</v>
       </c>
       <c r="F7" t="n">
-        <v>18858</v>
+        <v>18863</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1525450</v>
+        <v>1525728</v>
       </c>
       <c r="E8" t="n">
         <v>62141</v>
       </c>
       <c r="F8" t="n">
-        <v>18237</v>
+        <v>18248</v>
       </c>
       <c r="G8" t="n">
         <v>1.2</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1031407</v>
+        <v>1031684</v>
       </c>
       <c r="E9" t="n">
         <v>73388</v>
       </c>
       <c r="F9" t="n">
-        <v>46523</v>
+        <v>46535</v>
       </c>
       <c r="G9" t="n">
         <v>4.51</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>655982</v>
+        <v>656453</v>
       </c>
       <c r="E10" t="n">
-        <v>30748</v>
+        <v>30786</v>
       </c>
       <c r="F10" t="n">
-        <v>16667</v>
+        <v>16669</v>
       </c>
       <c r="G10" t="n">
         <v>2.54</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>593829</v>
+        <v>594029</v>
       </c>
       <c r="E11" t="n">
-        <v>47148</v>
+        <v>47195</v>
       </c>
       <c r="F11" t="n">
-        <v>7074</v>
+        <v>7075</v>
       </c>
       <c r="G11" t="n">
         <v>1.19</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>562079</v>
+        <v>562106</v>
       </c>
       <c r="E12" t="n">
         <v>45723</v>
       </c>
       <c r="F12" t="n">
-        <v>7222</v>
+        <v>7223</v>
       </c>
       <c r="G12" t="n">
         <v>1.28</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>372162</v>
+        <v>372219</v>
       </c>
       <c r="E13" t="n">
         <v>16908</v>
       </c>
       <c r="F13" t="n">
-        <v>22379</v>
+        <v>22384</v>
       </c>
       <c r="G13" t="n">
         <v>6.01</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>300864</v>
+        <v>300921</v>
       </c>
       <c r="E14" t="n">
-        <v>21528</v>
+        <v>21530</v>
       </c>
       <c r="F14" t="n">
-        <v>17440</v>
+        <v>17441</v>
       </c>
       <c r="G14" t="n">
         <v>5.8</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>205550</v>
+        <v>205715</v>
       </c>
       <c r="E16" t="n">
-        <v>17112</v>
+        <v>17172</v>
       </c>
       <c r="F16" t="n">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="G16" t="n">
         <v>2.01</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,14 +470,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:36:23</t>
+          <t>Last Updated: 30-10-2026 23:41:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MTD (01-10-2026 → 29-10-2026)</t>
+          <t>MTD (01-10-2026 → 30-10-2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>455992.03</v>
+        <v>470480.07</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>581414.53</v>
+        <v>595902.5699999999</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (01-10-2026 → 28-10-2026)</t>
+          <t>MTD-1 (01-10-2026 → 29-10-2026)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
         <v>8563.34</v>
       </c>
       <c r="D11" t="n">
-        <v>440468.62</v>
+        <v>456160.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>8563.34</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>565891.12</v>
+        <v>581582.75</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15523.41</v>
+        <v>14319.82</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>15523.41</v>
+        <v>14319.82</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,14 +1440,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:36:53</t>
+          <t>Last Updated: 30-10-2026 23:41:53</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-29 | MTD-1: 2026-10-01 → 2026-10-28</t>
+          <t>MTD: 2026-10-01 → 2026-10-30 | MTD-1: 2026-10-01 → 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD (2026-10-01 → 2026-10-29)</t>
+          <t>KYC — MTD (2026-10-01 → 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD (2026-10-01 → 2026-10-29)</t>
+          <t>First Txn — MTD (2026-10-01 → 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KYC — MTD-1 (2026-10-01 → 2026-10-28)</t>
+          <t>KYC — MTD-1 (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-28)</t>
+          <t>First Txn — MTD-1 (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -2354,14 +2354,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:37:33</t>
+          <t>Last Updated: 30-10-2026 23:42:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Retention — MTD (2026-10-01 → 2026-10-29)</t>
+          <t>Retention — MTD (2026-10-01 → 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>154409</v>
+        <v>156582</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3004740</v>
+        <v>3106339</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>193585.81</v>
+        <v>200294.1</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>154409</v>
+        <v>156582</v>
       </c>
       <c r="C7" t="n">
-        <v>4803929</v>
+        <v>4905528</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>273073.16</v>
+        <v>279781.45</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-29)</t>
+          <t>Meta Ad Performance — MTD (2026-10-01 → 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1754258</v>
+        <v>1807743</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>109258.73</v>
+        <v>112248.92</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1250482</v>
+        <v>1298596</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>84327.08</v>
+        <v>88045.17999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2578,7 +2578,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-29)</t>
+          <t>Google Ad Group Performance — MTD (2026-10-01 → 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTD-1 (2026-10-01 → 2026-10-28)</t>
+          <t>MTD-1 (2026-10-01 → 2026-10-29)</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>154409</v>
+        <v>156582</v>
       </c>
       <c r="C38" t="n">
-        <v>1195695</v>
+        <v>1251817</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>79787.56</v>
+        <v>84383.35000000001</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>154409</v>
+        <v>156582</v>
       </c>
       <c r="C39" t="n">
-        <v>1701157</v>
+        <v>1754772</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>106194.06</v>
+        <v>109293.84</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:38:09</t>
+          <t>Last Updated: 30-10-2026 23:43:10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MTD: 2026-10-01 → 2026-10-29</t>
+          <t>MTD: 2026-10-01 → 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>554975</v>
+        <v>575738</v>
       </c>
       <c r="E5" t="n">
-        <v>1250482</v>
+        <v>1298596</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>84327.08</v>
+        <v>88045.17999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:38:45</t>
+          <t>Last Updated: 30-10-2026 23:43:46</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:38:45</t>
+          <t>Last Updated: 30-10-2026 23:43:46</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:39:20</t>
+          <t>Last Updated: 30-10-2026 23:44:21</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 07:39:56</t>
+          <t>Last Updated: 30-10-2026 23:44:57</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2584174</v>
+        <v>2631476</v>
       </c>
       <c r="E7" t="n">
-        <v>204411</v>
+        <v>206803</v>
       </c>
       <c r="F7" t="n">
-        <v>18863</v>
+        <v>19218</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,16 +4812,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1525728</v>
+        <v>1579213</v>
       </c>
       <c r="E8" t="n">
-        <v>62141</v>
+        <v>62787</v>
       </c>
       <c r="F8" t="n">
-        <v>18248</v>
+        <v>18856</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4856,16 +4856,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1031684</v>
+        <v>1079124</v>
       </c>
       <c r="E9" t="n">
-        <v>73388</v>
+        <v>74012</v>
       </c>
       <c r="F9" t="n">
-        <v>46535</v>
+        <v>48754</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4900,16 +4900,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>656453</v>
+        <v>688331</v>
       </c>
       <c r="E10" t="n">
-        <v>30786</v>
+        <v>31322</v>
       </c>
       <c r="F10" t="n">
-        <v>16669</v>
+        <v>17103</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>594029</v>
+        <v>610265</v>
       </c>
       <c r="E11" t="n">
-        <v>47195</v>
+        <v>48176</v>
       </c>
       <c r="F11" t="n">
-        <v>7075</v>
+        <v>7244</v>
       </c>
       <c r="G11" t="n">
         <v>1.19</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>562106</v>
+        <v>565966</v>
       </c>
       <c r="E12" t="n">
-        <v>45723</v>
+        <v>45812</v>
       </c>
       <c r="F12" t="n">
-        <v>7223</v>
+        <v>7259</v>
       </c>
       <c r="G12" t="n">
         <v>1.28</v>
@@ -5032,16 +5032,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>372219</v>
+        <v>382287</v>
       </c>
       <c r="E13" t="n">
-        <v>16908</v>
+        <v>17043</v>
       </c>
       <c r="F13" t="n">
-        <v>22384</v>
+        <v>22850</v>
       </c>
       <c r="G13" t="n">
-        <v>6.01</v>
+        <v>5.98</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -5076,16 +5076,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>300921</v>
+        <v>311915</v>
       </c>
       <c r="E14" t="n">
-        <v>21530</v>
+        <v>21793</v>
       </c>
       <c r="F14" t="n">
-        <v>17441</v>
+        <v>18057</v>
       </c>
       <c r="G14" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>205715</v>
+        <v>216587</v>
       </c>
       <c r="E16" t="n">
-        <v>17172</v>
+        <v>17891</v>
       </c>
       <c r="F16" t="n">
-        <v>4127</v>
+        <v>4350</v>
       </c>
       <c r="G16" t="n">
         <v>2.01</v>

--- a/reports/Team Wise Cost.xlsx
+++ b/reports/Team Wise Cost.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:41:23</t>
+          <t>Last Updated: 31-10-2026 07:16:46</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>8563.34</v>
       </c>
       <c r="D5" t="n">
-        <v>470480.07</v>
+        <v>470697.51</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>8563.34</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>595902.5699999999</v>
+        <v>596120.01</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14319.82</v>
+        <v>14537.26</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14319.82</v>
+        <v>14537.26</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:41:53</t>
+          <t>Last Updated: 31-10-2026 07:17:17</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:42:33</t>
+          <t>Last Updated: 31-10-2026 07:17:59</t>
         </is>
       </c>
     </row>
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>156582</v>
+        <v>156735</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3106339</v>
+        <v>3107685</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>200294.1</v>
+        <v>200415.28</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156582</v>
+        <v>156735</v>
       </c>
       <c r="C7" t="n">
-        <v>4905528</v>
+        <v>4906874</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>279781.45</v>
+        <v>279902.63</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1807743</v>
+        <v>1808315</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>112248.92</v>
+        <v>112285.66</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1298596</v>
+        <v>1299370</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>88045.17999999999</v>
+        <v>88129.62</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>156582</v>
+        <v>156735</v>
       </c>
       <c r="C38" t="n">
         <v>1251817</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>156582</v>
+        <v>156735</v>
       </c>
       <c r="C39" t="n">
         <v>1754772</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:43:10</t>
+          <t>Last Updated: 31-10-2026 07:18:35</t>
         </is>
       </c>
     </row>
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>575738</v>
+        <v>576158</v>
       </c>
       <c r="E5" t="n">
-        <v>1298596</v>
+        <v>1299370</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>88045.17999999999</v>
+        <v>88129.62</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:43:46</t>
+          <t>Last Updated: 31-10-2026 07:19:11</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:43:46</t>
+          <t>Last Updated: 31-10-2026 07:19:11</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:44:21</t>
+          <t>Last Updated: 31-10-2026 07:19:46</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Last Updated: 30-10-2026 23:44:57</t>
+          <t>Last Updated: 31-10-2026 07:20:22</t>
         </is>
       </c>
     </row>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2631476</v>
+        <v>2631999</v>
       </c>
       <c r="E7" t="n">
         <v>206803</v>
       </c>
       <c r="F7" t="n">
-        <v>19218</v>
+        <v>19224</v>
       </c>
       <c r="G7" t="n">
         <v>0.73</v>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1579213</v>
+        <v>1579785</v>
       </c>
       <c r="E8" t="n">
-        <v>62787</v>
+        <v>62827</v>
       </c>
       <c r="F8" t="n">
-        <v>18856</v>
+        <v>18862</v>
       </c>
       <c r="G8" t="n">
         <v>1.19</v>
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1079124</v>
+        <v>1079553</v>
       </c>
       <c r="E9" t="n">
         <v>74012</v>
       </c>
       <c r="F9" t="n">
-        <v>48754</v>
+        <v>48778</v>
       </c>
       <c r="G9" t="n">
         <v>4.52</v>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>688331</v>
+        <v>688831</v>
       </c>
       <c r="E10" t="n">
-        <v>31322</v>
+        <v>31328</v>
       </c>
       <c r="F10" t="n">
-        <v>17103</v>
+        <v>17114</v>
       </c>
       <c r="G10" t="n">
         <v>2.48</v>
@@ -4944,13 +4944,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>610265</v>
+        <v>610539</v>
       </c>
       <c r="E11" t="n">
-        <v>48176</v>
+        <v>48300</v>
       </c>
       <c r="F11" t="n">
-        <v>7244</v>
+        <v>7246</v>
       </c>
       <c r="G11" t="n">
         <v>1.19</v>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>565966</v>
+        <v>566000</v>
       </c>
       <c r="E12" t="n">
         <v>45812</v>
       </c>
       <c r="F12" t="n">
-        <v>7259</v>
+        <v>7261</v>
       </c>
       <c r="G12" t="n">
         <v>1.28</v>
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>382287</v>
+        <v>382376</v>
       </c>
       <c r="E13" t="n">
         <v>17043</v>
       </c>
       <c r="F13" t="n">
-        <v>22850</v>
+        <v>22860</v>
       </c>
       <c r="G13" t="n">
         <v>5.98</v>
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>311915</v>
+        <v>312022</v>
       </c>
       <c r="E14" t="n">
-        <v>21793</v>
+        <v>21812</v>
       </c>
       <c r="F14" t="n">
-        <v>18057</v>
+        <v>18063</v>
       </c>
       <c r="G14" t="n">
         <v>5.79</v>
@@ -5164,13 +5164,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>216587</v>
+        <v>216760</v>
       </c>
       <c r="E16" t="n">
-        <v>17891</v>
+        <v>17915</v>
       </c>
       <c r="F16" t="n">
-        <v>4350</v>
+        <v>4354</v>
       </c>
       <c r="G16" t="n">
         <v>2.01</v>
